--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6626" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{771DC419-B5DC-4C71-BCA4-11EE20A6BE62}"/>
+  <xr:revisionPtr revIDLastSave="6674" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1EC4730-2E0F-42CA-949F-51357F1CDBE7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2846,13 +2846,43 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="33" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2861,74 +2891,20 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="33" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2937,6 +2913,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2960,6 +2945,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2968,6 +2962,12 @@
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="69" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3029,6 +3029,24 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3071,31 +3089,28 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="26" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3196,21 +3211,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6262,7 +6262,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C8D87BDD-F85A-424D-87CD-22D61D2063AC}" type="CELLRANGE">
+                    <a:fld id="{065FAF6D-4106-48BA-BF87-AEB7D9E49454}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6296,7 +6296,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9AA209F7-41EA-4D9E-87A0-7A7759E1F044}" type="CELLRANGE">
+                    <a:fld id="{67563F28-F123-42CE-A057-30F47DC48E4D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6330,7 +6330,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{042C6248-E944-419A-B54D-439FD3279CA1}" type="CELLRANGE">
+                    <a:fld id="{7FCB3E56-213B-4FEC-9650-F130D9CBD8D8}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6364,7 +6364,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B1E051FA-6F27-4CC1-A08F-BFC93D377178}" type="CELLRANGE">
+                    <a:fld id="{784E2146-AD47-453D-B050-A0AE097A559C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6398,7 +6398,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F727E572-70CF-482F-A5CD-1F54A972C5EC}" type="CELLRANGE">
+                    <a:fld id="{E9BDB4F9-1F15-42BF-86BA-B6E06E0D017D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6432,7 +6432,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{814A56B1-7CBB-4E8B-9C43-65C3160CA583}" type="CELLRANGE">
+                    <a:fld id="{9E1E49B6-33C1-45AC-B045-06312631E24F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6466,7 +6466,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{140F1385-5BF6-4E72-8AD4-5422E6D8DB59}" type="CELLRANGE">
+                    <a:fld id="{7EB2E143-63FD-4441-BFBF-01091438003E}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6500,7 +6500,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0BD40F40-2198-4C5A-933F-263852357764}" type="CELLRANGE">
+                    <a:fld id="{BC958521-79BB-47E1-AE3D-1345CC53E8E9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6534,7 +6534,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{77E27A50-C1AC-4C8B-A8F4-69A68A3C59D7}" type="CELLRANGE">
+                    <a:fld id="{567A2A9E-7E58-43AC-AADC-A857EE8B5CAC}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6568,7 +6568,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{19E4C1AF-964E-4DE5-8389-7A51937CB061}" type="CELLRANGE">
+                    <a:fld id="{23C55975-1830-4753-BA63-0E806F582504}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6602,7 +6602,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C09C5A89-905D-4271-A055-BBF452FDBD09}" type="CELLRANGE">
+                    <a:fld id="{CC154B45-B2C2-45B2-954B-558E6AD226C2}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6636,7 +6636,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{65AA60D9-F6B6-42C8-98A0-ED296F8ED4B9}" type="CELLRANGE">
+                    <a:fld id="{9EC5BF9F-2DFD-438D-983D-8B99CB5F5A81}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6685,7 +6685,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{C2C661CE-B33F-4087-B547-B23A75B7ED8C}" type="CELLRANGE">
+                    <a:fld id="{3D9C9313-B24D-4EAF-B452-6858564D4CCB}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6744,7 +6744,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CE4D1AE6-3103-4E10-B7E5-683939C83FF7}" type="CELLRANGE">
+                    <a:fld id="{1872C0DF-D279-40C6-BFBA-2E40E7718A59}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6778,7 +6778,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{651EEA4E-FBFE-4713-88A3-CDC32832B4E0}" type="CELLRANGE">
+                    <a:fld id="{37A9DA76-51B2-419C-8EAA-C0E0CA444CD6}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6812,7 +6812,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4C649EEF-30BB-4C5F-8467-803BA6CBC5A1}" type="CELLRANGE">
+                    <a:fld id="{05D0C918-7348-470D-B3AB-D5FEBD449161}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6846,7 +6846,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FCCF2288-9128-4AC2-880D-438D9CC01243}" type="CELLRANGE">
+                    <a:fld id="{D9A264FC-B330-4404-8E54-A5D16391CA88}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6880,7 +6880,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4C9CFA64-9AC6-49F5-BD2C-8A6ABDD29215}" type="CELLRANGE">
+                    <a:fld id="{59381A38-9CA5-430F-98FB-9B02C6BE6744}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6914,7 +6914,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{11B9EB8B-4F9C-426D-B7D3-337717B9E46C}" type="CELLRANGE">
+                    <a:fld id="{59DCEADF-5CD2-4E47-94D5-DC9DCFC2D355}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6948,7 +6948,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D95BD3BD-C073-4BD0-BF4F-214DE8330347}" type="CELLRANGE">
+                    <a:fld id="{1CF15852-E4F0-4DA7-98C6-9BF57F758C7F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7126,10 +7126,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>189</c:v>
+                  <c:v>190</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>261</c:v>
@@ -7138,7 +7138,7 @@
                   <c:v>312</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>233</c:v>
+                  <c:v>234</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>123</c:v>
@@ -7147,7 +7147,7 @@
                   <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>276</c:v>
+                  <c:v>278</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>95</c:v>
@@ -7171,7 +7171,7 @@
                   <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>79</c:v>
+                  <c:v>78</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>90</c:v>
@@ -7183,7 +7183,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>63</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>2</c:v>
@@ -7216,7 +7216,7 @@
                   <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>62</c:v>
@@ -7470,7 +7470,7 @@
                         <c:v>32</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>9</c:v>
+                        <c:v>10</c:v>
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>62</c:v>
@@ -33389,320 +33389,320 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:80" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E1" s="214">
-        <v>1</v>
-      </c>
-      <c r="F1" s="214"/>
-      <c r="G1" s="212">
+      <c r="E1" s="221">
+        <v>1</v>
+      </c>
+      <c r="F1" s="221"/>
+      <c r="G1" s="222">
         <v>2</v>
       </c>
-      <c r="H1" s="212"/>
-      <c r="I1" s="213">
-        <v>3</v>
-      </c>
-      <c r="J1" s="213"/>
-      <c r="K1" s="212">
+      <c r="H1" s="222"/>
+      <c r="I1" s="223">
+        <v>3</v>
+      </c>
+      <c r="J1" s="223"/>
+      <c r="K1" s="222">
         <v>4</v>
       </c>
-      <c r="L1" s="212"/>
-      <c r="M1" s="212">
+      <c r="L1" s="222"/>
+      <c r="M1" s="222">
         <v>5</v>
       </c>
-      <c r="N1" s="212"/>
-      <c r="O1" s="214">
+      <c r="N1" s="222"/>
+      <c r="O1" s="221">
         <v>6</v>
       </c>
-      <c r="P1" s="214"/>
-      <c r="Q1" s="212">
+      <c r="P1" s="221"/>
+      <c r="Q1" s="222">
         <v>7</v>
       </c>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212">
+      <c r="R1" s="222"/>
+      <c r="S1" s="222">
         <v>8</v>
       </c>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212">
+      <c r="T1" s="222"/>
+      <c r="U1" s="222">
         <v>9</v>
       </c>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212">
+      <c r="V1" s="222"/>
+      <c r="W1" s="222">
         <v>10</v>
       </c>
-      <c r="X1" s="212"/>
-      <c r="Y1" s="212">
+      <c r="X1" s="222"/>
+      <c r="Y1" s="222">
         <v>11</v>
       </c>
-      <c r="Z1" s="212"/>
-      <c r="AA1" s="213">
+      <c r="Z1" s="222"/>
+      <c r="AA1" s="223">
         <v>12</v>
       </c>
-      <c r="AB1" s="213"/>
-      <c r="AC1" s="214">
+      <c r="AB1" s="223"/>
+      <c r="AC1" s="221">
         <v>13</v>
       </c>
-      <c r="AD1" s="214"/>
-      <c r="AE1" s="213">
+      <c r="AD1" s="221"/>
+      <c r="AE1" s="223">
         <v>14</v>
       </c>
-      <c r="AF1" s="213"/>
-      <c r="AG1" s="215">
+      <c r="AF1" s="223"/>
+      <c r="AG1" s="224">
         <v>15</v>
       </c>
-      <c r="AH1" s="216"/>
-      <c r="AI1" s="212">
+      <c r="AH1" s="225"/>
+      <c r="AI1" s="222">
         <v>16</v>
       </c>
-      <c r="AJ1" s="212"/>
-      <c r="AK1" s="212">
+      <c r="AJ1" s="222"/>
+      <c r="AK1" s="222">
         <v>17</v>
       </c>
-      <c r="AL1" s="212"/>
-      <c r="AM1" s="212">
+      <c r="AL1" s="222"/>
+      <c r="AM1" s="222">
         <v>18</v>
       </c>
-      <c r="AN1" s="212"/>
-      <c r="AO1" s="211">
+      <c r="AN1" s="222"/>
+      <c r="AO1" s="226">
         <v>19</v>
       </c>
-      <c r="AP1" s="211"/>
-      <c r="AQ1" s="211">
+      <c r="AP1" s="226"/>
+      <c r="AQ1" s="226">
         <v>20</v>
       </c>
-      <c r="AR1" s="211"/>
-      <c r="AS1" s="211">
+      <c r="AR1" s="226"/>
+      <c r="AS1" s="226">
         <v>21</v>
       </c>
-      <c r="AT1" s="211"/>
-      <c r="AU1" s="211">
+      <c r="AT1" s="226"/>
+      <c r="AU1" s="226">
         <v>22</v>
       </c>
-      <c r="AV1" s="211"/>
-      <c r="AW1" s="211">
+      <c r="AV1" s="226"/>
+      <c r="AW1" s="226">
         <v>23</v>
       </c>
-      <c r="AX1" s="211"/>
-      <c r="AY1" s="211">
+      <c r="AX1" s="226"/>
+      <c r="AY1" s="226">
         <v>24</v>
       </c>
-      <c r="AZ1" s="211"/>
-      <c r="BA1" s="211">
+      <c r="AZ1" s="226"/>
+      <c r="BA1" s="226">
         <v>25</v>
       </c>
-      <c r="BB1" s="211"/>
-      <c r="BC1" s="211">
+      <c r="BB1" s="226"/>
+      <c r="BC1" s="226">
         <v>26</v>
       </c>
-      <c r="BD1" s="211"/>
-      <c r="BE1" s="211">
+      <c r="BD1" s="226"/>
+      <c r="BE1" s="226">
         <v>27</v>
       </c>
-      <c r="BF1" s="211"/>
-      <c r="BG1" s="211">
+      <c r="BF1" s="226"/>
+      <c r="BG1" s="226">
         <v>28</v>
       </c>
-      <c r="BH1" s="211"/>
-      <c r="BI1" s="211">
+      <c r="BH1" s="226"/>
+      <c r="BI1" s="226">
         <v>29</v>
       </c>
-      <c r="BJ1" s="211"/>
-      <c r="BK1" s="211">
+      <c r="BJ1" s="226"/>
+      <c r="BK1" s="226">
         <v>30</v>
       </c>
-      <c r="BL1" s="211"/>
-      <c r="BM1" s="211">
+      <c r="BL1" s="226"/>
+      <c r="BM1" s="226">
         <v>31</v>
       </c>
-      <c r="BN1" s="211"/>
-      <c r="BO1" s="211">
+      <c r="BN1" s="226"/>
+      <c r="BO1" s="226">
         <v>32</v>
       </c>
-      <c r="BP1" s="211"/>
-      <c r="BQ1" s="211">
+      <c r="BP1" s="226"/>
+      <c r="BQ1" s="226">
         <v>33</v>
       </c>
-      <c r="BR1" s="211"/>
-      <c r="BS1" s="211">
+      <c r="BR1" s="226"/>
+      <c r="BS1" s="226">
         <v>34</v>
       </c>
-      <c r="BT1" s="211"/>
-      <c r="BU1" s="211">
+      <c r="BT1" s="226"/>
+      <c r="BU1" s="226">
         <v>35</v>
       </c>
-      <c r="BV1" s="211"/>
-      <c r="BW1" s="211">
+      <c r="BV1" s="226"/>
+      <c r="BW1" s="226">
         <v>36</v>
       </c>
-      <c r="BX1" s="211"/>
-      <c r="BY1" s="211">
+      <c r="BX1" s="226"/>
+      <c r="BY1" s="226">
         <v>37</v>
       </c>
-      <c r="BZ1" s="211"/>
-      <c r="CA1" s="211">
+      <c r="BZ1" s="226"/>
+      <c r="CA1" s="226">
         <v>38</v>
       </c>
-      <c r="CB1" s="211"/>
+      <c r="CB1" s="226"/>
     </row>
     <row r="2" spans="1:80" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="209" t="s">
+      <c r="C2" s="227" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="209" t="s">
+      <c r="D2" s="227" t="s">
         <v>99</v>
       </c>
-      <c r="E2" s="225" t="s">
+      <c r="E2" s="213" t="s">
         <v>356</v>
       </c>
-      <c r="F2" s="226"/>
-      <c r="G2" s="217" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="215" t="s">
         <v>341</v>
       </c>
-      <c r="H2" s="218"/>
-      <c r="I2" s="219" t="s">
+      <c r="H2" s="216"/>
+      <c r="I2" s="211" t="s">
         <v>340</v>
       </c>
-      <c r="J2" s="220"/>
-      <c r="K2" s="219" t="s">
+      <c r="J2" s="212"/>
+      <c r="K2" s="211" t="s">
         <v>338</v>
       </c>
-      <c r="L2" s="220"/>
-      <c r="M2" s="227" t="s">
+      <c r="L2" s="212"/>
+      <c r="M2" s="209" t="s">
         <v>345</v>
       </c>
-      <c r="N2" s="228"/>
-      <c r="O2" s="219" t="s">
+      <c r="N2" s="210"/>
+      <c r="O2" s="211" t="s">
         <v>330</v>
       </c>
-      <c r="P2" s="220"/>
-      <c r="Q2" s="219" t="s">
+      <c r="P2" s="212"/>
+      <c r="Q2" s="211" t="s">
         <v>347</v>
       </c>
-      <c r="R2" s="220"/>
-      <c r="S2" s="219" t="s">
+      <c r="R2" s="212"/>
+      <c r="S2" s="211" t="s">
         <v>344</v>
       </c>
-      <c r="T2" s="220"/>
-      <c r="U2" s="219" t="s">
+      <c r="T2" s="212"/>
+      <c r="U2" s="211" t="s">
         <v>331</v>
       </c>
-      <c r="V2" s="220"/>
-      <c r="W2" s="219" t="s">
+      <c r="V2" s="212"/>
+      <c r="W2" s="211" t="s">
         <v>357</v>
       </c>
-      <c r="X2" s="220"/>
-      <c r="Y2" s="219" t="s">
+      <c r="X2" s="212"/>
+      <c r="Y2" s="211" t="s">
         <v>334</v>
       </c>
-      <c r="Z2" s="220"/>
-      <c r="AA2" s="219" t="s">
+      <c r="Z2" s="212"/>
+      <c r="AA2" s="211" t="s">
         <v>333</v>
       </c>
-      <c r="AB2" s="220"/>
-      <c r="AC2" s="227" t="s">
+      <c r="AB2" s="212"/>
+      <c r="AC2" s="209" t="s">
         <v>342</v>
       </c>
-      <c r="AD2" s="228"/>
-      <c r="AE2" s="227" t="s">
+      <c r="AD2" s="210"/>
+      <c r="AE2" s="209" t="s">
         <v>339</v>
       </c>
-      <c r="AF2" s="228"/>
-      <c r="AG2" s="227" t="s">
+      <c r="AF2" s="210"/>
+      <c r="AG2" s="209" t="s">
         <v>346</v>
       </c>
-      <c r="AH2" s="228"/>
-      <c r="AI2" s="227" t="s">
+      <c r="AH2" s="210"/>
+      <c r="AI2" s="209" t="s">
         <v>315</v>
       </c>
-      <c r="AJ2" s="228"/>
-      <c r="AK2" s="219" t="s">
+      <c r="AJ2" s="210"/>
+      <c r="AK2" s="211" t="s">
         <v>336</v>
       </c>
-      <c r="AL2" s="220"/>
-      <c r="AM2" s="225" t="s">
+      <c r="AL2" s="212"/>
+      <c r="AM2" s="213" t="s">
         <v>335</v>
       </c>
-      <c r="AN2" s="226"/>
-      <c r="AO2" s="225" t="s">
+      <c r="AN2" s="214"/>
+      <c r="AO2" s="213" t="s">
         <v>358</v>
       </c>
-      <c r="AP2" s="226"/>
-      <c r="AQ2" s="223" t="s">
+      <c r="AP2" s="214"/>
+      <c r="AQ2" s="217" t="s">
         <v>342</v>
       </c>
-      <c r="AR2" s="224"/>
-      <c r="AS2" s="223" t="s">
+      <c r="AR2" s="218"/>
+      <c r="AS2" s="217" t="s">
         <v>357</v>
       </c>
-      <c r="AT2" s="224"/>
-      <c r="AU2" s="221" t="s">
+      <c r="AT2" s="218"/>
+      <c r="AU2" s="219" t="s">
         <v>334</v>
       </c>
-      <c r="AV2" s="222"/>
-      <c r="AW2" s="221" t="s">
+      <c r="AV2" s="220"/>
+      <c r="AW2" s="219" t="s">
         <v>333</v>
       </c>
-      <c r="AX2" s="222"/>
-      <c r="AY2" s="225" t="s">
+      <c r="AX2" s="220"/>
+      <c r="AY2" s="213" t="s">
         <v>331</v>
       </c>
-      <c r="AZ2" s="226"/>
-      <c r="BA2" s="221" t="s">
+      <c r="AZ2" s="214"/>
+      <c r="BA2" s="219" t="s">
         <v>358</v>
       </c>
-      <c r="BB2" s="222"/>
-      <c r="BC2" s="223" t="s">
+      <c r="BB2" s="220"/>
+      <c r="BC2" s="217" t="s">
         <v>335</v>
       </c>
-      <c r="BD2" s="224"/>
-      <c r="BE2" s="223" t="s">
+      <c r="BD2" s="218"/>
+      <c r="BE2" s="217" t="s">
         <v>315</v>
       </c>
-      <c r="BF2" s="224"/>
-      <c r="BG2" s="225" t="s">
+      <c r="BF2" s="218"/>
+      <c r="BG2" s="213" t="s">
         <v>336</v>
       </c>
-      <c r="BH2" s="226"/>
-      <c r="BI2" s="225" t="s">
+      <c r="BH2" s="214"/>
+      <c r="BI2" s="213" t="s">
         <v>340</v>
       </c>
-      <c r="BJ2" s="226"/>
-      <c r="BK2" s="221" t="s">
+      <c r="BJ2" s="214"/>
+      <c r="BK2" s="219" t="s">
         <v>338</v>
       </c>
-      <c r="BL2" s="222"/>
-      <c r="BM2" s="219" t="s">
+      <c r="BL2" s="220"/>
+      <c r="BM2" s="211" t="s">
         <v>356</v>
       </c>
-      <c r="BN2" s="220"/>
-      <c r="BO2" s="219" t="s">
+      <c r="BN2" s="212"/>
+      <c r="BO2" s="211" t="s">
         <v>341</v>
       </c>
-      <c r="BP2" s="220"/>
-      <c r="BQ2" s="217" t="s">
+      <c r="BP2" s="212"/>
+      <c r="BQ2" s="215" t="s">
         <v>346</v>
       </c>
-      <c r="BR2" s="218"/>
-      <c r="BS2" s="217" t="s">
+      <c r="BR2" s="216"/>
+      <c r="BS2" s="215" t="s">
         <v>339</v>
       </c>
-      <c r="BT2" s="218"/>
-      <c r="BU2" s="217" t="s">
+      <c r="BT2" s="216"/>
+      <c r="BU2" s="215" t="s">
         <v>330</v>
       </c>
-      <c r="BV2" s="218"/>
-      <c r="BW2" s="217" t="s">
+      <c r="BV2" s="216"/>
+      <c r="BW2" s="215" t="s">
         <v>347</v>
       </c>
-      <c r="BX2" s="218"/>
-      <c r="BY2" s="219" t="s">
+      <c r="BX2" s="216"/>
+      <c r="BY2" s="211" t="s">
         <v>344</v>
       </c>
-      <c r="BZ2" s="220"/>
-      <c r="CA2" s="217" t="s">
+      <c r="BZ2" s="212"/>
+      <c r="CA2" s="215" t="s">
         <v>345</v>
       </c>
-      <c r="CB2" s="218"/>
+      <c r="CB2" s="216"/>
     </row>
     <row r="3" spans="1:80" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -33711,8 +33711,8 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="210"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="228"/>
+      <c r="D3" s="228"/>
       <c r="E3" s="147" t="s">
         <v>87</v>
       </c>
@@ -37658,68 +37658,6 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="AS2:AT2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="AI2:AJ2"/>
-    <mergeCell ref="AK2:AL2"/>
-    <mergeCell ref="AM2:AN2"/>
-    <mergeCell ref="AO2:AP2"/>
-    <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AG2:AH2"/>
-    <mergeCell ref="BQ2:BR2"/>
-    <mergeCell ref="BA2:BB2"/>
-    <mergeCell ref="BC2:BD2"/>
-    <mergeCell ref="BE2:BF2"/>
-    <mergeCell ref="AU2:AV2"/>
-    <mergeCell ref="AW2:AX2"/>
-    <mergeCell ref="AY2:AZ2"/>
-    <mergeCell ref="BG2:BH2"/>
-    <mergeCell ref="BI2:BJ2"/>
-    <mergeCell ref="BK2:BL2"/>
-    <mergeCell ref="BM2:BN2"/>
-    <mergeCell ref="BO2:BP2"/>
-    <mergeCell ref="BS2:BT2"/>
-    <mergeCell ref="BU2:BV2"/>
-    <mergeCell ref="BW2:BX2"/>
-    <mergeCell ref="BY2:BZ2"/>
-    <mergeCell ref="CA2:CB2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AY1:AZ1"/>
-    <mergeCell ref="BA1:BB1"/>
-    <mergeCell ref="BC1:BD1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="AS1:AT1"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="BY1:BZ1"/>
@@ -37736,6 +37674,68 @@
     <mergeCell ref="BM1:BN1"/>
     <mergeCell ref="AU1:AV1"/>
     <mergeCell ref="AW1:AX1"/>
+    <mergeCell ref="AY1:AZ1"/>
+    <mergeCell ref="BA1:BB1"/>
+    <mergeCell ref="BC1:BD1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="BS2:BT2"/>
+    <mergeCell ref="BU2:BV2"/>
+    <mergeCell ref="BW2:BX2"/>
+    <mergeCell ref="BY2:BZ2"/>
+    <mergeCell ref="CA2:CB2"/>
+    <mergeCell ref="BQ2:BR2"/>
+    <mergeCell ref="BA2:BB2"/>
+    <mergeCell ref="BC2:BD2"/>
+    <mergeCell ref="BE2:BF2"/>
+    <mergeCell ref="AU2:AV2"/>
+    <mergeCell ref="AW2:AX2"/>
+    <mergeCell ref="AY2:AZ2"/>
+    <mergeCell ref="BG2:BH2"/>
+    <mergeCell ref="BI2:BJ2"/>
+    <mergeCell ref="BK2:BL2"/>
+    <mergeCell ref="BM2:BN2"/>
+    <mergeCell ref="BO2:BP2"/>
+    <mergeCell ref="AS2:AT2"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AE2:AF2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="AI2:AJ2"/>
+    <mergeCell ref="AK2:AL2"/>
+    <mergeCell ref="AM2:AN2"/>
+    <mergeCell ref="AO2:AP2"/>
+    <mergeCell ref="AQ2:AR2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AG2:AH2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:CB40">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -37770,88 +37770,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="209" t="s">
+      <c r="C1" s="227" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="209" t="s">
+      <c r="D1" s="227" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="232" t="s">
+      <c r="E1" s="242" t="s">
         <v>312</v>
       </c>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
-      <c r="S1" s="233"/>
-      <c r="T1" s="234"/>
-      <c r="U1" s="249" t="s">
+      <c r="F1" s="243"/>
+      <c r="G1" s="243"/>
+      <c r="H1" s="243"/>
+      <c r="I1" s="243"/>
+      <c r="J1" s="243"/>
+      <c r="K1" s="243"/>
+      <c r="L1" s="243"/>
+      <c r="M1" s="243"/>
+      <c r="N1" s="243"/>
+      <c r="O1" s="243"/>
+      <c r="P1" s="243"/>
+      <c r="Q1" s="243"/>
+      <c r="R1" s="243"/>
+      <c r="S1" s="243"/>
+      <c r="T1" s="244"/>
+      <c r="U1" s="247" t="s">
         <v>291</v>
       </c>
-      <c r="V1" s="249"/>
-      <c r="W1" s="249"/>
-      <c r="X1" s="249"/>
-      <c r="Y1" s="232" t="s">
+      <c r="V1" s="247"/>
+      <c r="W1" s="247"/>
+      <c r="X1" s="247"/>
+      <c r="Y1" s="242" t="s">
         <v>292</v>
       </c>
-      <c r="Z1" s="233"/>
-      <c r="AA1" s="233"/>
-      <c r="AB1" s="234"/>
-      <c r="AC1" s="247" t="s">
+      <c r="Z1" s="243"/>
+      <c r="AA1" s="243"/>
+      <c r="AB1" s="244"/>
+      <c r="AC1" s="245" t="s">
         <v>293</v>
       </c>
-      <c r="AD1" s="247"/>
-      <c r="AE1" s="247"/>
-      <c r="AF1" s="248"/>
-      <c r="AG1" s="245" t="s">
+      <c r="AD1" s="245"/>
+      <c r="AE1" s="245"/>
+      <c r="AF1" s="246"/>
+      <c r="AG1" s="240" t="s">
         <v>89</v>
       </c>
-      <c r="AH1" s="246"/>
+      <c r="AH1" s="241"/>
     </row>
     <row r="2" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="210"/>
-      <c r="D2" s="210"/>
-      <c r="E2" s="229"/>
-      <c r="F2" s="230"/>
-      <c r="G2" s="235"/>
-      <c r="H2" s="236"/>
-      <c r="I2" s="229"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="229"/>
-      <c r="L2" s="230"/>
-      <c r="M2" s="229"/>
-      <c r="N2" s="231"/>
-      <c r="O2" s="229"/>
-      <c r="P2" s="230"/>
-      <c r="Q2" s="229"/>
-      <c r="R2" s="230"/>
-      <c r="S2" s="229"/>
-      <c r="T2" s="230"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="239"/>
-      <c r="Y2" s="229"/>
-      <c r="Z2" s="231"/>
-      <c r="AA2" s="231"/>
-      <c r="AB2" s="230"/>
-      <c r="AC2" s="240"/>
-      <c r="AD2" s="241"/>
-      <c r="AE2" s="241"/>
-      <c r="AF2" s="242"/>
-      <c r="AG2" s="243"/>
-      <c r="AH2" s="244"/>
+      <c r="C2" s="228"/>
+      <c r="D2" s="228"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="234"/>
+      <c r="G2" s="248"/>
+      <c r="H2" s="249"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="234"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="234"/>
+      <c r="M2" s="232"/>
+      <c r="N2" s="233"/>
+      <c r="O2" s="232"/>
+      <c r="P2" s="234"/>
+      <c r="Q2" s="232"/>
+      <c r="R2" s="234"/>
+      <c r="S2" s="232"/>
+      <c r="T2" s="234"/>
+      <c r="U2" s="229"/>
+      <c r="V2" s="230"/>
+      <c r="W2" s="230"/>
+      <c r="X2" s="231"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="233"/>
+      <c r="AA2" s="233"/>
+      <c r="AB2" s="234"/>
+      <c r="AC2" s="235"/>
+      <c r="AD2" s="236"/>
+      <c r="AE2" s="236"/>
+      <c r="AF2" s="237"/>
+      <c r="AG2" s="238"/>
+      <c r="AH2" s="239"/>
     </row>
     <row r="3" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -39779,6 +39779,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="E1:T1"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
     <mergeCell ref="U2:X2"/>
     <mergeCell ref="Y2:AB2"/>
     <mergeCell ref="AC2:AF2"/>
@@ -39787,17 +39798,6 @@
     <mergeCell ref="Y1:AB1"/>
     <mergeCell ref="AC1:AF1"/>
     <mergeCell ref="U1:X1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="E1:T1"/>
-    <mergeCell ref="Q2:R2"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AH31">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -39830,10 +39830,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="209" t="s">
+      <c r="C1" s="227" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="209" t="s">
+      <c r="D1" s="227" t="s">
         <v>99</v>
       </c>
       <c r="E1" s="264" t="s">
@@ -39864,8 +39864,8 @@
     <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="210"/>
-      <c r="D2" s="210"/>
+      <c r="C2" s="228"/>
+      <c r="D2" s="228"/>
       <c r="E2" s="256"/>
       <c r="F2" s="257"/>
       <c r="G2" s="258"/>
@@ -39874,8 +39874,8 @@
       <c r="J2" s="261"/>
       <c r="K2" s="262"/>
       <c r="L2" s="263"/>
-      <c r="M2" s="231"/>
-      <c r="N2" s="231"/>
+      <c r="M2" s="233"/>
+      <c r="N2" s="233"/>
       <c r="O2" s="252"/>
       <c r="P2" s="253"/>
     </row>
@@ -41644,7 +41644,7 @@
         <v>229</v>
       </c>
       <c r="L9" s="26">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M9" s="26">
         <v>0</v>
@@ -41660,7 +41660,7 @@
       </c>
       <c r="Q9" s="26">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R9" s="26">
         <f t="shared" si="3"/>
@@ -41779,7 +41779,7 @@
         <v>328</v>
       </c>
       <c r="L10" s="26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M10" s="26">
         <v>0</v>
@@ -41795,7 +41795,7 @@
       </c>
       <c r="Q10" s="26">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R10" s="26">
         <f t="shared" si="3"/>
@@ -42184,7 +42184,7 @@
         <v>227</v>
       </c>
       <c r="L13" s="26">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M13" s="26">
         <v>6</v>
@@ -42200,7 +42200,7 @@
       </c>
       <c r="Q13" s="26">
         <f t="shared" si="2"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R13" s="26">
         <f t="shared" si="3"/>
@@ -42431,7 +42431,7 @@
         <v>32</v>
       </c>
       <c r="D15" s="25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" s="25"/>
       <c r="F15" s="21">
@@ -42448,7 +42448,7 @@
       </c>
       <c r="I15" s="25">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>329</v>
@@ -42563,7 +42563,7 @@
         <v>196</v>
       </c>
       <c r="C16" s="25">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D16" s="25">
         <v>41</v>
@@ -42579,7 +42579,7 @@
       </c>
       <c r="H16" s="25">
         <f t="shared" si="10"/>
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I16" s="25">
         <f t="shared" si="11"/>
@@ -42589,7 +42589,7 @@
         <v>196</v>
       </c>
       <c r="L16" s="26">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M16" s="26">
         <v>13</v>
@@ -42605,7 +42605,7 @@
       </c>
       <c r="Q16" s="26">
         <f t="shared" si="2"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R16" s="26">
         <f t="shared" si="3"/>
@@ -43669,7 +43669,7 @@
         <v>303</v>
       </c>
       <c r="L24" s="26">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M24" s="26">
         <v>4</v>
@@ -43685,7 +43685,7 @@
       </c>
       <c r="Q24" s="26">
         <f t="shared" si="14"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R24" s="26">
         <f t="shared" si="15"/>
@@ -44209,7 +44209,7 @@
         <v>301</v>
       </c>
       <c r="L28" s="26">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M28" s="26">
         <v>1</v>
@@ -44225,7 +44225,7 @@
       </c>
       <c r="Q28" s="26">
         <f t="shared" si="24"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R28" s="26">
         <f t="shared" si="25"/>
@@ -44479,7 +44479,7 @@
         <v>323</v>
       </c>
       <c r="L30" s="26">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M30" s="26">
         <v>0</v>
@@ -44495,7 +44495,7 @@
       </c>
       <c r="Q30" s="26">
         <f t="shared" si="24"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R30" s="26">
         <f t="shared" si="25"/>
@@ -46231,52 +46231,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="209" t="s">
+      <c r="C1" s="227" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="209" t="s">
+      <c r="D1" s="227" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="273" t="s">
+      <c r="E1" s="279" t="s">
         <v>91</v>
       </c>
-      <c r="F1" s="274"/>
-      <c r="G1" s="275" t="s">
+      <c r="F1" s="280"/>
+      <c r="G1" s="281" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="276"/>
-      <c r="I1" s="277" t="s">
+      <c r="H1" s="282"/>
+      <c r="I1" s="283" t="s">
         <v>207</v>
       </c>
-      <c r="J1" s="278"/>
-      <c r="K1" s="281" t="s">
+      <c r="J1" s="284"/>
+      <c r="K1" s="287" t="s">
         <v>208</v>
       </c>
-      <c r="L1" s="282"/>
-      <c r="M1" s="282"/>
-      <c r="N1" s="283"/>
-      <c r="O1" s="279" t="s">
+      <c r="L1" s="288"/>
+      <c r="M1" s="288"/>
+      <c r="N1" s="289"/>
+      <c r="O1" s="285" t="s">
         <v>316</v>
       </c>
-      <c r="P1" s="280"/>
+      <c r="P1" s="286"/>
     </row>
     <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="210"/>
-      <c r="D2" s="210"/>
-      <c r="E2" s="284"/>
-      <c r="F2" s="285"/>
-      <c r="G2" s="286"/>
-      <c r="H2" s="287"/>
-      <c r="I2" s="288"/>
-      <c r="J2" s="289"/>
-      <c r="K2" s="270"/>
-      <c r="L2" s="271"/>
-      <c r="M2" s="270"/>
-      <c r="N2" s="271"/>
-      <c r="O2" s="270"/>
-      <c r="P2" s="272"/>
+      <c r="C2" s="228"/>
+      <c r="D2" s="228"/>
+      <c r="E2" s="270"/>
+      <c r="F2" s="271"/>
+      <c r="G2" s="272"/>
+      <c r="H2" s="273"/>
+      <c r="I2" s="274"/>
+      <c r="J2" s="275"/>
+      <c r="K2" s="276"/>
+      <c r="L2" s="277"/>
+      <c r="M2" s="276"/>
+      <c r="N2" s="277"/>
+      <c r="O2" s="276"/>
+      <c r="P2" s="278"/>
     </row>
     <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -47412,11 +47412,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="E1:F1"/>
@@ -47425,6 +47420,11 @@
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:P35">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -47868,51 +47868,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="293" t="s">
+      <c r="C1" s="298" t="s">
         <v>210</v>
       </c>
-      <c r="D1" s="294"/>
-      <c r="E1" s="294"/>
-      <c r="F1" s="294"/>
-      <c r="G1" s="294"/>
-      <c r="H1" s="294"/>
-      <c r="I1" s="295"/>
+      <c r="D1" s="299"/>
+      <c r="E1" s="299"/>
+      <c r="F1" s="299"/>
+      <c r="G1" s="299"/>
+      <c r="H1" s="299"/>
+      <c r="I1" s="300"/>
       <c r="J1" s="135" t="s">
         <v>203</v>
       </c>
       <c r="K1" s="136" t="s">
         <v>202</v>
       </c>
-      <c r="L1" s="326" t="s">
+      <c r="L1" s="292" t="s">
         <v>297</v>
       </c>
-      <c r="M1" s="329"/>
-      <c r="N1" s="329"/>
-      <c r="O1" s="329"/>
-      <c r="P1" s="329"/>
-      <c r="Q1" s="329"/>
-      <c r="R1" s="329"/>
-      <c r="S1" s="329"/>
-      <c r="T1" s="329"/>
-      <c r="U1" s="329"/>
-      <c r="V1" s="329"/>
-      <c r="W1" s="329"/>
-      <c r="X1" s="329"/>
-      <c r="Y1" s="329"/>
-      <c r="Z1" s="329"/>
-      <c r="AA1" s="329"/>
-      <c r="AB1" s="329"/>
-      <c r="AC1" s="329"/>
-      <c r="AD1" s="329"/>
-      <c r="AE1" s="329"/>
-      <c r="AF1" s="329"/>
-      <c r="AG1" s="330"/>
-      <c r="AH1" s="326" t="s">
+      <c r="M1" s="296"/>
+      <c r="N1" s="296"/>
+      <c r="O1" s="296"/>
+      <c r="P1" s="296"/>
+      <c r="Q1" s="296"/>
+      <c r="R1" s="296"/>
+      <c r="S1" s="296"/>
+      <c r="T1" s="296"/>
+      <c r="U1" s="296"/>
+      <c r="V1" s="296"/>
+      <c r="W1" s="296"/>
+      <c r="X1" s="296"/>
+      <c r="Y1" s="296"/>
+      <c r="Z1" s="296"/>
+      <c r="AA1" s="296"/>
+      <c r="AB1" s="296"/>
+      <c r="AC1" s="296"/>
+      <c r="AD1" s="296"/>
+      <c r="AE1" s="296"/>
+      <c r="AF1" s="296"/>
+      <c r="AG1" s="297"/>
+      <c r="AH1" s="292" t="s">
         <v>183</v>
       </c>
-      <c r="AI1" s="327"/>
-      <c r="AJ1" s="327"/>
-      <c r="AK1" s="328"/>
+      <c r="AI1" s="293"/>
+      <c r="AJ1" s="293"/>
+      <c r="AK1" s="294"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="132"/>
@@ -53100,15 +53100,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="317" t="s">
+      <c r="K80" s="322" t="s">
         <v>183</v>
       </c>
-      <c r="L80" s="318"/>
-      <c r="M80" s="319"/>
+      <c r="L80" s="323"/>
+      <c r="M80" s="324"/>
       <c r="O80" s="157"/>
       <c r="P80" s="157"/>
-      <c r="W80" s="292"/>
-      <c r="X80" s="292"/>
+      <c r="W80" s="295"/>
+      <c r="X80" s="295"/>
       <c r="Y80" s="89" t="s">
         <v>220</v>
       </c>
@@ -53158,15 +53158,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="320"/>
-      <c r="L81" s="321"/>
-      <c r="M81" s="322"/>
+      <c r="K81" s="325"/>
+      <c r="L81" s="326"/>
+      <c r="M81" s="327"/>
       <c r="O81" s="157"/>
       <c r="P81" s="157"/>
-      <c r="W81" s="292" t="s">
+      <c r="W81" s="295" t="s">
         <v>217</v>
       </c>
-      <c r="X81" s="292"/>
+      <c r="X81" s="295"/>
       <c r="Y81" s="89">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -53222,15 +53222,15 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="320"/>
-      <c r="L82" s="321"/>
-      <c r="M82" s="322"/>
+      <c r="K82" s="325"/>
+      <c r="L82" s="326"/>
+      <c r="M82" s="327"/>
       <c r="O82" s="157"/>
       <c r="P82" s="157"/>
-      <c r="W82" s="292" t="s">
+      <c r="W82" s="295" t="s">
         <v>218</v>
       </c>
-      <c r="X82" s="292"/>
+      <c r="X82" s="295"/>
       <c r="Y82" s="89">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -53286,15 +53286,15 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="323"/>
-      <c r="L83" s="324"/>
-      <c r="M83" s="325"/>
+      <c r="K83" s="328"/>
+      <c r="L83" s="329"/>
+      <c r="M83" s="330"/>
       <c r="O83" s="157"/>
       <c r="P83" s="157"/>
-      <c r="W83" s="292" t="s">
+      <c r="W83" s="295" t="s">
         <v>219</v>
       </c>
-      <c r="X83" s="292"/>
+      <c r="X83" s="295"/>
       <c r="Y83" s="89">
         <f>COUNTIF(J16:J20,3)</f>
         <v>1</v>
@@ -53350,17 +53350,17 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="308" t="s">
+      <c r="K84" s="313" t="s">
         <v>294</v>
       </c>
-      <c r="L84" s="309"/>
-      <c r="M84" s="310"/>
+      <c r="L84" s="314"/>
+      <c r="M84" s="315"/>
       <c r="O84" s="165"/>
       <c r="P84" s="165"/>
-      <c r="W84" s="292" t="s">
+      <c r="W84" s="295" t="s">
         <v>103</v>
       </c>
-      <c r="X84" s="292"/>
+      <c r="X84" s="295"/>
       <c r="Y84" s="89">
         <f>COUNTIF(J21:J40,3)+COUNTIF(I3:I40,3)+COUNTIF(H3:H40,3)+COUNTIF(G3:G40,3)+COUNTIF(F3:F40,3)+COUNTIF(E3:E40,3)</f>
         <v>123</v>
@@ -53416,9 +53416,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="311"/>
-      <c r="L85" s="312"/>
-      <c r="M85" s="313"/>
+      <c r="K85" s="316"/>
+      <c r="L85" s="317"/>
+      <c r="M85" s="318"/>
       <c r="O85" s="165"/>
       <c r="P85" s="165"/>
     </row>
@@ -53452,9 +53452,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="311"/>
-      <c r="L86" s="312"/>
-      <c r="M86" s="313"/>
+      <c r="K86" s="316"/>
+      <c r="L86" s="317"/>
+      <c r="M86" s="318"/>
       <c r="O86" s="165"/>
       <c r="P86" s="165"/>
     </row>
@@ -53488,9 +53488,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="311"/>
-      <c r="L87" s="312"/>
-      <c r="M87" s="313"/>
+      <c r="K87" s="316"/>
+      <c r="L87" s="317"/>
+      <c r="M87" s="318"/>
       <c r="O87" s="165"/>
       <c r="P87" s="165"/>
     </row>
@@ -53524,9 +53524,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="311"/>
-      <c r="L88" s="312"/>
-      <c r="M88" s="313"/>
+      <c r="K88" s="316"/>
+      <c r="L88" s="317"/>
+      <c r="M88" s="318"/>
       <c r="O88" s="165"/>
       <c r="P88" s="165"/>
     </row>
@@ -53560,9 +53560,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="311"/>
-      <c r="L89" s="312"/>
-      <c r="M89" s="313"/>
+      <c r="K89" s="316"/>
+      <c r="L89" s="317"/>
+      <c r="M89" s="318"/>
       <c r="O89" s="165"/>
       <c r="P89" s="165"/>
     </row>
@@ -53596,9 +53596,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="311"/>
-      <c r="L90" s="312"/>
-      <c r="M90" s="313"/>
+      <c r="K90" s="316"/>
+      <c r="L90" s="317"/>
+      <c r="M90" s="318"/>
       <c r="O90" s="165"/>
       <c r="P90" s="165"/>
     </row>
@@ -53632,9 +53632,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="311"/>
-      <c r="L91" s="312"/>
-      <c r="M91" s="313"/>
+      <c r="K91" s="316"/>
+      <c r="L91" s="317"/>
+      <c r="M91" s="318"/>
       <c r="O91" s="165"/>
       <c r="P91" s="165"/>
     </row>
@@ -53668,9 +53668,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="311"/>
-      <c r="L92" s="312"/>
-      <c r="M92" s="313"/>
+      <c r="K92" s="316"/>
+      <c r="L92" s="317"/>
+      <c r="M92" s="318"/>
       <c r="O92" s="165"/>
       <c r="P92" s="165"/>
     </row>
@@ -53704,9 +53704,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="311"/>
-      <c r="L93" s="312"/>
-      <c r="M93" s="313"/>
+      <c r="K93" s="316"/>
+      <c r="L93" s="317"/>
+      <c r="M93" s="318"/>
       <c r="O93" s="165"/>
       <c r="P93" s="165"/>
     </row>
@@ -53740,9 +53740,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="311"/>
-      <c r="L94" s="312"/>
-      <c r="M94" s="313"/>
+      <c r="K94" s="316"/>
+      <c r="L94" s="317"/>
+      <c r="M94" s="318"/>
       <c r="O94" s="165"/>
       <c r="P94" s="165"/>
     </row>
@@ -53776,9 +53776,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="311"/>
-      <c r="L95" s="312"/>
-      <c r="M95" s="313"/>
+      <c r="K95" s="316"/>
+      <c r="L95" s="317"/>
+      <c r="M95" s="318"/>
       <c r="O95" s="165"/>
       <c r="P95" s="165"/>
     </row>
@@ -53812,9 +53812,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="311"/>
-      <c r="L96" s="312"/>
-      <c r="M96" s="313"/>
+      <c r="K96" s="316"/>
+      <c r="L96" s="317"/>
+      <c r="M96" s="318"/>
       <c r="O96" s="165"/>
       <c r="P96" s="165"/>
     </row>
@@ -53848,9 +53848,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="311"/>
-      <c r="L97" s="312"/>
-      <c r="M97" s="313"/>
+      <c r="K97" s="316"/>
+      <c r="L97" s="317"/>
+      <c r="M97" s="318"/>
       <c r="O97" s="165"/>
       <c r="P97" s="165"/>
     </row>
@@ -53884,9 +53884,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="311"/>
-      <c r="L98" s="312"/>
-      <c r="M98" s="313"/>
+      <c r="K98" s="316"/>
+      <c r="L98" s="317"/>
+      <c r="M98" s="318"/>
       <c r="O98" s="165"/>
       <c r="P98" s="165"/>
     </row>
@@ -53920,9 +53920,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="311"/>
-      <c r="L99" s="312"/>
-      <c r="M99" s="313"/>
+      <c r="K99" s="316"/>
+      <c r="L99" s="317"/>
+      <c r="M99" s="318"/>
       <c r="O99" s="165"/>
       <c r="P99" s="165"/>
     </row>
@@ -53956,9 +53956,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="311"/>
-      <c r="L100" s="312"/>
-      <c r="M100" s="313"/>
+      <c r="K100" s="316"/>
+      <c r="L100" s="317"/>
+      <c r="M100" s="318"/>
       <c r="O100" s="165"/>
       <c r="P100" s="165"/>
     </row>
@@ -53992,9 +53992,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="311"/>
-      <c r="L101" s="312"/>
-      <c r="M101" s="313"/>
+      <c r="K101" s="316"/>
+      <c r="L101" s="317"/>
+      <c r="M101" s="318"/>
       <c r="O101" s="165"/>
       <c r="P101" s="165"/>
     </row>
@@ -54028,9 +54028,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="311"/>
-      <c r="L102" s="312"/>
-      <c r="M102" s="313"/>
+      <c r="K102" s="316"/>
+      <c r="L102" s="317"/>
+      <c r="M102" s="318"/>
       <c r="O102" s="165"/>
       <c r="P102" s="165"/>
     </row>
@@ -54064,9 +54064,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="311"/>
-      <c r="L103" s="312"/>
-      <c r="M103" s="313"/>
+      <c r="K103" s="316"/>
+      <c r="L103" s="317"/>
+      <c r="M103" s="318"/>
       <c r="O103" s="165"/>
       <c r="P103" s="165"/>
     </row>
@@ -54100,9 +54100,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="311"/>
-      <c r="L104" s="312"/>
-      <c r="M104" s="313"/>
+      <c r="K104" s="316"/>
+      <c r="L104" s="317"/>
+      <c r="M104" s="318"/>
       <c r="O104" s="165"/>
       <c r="P104" s="165"/>
     </row>
@@ -54136,9 +54136,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="314"/>
-      <c r="L105" s="315"/>
-      <c r="M105" s="316"/>
+      <c r="K105" s="319"/>
+      <c r="L105" s="320"/>
+      <c r="M105" s="321"/>
       <c r="O105" s="165"/>
       <c r="P105" s="165"/>
     </row>
@@ -54172,11 +54172,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="305" t="s">
+      <c r="K106" s="310" t="s">
         <v>296</v>
       </c>
-      <c r="L106" s="306"/>
-      <c r="M106" s="307"/>
+      <c r="L106" s="311"/>
+      <c r="M106" s="312"/>
       <c r="O106" s="150"/>
       <c r="P106" s="150"/>
     </row>
@@ -54210,11 +54210,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="305" t="s">
+      <c r="K107" s="310" t="s">
         <v>298</v>
       </c>
-      <c r="L107" s="306"/>
-      <c r="M107" s="307"/>
+      <c r="L107" s="311"/>
+      <c r="M107" s="312"/>
       <c r="O107" s="150"/>
       <c r="P107" s="150"/>
     </row>
@@ -54248,11 +54248,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="296" t="s">
+      <c r="K108" s="301" t="s">
         <v>299</v>
       </c>
-      <c r="L108" s="297"/>
-      <c r="M108" s="298"/>
+      <c r="L108" s="302"/>
+      <c r="M108" s="303"/>
       <c r="O108" s="150"/>
       <c r="P108" s="150"/>
     </row>
@@ -54286,9 +54286,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="299"/>
-      <c r="L109" s="300"/>
-      <c r="M109" s="301"/>
+      <c r="K109" s="304"/>
+      <c r="L109" s="305"/>
+      <c r="M109" s="306"/>
       <c r="O109" s="150"/>
       <c r="P109" s="150"/>
     </row>
@@ -54322,9 +54322,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="299"/>
-      <c r="L110" s="300"/>
-      <c r="M110" s="301"/>
+      <c r="K110" s="304"/>
+      <c r="L110" s="305"/>
+      <c r="M110" s="306"/>
       <c r="O110" s="150"/>
       <c r="P110" s="150"/>
     </row>
@@ -54358,9 +54358,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="299"/>
-      <c r="L111" s="300"/>
-      <c r="M111" s="301"/>
+      <c r="K111" s="304"/>
+      <c r="L111" s="305"/>
+      <c r="M111" s="306"/>
       <c r="O111" s="150"/>
       <c r="P111" s="150"/>
     </row>
@@ -54398,9 +54398,9 @@
         <f t="shared" ref="J112:J113" si="7">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="299"/>
-      <c r="L112" s="300"/>
-      <c r="M112" s="301"/>
+      <c r="K112" s="304"/>
+      <c r="L112" s="305"/>
+      <c r="M112" s="306"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="199" t="s">
@@ -54436,19 +54436,13 @@
         <f t="shared" si="7"/>
         <v>43</v>
       </c>
-      <c r="K113" s="302"/>
-      <c r="L113" s="303"/>
-      <c r="M113" s="304"/>
+      <c r="K113" s="307"/>
+      <c r="L113" s="308"/>
+      <c r="M113" s="309"/>
     </row>
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="13">
-    <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="W80:X80"/>
-    <mergeCell ref="W81:X81"/>
-    <mergeCell ref="W82:X82"/>
-    <mergeCell ref="W83:X83"/>
-    <mergeCell ref="L1:AG1"/>
     <mergeCell ref="W84:X84"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="K108:M113"/>
@@ -54456,6 +54450,12 @@
     <mergeCell ref="K107:M107"/>
     <mergeCell ref="K84:M105"/>
     <mergeCell ref="K80:M83"/>
+    <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="W80:X80"/>
+    <mergeCell ref="W81:X81"/>
+    <mergeCell ref="W82:X82"/>
+    <mergeCell ref="W83:X83"/>
+    <mergeCell ref="L1:AG1"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -55673,7 +55673,7 @@
       </c>
       <c r="N2" s="202"/>
       <c r="R2" s="149">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -55905,7 +55905,7 @@
       </c>
       <c r="E7" s="4">
         <f>'#'!Q9</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7" s="4">
         <f>'#'!R9</f>
@@ -55937,7 +55937,7 @@
       </c>
       <c r="M7" s="2">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N7" s="2">
         <f t="shared" si="1"/>
@@ -55961,7 +55961,7 @@
       </c>
       <c r="E8" s="4">
         <f>'#'!Q10</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" s="4">
         <f>'#'!R10</f>
@@ -55993,7 +55993,7 @@
       </c>
       <c r="M8" s="2">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N8" s="2">
         <f t="shared" si="1"/>
@@ -56129,7 +56129,7 @@
       </c>
       <c r="E11" s="4">
         <f>'#'!Q13</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F11" s="4">
         <f>'#'!R13</f>
@@ -56161,7 +56161,7 @@
       </c>
       <c r="M11" s="2">
         <f t="shared" si="0"/>
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N11" s="2">
         <f t="shared" si="1"/>
@@ -56237,7 +56237,7 @@
       </c>
       <c r="D13" s="6">
         <f>'#'!I15</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="4">
         <f>'#'!Q15</f>
@@ -56277,7 +56277,7 @@
       </c>
       <c r="N13" s="2">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -56289,7 +56289,7 @@
       </c>
       <c r="C14" s="6">
         <f>'#'!H16</f>
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D14" s="6">
         <f>'#'!I16</f>
@@ -56297,7 +56297,7 @@
       </c>
       <c r="E14" s="4">
         <f>'#'!Q16</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F14" s="4">
         <f>'#'!R16</f>
@@ -56329,7 +56329,7 @@
       </c>
       <c r="M14" s="2">
         <f t="shared" si="0"/>
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N14" s="2">
         <f t="shared" si="1"/>
@@ -56745,7 +56745,7 @@
       </c>
       <c r="E22" s="4">
         <f>'#'!Q24</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F22" s="4">
         <f>'#'!R24</f>
@@ -56777,7 +56777,7 @@
       </c>
       <c r="M22" s="2">
         <f t="shared" si="2"/>
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N22" s="2">
         <f t="shared" si="3"/>
@@ -56969,7 +56969,7 @@
       </c>
       <c r="E26" s="4">
         <f>'#'!Q28</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F26" s="4">
         <f>'#'!R28</f>
@@ -57001,7 +57001,7 @@
       </c>
       <c r="M26" s="2">
         <f t="shared" si="4"/>
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N26" s="2">
         <f t="shared" si="5"/>
@@ -57081,7 +57081,7 @@
       </c>
       <c r="E28" s="4">
         <f>'#'!Q30</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F28" s="4">
         <f>'#'!R30</f>
@@ -57113,7 +57113,7 @@
       </c>
       <c r="M28" s="2">
         <f t="shared" si="4"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N28" s="2">
         <f t="shared" si="5"/>

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6674" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1EC4730-2E0F-42CA-949F-51357F1CDBE7}"/>
+  <xr:revisionPtr revIDLastSave="6756" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2A7AE10-A557-410B-83DE-8F7E9F3EBACF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'#'!$A$5:$AS$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'All-time records'!$H$2:$L$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Apps &amp; Goals'!$A$3:$N$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Apps &amp; Goals'!$A$3:$P$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Apps &amp; Goals 16-17'!$A$3:$O$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Apps &amp; Goals 17-18'!$A$3:$O$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Apps &amp; Goals 18-19'!$A$3:$O$32</definedName>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="375">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -1155,6 +1155,54 @@
   </si>
   <si>
     <t>IPS</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
+    <t>GK</t>
+  </si>
+  <si>
+    <t>FRA</t>
+  </si>
+  <si>
+    <t>DF</t>
+  </si>
+  <si>
+    <t>MF</t>
+  </si>
+  <si>
+    <t>FW</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>NED</t>
+  </si>
+  <si>
+    <t>BRA</t>
+  </si>
+  <si>
+    <t>ECU</t>
+  </si>
+  <si>
+    <t>NOR</t>
+  </si>
+  <si>
+    <t>SWE</t>
+  </si>
+  <si>
+    <t>GRE</t>
+  </si>
+  <si>
+    <t>POR</t>
+  </si>
+  <si>
+    <t>GER</t>
+  </si>
+  <si>
+    <t>ITA</t>
   </si>
 </sst>
 </file>
@@ -2846,10 +2894,34 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="33" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2858,16 +2930,10 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2876,35 +2942,41 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="33" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2913,15 +2985,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2945,15 +3008,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2962,12 +3016,6 @@
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="69" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3029,24 +3077,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3089,28 +3119,31 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="26" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3211,6 +3244,21 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4875,7 +4923,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Apps &amp; Goals'!$M$3:$N$3</c:f>
+              <c:f>'Apps &amp; Goals'!$O$3:$P$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6262,7 +6310,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{065FAF6D-4106-48BA-BF87-AEB7D9E49454}" type="CELLRANGE">
+                    <a:fld id="{D967EA6F-B387-40C9-8D7C-17A01E381FA3}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6296,7 +6344,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{67563F28-F123-42CE-A057-30F47DC48E4D}" type="CELLRANGE">
+                    <a:fld id="{BB64A933-94B6-4819-8B5C-0304DCA1820C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6330,7 +6378,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7FCB3E56-213B-4FEC-9650-F130D9CBD8D8}" type="CELLRANGE">
+                    <a:fld id="{E6EEF690-B9D1-4BD2-ACC9-B61A5549BDFA}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6364,7 +6412,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{784E2146-AD47-453D-B050-A0AE097A559C}" type="CELLRANGE">
+                    <a:fld id="{A917072C-A83A-4F2E-B42E-C181D05066DD}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6398,7 +6446,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E9BDB4F9-1F15-42BF-86BA-B6E06E0D017D}" type="CELLRANGE">
+                    <a:fld id="{1D2707B2-B211-46CE-A69C-D66D90693718}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6432,7 +6480,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9E1E49B6-33C1-45AC-B045-06312631E24F}" type="CELLRANGE">
+                    <a:fld id="{38D64F55-2236-4377-86B9-ED46D8FC0D31}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6466,7 +6514,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7EB2E143-63FD-4441-BFBF-01091438003E}" type="CELLRANGE">
+                    <a:fld id="{DEA838CB-4774-4110-A332-66689F724E19}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6500,7 +6548,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BC958521-79BB-47E1-AE3D-1345CC53E8E9}" type="CELLRANGE">
+                    <a:fld id="{C6ABD7F1-ECAD-45A5-8386-EB85C6C70D04}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6534,7 +6582,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{567A2A9E-7E58-43AC-AADC-A857EE8B5CAC}" type="CELLRANGE">
+                    <a:fld id="{D223D634-20EE-439F-AE09-B0CFDFF72EDE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6568,7 +6616,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{23C55975-1830-4753-BA63-0E806F582504}" type="CELLRANGE">
+                    <a:fld id="{38583AF5-F5BF-42E8-823E-BD4E5B158A27}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6602,7 +6650,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CC154B45-B2C2-45B2-954B-558E6AD226C2}" type="CELLRANGE">
+                    <a:fld id="{DD2264BC-6031-4139-8792-F4918E0526EE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6636,7 +6684,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9EC5BF9F-2DFD-438D-983D-8B99CB5F5A81}" type="CELLRANGE">
+                    <a:fld id="{E8E6FFB7-FA6A-4381-9B66-C77274066E38}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6685,7 +6733,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{3D9C9313-B24D-4EAF-B452-6858564D4CCB}" type="CELLRANGE">
+                    <a:fld id="{9AC872F5-8C71-4F74-8410-86E4E8BA9901}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6744,7 +6792,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1872C0DF-D279-40C6-BFBA-2E40E7718A59}" type="CELLRANGE">
+                    <a:fld id="{FCE7BDE6-A85A-4E46-B291-E7B86738E9D3}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6778,7 +6826,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{37A9DA76-51B2-419C-8EAA-C0E0CA444CD6}" type="CELLRANGE">
+                    <a:fld id="{05290F49-6D26-4D00-B677-1DEDE04A5A03}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6812,7 +6860,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{05D0C918-7348-470D-B3AB-D5FEBD449161}" type="CELLRANGE">
+                    <a:fld id="{BA935D04-6047-47D2-BEFB-FD95C47F1D32}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6846,7 +6894,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D9A264FC-B330-4404-8E54-A5D16391CA88}" type="CELLRANGE">
+                    <a:fld id="{F0DAF8C5-1643-44E1-B649-6C7EC551C395}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6880,7 +6928,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{59381A38-9CA5-430F-98FB-9B02C6BE6744}" type="CELLRANGE">
+                    <a:fld id="{8F96025C-BF8C-4042-9042-B422221D876C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6914,7 +6962,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{59DCEADF-5CD2-4E47-94D5-DC9DCFC2D355}" type="CELLRANGE">
+                    <a:fld id="{2E58A367-5B77-429A-966F-FBC6965DAA2F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6948,7 +6996,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1CF15852-E4F0-4DA7-98C6-9BF57F758C7F}" type="CELLRANGE">
+                    <a:fld id="{F1140EF5-131F-41E6-8886-64DF99B4CA9F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7121,7 +7169,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'Apps &amp; Goals'!$M$7:$M$27</c:f>
+              <c:f>'Apps &amp; Goals'!$O$7:$O$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
@@ -7193,7 +7241,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Apps &amp; Goals'!$N$7:$N$27</c:f>
+              <c:f>'Apps &amp; Goals'!$P$7:$P$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
@@ -7267,7 +7315,7 @@
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:datalabelsRange>
-                <c15:f>'Apps &amp; Goals'!$B$7:$B$27</c15:f>
+                <c15:f>'Apps &amp; Goals'!$D$7:$D$27</c15:f>
                 <c15:dlblRangeCache>
                   <c:ptCount val="21"/>
                   <c:pt idx="0">
@@ -7367,7 +7415,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'Apps &amp; Goals'!$B$7:$B$27</c15:sqref>
+                          <c15:sqref>'Apps &amp; Goals'!$D$7:$D$27</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -7444,7 +7492,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'Apps &amp; Goals'!$N$7:$N$27</c15:sqref>
+                          <c15:sqref>'Apps &amp; Goals'!$P$7:$P$27</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -33389,320 +33437,320 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:80" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E1" s="221">
-        <v>1</v>
-      </c>
-      <c r="F1" s="221"/>
-      <c r="G1" s="222">
+      <c r="E1" s="214">
+        <v>1</v>
+      </c>
+      <c r="F1" s="214"/>
+      <c r="G1" s="212">
         <v>2</v>
       </c>
-      <c r="H1" s="222"/>
-      <c r="I1" s="223">
-        <v>3</v>
-      </c>
-      <c r="J1" s="223"/>
-      <c r="K1" s="222">
+      <c r="H1" s="212"/>
+      <c r="I1" s="213">
+        <v>3</v>
+      </c>
+      <c r="J1" s="213"/>
+      <c r="K1" s="212">
         <v>4</v>
       </c>
-      <c r="L1" s="222"/>
-      <c r="M1" s="222">
+      <c r="L1" s="212"/>
+      <c r="M1" s="212">
         <v>5</v>
       </c>
-      <c r="N1" s="222"/>
-      <c r="O1" s="221">
+      <c r="N1" s="212"/>
+      <c r="O1" s="214">
         <v>6</v>
       </c>
-      <c r="P1" s="221"/>
-      <c r="Q1" s="222">
+      <c r="P1" s="214"/>
+      <c r="Q1" s="212">
         <v>7</v>
       </c>
-      <c r="R1" s="222"/>
-      <c r="S1" s="222">
+      <c r="R1" s="212"/>
+      <c r="S1" s="212">
         <v>8</v>
       </c>
-      <c r="T1" s="222"/>
-      <c r="U1" s="222">
+      <c r="T1" s="212"/>
+      <c r="U1" s="212">
         <v>9</v>
       </c>
-      <c r="V1" s="222"/>
-      <c r="W1" s="222">
+      <c r="V1" s="212"/>
+      <c r="W1" s="212">
         <v>10</v>
       </c>
-      <c r="X1" s="222"/>
-      <c r="Y1" s="222">
+      <c r="X1" s="212"/>
+      <c r="Y1" s="212">
         <v>11</v>
       </c>
-      <c r="Z1" s="222"/>
-      <c r="AA1" s="223">
+      <c r="Z1" s="212"/>
+      <c r="AA1" s="213">
         <v>12</v>
       </c>
-      <c r="AB1" s="223"/>
-      <c r="AC1" s="221">
+      <c r="AB1" s="213"/>
+      <c r="AC1" s="214">
         <v>13</v>
       </c>
-      <c r="AD1" s="221"/>
-      <c r="AE1" s="223">
+      <c r="AD1" s="214"/>
+      <c r="AE1" s="213">
         <v>14</v>
       </c>
-      <c r="AF1" s="223"/>
-      <c r="AG1" s="224">
+      <c r="AF1" s="213"/>
+      <c r="AG1" s="215">
         <v>15</v>
       </c>
-      <c r="AH1" s="225"/>
-      <c r="AI1" s="222">
+      <c r="AH1" s="216"/>
+      <c r="AI1" s="212">
         <v>16</v>
       </c>
-      <c r="AJ1" s="222"/>
-      <c r="AK1" s="222">
+      <c r="AJ1" s="212"/>
+      <c r="AK1" s="212">
         <v>17</v>
       </c>
-      <c r="AL1" s="222"/>
-      <c r="AM1" s="222">
+      <c r="AL1" s="212"/>
+      <c r="AM1" s="212">
         <v>18</v>
       </c>
-      <c r="AN1" s="222"/>
-      <c r="AO1" s="226">
+      <c r="AN1" s="212"/>
+      <c r="AO1" s="211">
         <v>19</v>
       </c>
-      <c r="AP1" s="226"/>
-      <c r="AQ1" s="226">
+      <c r="AP1" s="211"/>
+      <c r="AQ1" s="211">
         <v>20</v>
       </c>
-      <c r="AR1" s="226"/>
-      <c r="AS1" s="226">
+      <c r="AR1" s="211"/>
+      <c r="AS1" s="211">
         <v>21</v>
       </c>
-      <c r="AT1" s="226"/>
-      <c r="AU1" s="226">
+      <c r="AT1" s="211"/>
+      <c r="AU1" s="211">
         <v>22</v>
       </c>
-      <c r="AV1" s="226"/>
-      <c r="AW1" s="226">
+      <c r="AV1" s="211"/>
+      <c r="AW1" s="211">
         <v>23</v>
       </c>
-      <c r="AX1" s="226"/>
-      <c r="AY1" s="226">
+      <c r="AX1" s="211"/>
+      <c r="AY1" s="211">
         <v>24</v>
       </c>
-      <c r="AZ1" s="226"/>
-      <c r="BA1" s="226">
+      <c r="AZ1" s="211"/>
+      <c r="BA1" s="211">
         <v>25</v>
       </c>
-      <c r="BB1" s="226"/>
-      <c r="BC1" s="226">
+      <c r="BB1" s="211"/>
+      <c r="BC1" s="211">
         <v>26</v>
       </c>
-      <c r="BD1" s="226"/>
-      <c r="BE1" s="226">
+      <c r="BD1" s="211"/>
+      <c r="BE1" s="211">
         <v>27</v>
       </c>
-      <c r="BF1" s="226"/>
-      <c r="BG1" s="226">
+      <c r="BF1" s="211"/>
+      <c r="BG1" s="211">
         <v>28</v>
       </c>
-      <c r="BH1" s="226"/>
-      <c r="BI1" s="226">
+      <c r="BH1" s="211"/>
+      <c r="BI1" s="211">
         <v>29</v>
       </c>
-      <c r="BJ1" s="226"/>
-      <c r="BK1" s="226">
+      <c r="BJ1" s="211"/>
+      <c r="BK1" s="211">
         <v>30</v>
       </c>
-      <c r="BL1" s="226"/>
-      <c r="BM1" s="226">
+      <c r="BL1" s="211"/>
+      <c r="BM1" s="211">
         <v>31</v>
       </c>
-      <c r="BN1" s="226"/>
-      <c r="BO1" s="226">
+      <c r="BN1" s="211"/>
+      <c r="BO1" s="211">
         <v>32</v>
       </c>
-      <c r="BP1" s="226"/>
-      <c r="BQ1" s="226">
+      <c r="BP1" s="211"/>
+      <c r="BQ1" s="211">
         <v>33</v>
       </c>
-      <c r="BR1" s="226"/>
-      <c r="BS1" s="226">
+      <c r="BR1" s="211"/>
+      <c r="BS1" s="211">
         <v>34</v>
       </c>
-      <c r="BT1" s="226"/>
-      <c r="BU1" s="226">
+      <c r="BT1" s="211"/>
+      <c r="BU1" s="211">
         <v>35</v>
       </c>
-      <c r="BV1" s="226"/>
-      <c r="BW1" s="226">
+      <c r="BV1" s="211"/>
+      <c r="BW1" s="211">
         <v>36</v>
       </c>
-      <c r="BX1" s="226"/>
-      <c r="BY1" s="226">
+      <c r="BX1" s="211"/>
+      <c r="BY1" s="211">
         <v>37</v>
       </c>
-      <c r="BZ1" s="226"/>
-      <c r="CA1" s="226">
+      <c r="BZ1" s="211"/>
+      <c r="CA1" s="211">
         <v>38</v>
       </c>
-      <c r="CB1" s="226"/>
+      <c r="CB1" s="211"/>
     </row>
     <row r="2" spans="1:80" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="227" t="s">
+      <c r="C2" s="209" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="227" t="s">
+      <c r="D2" s="209" t="s">
         <v>99</v>
       </c>
-      <c r="E2" s="213" t="s">
+      <c r="E2" s="225" t="s">
         <v>356</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="215" t="s">
+      <c r="F2" s="226"/>
+      <c r="G2" s="217" t="s">
         <v>341</v>
       </c>
-      <c r="H2" s="216"/>
-      <c r="I2" s="211" t="s">
+      <c r="H2" s="218"/>
+      <c r="I2" s="219" t="s">
         <v>340</v>
       </c>
-      <c r="J2" s="212"/>
-      <c r="K2" s="211" t="s">
+      <c r="J2" s="220"/>
+      <c r="K2" s="219" t="s">
         <v>338</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="209" t="s">
+      <c r="L2" s="220"/>
+      <c r="M2" s="227" t="s">
         <v>345</v>
       </c>
-      <c r="N2" s="210"/>
-      <c r="O2" s="211" t="s">
+      <c r="N2" s="228"/>
+      <c r="O2" s="219" t="s">
         <v>330</v>
       </c>
-      <c r="P2" s="212"/>
-      <c r="Q2" s="211" t="s">
+      <c r="P2" s="220"/>
+      <c r="Q2" s="219" t="s">
         <v>347</v>
       </c>
-      <c r="R2" s="212"/>
-      <c r="S2" s="211" t="s">
+      <c r="R2" s="220"/>
+      <c r="S2" s="219" t="s">
         <v>344</v>
       </c>
-      <c r="T2" s="212"/>
-      <c r="U2" s="211" t="s">
+      <c r="T2" s="220"/>
+      <c r="U2" s="219" t="s">
         <v>331</v>
       </c>
-      <c r="V2" s="212"/>
-      <c r="W2" s="211" t="s">
+      <c r="V2" s="220"/>
+      <c r="W2" s="219" t="s">
         <v>357</v>
       </c>
-      <c r="X2" s="212"/>
-      <c r="Y2" s="211" t="s">
+      <c r="X2" s="220"/>
+      <c r="Y2" s="219" t="s">
         <v>334</v>
       </c>
-      <c r="Z2" s="212"/>
-      <c r="AA2" s="211" t="s">
+      <c r="Z2" s="220"/>
+      <c r="AA2" s="219" t="s">
         <v>333</v>
       </c>
-      <c r="AB2" s="212"/>
-      <c r="AC2" s="209" t="s">
+      <c r="AB2" s="220"/>
+      <c r="AC2" s="227" t="s">
         <v>342</v>
       </c>
-      <c r="AD2" s="210"/>
-      <c r="AE2" s="209" t="s">
+      <c r="AD2" s="228"/>
+      <c r="AE2" s="227" t="s">
         <v>339</v>
       </c>
-      <c r="AF2" s="210"/>
-      <c r="AG2" s="209" t="s">
+      <c r="AF2" s="228"/>
+      <c r="AG2" s="227" t="s">
         <v>346</v>
       </c>
-      <c r="AH2" s="210"/>
-      <c r="AI2" s="209" t="s">
+      <c r="AH2" s="228"/>
+      <c r="AI2" s="227" t="s">
         <v>315</v>
       </c>
-      <c r="AJ2" s="210"/>
-      <c r="AK2" s="211" t="s">
+      <c r="AJ2" s="228"/>
+      <c r="AK2" s="219" t="s">
         <v>336</v>
       </c>
-      <c r="AL2" s="212"/>
-      <c r="AM2" s="213" t="s">
+      <c r="AL2" s="220"/>
+      <c r="AM2" s="225" t="s">
         <v>335</v>
       </c>
-      <c r="AN2" s="214"/>
-      <c r="AO2" s="213" t="s">
+      <c r="AN2" s="226"/>
+      <c r="AO2" s="225" t="s">
         <v>358</v>
       </c>
-      <c r="AP2" s="214"/>
-      <c r="AQ2" s="217" t="s">
+      <c r="AP2" s="226"/>
+      <c r="AQ2" s="223" t="s">
         <v>342</v>
       </c>
-      <c r="AR2" s="218"/>
-      <c r="AS2" s="217" t="s">
+      <c r="AR2" s="224"/>
+      <c r="AS2" s="223" t="s">
         <v>357</v>
       </c>
-      <c r="AT2" s="218"/>
-      <c r="AU2" s="219" t="s">
+      <c r="AT2" s="224"/>
+      <c r="AU2" s="221" t="s">
         <v>334</v>
       </c>
-      <c r="AV2" s="220"/>
-      <c r="AW2" s="219" t="s">
+      <c r="AV2" s="222"/>
+      <c r="AW2" s="221" t="s">
         <v>333</v>
       </c>
-      <c r="AX2" s="220"/>
-      <c r="AY2" s="213" t="s">
+      <c r="AX2" s="222"/>
+      <c r="AY2" s="225" t="s">
         <v>331</v>
       </c>
-      <c r="AZ2" s="214"/>
-      <c r="BA2" s="219" t="s">
+      <c r="AZ2" s="226"/>
+      <c r="BA2" s="221" t="s">
         <v>358</v>
       </c>
-      <c r="BB2" s="220"/>
-      <c r="BC2" s="217" t="s">
+      <c r="BB2" s="222"/>
+      <c r="BC2" s="223" t="s">
         <v>335</v>
       </c>
-      <c r="BD2" s="218"/>
-      <c r="BE2" s="217" t="s">
+      <c r="BD2" s="224"/>
+      <c r="BE2" s="223" t="s">
         <v>315</v>
       </c>
-      <c r="BF2" s="218"/>
-      <c r="BG2" s="213" t="s">
+      <c r="BF2" s="224"/>
+      <c r="BG2" s="225" t="s">
         <v>336</v>
       </c>
-      <c r="BH2" s="214"/>
-      <c r="BI2" s="213" t="s">
+      <c r="BH2" s="226"/>
+      <c r="BI2" s="225" t="s">
         <v>340</v>
       </c>
-      <c r="BJ2" s="214"/>
-      <c r="BK2" s="219" t="s">
+      <c r="BJ2" s="226"/>
+      <c r="BK2" s="221" t="s">
         <v>338</v>
       </c>
-      <c r="BL2" s="220"/>
-      <c r="BM2" s="211" t="s">
+      <c r="BL2" s="222"/>
+      <c r="BM2" s="219" t="s">
         <v>356</v>
       </c>
-      <c r="BN2" s="212"/>
-      <c r="BO2" s="211" t="s">
+      <c r="BN2" s="220"/>
+      <c r="BO2" s="219" t="s">
         <v>341</v>
       </c>
-      <c r="BP2" s="212"/>
-      <c r="BQ2" s="215" t="s">
+      <c r="BP2" s="220"/>
+      <c r="BQ2" s="217" t="s">
         <v>346</v>
       </c>
-      <c r="BR2" s="216"/>
-      <c r="BS2" s="215" t="s">
+      <c r="BR2" s="218"/>
+      <c r="BS2" s="217" t="s">
         <v>339</v>
       </c>
-      <c r="BT2" s="216"/>
-      <c r="BU2" s="215" t="s">
+      <c r="BT2" s="218"/>
+      <c r="BU2" s="217" t="s">
         <v>330</v>
       </c>
-      <c r="BV2" s="216"/>
-      <c r="BW2" s="215" t="s">
+      <c r="BV2" s="218"/>
+      <c r="BW2" s="217" t="s">
         <v>347</v>
       </c>
-      <c r="BX2" s="216"/>
-      <c r="BY2" s="211" t="s">
+      <c r="BX2" s="218"/>
+      <c r="BY2" s="219" t="s">
         <v>344</v>
       </c>
-      <c r="BZ2" s="212"/>
-      <c r="CA2" s="215" t="s">
+      <c r="BZ2" s="220"/>
+      <c r="CA2" s="217" t="s">
         <v>345</v>
       </c>
-      <c r="CB2" s="216"/>
+      <c r="CB2" s="218"/>
     </row>
     <row r="3" spans="1:80" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -33711,8 +33759,8 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="228"/>
-      <c r="D3" s="228"/>
+      <c r="C3" s="210"/>
+      <c r="D3" s="210"/>
       <c r="E3" s="147" t="s">
         <v>87</v>
       </c>
@@ -37658,6 +37706,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="AS2:AT2"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AE2:AF2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="AI2:AJ2"/>
+    <mergeCell ref="AK2:AL2"/>
+    <mergeCell ref="AM2:AN2"/>
+    <mergeCell ref="AO2:AP2"/>
+    <mergeCell ref="AQ2:AR2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AG2:AH2"/>
+    <mergeCell ref="BQ2:BR2"/>
+    <mergeCell ref="BA2:BB2"/>
+    <mergeCell ref="BC2:BD2"/>
+    <mergeCell ref="BE2:BF2"/>
+    <mergeCell ref="AU2:AV2"/>
+    <mergeCell ref="AW2:AX2"/>
+    <mergeCell ref="AY2:AZ2"/>
+    <mergeCell ref="BG2:BH2"/>
+    <mergeCell ref="BI2:BJ2"/>
+    <mergeCell ref="BK2:BL2"/>
+    <mergeCell ref="BM2:BN2"/>
+    <mergeCell ref="BO2:BP2"/>
+    <mergeCell ref="BS2:BT2"/>
+    <mergeCell ref="BU2:BV2"/>
+    <mergeCell ref="BW2:BX2"/>
+    <mergeCell ref="BY2:BZ2"/>
+    <mergeCell ref="CA2:CB2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="AY1:AZ1"/>
+    <mergeCell ref="BA1:BB1"/>
+    <mergeCell ref="BC1:BD1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="AS1:AT1"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="BY1:BZ1"/>
@@ -37674,68 +37784,6 @@
     <mergeCell ref="BM1:BN1"/>
     <mergeCell ref="AU1:AV1"/>
     <mergeCell ref="AW1:AX1"/>
-    <mergeCell ref="AY1:AZ1"/>
-    <mergeCell ref="BA1:BB1"/>
-    <mergeCell ref="BC1:BD1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="BS2:BT2"/>
-    <mergeCell ref="BU2:BV2"/>
-    <mergeCell ref="BW2:BX2"/>
-    <mergeCell ref="BY2:BZ2"/>
-    <mergeCell ref="CA2:CB2"/>
-    <mergeCell ref="BQ2:BR2"/>
-    <mergeCell ref="BA2:BB2"/>
-    <mergeCell ref="BC2:BD2"/>
-    <mergeCell ref="BE2:BF2"/>
-    <mergeCell ref="AU2:AV2"/>
-    <mergeCell ref="AW2:AX2"/>
-    <mergeCell ref="AY2:AZ2"/>
-    <mergeCell ref="BG2:BH2"/>
-    <mergeCell ref="BI2:BJ2"/>
-    <mergeCell ref="BK2:BL2"/>
-    <mergeCell ref="BM2:BN2"/>
-    <mergeCell ref="BO2:BP2"/>
-    <mergeCell ref="AS2:AT2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="AI2:AJ2"/>
-    <mergeCell ref="AK2:AL2"/>
-    <mergeCell ref="AM2:AN2"/>
-    <mergeCell ref="AO2:AP2"/>
-    <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AG2:AH2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:CB40">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -37770,88 +37818,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="227" t="s">
+      <c r="C1" s="209" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="227" t="s">
+      <c r="D1" s="209" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="242" t="s">
+      <c r="E1" s="232" t="s">
         <v>312</v>
       </c>
-      <c r="F1" s="243"/>
-      <c r="G1" s="243"/>
-      <c r="H1" s="243"/>
-      <c r="I1" s="243"/>
-      <c r="J1" s="243"/>
-      <c r="K1" s="243"/>
-      <c r="L1" s="243"/>
-      <c r="M1" s="243"/>
-      <c r="N1" s="243"/>
-      <c r="O1" s="243"/>
-      <c r="P1" s="243"/>
-      <c r="Q1" s="243"/>
-      <c r="R1" s="243"/>
-      <c r="S1" s="243"/>
-      <c r="T1" s="244"/>
-      <c r="U1" s="247" t="s">
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="233"/>
+      <c r="J1" s="233"/>
+      <c r="K1" s="233"/>
+      <c r="L1" s="233"/>
+      <c r="M1" s="233"/>
+      <c r="N1" s="233"/>
+      <c r="O1" s="233"/>
+      <c r="P1" s="233"/>
+      <c r="Q1" s="233"/>
+      <c r="R1" s="233"/>
+      <c r="S1" s="233"/>
+      <c r="T1" s="234"/>
+      <c r="U1" s="249" t="s">
         <v>291</v>
       </c>
-      <c r="V1" s="247"/>
-      <c r="W1" s="247"/>
-      <c r="X1" s="247"/>
-      <c r="Y1" s="242" t="s">
+      <c r="V1" s="249"/>
+      <c r="W1" s="249"/>
+      <c r="X1" s="249"/>
+      <c r="Y1" s="232" t="s">
         <v>292</v>
       </c>
-      <c r="Z1" s="243"/>
-      <c r="AA1" s="243"/>
-      <c r="AB1" s="244"/>
-      <c r="AC1" s="245" t="s">
+      <c r="Z1" s="233"/>
+      <c r="AA1" s="233"/>
+      <c r="AB1" s="234"/>
+      <c r="AC1" s="247" t="s">
         <v>293</v>
       </c>
-      <c r="AD1" s="245"/>
-      <c r="AE1" s="245"/>
-      <c r="AF1" s="246"/>
-      <c r="AG1" s="240" t="s">
+      <c r="AD1" s="247"/>
+      <c r="AE1" s="247"/>
+      <c r="AF1" s="248"/>
+      <c r="AG1" s="245" t="s">
         <v>89</v>
       </c>
-      <c r="AH1" s="241"/>
+      <c r="AH1" s="246"/>
     </row>
     <row r="2" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="228"/>
-      <c r="D2" s="228"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="249"/>
-      <c r="I2" s="232"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="234"/>
-      <c r="M2" s="232"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="232"/>
-      <c r="P2" s="234"/>
-      <c r="Q2" s="232"/>
-      <c r="R2" s="234"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="234"/>
-      <c r="U2" s="229"/>
-      <c r="V2" s="230"/>
-      <c r="W2" s="230"/>
-      <c r="X2" s="231"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="233"/>
-      <c r="AA2" s="233"/>
-      <c r="AB2" s="234"/>
-      <c r="AC2" s="235"/>
-      <c r="AD2" s="236"/>
-      <c r="AE2" s="236"/>
-      <c r="AF2" s="237"/>
-      <c r="AG2" s="238"/>
-      <c r="AH2" s="239"/>
+      <c r="C2" s="210"/>
+      <c r="D2" s="210"/>
+      <c r="E2" s="229"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="235"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="229"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="229"/>
+      <c r="L2" s="230"/>
+      <c r="M2" s="229"/>
+      <c r="N2" s="231"/>
+      <c r="O2" s="229"/>
+      <c r="P2" s="230"/>
+      <c r="Q2" s="229"/>
+      <c r="R2" s="230"/>
+      <c r="S2" s="229"/>
+      <c r="T2" s="230"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="238"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="239"/>
+      <c r="Y2" s="229"/>
+      <c r="Z2" s="231"/>
+      <c r="AA2" s="231"/>
+      <c r="AB2" s="230"/>
+      <c r="AC2" s="240"/>
+      <c r="AD2" s="241"/>
+      <c r="AE2" s="241"/>
+      <c r="AF2" s="242"/>
+      <c r="AG2" s="243"/>
+      <c r="AH2" s="244"/>
     </row>
     <row r="3" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -39779,17 +39827,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="E1:T1"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
     <mergeCell ref="U2:X2"/>
     <mergeCell ref="Y2:AB2"/>
     <mergeCell ref="AC2:AF2"/>
@@ -39798,6 +39835,17 @@
     <mergeCell ref="Y1:AB1"/>
     <mergeCell ref="AC1:AF1"/>
     <mergeCell ref="U1:X1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="E1:T1"/>
+    <mergeCell ref="Q2:R2"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AH31">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -39830,10 +39878,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="227" t="s">
+      <c r="C1" s="209" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="227" t="s">
+      <c r="D1" s="209" t="s">
         <v>99</v>
       </c>
       <c r="E1" s="264" t="s">
@@ -39864,8 +39912,8 @@
     <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="228"/>
-      <c r="D2" s="228"/>
+      <c r="C2" s="210"/>
+      <c r="D2" s="210"/>
       <c r="E2" s="256"/>
       <c r="F2" s="257"/>
       <c r="G2" s="258"/>
@@ -39874,8 +39922,8 @@
       <c r="J2" s="261"/>
       <c r="K2" s="262"/>
       <c r="L2" s="263"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
+      <c r="M2" s="231"/>
+      <c r="N2" s="231"/>
       <c r="O2" s="252"/>
       <c r="P2" s="253"/>
     </row>
@@ -46231,52 +46279,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="227" t="s">
+      <c r="C1" s="209" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="227" t="s">
+      <c r="D1" s="209" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="279" t="s">
+      <c r="E1" s="273" t="s">
         <v>91</v>
       </c>
-      <c r="F1" s="280"/>
-      <c r="G1" s="281" t="s">
+      <c r="F1" s="274"/>
+      <c r="G1" s="275" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="282"/>
-      <c r="I1" s="283" t="s">
+      <c r="H1" s="276"/>
+      <c r="I1" s="277" t="s">
         <v>207</v>
       </c>
-      <c r="J1" s="284"/>
-      <c r="K1" s="287" t="s">
+      <c r="J1" s="278"/>
+      <c r="K1" s="281" t="s">
         <v>208</v>
       </c>
-      <c r="L1" s="288"/>
-      <c r="M1" s="288"/>
-      <c r="N1" s="289"/>
-      <c r="O1" s="285" t="s">
+      <c r="L1" s="282"/>
+      <c r="M1" s="282"/>
+      <c r="N1" s="283"/>
+      <c r="O1" s="279" t="s">
         <v>316</v>
       </c>
-      <c r="P1" s="286"/>
+      <c r="P1" s="280"/>
     </row>
     <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="228"/>
-      <c r="D2" s="228"/>
-      <c r="E2" s="270"/>
-      <c r="F2" s="271"/>
-      <c r="G2" s="272"/>
-      <c r="H2" s="273"/>
-      <c r="I2" s="274"/>
-      <c r="J2" s="275"/>
-      <c r="K2" s="276"/>
-      <c r="L2" s="277"/>
-      <c r="M2" s="276"/>
-      <c r="N2" s="277"/>
-      <c r="O2" s="276"/>
-      <c r="P2" s="278"/>
+      <c r="C2" s="210"/>
+      <c r="D2" s="210"/>
+      <c r="E2" s="284"/>
+      <c r="F2" s="285"/>
+      <c r="G2" s="286"/>
+      <c r="H2" s="287"/>
+      <c r="I2" s="288"/>
+      <c r="J2" s="289"/>
+      <c r="K2" s="270"/>
+      <c r="L2" s="271"/>
+      <c r="M2" s="270"/>
+      <c r="N2" s="271"/>
+      <c r="O2" s="270"/>
+      <c r="P2" s="272"/>
     </row>
     <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -47412,6 +47460,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="E1:F1"/>
@@ -47420,11 +47473,6 @@
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="K1:N1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:P35">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -47868,51 +47916,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="298" t="s">
+      <c r="C1" s="293" t="s">
         <v>210</v>
       </c>
-      <c r="D1" s="299"/>
-      <c r="E1" s="299"/>
-      <c r="F1" s="299"/>
-      <c r="G1" s="299"/>
-      <c r="H1" s="299"/>
-      <c r="I1" s="300"/>
+      <c r="D1" s="294"/>
+      <c r="E1" s="294"/>
+      <c r="F1" s="294"/>
+      <c r="G1" s="294"/>
+      <c r="H1" s="294"/>
+      <c r="I1" s="295"/>
       <c r="J1" s="135" t="s">
         <v>203</v>
       </c>
       <c r="K1" s="136" t="s">
         <v>202</v>
       </c>
-      <c r="L1" s="292" t="s">
+      <c r="L1" s="326" t="s">
         <v>297</v>
       </c>
-      <c r="M1" s="296"/>
-      <c r="N1" s="296"/>
-      <c r="O1" s="296"/>
-      <c r="P1" s="296"/>
-      <c r="Q1" s="296"/>
-      <c r="R1" s="296"/>
-      <c r="S1" s="296"/>
-      <c r="T1" s="296"/>
-      <c r="U1" s="296"/>
-      <c r="V1" s="296"/>
-      <c r="W1" s="296"/>
-      <c r="X1" s="296"/>
-      <c r="Y1" s="296"/>
-      <c r="Z1" s="296"/>
-      <c r="AA1" s="296"/>
-      <c r="AB1" s="296"/>
-      <c r="AC1" s="296"/>
-      <c r="AD1" s="296"/>
-      <c r="AE1" s="296"/>
-      <c r="AF1" s="296"/>
-      <c r="AG1" s="297"/>
-      <c r="AH1" s="292" t="s">
+      <c r="M1" s="329"/>
+      <c r="N1" s="329"/>
+      <c r="O1" s="329"/>
+      <c r="P1" s="329"/>
+      <c r="Q1" s="329"/>
+      <c r="R1" s="329"/>
+      <c r="S1" s="329"/>
+      <c r="T1" s="329"/>
+      <c r="U1" s="329"/>
+      <c r="V1" s="329"/>
+      <c r="W1" s="329"/>
+      <c r="X1" s="329"/>
+      <c r="Y1" s="329"/>
+      <c r="Z1" s="329"/>
+      <c r="AA1" s="329"/>
+      <c r="AB1" s="329"/>
+      <c r="AC1" s="329"/>
+      <c r="AD1" s="329"/>
+      <c r="AE1" s="329"/>
+      <c r="AF1" s="329"/>
+      <c r="AG1" s="330"/>
+      <c r="AH1" s="326" t="s">
         <v>183</v>
       </c>
-      <c r="AI1" s="293"/>
-      <c r="AJ1" s="293"/>
-      <c r="AK1" s="294"/>
+      <c r="AI1" s="327"/>
+      <c r="AJ1" s="327"/>
+      <c r="AK1" s="328"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="132"/>
@@ -53100,15 +53148,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="322" t="s">
+      <c r="K80" s="317" t="s">
         <v>183</v>
       </c>
-      <c r="L80" s="323"/>
-      <c r="M80" s="324"/>
+      <c r="L80" s="318"/>
+      <c r="M80" s="319"/>
       <c r="O80" s="157"/>
       <c r="P80" s="157"/>
-      <c r="W80" s="295"/>
-      <c r="X80" s="295"/>
+      <c r="W80" s="292"/>
+      <c r="X80" s="292"/>
       <c r="Y80" s="89" t="s">
         <v>220</v>
       </c>
@@ -53158,15 +53206,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="325"/>
-      <c r="L81" s="326"/>
-      <c r="M81" s="327"/>
+      <c r="K81" s="320"/>
+      <c r="L81" s="321"/>
+      <c r="M81" s="322"/>
       <c r="O81" s="157"/>
       <c r="P81" s="157"/>
-      <c r="W81" s="295" t="s">
+      <c r="W81" s="292" t="s">
         <v>217</v>
       </c>
-      <c r="X81" s="295"/>
+      <c r="X81" s="292"/>
       <c r="Y81" s="89">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -53222,15 +53270,15 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="325"/>
-      <c r="L82" s="326"/>
-      <c r="M82" s="327"/>
+      <c r="K82" s="320"/>
+      <c r="L82" s="321"/>
+      <c r="M82" s="322"/>
       <c r="O82" s="157"/>
       <c r="P82" s="157"/>
-      <c r="W82" s="295" t="s">
+      <c r="W82" s="292" t="s">
         <v>218</v>
       </c>
-      <c r="X82" s="295"/>
+      <c r="X82" s="292"/>
       <c r="Y82" s="89">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -53286,15 +53334,15 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="328"/>
-      <c r="L83" s="329"/>
-      <c r="M83" s="330"/>
+      <c r="K83" s="323"/>
+      <c r="L83" s="324"/>
+      <c r="M83" s="325"/>
       <c r="O83" s="157"/>
       <c r="P83" s="157"/>
-      <c r="W83" s="295" t="s">
+      <c r="W83" s="292" t="s">
         <v>219</v>
       </c>
-      <c r="X83" s="295"/>
+      <c r="X83" s="292"/>
       <c r="Y83" s="89">
         <f>COUNTIF(J16:J20,3)</f>
         <v>1</v>
@@ -53350,17 +53398,17 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="313" t="s">
+      <c r="K84" s="308" t="s">
         <v>294</v>
       </c>
-      <c r="L84" s="314"/>
-      <c r="M84" s="315"/>
+      <c r="L84" s="309"/>
+      <c r="M84" s="310"/>
       <c r="O84" s="165"/>
       <c r="P84" s="165"/>
-      <c r="W84" s="295" t="s">
+      <c r="W84" s="292" t="s">
         <v>103</v>
       </c>
-      <c r="X84" s="295"/>
+      <c r="X84" s="292"/>
       <c r="Y84" s="89">
         <f>COUNTIF(J21:J40,3)+COUNTIF(I3:I40,3)+COUNTIF(H3:H40,3)+COUNTIF(G3:G40,3)+COUNTIF(F3:F40,3)+COUNTIF(E3:E40,3)</f>
         <v>123</v>
@@ -53416,9 +53464,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="316"/>
-      <c r="L85" s="317"/>
-      <c r="M85" s="318"/>
+      <c r="K85" s="311"/>
+      <c r="L85" s="312"/>
+      <c r="M85" s="313"/>
       <c r="O85" s="165"/>
       <c r="P85" s="165"/>
     </row>
@@ -53452,9 +53500,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="316"/>
-      <c r="L86" s="317"/>
-      <c r="M86" s="318"/>
+      <c r="K86" s="311"/>
+      <c r="L86" s="312"/>
+      <c r="M86" s="313"/>
       <c r="O86" s="165"/>
       <c r="P86" s="165"/>
     </row>
@@ -53488,9 +53536,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="316"/>
-      <c r="L87" s="317"/>
-      <c r="M87" s="318"/>
+      <c r="K87" s="311"/>
+      <c r="L87" s="312"/>
+      <c r="M87" s="313"/>
       <c r="O87" s="165"/>
       <c r="P87" s="165"/>
     </row>
@@ -53524,9 +53572,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="316"/>
-      <c r="L88" s="317"/>
-      <c r="M88" s="318"/>
+      <c r="K88" s="311"/>
+      <c r="L88" s="312"/>
+      <c r="M88" s="313"/>
       <c r="O88" s="165"/>
       <c r="P88" s="165"/>
     </row>
@@ -53560,9 +53608,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="316"/>
-      <c r="L89" s="317"/>
-      <c r="M89" s="318"/>
+      <c r="K89" s="311"/>
+      <c r="L89" s="312"/>
+      <c r="M89" s="313"/>
       <c r="O89" s="165"/>
       <c r="P89" s="165"/>
     </row>
@@ -53596,9 +53644,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="316"/>
-      <c r="L90" s="317"/>
-      <c r="M90" s="318"/>
+      <c r="K90" s="311"/>
+      <c r="L90" s="312"/>
+      <c r="M90" s="313"/>
       <c r="O90" s="165"/>
       <c r="P90" s="165"/>
     </row>
@@ -53632,9 +53680,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="316"/>
-      <c r="L91" s="317"/>
-      <c r="M91" s="318"/>
+      <c r="K91" s="311"/>
+      <c r="L91" s="312"/>
+      <c r="M91" s="313"/>
       <c r="O91" s="165"/>
       <c r="P91" s="165"/>
     </row>
@@ -53668,9 +53716,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="316"/>
-      <c r="L92" s="317"/>
-      <c r="M92" s="318"/>
+      <c r="K92" s="311"/>
+      <c r="L92" s="312"/>
+      <c r="M92" s="313"/>
       <c r="O92" s="165"/>
       <c r="P92" s="165"/>
     </row>
@@ -53704,9 +53752,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="316"/>
-      <c r="L93" s="317"/>
-      <c r="M93" s="318"/>
+      <c r="K93" s="311"/>
+      <c r="L93" s="312"/>
+      <c r="M93" s="313"/>
       <c r="O93" s="165"/>
       <c r="P93" s="165"/>
     </row>
@@ -53740,9 +53788,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="316"/>
-      <c r="L94" s="317"/>
-      <c r="M94" s="318"/>
+      <c r="K94" s="311"/>
+      <c r="L94" s="312"/>
+      <c r="M94" s="313"/>
       <c r="O94" s="165"/>
       <c r="P94" s="165"/>
     </row>
@@ -53776,9 +53824,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="316"/>
-      <c r="L95" s="317"/>
-      <c r="M95" s="318"/>
+      <c r="K95" s="311"/>
+      <c r="L95" s="312"/>
+      <c r="M95" s="313"/>
       <c r="O95" s="165"/>
       <c r="P95" s="165"/>
     </row>
@@ -53812,9 +53860,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="316"/>
-      <c r="L96" s="317"/>
-      <c r="M96" s="318"/>
+      <c r="K96" s="311"/>
+      <c r="L96" s="312"/>
+      <c r="M96" s="313"/>
       <c r="O96" s="165"/>
       <c r="P96" s="165"/>
     </row>
@@ -53848,9 +53896,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="316"/>
-      <c r="L97" s="317"/>
-      <c r="M97" s="318"/>
+      <c r="K97" s="311"/>
+      <c r="L97" s="312"/>
+      <c r="M97" s="313"/>
       <c r="O97" s="165"/>
       <c r="P97" s="165"/>
     </row>
@@ -53884,9 +53932,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="316"/>
-      <c r="L98" s="317"/>
-      <c r="M98" s="318"/>
+      <c r="K98" s="311"/>
+      <c r="L98" s="312"/>
+      <c r="M98" s="313"/>
       <c r="O98" s="165"/>
       <c r="P98" s="165"/>
     </row>
@@ -53920,9 +53968,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="316"/>
-      <c r="L99" s="317"/>
-      <c r="M99" s="318"/>
+      <c r="K99" s="311"/>
+      <c r="L99" s="312"/>
+      <c r="M99" s="313"/>
       <c r="O99" s="165"/>
       <c r="P99" s="165"/>
     </row>
@@ -53956,9 +54004,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="316"/>
-      <c r="L100" s="317"/>
-      <c r="M100" s="318"/>
+      <c r="K100" s="311"/>
+      <c r="L100" s="312"/>
+      <c r="M100" s="313"/>
       <c r="O100" s="165"/>
       <c r="P100" s="165"/>
     </row>
@@ -53992,9 +54040,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="316"/>
-      <c r="L101" s="317"/>
-      <c r="M101" s="318"/>
+      <c r="K101" s="311"/>
+      <c r="L101" s="312"/>
+      <c r="M101" s="313"/>
       <c r="O101" s="165"/>
       <c r="P101" s="165"/>
     </row>
@@ -54028,9 +54076,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="316"/>
-      <c r="L102" s="317"/>
-      <c r="M102" s="318"/>
+      <c r="K102" s="311"/>
+      <c r="L102" s="312"/>
+      <c r="M102" s="313"/>
       <c r="O102" s="165"/>
       <c r="P102" s="165"/>
     </row>
@@ -54064,9 +54112,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="316"/>
-      <c r="L103" s="317"/>
-      <c r="M103" s="318"/>
+      <c r="K103" s="311"/>
+      <c r="L103" s="312"/>
+      <c r="M103" s="313"/>
       <c r="O103" s="165"/>
       <c r="P103" s="165"/>
     </row>
@@ -54100,9 +54148,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="316"/>
-      <c r="L104" s="317"/>
-      <c r="M104" s="318"/>
+      <c r="K104" s="311"/>
+      <c r="L104" s="312"/>
+      <c r="M104" s="313"/>
       <c r="O104" s="165"/>
       <c r="P104" s="165"/>
     </row>
@@ -54136,9 +54184,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="319"/>
-      <c r="L105" s="320"/>
-      <c r="M105" s="321"/>
+      <c r="K105" s="314"/>
+      <c r="L105" s="315"/>
+      <c r="M105" s="316"/>
       <c r="O105" s="165"/>
       <c r="P105" s="165"/>
     </row>
@@ -54172,11 +54220,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="310" t="s">
+      <c r="K106" s="305" t="s">
         <v>296</v>
       </c>
-      <c r="L106" s="311"/>
-      <c r="M106" s="312"/>
+      <c r="L106" s="306"/>
+      <c r="M106" s="307"/>
       <c r="O106" s="150"/>
       <c r="P106" s="150"/>
     </row>
@@ -54210,11 +54258,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="310" t="s">
+      <c r="K107" s="305" t="s">
         <v>298</v>
       </c>
-      <c r="L107" s="311"/>
-      <c r="M107" s="312"/>
+      <c r="L107" s="306"/>
+      <c r="M107" s="307"/>
       <c r="O107" s="150"/>
       <c r="P107" s="150"/>
     </row>
@@ -54248,11 +54296,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="301" t="s">
+      <c r="K108" s="296" t="s">
         <v>299</v>
       </c>
-      <c r="L108" s="302"/>
-      <c r="M108" s="303"/>
+      <c r="L108" s="297"/>
+      <c r="M108" s="298"/>
       <c r="O108" s="150"/>
       <c r="P108" s="150"/>
     </row>
@@ -54286,9 +54334,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="304"/>
-      <c r="L109" s="305"/>
-      <c r="M109" s="306"/>
+      <c r="K109" s="299"/>
+      <c r="L109" s="300"/>
+      <c r="M109" s="301"/>
       <c r="O109" s="150"/>
       <c r="P109" s="150"/>
     </row>
@@ -54322,9 +54370,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="304"/>
-      <c r="L110" s="305"/>
-      <c r="M110" s="306"/>
+      <c r="K110" s="299"/>
+      <c r="L110" s="300"/>
+      <c r="M110" s="301"/>
       <c r="O110" s="150"/>
       <c r="P110" s="150"/>
     </row>
@@ -54358,9 +54406,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="304"/>
-      <c r="L111" s="305"/>
-      <c r="M111" s="306"/>
+      <c r="K111" s="299"/>
+      <c r="L111" s="300"/>
+      <c r="M111" s="301"/>
       <c r="O111" s="150"/>
       <c r="P111" s="150"/>
     </row>
@@ -54398,9 +54446,9 @@
         <f t="shared" ref="J112:J113" si="7">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="304"/>
-      <c r="L112" s="305"/>
-      <c r="M112" s="306"/>
+      <c r="K112" s="299"/>
+      <c r="L112" s="300"/>
+      <c r="M112" s="301"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="199" t="s">
@@ -54436,13 +54484,19 @@
         <f t="shared" si="7"/>
         <v>43</v>
       </c>
-      <c r="K113" s="307"/>
-      <c r="L113" s="308"/>
-      <c r="M113" s="309"/>
+      <c r="K113" s="302"/>
+      <c r="L113" s="303"/>
+      <c r="M113" s="304"/>
     </row>
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="13">
+    <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="W80:X80"/>
+    <mergeCell ref="W81:X81"/>
+    <mergeCell ref="W82:X82"/>
+    <mergeCell ref="W83:X83"/>
+    <mergeCell ref="L1:AG1"/>
     <mergeCell ref="W84:X84"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="K108:M113"/>
@@ -54450,12 +54504,6 @@
     <mergeCell ref="K107:M107"/>
     <mergeCell ref="K84:M105"/>
     <mergeCell ref="K80:M83"/>
-    <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="W80:X80"/>
-    <mergeCell ref="W81:X81"/>
-    <mergeCell ref="W82:X82"/>
-    <mergeCell ref="W83:X83"/>
-    <mergeCell ref="L1:AG1"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -55521,11 +55569,11 @@
         <v>188</v>
       </c>
       <c r="J30" s="11">
-        <f>'Apps &amp; Goals'!N10</f>
+        <f>'Apps &amp; Goals'!P10</f>
         <v>81</v>
       </c>
       <c r="K30" s="9">
-        <f>'Apps &amp; Goals'!M10</f>
+        <f>'Apps &amp; Goals'!O10</f>
         <v>312</v>
       </c>
       <c r="L30" s="14">
@@ -55615,25 +55663,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Arkusz1"/>
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:T42"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" customWidth="1"/>
-    <col min="18" max="18" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" customWidth="1"/>
+    <col min="20" max="20" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -55641,2179 +55691,2407 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-      <c r="R1" t="s">
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="T1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="203" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="203" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="203"/>
-      <c r="E2" s="205" t="s">
+      <c r="F2" s="203"/>
+      <c r="G2" s="205" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="205"/>
-      <c r="G2" s="203" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="203" t="s">
         <v>114</v>
       </c>
-      <c r="H2" s="203"/>
-      <c r="I2" s="205" t="s">
+      <c r="J2" s="203"/>
+      <c r="K2" s="205" t="s">
         <v>116</v>
       </c>
-      <c r="J2" s="205"/>
-      <c r="K2" s="203" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="203" t="s">
         <v>40</v>
       </c>
-      <c r="L2" s="203"/>
-      <c r="M2" s="202" t="s">
+      <c r="N2" s="203"/>
+      <c r="O2" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="202"/>
-      <c r="R2" s="149">
+      <c r="P2" s="202"/>
+      <c r="T2" s="149">
         <v>46247</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="M3" s="8" t="s">
+      <c r="N3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="O3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="N3" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="P3" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="D4" s="38" t="s">
         <v>287</v>
       </c>
-      <c r="C4" s="6">
+      <c r="E4" s="6">
         <f>'#'!H6</f>
         <v>107</v>
       </c>
-      <c r="D4" s="6">
+      <c r="F4" s="6">
         <f>'#'!I6</f>
         <v>0</v>
       </c>
-      <c r="E4" s="4">
+      <c r="G4" s="4">
         <f>'#'!Q6</f>
         <v>36</v>
       </c>
-      <c r="F4" s="4">
+      <c r="H4" s="4">
         <f>'#'!R6</f>
         <v>0</v>
       </c>
-      <c r="G4" s="6">
+      <c r="I4" s="6">
         <f>'#'!Z6</f>
         <v>1</v>
       </c>
-      <c r="H4" s="6">
+      <c r="J4" s="6">
         <f>'#'!AA6</f>
         <v>0</v>
       </c>
-      <c r="I4" s="4">
+      <c r="K4" s="4">
         <f>'#'!AI6</f>
         <v>3</v>
       </c>
-      <c r="J4" s="4">
+      <c r="L4" s="4">
         <f>'#'!AJ6</f>
         <v>0</v>
       </c>
-      <c r="K4" s="6">
+      <c r="M4" s="6">
         <f>'#'!AR6</f>
         <v>0</v>
       </c>
-      <c r="L4" s="6">
+      <c r="N4" s="6">
         <f>'#'!AS6</f>
         <v>0</v>
       </c>
-      <c r="M4" s="2">
-        <f t="shared" ref="M4:M17" si="0">SUM(C4,E4,G4,I4,K4)</f>
+      <c r="O4" s="2">
+        <f t="shared" ref="O4:O17" si="0">SUM(E4,G4,I4,K4,M4)</f>
         <v>147</v>
       </c>
-      <c r="N4" s="2">
-        <f t="shared" ref="N4:N17" si="1">SUM(D4,F4,H4,J4,L4)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="P4" s="2">
+        <f t="shared" ref="P4:P17" si="1">SUM(F4,H4,J4,L4,N4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D5" s="36" t="s">
         <v>204</v>
       </c>
-      <c r="C5" s="6">
+      <c r="E5" s="6">
         <f>'#'!H7</f>
         <v>131</v>
       </c>
-      <c r="D5" s="6">
+      <c r="F5" s="6">
         <f>'#'!I7</f>
         <v>7</v>
       </c>
-      <c r="E5" s="4">
+      <c r="G5" s="4">
         <f>'#'!Q7</f>
         <v>37</v>
       </c>
-      <c r="F5" s="4">
+      <c r="H5" s="4">
         <f>'#'!R7</f>
         <v>1</v>
       </c>
-      <c r="G5" s="6">
+      <c r="I5" s="6">
         <f>'#'!Z7</f>
         <v>5</v>
       </c>
-      <c r="H5" s="6">
+      <c r="J5" s="6">
         <f>'#'!AA7</f>
         <v>0</v>
       </c>
-      <c r="I5" s="4">
+      <c r="K5" s="4">
         <f>'#'!AI7</f>
         <v>10</v>
       </c>
-      <c r="J5" s="4">
+      <c r="L5" s="4">
         <f>'#'!AJ7</f>
         <v>0</v>
       </c>
-      <c r="K5" s="6">
+      <c r="M5" s="6">
         <f>'#'!AR7</f>
         <v>1</v>
       </c>
-      <c r="L5" s="6">
+      <c r="N5" s="6">
         <f>'#'!AS7</f>
         <v>0</v>
       </c>
-      <c r="M5" s="2">
+      <c r="O5" s="2">
         <f t="shared" si="0"/>
         <v>184</v>
       </c>
-      <c r="N5" s="2">
+      <c r="P5" s="2">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="27" t="s">
+        <v>359</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D6" s="36" t="s">
         <v>326</v>
       </c>
-      <c r="C6" s="6">
+      <c r="E6" s="6">
         <f>'#'!H8</f>
         <v>20</v>
       </c>
-      <c r="D6" s="6">
+      <c r="F6" s="6">
         <f>'#'!I8</f>
         <v>0</v>
       </c>
-      <c r="E6" s="4">
+      <c r="G6" s="4">
         <f>'#'!Q8</f>
         <v>10</v>
       </c>
-      <c r="F6" s="4">
+      <c r="H6" s="4">
         <f>'#'!R8</f>
         <v>0</v>
       </c>
-      <c r="G6" s="6">
+      <c r="I6" s="6">
         <f>'#'!Z8</f>
         <v>3</v>
       </c>
-      <c r="H6" s="6">
+      <c r="J6" s="6">
         <f>'#'!AA8</f>
         <v>0</v>
       </c>
-      <c r="I6" s="4">
+      <c r="K6" s="4">
         <f>'#'!AI8</f>
         <v>2</v>
       </c>
-      <c r="J6" s="4">
+      <c r="L6" s="4">
         <f>'#'!AJ8</f>
         <v>0</v>
       </c>
-      <c r="K6" s="6">
+      <c r="M6" s="6">
         <f>'#'!AR8</f>
         <v>0</v>
       </c>
-      <c r="L6" s="6">
+      <c r="N6" s="6">
         <f>'#'!AS8</f>
         <v>0</v>
       </c>
-      <c r="M6" s="2">
+      <c r="O6" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="N6" s="2">
+      <c r="P6" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="67" t="s">
+        <v>365</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D7" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="C7" s="6">
+      <c r="E7" s="6">
         <f>'#'!H9</f>
         <v>136</v>
       </c>
-      <c r="D7" s="6">
+      <c r="F7" s="6">
         <f>'#'!I9</f>
         <v>6</v>
       </c>
-      <c r="E7" s="4">
+      <c r="G7" s="4">
         <f>'#'!Q9</f>
         <v>37</v>
       </c>
-      <c r="F7" s="4">
+      <c r="H7" s="4">
         <f>'#'!R9</f>
         <v>0</v>
       </c>
-      <c r="G7" s="6">
+      <c r="I7" s="6">
         <f>'#'!Z9</f>
         <v>6</v>
       </c>
-      <c r="H7" s="6">
+      <c r="J7" s="6">
         <f>'#'!AA9</f>
         <v>0</v>
       </c>
-      <c r="I7" s="4">
+      <c r="K7" s="4">
         <f>'#'!AI9</f>
         <v>10</v>
       </c>
-      <c r="J7" s="4">
+      <c r="L7" s="4">
         <f>'#'!AJ9</f>
         <v>1</v>
       </c>
-      <c r="K7" s="6">
+      <c r="M7" s="6">
         <f>'#'!AR9</f>
         <v>1</v>
       </c>
-      <c r="L7" s="6">
+      <c r="N7" s="6">
         <f>'#'!AS9</f>
         <v>0</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <f t="shared" si="0"/>
         <v>190</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D8" s="38" t="s">
         <v>328</v>
       </c>
-      <c r="C8" s="6">
+      <c r="E8" s="6">
         <f>'#'!H10</f>
         <v>25</v>
       </c>
-      <c r="D8" s="6">
+      <c r="F8" s="6">
         <f>'#'!I10</f>
         <v>1</v>
       </c>
-      <c r="E8" s="4">
+      <c r="G8" s="4">
         <f>'#'!Q10</f>
         <v>10</v>
       </c>
-      <c r="F8" s="4">
+      <c r="H8" s="4">
         <f>'#'!R10</f>
         <v>0</v>
       </c>
-      <c r="G8" s="6">
+      <c r="I8" s="6">
         <f>'#'!Z10</f>
         <v>1</v>
       </c>
-      <c r="H8" s="6">
+      <c r="J8" s="6">
         <f>'#'!AA10</f>
         <v>0</v>
       </c>
-      <c r="I8" s="4">
+      <c r="K8" s="4">
         <f>'#'!AI10</f>
         <v>3</v>
       </c>
-      <c r="J8" s="4">
+      <c r="L8" s="4">
         <f>'#'!AJ10</f>
         <v>0</v>
       </c>
-      <c r="K8" s="6">
+      <c r="M8" s="6">
         <f>'#'!AR10</f>
         <v>0</v>
       </c>
-      <c r="L8" s="6">
+      <c r="N8" s="6">
         <f>'#'!AS10</f>
         <v>0</v>
       </c>
-      <c r="M8" s="2">
+      <c r="O8" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="N8" s="2">
+      <c r="P8" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>6</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D9" s="38" t="s">
         <v>206</v>
       </c>
-      <c r="C9" s="6">
+      <c r="E9" s="6">
         <f>'#'!H11</f>
         <v>192</v>
       </c>
-      <c r="D9" s="6">
+      <c r="F9" s="6">
         <f>'#'!I11</f>
         <v>20</v>
       </c>
-      <c r="E9" s="4">
+      <c r="G9" s="4">
         <f>'#'!Q11</f>
         <v>44</v>
       </c>
-      <c r="F9" s="4">
+      <c r="H9" s="4">
         <f>'#'!R11</f>
         <v>3</v>
       </c>
-      <c r="G9" s="6">
+      <c r="I9" s="6">
         <f>'#'!Z11</f>
         <v>7</v>
       </c>
-      <c r="H9" s="6">
+      <c r="J9" s="6">
         <f>'#'!AA11</f>
         <v>1</v>
       </c>
-      <c r="I9" s="4">
+      <c r="K9" s="4">
         <f>'#'!AI11</f>
         <v>17</v>
       </c>
-      <c r="J9" s="4">
+      <c r="L9" s="4">
         <f>'#'!AJ11</f>
         <v>0</v>
       </c>
-      <c r="K9" s="6">
+      <c r="M9" s="6">
         <f>'#'!AR11</f>
         <v>1</v>
       </c>
-      <c r="L9" s="6">
+      <c r="N9" s="6">
         <f>'#'!AS11</f>
         <v>0</v>
       </c>
-      <c r="M9" s="2">
+      <c r="O9" s="2">
         <f t="shared" si="0"/>
         <v>261</v>
       </c>
-      <c r="N9" s="2">
+      <c r="P9" s="2">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>7</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="67" t="s">
+        <v>365</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D10" s="38" t="s">
         <v>188</v>
       </c>
-      <c r="C10" s="6">
+      <c r="E10" s="6">
         <f>'#'!H12</f>
         <v>226</v>
       </c>
-      <c r="D10" s="6">
+      <c r="F10" s="6">
         <f>'#'!I12</f>
         <v>60</v>
       </c>
-      <c r="E10" s="4">
+      <c r="G10" s="4">
         <f>'#'!Q12</f>
         <v>54</v>
       </c>
-      <c r="F10" s="4">
+      <c r="H10" s="4">
         <f>'#'!R12</f>
         <v>18</v>
       </c>
-      <c r="G10" s="6">
+      <c r="I10" s="6">
         <f>'#'!Z12</f>
         <v>13</v>
       </c>
-      <c r="H10" s="6">
+      <c r="J10" s="6">
         <f>'#'!AA12</f>
         <v>1</v>
       </c>
-      <c r="I10" s="4">
+      <c r="K10" s="4">
         <f>'#'!AI12</f>
         <v>17</v>
       </c>
-      <c r="J10" s="4">
+      <c r="L10" s="4">
         <f>'#'!AJ12</f>
         <v>2</v>
       </c>
-      <c r="K10" s="6">
+      <c r="M10" s="6">
         <f>'#'!AR12</f>
         <v>2</v>
       </c>
-      <c r="L10" s="6">
+      <c r="N10" s="6">
         <f>'#'!AS12</f>
         <v>0</v>
       </c>
-      <c r="M10" s="2">
+      <c r="O10" s="2">
         <f t="shared" si="0"/>
         <v>312</v>
       </c>
-      <c r="N10" s="2">
+      <c r="P10" s="2">
         <f t="shared" si="1"/>
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>8</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="D11" s="38" t="s">
         <v>227</v>
       </c>
-      <c r="C11" s="6">
+      <c r="E11" s="6">
         <f>'#'!H13</f>
         <v>176</v>
       </c>
-      <c r="D11" s="6">
+      <c r="F11" s="6">
         <f>'#'!I13</f>
         <v>35</v>
       </c>
-      <c r="E11" s="4">
+      <c r="G11" s="4">
         <f>'#'!Q13</f>
         <v>41</v>
       </c>
-      <c r="F11" s="4">
+      <c r="H11" s="4">
         <f>'#'!R13</f>
         <v>6</v>
       </c>
-      <c r="G11" s="6">
+      <c r="I11" s="6">
         <f>'#'!Z13</f>
         <v>6</v>
       </c>
-      <c r="H11" s="6">
+      <c r="J11" s="6">
         <f>'#'!AA13</f>
         <v>0</v>
       </c>
-      <c r="I11" s="4">
+      <c r="K11" s="4">
         <f>'#'!AI13</f>
         <v>10</v>
       </c>
-      <c r="J11" s="4">
+      <c r="L11" s="4">
         <f>'#'!AJ13</f>
         <v>1</v>
       </c>
-      <c r="K11" s="6">
+      <c r="M11" s="6">
         <f>'#'!AR13</f>
         <v>1</v>
       </c>
-      <c r="L11" s="6">
+      <c r="N11" s="6">
         <f>'#'!AS13</f>
         <v>0</v>
       </c>
-      <c r="M11" s="2">
+      <c r="O11" s="2">
         <f t="shared" si="0"/>
         <v>234</v>
       </c>
-      <c r="N11" s="2">
+      <c r="P11" s="2">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>9</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D12" s="38" t="s">
         <v>268</v>
       </c>
-      <c r="C12" s="6">
+      <c r="E12" s="6">
         <f>'#'!H14</f>
         <v>84</v>
       </c>
-      <c r="D12" s="6">
+      <c r="F12" s="6">
         <f>'#'!I14</f>
         <v>21</v>
       </c>
-      <c r="E12" s="4">
+      <c r="G12" s="4">
         <f>'#'!Q14</f>
         <v>25</v>
       </c>
-      <c r="F12" s="4">
+      <c r="H12" s="4">
         <f>'#'!R14</f>
         <v>6</v>
       </c>
-      <c r="G12" s="6">
+      <c r="I12" s="6">
         <f>'#'!Z14</f>
         <v>5</v>
       </c>
-      <c r="H12" s="6">
+      <c r="J12" s="6">
         <f>'#'!AA14</f>
         <v>1</v>
       </c>
-      <c r="I12" s="4">
+      <c r="K12" s="4">
         <f>'#'!AI14</f>
         <v>9</v>
       </c>
-      <c r="J12" s="4">
+      <c r="L12" s="4">
         <f>'#'!AJ14</f>
         <v>4</v>
       </c>
-      <c r="K12" s="6">
+      <c r="M12" s="6">
         <f>'#'!AR14</f>
         <v>0</v>
       </c>
-      <c r="L12" s="6">
+      <c r="N12" s="6">
         <f>'#'!AS14</f>
         <v>0</v>
       </c>
-      <c r="M12" s="2">
+      <c r="O12" s="2">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
-      <c r="N12" s="2">
+      <c r="P12" s="2">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>10</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="67" t="s">
+        <v>365</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="D13" s="38" t="s">
         <v>329</v>
       </c>
-      <c r="C13" s="6">
+      <c r="E13" s="6">
         <f>'#'!H15</f>
         <v>32</v>
       </c>
-      <c r="D13" s="6">
+      <c r="F13" s="6">
         <f>'#'!I15</f>
         <v>7</v>
       </c>
-      <c r="E13" s="4">
+      <c r="G13" s="4">
         <f>'#'!Q15</f>
         <v>13</v>
       </c>
-      <c r="F13" s="4">
+      <c r="H13" s="4">
         <f>'#'!R15</f>
         <v>1</v>
       </c>
-      <c r="G13" s="6">
+      <c r="I13" s="6">
         <f>'#'!Z15</f>
         <v>3</v>
       </c>
-      <c r="H13" s="6">
+      <c r="J13" s="6">
         <f>'#'!AA15</f>
         <v>1</v>
       </c>
-      <c r="I13" s="4">
+      <c r="K13" s="4">
         <f>'#'!AI15</f>
         <v>4</v>
       </c>
-      <c r="J13" s="4">
+      <c r="L13" s="4">
         <f>'#'!AJ15</f>
         <v>1</v>
       </c>
-      <c r="K13" s="6">
+      <c r="M13" s="6">
         <f>'#'!AR15</f>
         <v>0</v>
       </c>
-      <c r="L13" s="6">
+      <c r="N13" s="6">
         <f>'#'!AS15</f>
         <v>0</v>
       </c>
-      <c r="M13" s="2">
+      <c r="O13" s="2">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="N13" s="2">
+      <c r="P13" s="2">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>11</v>
       </c>
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D14" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="C14" s="6">
+      <c r="E14" s="6">
         <f>'#'!H16</f>
         <v>191</v>
       </c>
-      <c r="D14" s="6">
+      <c r="F14" s="6">
         <f>'#'!I16</f>
         <v>41</v>
       </c>
-      <c r="E14" s="4">
+      <c r="G14" s="4">
         <f>'#'!Q16</f>
         <v>53</v>
       </c>
-      <c r="F14" s="4">
+      <c r="H14" s="4">
         <f>'#'!R16</f>
         <v>13</v>
       </c>
-      <c r="G14" s="6">
+      <c r="I14" s="6">
         <f>'#'!Z16</f>
         <v>13</v>
       </c>
-      <c r="H14" s="6">
+      <c r="J14" s="6">
         <f>'#'!AA16</f>
         <v>4</v>
       </c>
-      <c r="I14" s="4">
+      <c r="K14" s="4">
         <f>'#'!AI16</f>
         <v>20</v>
       </c>
-      <c r="J14" s="4">
+      <c r="L14" s="4">
         <f>'#'!AJ16</f>
         <v>4</v>
       </c>
-      <c r="K14" s="6">
+      <c r="M14" s="6">
         <f>'#'!AR16</f>
         <v>1</v>
       </c>
-      <c r="L14" s="6">
+      <c r="N14" s="6">
         <f>'#'!AS16</f>
         <v>0</v>
       </c>
-      <c r="M14" s="2">
+      <c r="O14" s="2">
         <f t="shared" si="0"/>
         <v>278</v>
       </c>
-      <c r="N14" s="2">
+      <c r="P14" s="2">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>12</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D15" s="36" t="s">
         <v>285</v>
       </c>
-      <c r="C15" s="6">
+      <c r="E15" s="6">
         <f>'#'!H17</f>
         <v>62</v>
       </c>
-      <c r="D15" s="6">
+      <c r="F15" s="6">
         <f>'#'!I17</f>
         <v>4</v>
       </c>
-      <c r="E15" s="4">
+      <c r="G15" s="4">
         <f>'#'!Q17</f>
         <v>21</v>
       </c>
-      <c r="F15" s="4">
+      <c r="H15" s="4">
         <f>'#'!R17</f>
         <v>2</v>
       </c>
-      <c r="G15" s="6">
+      <c r="I15" s="6">
         <f>'#'!Z17</f>
         <v>3</v>
       </c>
-      <c r="H15" s="6">
+      <c r="J15" s="6">
         <f>'#'!AA17</f>
         <v>0</v>
       </c>
-      <c r="I15" s="4">
+      <c r="K15" s="4">
         <f>'#'!AI17</f>
         <v>8</v>
       </c>
-      <c r="J15" s="4">
+      <c r="L15" s="4">
         <f>'#'!AJ17</f>
         <v>0</v>
       </c>
-      <c r="K15" s="6">
+      <c r="M15" s="6">
         <f>'#'!AR17</f>
         <v>1</v>
       </c>
-      <c r="L15" s="6">
+      <c r="N15" s="6">
         <f>'#'!AS17</f>
         <v>0</v>
       </c>
-      <c r="M15" s="2">
+      <c r="O15" s="2">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="N15" s="2">
+      <c r="P15" s="2">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>13</v>
       </c>
-      <c r="B16" s="181" t="s">
+      <c r="B16" s="27" t="s">
+        <v>359</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="D16" s="181" t="s">
         <v>322</v>
       </c>
-      <c r="C16" s="6">
+      <c r="E16" s="6">
         <f>'#'!H18</f>
         <v>1</v>
       </c>
-      <c r="D16" s="6">
+      <c r="F16" s="6">
         <f>'#'!I18</f>
         <v>0</v>
       </c>
-      <c r="E16" s="4">
+      <c r="G16" s="4">
         <f>'#'!Q18</f>
         <v>1</v>
       </c>
-      <c r="F16" s="4">
+      <c r="H16" s="4">
         <f>'#'!R18</f>
         <v>0</v>
       </c>
-      <c r="G16" s="6">
+      <c r="I16" s="6">
         <f>'#'!Z18</f>
         <v>4</v>
       </c>
-      <c r="H16" s="6">
+      <c r="J16" s="6">
         <f>'#'!AA18</f>
         <v>0</v>
       </c>
-      <c r="I16" s="4">
+      <c r="K16" s="4">
         <f>'#'!AI18</f>
         <v>6</v>
       </c>
-      <c r="J16" s="4">
+      <c r="L16" s="4">
         <f>'#'!AJ18</f>
         <v>0</v>
       </c>
-      <c r="K16" s="6">
+      <c r="M16" s="6">
         <f>'#'!AR18</f>
         <v>0</v>
       </c>
-      <c r="L16" s="6">
+      <c r="N16" s="6">
         <f>'#'!AS18</f>
         <v>0</v>
       </c>
-      <c r="M16" s="2">
+      <c r="O16" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="N16" s="2">
+      <c r="P16" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>14</v>
       </c>
-      <c r="B17" s="181" t="s">
+      <c r="B17" s="27" t="s">
+        <v>370</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D17" s="181" t="s">
         <v>327</v>
       </c>
-      <c r="C17" s="6">
+      <c r="E17" s="6">
         <f>'#'!H19</f>
         <v>36</v>
       </c>
-      <c r="D17" s="6">
+      <c r="F17" s="6">
         <f>'#'!I19</f>
         <v>14</v>
       </c>
-      <c r="E17" s="4">
+      <c r="G17" s="4">
         <f>'#'!Q19</f>
         <v>13</v>
       </c>
-      <c r="F17" s="4">
+      <c r="H17" s="4">
         <f>'#'!R19</f>
         <v>5</v>
       </c>
-      <c r="G17" s="6">
+      <c r="I17" s="6">
         <f>'#'!Z19</f>
         <v>2</v>
       </c>
-      <c r="H17" s="6">
+      <c r="J17" s="6">
         <f>'#'!AA19</f>
         <v>1</v>
       </c>
-      <c r="I17" s="4">
+      <c r="K17" s="4">
         <f>'#'!AI19</f>
         <v>4</v>
       </c>
-      <c r="J17" s="4">
+      <c r="L17" s="4">
         <f>'#'!AJ19</f>
         <v>1</v>
       </c>
-      <c r="K17" s="6">
+      <c r="M17" s="6">
         <f>'#'!AR19</f>
         <v>0</v>
       </c>
-      <c r="L17" s="6">
+      <c r="N17" s="6">
         <f>'#'!AS19</f>
         <v>0</v>
       </c>
-      <c r="M17" s="2">
+      <c r="O17" s="2">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="N17" s="2">
+      <c r="P17" s="2">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" s="180" t="s">
+      <c r="B18" s="27" t="s">
+        <v>371</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D18" s="180" t="s">
         <v>353</v>
       </c>
-      <c r="C18" s="6">
+      <c r="E18" s="6">
         <f>'#'!H20</f>
         <v>0</v>
       </c>
-      <c r="D18" s="6">
+      <c r="F18" s="6">
         <f>'#'!I20</f>
         <v>0</v>
       </c>
-      <c r="E18" s="4">
+      <c r="G18" s="4">
         <f>'#'!Q20</f>
         <v>0</v>
       </c>
-      <c r="F18" s="4">
+      <c r="H18" s="4">
         <f>'#'!R20</f>
         <v>0</v>
       </c>
-      <c r="G18" s="6">
+      <c r="I18" s="6">
         <f>'#'!Z20</f>
         <v>0</v>
       </c>
-      <c r="H18" s="6">
+      <c r="J18" s="6">
         <f>'#'!AA20</f>
         <v>0</v>
       </c>
-      <c r="I18" s="4">
+      <c r="K18" s="4">
         <f>'#'!AI20</f>
         <v>0</v>
       </c>
-      <c r="J18" s="4">
+      <c r="L18" s="4">
         <f>'#'!AJ20</f>
         <v>0</v>
       </c>
-      <c r="K18" s="6">
+      <c r="M18" s="6">
         <f>'#'!AR20</f>
         <v>0</v>
       </c>
-      <c r="L18" s="6">
+      <c r="N18" s="6">
         <f>'#'!AS20</f>
         <v>0</v>
       </c>
-      <c r="M18" s="2">
-        <f t="shared" ref="M18:M24" si="2">SUM(C18,E18,G18,I18,K18)</f>
-        <v>0</v>
-      </c>
-      <c r="N18" s="2">
-        <f t="shared" ref="N18:N24" si="3">SUM(D18,F18,H18,J18,L18)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O18" s="2">
+        <f t="shared" ref="O18:O24" si="2">SUM(E18,G18,I18,K18,M18)</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="2">
+        <f t="shared" ref="P18:P24" si="3">SUM(F18,H18,J18,L18,N18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>20</v>
       </c>
-      <c r="B19" s="180" t="s">
+      <c r="B19" s="67" t="s">
+        <v>365</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D19" s="180" t="s">
         <v>325</v>
       </c>
-      <c r="C19" s="6">
+      <c r="E19" s="6">
         <f>'#'!H21</f>
         <v>26</v>
       </c>
-      <c r="D19" s="6">
+      <c r="F19" s="6">
         <f>'#'!I21</f>
         <v>3</v>
       </c>
-      <c r="E19" s="4">
+      <c r="G19" s="4">
         <f>'#'!Q21</f>
         <v>9</v>
       </c>
-      <c r="F19" s="4">
+      <c r="H19" s="4">
         <f>'#'!R21</f>
         <v>3</v>
       </c>
-      <c r="G19" s="6">
+      <c r="I19" s="6">
         <f>'#'!Z21</f>
         <v>4</v>
       </c>
-      <c r="H19" s="6">
+      <c r="J19" s="6">
         <f>'#'!AA21</f>
         <v>2</v>
       </c>
-      <c r="I19" s="4">
+      <c r="K19" s="4">
         <f>'#'!AI21</f>
         <v>3</v>
       </c>
-      <c r="J19" s="4">
+      <c r="L19" s="4">
         <f>'#'!AJ21</f>
         <v>0</v>
       </c>
-      <c r="K19" s="6">
+      <c r="M19" s="6">
         <f>'#'!AR21</f>
         <v>0</v>
       </c>
-      <c r="L19" s="6">
+      <c r="N19" s="6">
         <f>'#'!AS21</f>
         <v>0</v>
       </c>
-      <c r="M19" s="2">
+      <c r="O19" s="2">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="N19" s="2">
+      <c r="P19" s="2">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="67">
         <v>21</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="67" t="s">
+        <v>372</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="D20" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="C20" s="6">
+      <c r="E20" s="6">
         <f>'#'!H22</f>
         <v>33</v>
       </c>
-      <c r="D20" s="6">
+      <c r="F20" s="6">
         <f>'#'!I22</f>
         <v>2</v>
       </c>
-      <c r="E20" s="4">
+      <c r="G20" s="4">
         <f>'#'!Q22</f>
         <v>11</v>
       </c>
-      <c r="F20" s="4">
+      <c r="H20" s="4">
         <f>'#'!R22</f>
         <v>1</v>
       </c>
-      <c r="G20" s="6">
+      <c r="I20" s="6">
         <f>'#'!Z22</f>
         <v>2</v>
       </c>
-      <c r="H20" s="6">
+      <c r="J20" s="6">
         <f>'#'!AA22</f>
         <v>0</v>
       </c>
-      <c r="I20" s="4">
+      <c r="K20" s="4">
         <f>'#'!AI22</f>
         <v>2</v>
       </c>
-      <c r="J20" s="4">
+      <c r="L20" s="4">
         <f>'#'!AJ22</f>
         <v>0</v>
       </c>
-      <c r="K20" s="6">
+      <c r="M20" s="6">
         <f>'#'!AR22</f>
         <v>1</v>
       </c>
-      <c r="L20" s="6">
+      <c r="N20" s="6">
         <f>'#'!AS22</f>
         <v>0</v>
       </c>
-      <c r="M20" s="2">
+      <c r="O20" s="2">
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="N20" s="2">
+      <c r="P20" s="2">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="67">
         <v>22</v>
       </c>
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="67" t="s">
+        <v>365</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="D21" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="C21" s="6">
+      <c r="E21" s="6">
         <f>'#'!H23</f>
         <v>34</v>
       </c>
-      <c r="D21" s="6">
+      <c r="F21" s="6">
         <f>'#'!I23</f>
         <v>4</v>
       </c>
-      <c r="E21" s="4">
+      <c r="G21" s="4">
         <f>'#'!Q23</f>
         <v>10</v>
       </c>
-      <c r="F21" s="4">
+      <c r="H21" s="4">
         <f>'#'!R23</f>
         <v>2</v>
       </c>
-      <c r="G21" s="6">
+      <c r="I21" s="6">
         <f>'#'!Z23</f>
         <v>1</v>
       </c>
-      <c r="H21" s="6">
+      <c r="J21" s="6">
         <f>'#'!AA23</f>
         <v>0</v>
       </c>
-      <c r="I21" s="4">
+      <c r="K21" s="4">
         <f>'#'!AI23</f>
         <v>6</v>
       </c>
-      <c r="J21" s="4">
+      <c r="L21" s="4">
         <f>'#'!AJ23</f>
         <v>4</v>
       </c>
-      <c r="K21" s="6">
+      <c r="M21" s="6">
         <f>'#'!AR23</f>
         <v>0</v>
       </c>
-      <c r="L21" s="6">
+      <c r="N21" s="6">
         <f>'#'!AS23</f>
         <v>0</v>
       </c>
-      <c r="M21" s="2">
+      <c r="O21" s="2">
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="N21" s="2">
+      <c r="P21" s="2">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>23</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="27" t="s">
+        <v>359</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="D22" s="38" t="s">
         <v>303</v>
       </c>
-      <c r="C22" s="6">
+      <c r="E22" s="6">
         <f>'#'!H24</f>
         <v>50</v>
       </c>
-      <c r="D22" s="6">
+      <c r="F22" s="6">
         <f>'#'!I24</f>
         <v>11</v>
       </c>
-      <c r="E22" s="4">
+      <c r="G22" s="4">
         <f>'#'!Q24</f>
         <v>19</v>
       </c>
-      <c r="F22" s="4">
+      <c r="H22" s="4">
         <f>'#'!R24</f>
         <v>4</v>
       </c>
-      <c r="G22" s="6">
+      <c r="I22" s="6">
         <f>'#'!Z24</f>
         <v>2</v>
       </c>
-      <c r="H22" s="6">
+      <c r="J22" s="6">
         <f>'#'!AA24</f>
         <v>0</v>
       </c>
-      <c r="I22" s="4">
+      <c r="K22" s="4">
         <f>'#'!AI24</f>
         <v>7</v>
       </c>
-      <c r="J22" s="4">
+      <c r="L22" s="4">
         <f>'#'!AJ24</f>
         <v>0</v>
       </c>
-      <c r="K22" s="6">
+      <c r="M22" s="6">
         <f>'#'!AR24</f>
         <v>0</v>
       </c>
-      <c r="L22" s="6">
+      <c r="N22" s="6">
         <f>'#'!AS24</f>
         <v>0</v>
       </c>
-      <c r="M22" s="2">
+      <c r="O22" s="2">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
-      <c r="N22" s="2">
+      <c r="P22" s="2">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>24</v>
       </c>
-      <c r="B23" s="180" t="s">
+      <c r="B23" s="67" t="s">
+        <v>365</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D23" s="180" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="6">
+      <c r="E23" s="6">
         <f>'#'!H25</f>
         <v>50</v>
       </c>
-      <c r="D23" s="6">
+      <c r="F23" s="6">
         <f>'#'!I25</f>
         <v>4</v>
       </c>
-      <c r="E23" s="4">
+      <c r="G23" s="4">
         <f>'#'!Q25</f>
         <v>25</v>
       </c>
-      <c r="F23" s="4">
+      <c r="H23" s="4">
         <f>'#'!R25</f>
         <v>1</v>
       </c>
-      <c r="G23" s="6">
+      <c r="I23" s="6">
         <f>'#'!Z25</f>
         <v>5</v>
       </c>
-      <c r="H23" s="6">
+      <c r="J23" s="6">
         <f>'#'!AA25</f>
         <v>1</v>
       </c>
-      <c r="I23" s="4">
+      <c r="K23" s="4">
         <f>'#'!AI25</f>
         <v>8</v>
       </c>
-      <c r="J23" s="4">
+      <c r="L23" s="4">
         <f>'#'!AJ25</f>
         <v>2</v>
       </c>
-      <c r="K23" s="6">
+      <c r="M23" s="6">
         <f>'#'!AR25</f>
         <v>2</v>
       </c>
-      <c r="L23" s="6">
+      <c r="N23" s="6">
         <f>'#'!AS25</f>
         <v>0</v>
       </c>
-      <c r="M23" s="2">
+      <c r="O23" s="2">
         <f t="shared" si="2"/>
         <v>90</v>
       </c>
-      <c r="N23" s="2">
+      <c r="P23" s="2">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>29</v>
       </c>
-      <c r="B24" s="180" t="s">
+      <c r="B24" s="27" t="s">
+        <v>373</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D24" s="180" t="s">
         <v>284</v>
       </c>
-      <c r="C24" s="6">
+      <c r="E24" s="6">
         <f>'#'!H26</f>
         <v>72</v>
       </c>
-      <c r="D24" s="6">
+      <c r="F24" s="6">
         <f>'#'!I26</f>
         <v>24</v>
       </c>
-      <c r="E24" s="4">
+      <c r="G24" s="4">
         <f>'#'!Q26</f>
         <v>24</v>
       </c>
-      <c r="F24" s="4">
+      <c r="H24" s="4">
         <f>'#'!R26</f>
         <v>9</v>
       </c>
-      <c r="G24" s="6">
+      <c r="I24" s="6">
         <f>'#'!Z26</f>
         <v>5</v>
       </c>
-      <c r="H24" s="6">
+      <c r="J24" s="6">
         <f>'#'!AA26</f>
         <v>0</v>
       </c>
-      <c r="I24" s="4">
+      <c r="K24" s="4">
         <f>'#'!AI26</f>
         <v>9</v>
       </c>
-      <c r="J24" s="4">
+      <c r="L24" s="4">
         <f>'#'!AJ26</f>
         <v>3</v>
       </c>
-      <c r="K24" s="6">
+      <c r="M24" s="6">
         <f>'#'!AR26</f>
         <v>1</v>
       </c>
-      <c r="L24" s="6">
+      <c r="N24" s="6">
         <f>'#'!AS26</f>
         <v>0</v>
       </c>
-      <c r="M24" s="2">
+      <c r="O24" s="2">
         <f t="shared" si="2"/>
         <v>111</v>
       </c>
-      <c r="N24" s="2">
+      <c r="P24" s="2">
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>30</v>
       </c>
-      <c r="B25" s="180" t="s">
+      <c r="B25" s="27" t="s">
+        <v>361</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="D25" s="180" t="s">
         <v>354</v>
       </c>
-      <c r="C25" s="6">
+      <c r="E25" s="6">
         <f>'#'!H27</f>
         <v>0</v>
       </c>
-      <c r="D25" s="6">
+      <c r="F25" s="6">
         <f>'#'!I27</f>
         <v>0</v>
       </c>
-      <c r="E25" s="4">
+      <c r="G25" s="4">
         <f>'#'!Q27</f>
         <v>0</v>
       </c>
-      <c r="F25" s="4">
+      <c r="H25" s="4">
         <f>'#'!R27</f>
         <v>0</v>
       </c>
-      <c r="G25" s="6">
+      <c r="I25" s="6">
         <f>'#'!Z27</f>
         <v>0</v>
       </c>
-      <c r="H25" s="6">
+      <c r="J25" s="6">
         <f>'#'!AA27</f>
         <v>0</v>
       </c>
-      <c r="I25" s="4">
+      <c r="K25" s="4">
         <f>'#'!AI27</f>
         <v>0</v>
       </c>
-      <c r="J25" s="4">
+      <c r="L25" s="4">
         <f>'#'!AJ27</f>
         <v>0</v>
       </c>
-      <c r="K25" s="6">
+      <c r="M25" s="6">
         <f>'#'!AR27</f>
         <v>0</v>
       </c>
-      <c r="L25" s="6">
+      <c r="N25" s="6">
         <f>'#'!AS27</f>
         <v>0</v>
       </c>
-      <c r="M25" s="2">
-        <f t="shared" ref="M25:M28" si="4">SUM(C25,E25,G25,I25,K25)</f>
-        <v>0</v>
-      </c>
-      <c r="N25" s="2">
-        <f t="shared" ref="N25:N28" si="5">SUM(D25,F25,H25,J25,L25)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O25" s="2">
+        <f t="shared" ref="O25:O28" si="4">SUM(E25,G25,I25,K25,M25)</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="2">
+        <f t="shared" ref="P25:P28" si="5">SUM(F25,H25,J25,L25,N25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>33</v>
       </c>
-      <c r="B26" s="180" t="s">
+      <c r="B26" s="27" t="s">
+        <v>374</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D26" s="180" t="s">
         <v>301</v>
       </c>
-      <c r="C26" s="6">
+      <c r="E26" s="6">
         <f>'#'!H28</f>
         <v>45</v>
       </c>
-      <c r="D26" s="6">
+      <c r="F26" s="6">
         <f>'#'!I28</f>
         <v>3</v>
       </c>
-      <c r="E26" s="4">
+      <c r="G26" s="4">
         <f>'#'!Q28</f>
         <v>14</v>
       </c>
-      <c r="F26" s="4">
+      <c r="H26" s="4">
         <f>'#'!R28</f>
         <v>1</v>
       </c>
-      <c r="G26" s="6">
+      <c r="I26" s="6">
         <f>'#'!Z28</f>
         <v>2</v>
       </c>
-      <c r="H26" s="6">
+      <c r="J26" s="6">
         <f>'#'!AA28</f>
         <v>0</v>
       </c>
-      <c r="I26" s="4">
+      <c r="K26" s="4">
         <f>'#'!AI28</f>
         <v>4</v>
       </c>
-      <c r="J26" s="4">
+      <c r="L26" s="4">
         <f>'#'!AJ28</f>
         <v>0</v>
       </c>
-      <c r="K26" s="6">
+      <c r="M26" s="6">
         <f>'#'!AR28</f>
         <v>0</v>
       </c>
-      <c r="L26" s="6">
+      <c r="N26" s="6">
         <f>'#'!AS28</f>
         <v>0</v>
       </c>
-      <c r="M26" s="2">
+      <c r="O26" s="2">
         <f t="shared" si="4"/>
         <v>65</v>
       </c>
-      <c r="N26" s="2">
+      <c r="P26" s="2">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>35</v>
       </c>
-      <c r="B27" s="180" t="s">
+      <c r="B27" s="67" t="s">
+        <v>365</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="D27" s="180" t="s">
         <v>313</v>
       </c>
-      <c r="C27" s="6">
+      <c r="E27" s="6">
         <f>'#'!H29</f>
         <v>0</v>
       </c>
-      <c r="D27" s="6">
+      <c r="F27" s="6">
         <f>'#'!I29</f>
         <v>0</v>
       </c>
-      <c r="E27" s="4">
+      <c r="G27" s="4">
         <f>'#'!Q29</f>
         <v>0</v>
       </c>
-      <c r="F27" s="4">
+      <c r="H27" s="4">
         <f>'#'!R29</f>
         <v>0</v>
       </c>
-      <c r="G27" s="6">
+      <c r="I27" s="6">
         <f>'#'!Z29</f>
         <v>1</v>
       </c>
-      <c r="H27" s="6">
+      <c r="J27" s="6">
         <f>'#'!AA29</f>
         <v>0</v>
       </c>
-      <c r="I27" s="4">
+      <c r="K27" s="4">
         <f>'#'!AI29</f>
         <v>1</v>
       </c>
-      <c r="J27" s="4">
+      <c r="L27" s="4">
         <f>'#'!AJ29</f>
         <v>0</v>
       </c>
-      <c r="K27" s="6">
+      <c r="M27" s="6">
         <f>'#'!AR29</f>
         <v>0</v>
       </c>
-      <c r="L27" s="6">
+      <c r="N27" s="6">
         <f>'#'!AS29</f>
         <v>0</v>
       </c>
-      <c r="M27" s="2">
+      <c r="O27" s="2">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="N27" s="2">
+      <c r="P27" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>36</v>
       </c>
-      <c r="B28" s="180" t="s">
+      <c r="B28" s="27" t="s">
+        <v>359</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="D28" s="180" t="s">
         <v>323</v>
       </c>
-      <c r="C28" s="6">
+      <c r="E28" s="6">
         <f>'#'!H30</f>
         <v>38</v>
       </c>
-      <c r="D28" s="6">
+      <c r="F28" s="6">
         <f>'#'!I30</f>
         <v>5</v>
       </c>
-      <c r="E28" s="4">
+      <c r="G28" s="4">
         <f>'#'!Q30</f>
         <v>13</v>
       </c>
-      <c r="F28" s="4">
+      <c r="H28" s="4">
         <f>'#'!R30</f>
         <v>0</v>
       </c>
-      <c r="G28" s="6">
+      <c r="I28" s="6">
         <f>'#'!Z30</f>
         <v>3</v>
       </c>
-      <c r="H28" s="6">
+      <c r="J28" s="6">
         <f>'#'!AA30</f>
         <v>0</v>
       </c>
-      <c r="I28" s="4">
+      <c r="K28" s="4">
         <f>'#'!AI30</f>
         <v>3</v>
       </c>
-      <c r="J28" s="4">
+      <c r="L28" s="4">
         <f>'#'!AJ30</f>
         <v>1</v>
       </c>
-      <c r="K28" s="6">
+      <c r="M28" s="6">
         <f>'#'!AR30</f>
         <v>0</v>
       </c>
-      <c r="L28" s="6">
+      <c r="N28" s="6">
         <f>'#'!AS30</f>
         <v>0</v>
       </c>
-      <c r="M28" s="2">
+      <c r="O28" s="2">
         <f t="shared" si="4"/>
         <v>57</v>
       </c>
-      <c r="N28" s="2">
+      <c r="P28" s="2">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>39</v>
       </c>
-      <c r="B29" s="180" t="s">
+      <c r="B29" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="D29" s="180" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="6">
+      <c r="E29" s="6">
         <f>'#'!H31</f>
         <v>0</v>
       </c>
-      <c r="D29" s="6">
+      <c r="F29" s="6">
         <f>'#'!I31</f>
         <v>0</v>
       </c>
-      <c r="E29" s="4">
+      <c r="G29" s="4">
         <f>'#'!Q31</f>
         <v>0</v>
       </c>
-      <c r="F29" s="4">
+      <c r="H29" s="4">
         <f>'#'!R31</f>
         <v>0</v>
       </c>
-      <c r="G29" s="6">
+      <c r="I29" s="6">
         <f>'#'!Z31</f>
         <v>0</v>
       </c>
-      <c r="H29" s="6">
+      <c r="J29" s="6">
         <f>'#'!AA31</f>
         <v>0</v>
       </c>
-      <c r="I29" s="4">
+      <c r="K29" s="4">
         <f>'#'!AI31</f>
         <v>0</v>
       </c>
-      <c r="J29" s="4">
+      <c r="L29" s="4">
         <f>'#'!AJ31</f>
         <v>0</v>
       </c>
-      <c r="K29" s="6">
+      <c r="M29" s="6">
         <f>'#'!AR31</f>
         <v>0</v>
       </c>
-      <c r="L29" s="6">
+      <c r="N29" s="6">
         <f>'#'!AS31</f>
         <v>0</v>
       </c>
-      <c r="M29" s="2">
-        <f t="shared" ref="M29:M40" si="6">SUM(C29,E29,G29,I29,K29)</f>
-        <v>0</v>
-      </c>
-      <c r="N29" s="2">
-        <f t="shared" ref="N29:N40" si="7">SUM(D29,F29,H29,J29,L29)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O29" s="2">
+        <f t="shared" ref="O29:O40" si="6">SUM(E29,G29,I29,K29,M29)</f>
+        <v>0</v>
+      </c>
+      <c r="P29" s="2">
+        <f t="shared" ref="P29:P40" si="7">SUM(F29,H29,J29,L29,N29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>41</v>
       </c>
-      <c r="B30" s="36" t="s">
+      <c r="B30" s="67" t="s">
+        <v>365</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="D30" s="36" t="s">
         <v>286</v>
       </c>
-      <c r="C30" s="6">
+      <c r="E30" s="6">
         <f>'#'!H32</f>
         <v>109</v>
       </c>
-      <c r="D30" s="6">
+      <c r="F30" s="6">
         <f>'#'!I32</f>
         <v>15</v>
       </c>
-      <c r="E30" s="4">
+      <c r="G30" s="4">
         <f>'#'!Q32</f>
         <v>36</v>
       </c>
-      <c r="F30" s="4">
+      <c r="H30" s="4">
         <f>'#'!R32</f>
         <v>5</v>
       </c>
-      <c r="G30" s="6">
+      <c r="I30" s="6">
         <f>'#'!Z32</f>
         <v>2</v>
       </c>
-      <c r="H30" s="6">
+      <c r="J30" s="6">
         <f>'#'!AA32</f>
         <v>0</v>
       </c>
-      <c r="I30" s="4">
+      <c r="K30" s="4">
         <f>'#'!AI32</f>
         <v>10</v>
       </c>
-      <c r="J30" s="4">
+      <c r="L30" s="4">
         <f>'#'!AJ32</f>
         <v>1</v>
       </c>
-      <c r="K30" s="6">
+      <c r="M30" s="6">
         <f>'#'!AR32</f>
         <v>1</v>
       </c>
-      <c r="L30" s="6">
+      <c r="N30" s="6">
         <f>'#'!AS32</f>
         <v>0</v>
       </c>
-      <c r="M30" s="2">
+      <c r="O30" s="2">
         <f t="shared" si="6"/>
         <v>158</v>
       </c>
-      <c r="N30" s="2">
+      <c r="P30" s="2">
         <f t="shared" si="7"/>
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>46</v>
       </c>
-      <c r="B31" s="35" t="s">
+      <c r="B31" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D31" s="35" t="s">
         <v>308</v>
       </c>
-      <c r="C31" s="6">
+      <c r="E31" s="6">
         <f>'#'!H33</f>
         <v>0</v>
       </c>
-      <c r="D31" s="6">
+      <c r="F31" s="6">
         <f>'#'!I33</f>
         <v>0</v>
       </c>
-      <c r="E31" s="4">
+      <c r="G31" s="4">
         <f>'#'!Q33</f>
         <v>0</v>
       </c>
-      <c r="F31" s="4">
+      <c r="H31" s="4">
         <f>'#'!R33</f>
         <v>0</v>
       </c>
-      <c r="G31" s="6">
+      <c r="I31" s="6">
         <f>'#'!Z33</f>
         <v>0</v>
       </c>
-      <c r="H31" s="6">
+      <c r="J31" s="6">
         <f>'#'!AA33</f>
         <v>0</v>
       </c>
-      <c r="I31" s="4">
+      <c r="K31" s="4">
         <f>'#'!AI33</f>
         <v>1</v>
       </c>
-      <c r="J31" s="4">
+      <c r="L31" s="4">
         <f>'#'!AJ33</f>
         <v>0</v>
       </c>
-      <c r="K31" s="6">
+      <c r="M31" s="6">
         <f>'#'!AR33</f>
         <v>0</v>
       </c>
-      <c r="L31" s="6">
+      <c r="N31" s="6">
         <f>'#'!AS33</f>
         <v>0</v>
       </c>
-      <c r="M31" s="2">
+      <c r="O31" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="N31" s="2">
+      <c r="P31" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="67">
         <v>49</v>
       </c>
-      <c r="B32" s="36" t="s">
+      <c r="B32" s="67" t="s">
+        <v>365</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D32" s="36" t="s">
         <v>307</v>
       </c>
-      <c r="C32" s="6">
+      <c r="E32" s="6">
         <f>'#'!H34</f>
         <v>43</v>
       </c>
-      <c r="D32" s="6">
+      <c r="F32" s="6">
         <f>'#'!I34</f>
         <v>1</v>
       </c>
-      <c r="E32" s="4">
+      <c r="G32" s="4">
         <f>'#'!Q34</f>
         <v>20</v>
       </c>
-      <c r="F32" s="4">
+      <c r="H32" s="4">
         <f>'#'!R34</f>
         <v>0</v>
       </c>
-      <c r="G32" s="6">
+      <c r="I32" s="6">
         <f>'#'!Z34</f>
         <v>4</v>
       </c>
-      <c r="H32" s="6">
+      <c r="J32" s="6">
         <f>'#'!AA34</f>
         <v>0</v>
       </c>
-      <c r="I32" s="4">
+      <c r="K32" s="4">
         <f>'#'!AI34</f>
         <v>8</v>
       </c>
-      <c r="J32" s="4">
+      <c r="L32" s="4">
         <f>'#'!AJ34</f>
         <v>0</v>
       </c>
-      <c r="K32" s="6">
+      <c r="M32" s="6">
         <f>'#'!AR34</f>
         <v>0</v>
       </c>
-      <c r="L32" s="6">
+      <c r="N32" s="6">
         <f>'#'!AS34</f>
         <v>0</v>
       </c>
-      <c r="M32" s="2">
+      <c r="O32" s="2">
         <f t="shared" si="6"/>
         <v>75</v>
       </c>
-      <c r="N32" s="2">
+      <c r="P32" s="2">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="67">
         <v>52</v>
       </c>
-      <c r="B33" s="181" t="s">
+      <c r="B33" s="67" t="s">
+        <v>365</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>362</v>
+      </c>
+      <c r="D33" s="181" t="s">
         <v>351</v>
       </c>
-      <c r="C33" s="6">
+      <c r="E33" s="6">
         <f>'#'!H35</f>
         <v>0</v>
       </c>
-      <c r="D33" s="6">
+      <c r="F33" s="6">
         <f>'#'!I35</f>
         <v>0</v>
       </c>
-      <c r="E33" s="4">
+      <c r="G33" s="4">
         <f>'#'!Q35</f>
         <v>0</v>
       </c>
-      <c r="F33" s="4">
+      <c r="H33" s="4">
         <f>'#'!R35</f>
         <v>0</v>
       </c>
-      <c r="G33" s="6">
+      <c r="I33" s="6">
         <f>'#'!Z35</f>
         <v>1</v>
       </c>
-      <c r="H33" s="6">
+      <c r="J33" s="6">
         <f>'#'!AA35</f>
         <v>0</v>
       </c>
-      <c r="I33" s="4">
+      <c r="K33" s="4">
         <f>'#'!AI35</f>
         <v>0</v>
       </c>
-      <c r="J33" s="4">
+      <c r="L33" s="4">
         <f>'#'!AJ35</f>
         <v>0</v>
       </c>
-      <c r="K33" s="6">
+      <c r="M33" s="6">
         <f>'#'!AR35</f>
         <v>0</v>
       </c>
-      <c r="L33" s="6">
+      <c r="N33" s="6">
         <f>'#'!AS35</f>
         <v>0</v>
       </c>
-      <c r="M33" s="2">
+      <c r="O33" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="N33" s="2">
+      <c r="P33" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="67">
         <v>53</v>
       </c>
-      <c r="B34" s="180" t="s">
+      <c r="B34" s="67" t="s">
+        <v>365</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>364</v>
+      </c>
+      <c r="D34" s="180" t="s">
         <v>302</v>
       </c>
-      <c r="C34" s="6">
+      <c r="E34" s="6">
         <f>'#'!H36</f>
         <v>0</v>
       </c>
-      <c r="D34" s="6">
+      <c r="F34" s="6">
         <f>'#'!I36</f>
         <v>0</v>
       </c>
-      <c r="E34" s="4">
+      <c r="G34" s="4">
         <f>'#'!Q36</f>
         <v>0</v>
       </c>
-      <c r="F34" s="4">
+      <c r="H34" s="4">
         <f>'#'!R36</f>
         <v>0</v>
       </c>
-      <c r="G34" s="6">
+      <c r="I34" s="6">
         <f>'#'!Z36</f>
         <v>0</v>
       </c>
-      <c r="H34" s="6">
+      <c r="J34" s="6">
         <f>'#'!AA36</f>
         <v>0</v>
       </c>
-      <c r="I34" s="4">
+      <c r="K34" s="4">
         <f>'#'!AI36</f>
         <v>1</v>
       </c>
-      <c r="J34" s="4">
+      <c r="L34" s="4">
         <f>'#'!AJ36</f>
         <v>0</v>
       </c>
-      <c r="K34" s="6">
+      <c r="M34" s="6">
         <f>'#'!AR36</f>
         <v>0</v>
       </c>
-      <c r="L34" s="6">
+      <c r="N34" s="6">
         <f>'#'!AS36</f>
         <v>0</v>
       </c>
-      <c r="M34" s="2">
+      <c r="O34" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="N34" s="2">
+      <c r="P34" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="67">
         <v>56</v>
       </c>
-      <c r="B35" s="181" t="s">
+      <c r="B35" s="67" t="s">
+        <v>365</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>364</v>
+      </c>
+      <c r="D35" s="181" t="s">
         <v>332</v>
       </c>
-      <c r="C35" s="6">
+      <c r="E35" s="6">
         <f>'#'!H37</f>
         <v>6</v>
       </c>
-      <c r="D35" s="6">
+      <c r="F35" s="6">
         <f>'#'!I37</f>
         <v>1</v>
       </c>
-      <c r="E35" s="4">
+      <c r="G35" s="4">
         <f>'#'!Q37</f>
         <v>3</v>
       </c>
-      <c r="F35" s="4">
+      <c r="H35" s="4">
         <f>'#'!R37</f>
         <v>0</v>
       </c>
-      <c r="G35" s="6">
+      <c r="I35" s="6">
         <f>'#'!Z37</f>
         <v>2</v>
       </c>
-      <c r="H35" s="6">
+      <c r="J35" s="6">
         <f>'#'!AA37</f>
         <v>0</v>
       </c>
-      <c r="I35" s="4">
+      <c r="K35" s="4">
         <f>'#'!AI37</f>
         <v>2</v>
       </c>
-      <c r="J35" s="4">
+      <c r="L35" s="4">
         <f>'#'!AJ37</f>
         <v>0</v>
       </c>
-      <c r="K35" s="6">
+      <c r="M35" s="6">
         <f>'#'!AR37</f>
         <v>0</v>
       </c>
-      <c r="L35" s="6">
+      <c r="N35" s="6">
         <f>'#'!AS37</f>
         <v>0</v>
       </c>
-      <c r="M35" s="2">
+      <c r="O35" s="2">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="N35" s="2">
+      <c r="P35" s="2">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="67">
         <v>71</v>
       </c>
-      <c r="B36" s="180" t="s">
+      <c r="B36" s="67" t="s">
+        <v>365</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>364</v>
+      </c>
+      <c r="D36" s="180" t="s">
         <v>337</v>
       </c>
-      <c r="C36" s="6">
+      <c r="E36" s="6">
         <f>'#'!H38</f>
         <v>0</v>
       </c>
-      <c r="D36" s="6">
+      <c r="F36" s="6">
         <f>'#'!I38</f>
         <v>0</v>
       </c>
-      <c r="E36" s="4">
+      <c r="G36" s="4">
         <f>'#'!Q38</f>
         <v>1</v>
       </c>
-      <c r="F36" s="4">
+      <c r="H36" s="4">
         <f>'#'!R38</f>
         <v>0</v>
       </c>
-      <c r="G36" s="6">
+      <c r="I36" s="6">
         <f>'#'!Z38</f>
         <v>0</v>
       </c>
-      <c r="H36" s="6">
+      <c r="J36" s="6">
         <f>'#'!AA38</f>
         <v>0</v>
       </c>
-      <c r="I36" s="4">
+      <c r="K36" s="4">
         <f>'#'!AI38</f>
         <v>1</v>
       </c>
-      <c r="J36" s="4">
+      <c r="L36" s="4">
         <f>'#'!AJ38</f>
         <v>0</v>
       </c>
-      <c r="K36" s="6">
+      <c r="M36" s="6">
         <f>'#'!AR38</f>
         <v>0</v>
       </c>
-      <c r="L36" s="6">
+      <c r="N36" s="6">
         <f>'#'!AS38</f>
         <v>0</v>
       </c>
-      <c r="M36" s="2">
+      <c r="O36" s="2">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="N36" s="2">
+      <c r="P36" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="28">
         <v>72</v>
       </c>
-      <c r="B37" s="180" t="s">
+      <c r="B37" s="67" t="s">
+        <v>365</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>363</v>
+      </c>
+      <c r="D37" s="180" t="s">
         <v>348</v>
       </c>
-      <c r="C37" s="6">
+      <c r="E37" s="6">
         <f>'#'!H39</f>
         <v>0</v>
       </c>
-      <c r="D37" s="6">
+      <c r="F37" s="6">
         <f>'#'!I39</f>
         <v>0</v>
       </c>
-      <c r="E37" s="4">
+      <c r="G37" s="4">
         <f>'#'!Q39</f>
         <v>1</v>
       </c>
-      <c r="F37" s="4">
+      <c r="H37" s="4">
         <f>'#'!R39</f>
         <v>0</v>
       </c>
-      <c r="G37" s="6">
+      <c r="I37" s="6">
         <f>'#'!Z39</f>
         <v>0</v>
       </c>
-      <c r="H37" s="6">
+      <c r="J37" s="6">
         <f>'#'!AA39</f>
         <v>0</v>
       </c>
-      <c r="I37" s="4">
+      <c r="K37" s="4">
         <f>'#'!AI39</f>
         <v>0</v>
       </c>
-      <c r="J37" s="4">
+      <c r="L37" s="4">
         <f>'#'!AJ39</f>
         <v>0</v>
       </c>
-      <c r="K37" s="6">
+      <c r="M37" s="6">
         <f>'#'!AR39</f>
         <v>0</v>
       </c>
-      <c r="L37" s="6">
+      <c r="N37" s="6">
         <f>'#'!AS39</f>
         <v>0</v>
       </c>
-      <c r="M37" s="2">
+      <c r="O37" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="N37" s="2">
+      <c r="P37" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="28">
         <v>81</v>
       </c>
-      <c r="B38" s="180" t="s">
+      <c r="B38" s="67" t="s">
+        <v>365</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>364</v>
+      </c>
+      <c r="D38" s="180" t="s">
         <v>349</v>
       </c>
-      <c r="C38" s="6">
+      <c r="E38" s="6">
         <f>'#'!H40</f>
         <v>0</v>
       </c>
-      <c r="D38" s="6">
+      <c r="F38" s="6">
         <f>'#'!I40</f>
         <v>0</v>
       </c>
-      <c r="E38" s="4">
+      <c r="G38" s="4">
         <f>'#'!Q40</f>
         <v>1</v>
       </c>
-      <c r="F38" s="4">
+      <c r="H38" s="4">
         <f>'#'!R40</f>
         <v>0</v>
       </c>
-      <c r="G38" s="6">
+      <c r="I38" s="6">
         <f>'#'!Z40</f>
         <v>0</v>
       </c>
-      <c r="H38" s="6">
+      <c r="J38" s="6">
         <f>'#'!AA40</f>
         <v>0</v>
       </c>
-      <c r="I38" s="4">
+      <c r="K38" s="4">
         <f>'#'!AI40</f>
         <v>0</v>
       </c>
-      <c r="J38" s="4">
+      <c r="L38" s="4">
         <f>'#'!AJ40</f>
         <v>0</v>
       </c>
-      <c r="K38" s="6">
+      <c r="M38" s="6">
         <f>'#'!AR40</f>
         <v>0</v>
       </c>
-      <c r="L38" s="6">
+      <c r="N38" s="6">
         <f>'#'!AS40</f>
         <v>0</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="28">
         <v>89</v>
       </c>
-      <c r="B39" s="180" t="s">
+      <c r="B39" s="67" t="s">
+        <v>365</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>362</v>
+      </c>
+      <c r="D39" s="180" t="s">
         <v>343</v>
       </c>
-      <c r="C39" s="6">
+      <c r="E39" s="6">
         <f>'#'!H41</f>
         <v>0</v>
       </c>
-      <c r="D39" s="6">
+      <c r="F39" s="6">
         <f>'#'!I41</f>
         <v>0</v>
       </c>
-      <c r="E39" s="4">
+      <c r="G39" s="4">
         <f>'#'!Q41</f>
         <v>1</v>
       </c>
-      <c r="F39" s="4">
+      <c r="H39" s="4">
         <f>'#'!R41</f>
         <v>0</v>
       </c>
-      <c r="G39" s="6">
+      <c r="I39" s="6">
         <f>'#'!Z41</f>
         <v>3</v>
       </c>
-      <c r="H39" s="6">
+      <c r="J39" s="6">
         <f>'#'!AA41</f>
         <v>0</v>
       </c>
-      <c r="I39" s="4">
+      <c r="K39" s="4">
         <f>'#'!AI41</f>
         <v>0</v>
       </c>
-      <c r="J39" s="4">
+      <c r="L39" s="4">
         <f>'#'!AJ41</f>
         <v>0</v>
       </c>
-      <c r="K39" s="6">
+      <c r="M39" s="6">
         <f>'#'!AR41</f>
         <v>0</v>
       </c>
-      <c r="L39" s="6">
+      <c r="N39" s="6">
         <f>'#'!AS41</f>
         <v>0</v>
       </c>
-      <c r="M39" s="2">
+      <c r="O39" s="2">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="N39" s="2">
+      <c r="P39" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="67">
         <v>92</v>
       </c>
-      <c r="B40" s="38" t="s">
+      <c r="B40" s="67" t="s">
+        <v>365</v>
+      </c>
+      <c r="C40" s="67" t="s">
+        <v>360</v>
+      </c>
+      <c r="D40" s="38" t="s">
         <v>311</v>
       </c>
-      <c r="C40" s="6">
+      <c r="E40" s="6">
         <f>'#'!H42</f>
         <v>0</v>
       </c>
-      <c r="D40" s="6">
+      <c r="F40" s="6">
         <f>'#'!I42</f>
         <v>0</v>
       </c>
-      <c r="E40" s="4">
+      <c r="G40" s="4">
         <f>'#'!Q42</f>
         <v>0</v>
       </c>
-      <c r="F40" s="4">
+      <c r="H40" s="4">
         <f>'#'!R42</f>
         <v>0</v>
       </c>
-      <c r="G40" s="6">
+      <c r="I40" s="6">
         <f>'#'!Z42</f>
         <v>0</v>
       </c>
-      <c r="H40" s="6">
+      <c r="J40" s="6">
         <f>'#'!AA42</f>
         <v>0</v>
       </c>
-      <c r="I40" s="4">
+      <c r="K40" s="4">
         <f>'#'!AI42</f>
         <v>1</v>
       </c>
-      <c r="J40" s="4">
+      <c r="L40" s="4">
         <f>'#'!AJ42</f>
         <v>0</v>
       </c>
-      <c r="K40" s="6">
+      <c r="M40" s="6">
         <f>'#'!AR42</f>
         <v>0</v>
       </c>
-      <c r="L40" s="6">
+      <c r="N40" s="6">
         <f>'#'!AS42</f>
         <v>0</v>
       </c>
-      <c r="M40" s="2">
+      <c r="O40" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="N40" s="2">
+      <c r="P40" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D42" t="s">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="F42" t="s">
         <v>318</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:P3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="7">
+    <mergeCell ref="O2:P2"/>
     <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="C2:D2"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="E2:F2"/>
   </mergeCells>
-  <conditionalFormatting sqref="M4:M40">
+  <conditionalFormatting sqref="O4:O40">
     <cfRule type="cellIs" dxfId="37" priority="20" operator="greaterThan">
       <formula>396</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:N40">
+  <conditionalFormatting sqref="P4:P40">
     <cfRule type="cellIs" dxfId="36" priority="15" operator="greaterThan">
       <formula>92</formula>
     </cfRule>
@@ -57837,7 +58115,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>M4:M40</xm:sqref>
+          <xm:sqref>O4:O40</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6986" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B3FB32F-BFE8-43CE-AE3B-72DEDFA99CC0}"/>
+  <xr:revisionPtr revIDLastSave="6988" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFDB738C-8CE3-4571-8814-A2AC90E54E46}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1250,9 +1250,6 @@
     <t>URU</t>
   </si>
   <si>
-    <t>JAP</t>
-  </si>
-  <si>
     <t>COL</t>
   </si>
   <si>
@@ -1284,6 +1281,9 @@
   </si>
   <si>
     <t>EST</t>
+  </si>
+  <si>
+    <t>JPN</t>
   </si>
 </sst>
 </file>
@@ -2975,10 +2975,34 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="33" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2987,16 +3011,10 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3005,35 +3023,41 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="33" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3042,15 +3066,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3074,15 +3089,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3091,12 +3097,6 @@
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="69" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3158,24 +3158,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3218,28 +3200,31 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="26" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3340,6 +3325,21 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6391,7 +6391,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3497C102-2185-4BA1-8BAC-D671D9F65780}" type="CELLRANGE">
+                    <a:fld id="{FAEF23B0-84BF-4635-9F59-EE5BB70A9AA9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6425,7 +6425,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8D529E15-0B64-479F-99FD-D8C7CE348DFF}" type="CELLRANGE">
+                    <a:fld id="{0C764DEC-027F-46B8-B899-C81A5CD7306B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6459,7 +6459,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8530108E-7AFF-480A-8165-94334D681D99}" type="CELLRANGE">
+                    <a:fld id="{9A7F8369-1E60-4071-894B-875873D86C08}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6493,7 +6493,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{45F8F137-BF69-4019-A7F0-83A010292BCE}" type="CELLRANGE">
+                    <a:fld id="{73481767-5403-4FC7-8EBB-E71DA75EDFBE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6527,7 +6527,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5E26B725-E7FC-4579-9E7B-7335D9C62C64}" type="CELLRANGE">
+                    <a:fld id="{4DE79C72-1043-4044-9562-FF310C89136C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6561,7 +6561,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3A264298-14B4-4431-A9F0-243AA69920D7}" type="CELLRANGE">
+                    <a:fld id="{94440C22-8B81-47D4-B41F-667397B9A22D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6595,7 +6595,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{915D507A-90F0-447B-A0F6-D27F41CD8F98}" type="CELLRANGE">
+                    <a:fld id="{8244ADCD-D394-44BF-8C02-999EB8B3058D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6629,7 +6629,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E2448F93-3352-4E9B-BE2A-612F82A3C532}" type="CELLRANGE">
+                    <a:fld id="{D1691C6C-89AA-494C-A3B1-5E88A23E1937}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6663,7 +6663,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{799E97FF-452A-4A2B-9954-E9403002A84E}" type="CELLRANGE">
+                    <a:fld id="{96FEC150-5966-4BA5-96EC-CA7334ECBE4B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6697,7 +6697,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{68309B2F-8D9C-430A-8EAF-B72AE09D9A74}" type="CELLRANGE">
+                    <a:fld id="{3351B251-A9D3-4B5F-90E2-35CA0A4BDE54}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6731,7 +6731,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9F7DEAAB-5AFD-4C14-AFAD-126F806E6749}" type="CELLRANGE">
+                    <a:fld id="{FED2B0B8-1742-42DC-BDF9-20C00E792F2A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6765,7 +6765,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{00FAD991-2387-4BD8-A9FB-314BF0E6DFC3}" type="CELLRANGE">
+                    <a:fld id="{57009207-11C2-48F0-A48B-1516BF55467E}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6814,7 +6814,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{4550078E-F4E1-413C-9AF7-0A55230F8021}" type="CELLRANGE">
+                    <a:fld id="{84762C4F-00BB-4418-9DD5-BF296A83BF68}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6873,7 +6873,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AAD48B4F-803F-4B45-84C9-1F8DE550F6AE}" type="CELLRANGE">
+                    <a:fld id="{F0E9680F-407C-4322-B8EC-ABA565179B3C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6907,7 +6907,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{10587ABE-6E64-4234-8FC7-728869F64352}" type="CELLRANGE">
+                    <a:fld id="{7530ABEB-F7FE-47F4-B508-0CBA5EF236B5}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6941,7 +6941,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{44992C1C-1B84-473B-8AC3-97E5200A65A9}" type="CELLRANGE">
+                    <a:fld id="{38A19622-F598-4893-9A16-C9B842E880CC}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6975,7 +6975,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{708030A8-F59F-4997-A68A-CEF229A3FFF5}" type="CELLRANGE">
+                    <a:fld id="{83DEDEBA-0B6C-472E-9BFE-FE1C86AC9F51}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7009,7 +7009,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{58E2C3A9-82BA-45A1-A974-8ED7C36F7051}" type="CELLRANGE">
+                    <a:fld id="{220D2FB1-D0E8-4245-A20F-E45C7C30F711}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7043,7 +7043,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9FFFC594-3ECE-4149-B28D-7EA075879375}" type="CELLRANGE">
+                    <a:fld id="{F5F0866F-7E83-44D0-92FC-CD2E7F05FE06}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7077,7 +7077,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CE69E41A-FC98-45FC-B3B8-37E7202E6316}" type="CELLRANGE">
+                    <a:fld id="{D3179B32-F17F-48F5-B2D7-DF554C23DC5D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -27544,7 +27544,7 @@
         <v>18</v>
       </c>
       <c r="B44" s="28" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="C44" s="28" t="s">
         <v>362</v>
@@ -27944,7 +27944,7 @@
         <v>13</v>
       </c>
       <c r="B52" s="67" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C52" s="67" t="s">
         <v>360</v>
@@ -28194,7 +28194,7 @@
         <v>7</v>
       </c>
       <c r="B57" s="67" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C57" s="67" t="s">
         <v>364</v>
@@ -28244,7 +28244,7 @@
         <v>28</v>
       </c>
       <c r="B58" s="67" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C58" s="67" t="s">
         <v>364</v>
@@ -28344,7 +28344,7 @@
         <v>26</v>
       </c>
       <c r="B60" s="67" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C60" s="67" t="s">
         <v>360</v>
@@ -28794,7 +28794,7 @@
         <v>16</v>
       </c>
       <c r="B69" s="67" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C69" s="67" t="s">
         <v>363</v>
@@ -28944,7 +28944,7 @@
         <v>26</v>
       </c>
       <c r="B72" s="67" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C72" s="67" t="s">
         <v>364</v>
@@ -29093,8 +29093,8 @@
       <c r="A75" s="4">
         <v>31</v>
       </c>
-      <c r="B75" s="4" t="s">
-        <v>390</v>
+      <c r="B75" s="28" t="s">
+        <v>401</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>364</v>
@@ -29144,7 +29144,7 @@
         <v>30</v>
       </c>
       <c r="B76" s="67" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C76" s="67" t="s">
         <v>360</v>
@@ -29244,7 +29244,7 @@
         <v>13</v>
       </c>
       <c r="B78" s="67" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C78" s="67" t="s">
         <v>360</v>
@@ -29894,7 +29894,7 @@
         <v>36</v>
       </c>
       <c r="B91" s="67" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C91" s="67" t="s">
         <v>363</v>
@@ -29994,7 +29994,7 @@
         <v>47</v>
       </c>
       <c r="B93" s="67" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C93" s="67" t="s">
         <v>363</v>
@@ -30194,7 +30194,7 @@
         <v>47</v>
       </c>
       <c r="B97" s="67" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C97" s="67" t="s">
         <v>362</v>
@@ -30244,7 +30244,7 @@
         <v>31</v>
       </c>
       <c r="B98" s="67" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C98" s="67" t="s">
         <v>360</v>
@@ -34564,320 +34564,320 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:80" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E1" s="221">
-        <v>1</v>
-      </c>
-      <c r="F1" s="221"/>
-      <c r="G1" s="222">
+      <c r="E1" s="214">
+        <v>1</v>
+      </c>
+      <c r="F1" s="214"/>
+      <c r="G1" s="212">
         <v>2</v>
       </c>
-      <c r="H1" s="222"/>
-      <c r="I1" s="223">
-        <v>3</v>
-      </c>
-      <c r="J1" s="223"/>
-      <c r="K1" s="222">
+      <c r="H1" s="212"/>
+      <c r="I1" s="213">
+        <v>3</v>
+      </c>
+      <c r="J1" s="213"/>
+      <c r="K1" s="212">
         <v>4</v>
       </c>
-      <c r="L1" s="222"/>
-      <c r="M1" s="222">
+      <c r="L1" s="212"/>
+      <c r="M1" s="212">
         <v>5</v>
       </c>
-      <c r="N1" s="222"/>
-      <c r="O1" s="221">
+      <c r="N1" s="212"/>
+      <c r="O1" s="214">
         <v>6</v>
       </c>
-      <c r="P1" s="221"/>
-      <c r="Q1" s="222">
+      <c r="P1" s="214"/>
+      <c r="Q1" s="212">
         <v>7</v>
       </c>
-      <c r="R1" s="222"/>
-      <c r="S1" s="222">
+      <c r="R1" s="212"/>
+      <c r="S1" s="212">
         <v>8</v>
       </c>
-      <c r="T1" s="222"/>
-      <c r="U1" s="222">
+      <c r="T1" s="212"/>
+      <c r="U1" s="212">
         <v>9</v>
       </c>
-      <c r="V1" s="222"/>
-      <c r="W1" s="222">
+      <c r="V1" s="212"/>
+      <c r="W1" s="212">
         <v>10</v>
       </c>
-      <c r="X1" s="222"/>
-      <c r="Y1" s="222">
+      <c r="X1" s="212"/>
+      <c r="Y1" s="212">
         <v>11</v>
       </c>
-      <c r="Z1" s="222"/>
-      <c r="AA1" s="223">
+      <c r="Z1" s="212"/>
+      <c r="AA1" s="213">
         <v>12</v>
       </c>
-      <c r="AB1" s="223"/>
-      <c r="AC1" s="221">
+      <c r="AB1" s="213"/>
+      <c r="AC1" s="214">
         <v>13</v>
       </c>
-      <c r="AD1" s="221"/>
-      <c r="AE1" s="223">
+      <c r="AD1" s="214"/>
+      <c r="AE1" s="213">
         <v>14</v>
       </c>
-      <c r="AF1" s="223"/>
-      <c r="AG1" s="224">
+      <c r="AF1" s="213"/>
+      <c r="AG1" s="215">
         <v>15</v>
       </c>
-      <c r="AH1" s="225"/>
-      <c r="AI1" s="222">
+      <c r="AH1" s="216"/>
+      <c r="AI1" s="212">
         <v>16</v>
       </c>
-      <c r="AJ1" s="222"/>
-      <c r="AK1" s="222">
+      <c r="AJ1" s="212"/>
+      <c r="AK1" s="212">
         <v>17</v>
       </c>
-      <c r="AL1" s="222"/>
-      <c r="AM1" s="222">
+      <c r="AL1" s="212"/>
+      <c r="AM1" s="212">
         <v>18</v>
       </c>
-      <c r="AN1" s="222"/>
-      <c r="AO1" s="226">
+      <c r="AN1" s="212"/>
+      <c r="AO1" s="211">
         <v>19</v>
       </c>
-      <c r="AP1" s="226"/>
-      <c r="AQ1" s="226">
+      <c r="AP1" s="211"/>
+      <c r="AQ1" s="211">
         <v>20</v>
       </c>
-      <c r="AR1" s="226"/>
-      <c r="AS1" s="226">
+      <c r="AR1" s="211"/>
+      <c r="AS1" s="211">
         <v>21</v>
       </c>
-      <c r="AT1" s="226"/>
-      <c r="AU1" s="226">
+      <c r="AT1" s="211"/>
+      <c r="AU1" s="211">
         <v>22</v>
       </c>
-      <c r="AV1" s="226"/>
-      <c r="AW1" s="226">
+      <c r="AV1" s="211"/>
+      <c r="AW1" s="211">
         <v>23</v>
       </c>
-      <c r="AX1" s="226"/>
-      <c r="AY1" s="226">
+      <c r="AX1" s="211"/>
+      <c r="AY1" s="211">
         <v>24</v>
       </c>
-      <c r="AZ1" s="226"/>
-      <c r="BA1" s="226">
+      <c r="AZ1" s="211"/>
+      <c r="BA1" s="211">
         <v>25</v>
       </c>
-      <c r="BB1" s="226"/>
-      <c r="BC1" s="226">
+      <c r="BB1" s="211"/>
+      <c r="BC1" s="211">
         <v>26</v>
       </c>
-      <c r="BD1" s="226"/>
-      <c r="BE1" s="226">
+      <c r="BD1" s="211"/>
+      <c r="BE1" s="211">
         <v>27</v>
       </c>
-      <c r="BF1" s="226"/>
-      <c r="BG1" s="226">
+      <c r="BF1" s="211"/>
+      <c r="BG1" s="211">
         <v>28</v>
       </c>
-      <c r="BH1" s="226"/>
-      <c r="BI1" s="226">
+      <c r="BH1" s="211"/>
+      <c r="BI1" s="211">
         <v>29</v>
       </c>
-      <c r="BJ1" s="226"/>
-      <c r="BK1" s="226">
+      <c r="BJ1" s="211"/>
+      <c r="BK1" s="211">
         <v>30</v>
       </c>
-      <c r="BL1" s="226"/>
-      <c r="BM1" s="226">
+      <c r="BL1" s="211"/>
+      <c r="BM1" s="211">
         <v>31</v>
       </c>
-      <c r="BN1" s="226"/>
-      <c r="BO1" s="226">
+      <c r="BN1" s="211"/>
+      <c r="BO1" s="211">
         <v>32</v>
       </c>
-      <c r="BP1" s="226"/>
-      <c r="BQ1" s="226">
+      <c r="BP1" s="211"/>
+      <c r="BQ1" s="211">
         <v>33</v>
       </c>
-      <c r="BR1" s="226"/>
-      <c r="BS1" s="226">
+      <c r="BR1" s="211"/>
+      <c r="BS1" s="211">
         <v>34</v>
       </c>
-      <c r="BT1" s="226"/>
-      <c r="BU1" s="226">
+      <c r="BT1" s="211"/>
+      <c r="BU1" s="211">
         <v>35</v>
       </c>
-      <c r="BV1" s="226"/>
-      <c r="BW1" s="226">
+      <c r="BV1" s="211"/>
+      <c r="BW1" s="211">
         <v>36</v>
       </c>
-      <c r="BX1" s="226"/>
-      <c r="BY1" s="226">
+      <c r="BX1" s="211"/>
+      <c r="BY1" s="211">
         <v>37</v>
       </c>
-      <c r="BZ1" s="226"/>
-      <c r="CA1" s="226">
+      <c r="BZ1" s="211"/>
+      <c r="CA1" s="211">
         <v>38</v>
       </c>
-      <c r="CB1" s="226"/>
+      <c r="CB1" s="211"/>
     </row>
     <row r="2" spans="1:80" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="227" t="s">
+      <c r="C2" s="209" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="227" t="s">
+      <c r="D2" s="209" t="s">
         <v>99</v>
       </c>
-      <c r="E2" s="213" t="s">
+      <c r="E2" s="225" t="s">
         <v>356</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="215" t="s">
+      <c r="F2" s="226"/>
+      <c r="G2" s="217" t="s">
         <v>341</v>
       </c>
-      <c r="H2" s="216"/>
-      <c r="I2" s="211" t="s">
+      <c r="H2" s="218"/>
+      <c r="I2" s="219" t="s">
         <v>340</v>
       </c>
-      <c r="J2" s="212"/>
-      <c r="K2" s="211" t="s">
+      <c r="J2" s="220"/>
+      <c r="K2" s="219" t="s">
         <v>338</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="209" t="s">
+      <c r="L2" s="220"/>
+      <c r="M2" s="227" t="s">
         <v>345</v>
       </c>
-      <c r="N2" s="210"/>
-      <c r="O2" s="211" t="s">
+      <c r="N2" s="228"/>
+      <c r="O2" s="219" t="s">
         <v>330</v>
       </c>
-      <c r="P2" s="212"/>
-      <c r="Q2" s="211" t="s">
+      <c r="P2" s="220"/>
+      <c r="Q2" s="219" t="s">
         <v>347</v>
       </c>
-      <c r="R2" s="212"/>
-      <c r="S2" s="211" t="s">
+      <c r="R2" s="220"/>
+      <c r="S2" s="219" t="s">
         <v>344</v>
       </c>
-      <c r="T2" s="212"/>
-      <c r="U2" s="211" t="s">
+      <c r="T2" s="220"/>
+      <c r="U2" s="219" t="s">
         <v>331</v>
       </c>
-      <c r="V2" s="212"/>
-      <c r="W2" s="211" t="s">
+      <c r="V2" s="220"/>
+      <c r="W2" s="219" t="s">
         <v>357</v>
       </c>
-      <c r="X2" s="212"/>
-      <c r="Y2" s="211" t="s">
+      <c r="X2" s="220"/>
+      <c r="Y2" s="219" t="s">
         <v>334</v>
       </c>
-      <c r="Z2" s="212"/>
-      <c r="AA2" s="211" t="s">
+      <c r="Z2" s="220"/>
+      <c r="AA2" s="219" t="s">
         <v>333</v>
       </c>
-      <c r="AB2" s="212"/>
-      <c r="AC2" s="209" t="s">
+      <c r="AB2" s="220"/>
+      <c r="AC2" s="227" t="s">
         <v>342</v>
       </c>
-      <c r="AD2" s="210"/>
-      <c r="AE2" s="209" t="s">
+      <c r="AD2" s="228"/>
+      <c r="AE2" s="227" t="s">
         <v>339</v>
       </c>
-      <c r="AF2" s="210"/>
-      <c r="AG2" s="209" t="s">
+      <c r="AF2" s="228"/>
+      <c r="AG2" s="227" t="s">
         <v>346</v>
       </c>
-      <c r="AH2" s="210"/>
-      <c r="AI2" s="209" t="s">
+      <c r="AH2" s="228"/>
+      <c r="AI2" s="227" t="s">
         <v>315</v>
       </c>
-      <c r="AJ2" s="210"/>
-      <c r="AK2" s="211" t="s">
+      <c r="AJ2" s="228"/>
+      <c r="AK2" s="219" t="s">
         <v>336</v>
       </c>
-      <c r="AL2" s="212"/>
-      <c r="AM2" s="213" t="s">
+      <c r="AL2" s="220"/>
+      <c r="AM2" s="225" t="s">
         <v>335</v>
       </c>
-      <c r="AN2" s="214"/>
-      <c r="AO2" s="213" t="s">
+      <c r="AN2" s="226"/>
+      <c r="AO2" s="225" t="s">
         <v>358</v>
       </c>
-      <c r="AP2" s="214"/>
-      <c r="AQ2" s="217" t="s">
+      <c r="AP2" s="226"/>
+      <c r="AQ2" s="223" t="s">
         <v>342</v>
       </c>
-      <c r="AR2" s="218"/>
-      <c r="AS2" s="217" t="s">
+      <c r="AR2" s="224"/>
+      <c r="AS2" s="223" t="s">
         <v>357</v>
       </c>
-      <c r="AT2" s="218"/>
-      <c r="AU2" s="219" t="s">
+      <c r="AT2" s="224"/>
+      <c r="AU2" s="221" t="s">
         <v>334</v>
       </c>
-      <c r="AV2" s="220"/>
-      <c r="AW2" s="219" t="s">
+      <c r="AV2" s="222"/>
+      <c r="AW2" s="221" t="s">
         <v>333</v>
       </c>
-      <c r="AX2" s="220"/>
-      <c r="AY2" s="213" t="s">
+      <c r="AX2" s="222"/>
+      <c r="AY2" s="225" t="s">
         <v>331</v>
       </c>
-      <c r="AZ2" s="214"/>
-      <c r="BA2" s="219" t="s">
+      <c r="AZ2" s="226"/>
+      <c r="BA2" s="221" t="s">
         <v>358</v>
       </c>
-      <c r="BB2" s="220"/>
-      <c r="BC2" s="217" t="s">
+      <c r="BB2" s="222"/>
+      <c r="BC2" s="223" t="s">
         <v>335</v>
       </c>
-      <c r="BD2" s="218"/>
-      <c r="BE2" s="217" t="s">
+      <c r="BD2" s="224"/>
+      <c r="BE2" s="223" t="s">
         <v>315</v>
       </c>
-      <c r="BF2" s="218"/>
-      <c r="BG2" s="213" t="s">
+      <c r="BF2" s="224"/>
+      <c r="BG2" s="225" t="s">
         <v>336</v>
       </c>
-      <c r="BH2" s="214"/>
-      <c r="BI2" s="213" t="s">
+      <c r="BH2" s="226"/>
+      <c r="BI2" s="225" t="s">
         <v>340</v>
       </c>
-      <c r="BJ2" s="214"/>
-      <c r="BK2" s="219" t="s">
+      <c r="BJ2" s="226"/>
+      <c r="BK2" s="221" t="s">
         <v>338</v>
       </c>
-      <c r="BL2" s="220"/>
-      <c r="BM2" s="211" t="s">
+      <c r="BL2" s="222"/>
+      <c r="BM2" s="219" t="s">
         <v>356</v>
       </c>
-      <c r="BN2" s="212"/>
-      <c r="BO2" s="211" t="s">
+      <c r="BN2" s="220"/>
+      <c r="BO2" s="219" t="s">
         <v>341</v>
       </c>
-      <c r="BP2" s="212"/>
-      <c r="BQ2" s="215" t="s">
+      <c r="BP2" s="220"/>
+      <c r="BQ2" s="217" t="s">
         <v>346</v>
       </c>
-      <c r="BR2" s="216"/>
-      <c r="BS2" s="215" t="s">
+      <c r="BR2" s="218"/>
+      <c r="BS2" s="217" t="s">
         <v>339</v>
       </c>
-      <c r="BT2" s="216"/>
-      <c r="BU2" s="215" t="s">
+      <c r="BT2" s="218"/>
+      <c r="BU2" s="217" t="s">
         <v>330</v>
       </c>
-      <c r="BV2" s="216"/>
-      <c r="BW2" s="215" t="s">
+      <c r="BV2" s="218"/>
+      <c r="BW2" s="217" t="s">
         <v>347</v>
       </c>
-      <c r="BX2" s="216"/>
-      <c r="BY2" s="211" t="s">
+      <c r="BX2" s="218"/>
+      <c r="BY2" s="219" t="s">
         <v>344</v>
       </c>
-      <c r="BZ2" s="212"/>
-      <c r="CA2" s="215" t="s">
+      <c r="BZ2" s="220"/>
+      <c r="CA2" s="217" t="s">
         <v>345</v>
       </c>
-      <c r="CB2" s="216"/>
+      <c r="CB2" s="218"/>
     </row>
     <row r="3" spans="1:80" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -34886,8 +34886,8 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="228"/>
-      <c r="D3" s="228"/>
+      <c r="C3" s="210"/>
+      <c r="D3" s="210"/>
       <c r="E3" s="147" t="s">
         <v>87</v>
       </c>
@@ -38833,6 +38833,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="AS2:AT2"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AE2:AF2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="AI2:AJ2"/>
+    <mergeCell ref="AK2:AL2"/>
+    <mergeCell ref="AM2:AN2"/>
+    <mergeCell ref="AO2:AP2"/>
+    <mergeCell ref="AQ2:AR2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AG2:AH2"/>
+    <mergeCell ref="BQ2:BR2"/>
+    <mergeCell ref="BA2:BB2"/>
+    <mergeCell ref="BC2:BD2"/>
+    <mergeCell ref="BE2:BF2"/>
+    <mergeCell ref="AU2:AV2"/>
+    <mergeCell ref="AW2:AX2"/>
+    <mergeCell ref="AY2:AZ2"/>
+    <mergeCell ref="BG2:BH2"/>
+    <mergeCell ref="BI2:BJ2"/>
+    <mergeCell ref="BK2:BL2"/>
+    <mergeCell ref="BM2:BN2"/>
+    <mergeCell ref="BO2:BP2"/>
+    <mergeCell ref="BS2:BT2"/>
+    <mergeCell ref="BU2:BV2"/>
+    <mergeCell ref="BW2:BX2"/>
+    <mergeCell ref="BY2:BZ2"/>
+    <mergeCell ref="CA2:CB2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="AY1:AZ1"/>
+    <mergeCell ref="BA1:BB1"/>
+    <mergeCell ref="BC1:BD1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="AS1:AT1"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="BY1:BZ1"/>
@@ -38849,68 +38911,6 @@
     <mergeCell ref="BM1:BN1"/>
     <mergeCell ref="AU1:AV1"/>
     <mergeCell ref="AW1:AX1"/>
-    <mergeCell ref="AY1:AZ1"/>
-    <mergeCell ref="BA1:BB1"/>
-    <mergeCell ref="BC1:BD1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="BS2:BT2"/>
-    <mergeCell ref="BU2:BV2"/>
-    <mergeCell ref="BW2:BX2"/>
-    <mergeCell ref="BY2:BZ2"/>
-    <mergeCell ref="CA2:CB2"/>
-    <mergeCell ref="BQ2:BR2"/>
-    <mergeCell ref="BA2:BB2"/>
-    <mergeCell ref="BC2:BD2"/>
-    <mergeCell ref="BE2:BF2"/>
-    <mergeCell ref="AU2:AV2"/>
-    <mergeCell ref="AW2:AX2"/>
-    <mergeCell ref="AY2:AZ2"/>
-    <mergeCell ref="BG2:BH2"/>
-    <mergeCell ref="BI2:BJ2"/>
-    <mergeCell ref="BK2:BL2"/>
-    <mergeCell ref="BM2:BN2"/>
-    <mergeCell ref="BO2:BP2"/>
-    <mergeCell ref="AS2:AT2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="AI2:AJ2"/>
-    <mergeCell ref="AK2:AL2"/>
-    <mergeCell ref="AM2:AN2"/>
-    <mergeCell ref="AO2:AP2"/>
-    <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AG2:AH2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:CB40">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -38945,88 +38945,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="227" t="s">
+      <c r="C1" s="209" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="227" t="s">
+      <c r="D1" s="209" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="242" t="s">
+      <c r="E1" s="232" t="s">
         <v>312</v>
       </c>
-      <c r="F1" s="243"/>
-      <c r="G1" s="243"/>
-      <c r="H1" s="243"/>
-      <c r="I1" s="243"/>
-      <c r="J1" s="243"/>
-      <c r="K1" s="243"/>
-      <c r="L1" s="243"/>
-      <c r="M1" s="243"/>
-      <c r="N1" s="243"/>
-      <c r="O1" s="243"/>
-      <c r="P1" s="243"/>
-      <c r="Q1" s="243"/>
-      <c r="R1" s="243"/>
-      <c r="S1" s="243"/>
-      <c r="T1" s="244"/>
-      <c r="U1" s="247" t="s">
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="233"/>
+      <c r="J1" s="233"/>
+      <c r="K1" s="233"/>
+      <c r="L1" s="233"/>
+      <c r="M1" s="233"/>
+      <c r="N1" s="233"/>
+      <c r="O1" s="233"/>
+      <c r="P1" s="233"/>
+      <c r="Q1" s="233"/>
+      <c r="R1" s="233"/>
+      <c r="S1" s="233"/>
+      <c r="T1" s="234"/>
+      <c r="U1" s="249" t="s">
         <v>291</v>
       </c>
-      <c r="V1" s="247"/>
-      <c r="W1" s="247"/>
-      <c r="X1" s="247"/>
-      <c r="Y1" s="242" t="s">
+      <c r="V1" s="249"/>
+      <c r="W1" s="249"/>
+      <c r="X1" s="249"/>
+      <c r="Y1" s="232" t="s">
         <v>292</v>
       </c>
-      <c r="Z1" s="243"/>
-      <c r="AA1" s="243"/>
-      <c r="AB1" s="244"/>
-      <c r="AC1" s="245" t="s">
+      <c r="Z1" s="233"/>
+      <c r="AA1" s="233"/>
+      <c r="AB1" s="234"/>
+      <c r="AC1" s="247" t="s">
         <v>293</v>
       </c>
-      <c r="AD1" s="245"/>
-      <c r="AE1" s="245"/>
-      <c r="AF1" s="246"/>
-      <c r="AG1" s="240" t="s">
+      <c r="AD1" s="247"/>
+      <c r="AE1" s="247"/>
+      <c r="AF1" s="248"/>
+      <c r="AG1" s="245" t="s">
         <v>89</v>
       </c>
-      <c r="AH1" s="241"/>
+      <c r="AH1" s="246"/>
     </row>
     <row r="2" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="228"/>
-      <c r="D2" s="228"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="249"/>
-      <c r="I2" s="232"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="234"/>
-      <c r="M2" s="232"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="232"/>
-      <c r="P2" s="234"/>
-      <c r="Q2" s="232"/>
-      <c r="R2" s="234"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="234"/>
-      <c r="U2" s="229"/>
-      <c r="V2" s="230"/>
-      <c r="W2" s="230"/>
-      <c r="X2" s="231"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="233"/>
-      <c r="AA2" s="233"/>
-      <c r="AB2" s="234"/>
-      <c r="AC2" s="235"/>
-      <c r="AD2" s="236"/>
-      <c r="AE2" s="236"/>
-      <c r="AF2" s="237"/>
-      <c r="AG2" s="238"/>
-      <c r="AH2" s="239"/>
+      <c r="C2" s="210"/>
+      <c r="D2" s="210"/>
+      <c r="E2" s="229"/>
+      <c r="F2" s="230"/>
+      <c r="G2" s="235"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="229"/>
+      <c r="J2" s="230"/>
+      <c r="K2" s="229"/>
+      <c r="L2" s="230"/>
+      <c r="M2" s="229"/>
+      <c r="N2" s="231"/>
+      <c r="O2" s="229"/>
+      <c r="P2" s="230"/>
+      <c r="Q2" s="229"/>
+      <c r="R2" s="230"/>
+      <c r="S2" s="229"/>
+      <c r="T2" s="230"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="238"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="239"/>
+      <c r="Y2" s="229"/>
+      <c r="Z2" s="231"/>
+      <c r="AA2" s="231"/>
+      <c r="AB2" s="230"/>
+      <c r="AC2" s="240"/>
+      <c r="AD2" s="241"/>
+      <c r="AE2" s="241"/>
+      <c r="AF2" s="242"/>
+      <c r="AG2" s="243"/>
+      <c r="AH2" s="244"/>
     </row>
     <row r="3" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -40954,17 +40954,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="E1:T1"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
     <mergeCell ref="U2:X2"/>
     <mergeCell ref="Y2:AB2"/>
     <mergeCell ref="AC2:AF2"/>
@@ -40973,6 +40962,17 @@
     <mergeCell ref="Y1:AB1"/>
     <mergeCell ref="AC1:AF1"/>
     <mergeCell ref="U1:X1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="E1:T1"/>
+    <mergeCell ref="Q2:R2"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AH31">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -41005,10 +41005,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="227" t="s">
+      <c r="C1" s="209" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="227" t="s">
+      <c r="D1" s="209" t="s">
         <v>99</v>
       </c>
       <c r="E1" s="264" t="s">
@@ -41039,8 +41039,8 @@
     <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="228"/>
-      <c r="D2" s="228"/>
+      <c r="C2" s="210"/>
+      <c r="D2" s="210"/>
       <c r="E2" s="256"/>
       <c r="F2" s="257"/>
       <c r="G2" s="258"/>
@@ -41049,8 +41049,8 @@
       <c r="J2" s="261"/>
       <c r="K2" s="262"/>
       <c r="L2" s="263"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
+      <c r="M2" s="231"/>
+      <c r="N2" s="231"/>
       <c r="O2" s="252"/>
       <c r="P2" s="253"/>
     </row>
@@ -47406,52 +47406,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="227" t="s">
+      <c r="C1" s="209" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="227" t="s">
+      <c r="D1" s="209" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="279" t="s">
+      <c r="E1" s="273" t="s">
         <v>91</v>
       </c>
-      <c r="F1" s="280"/>
-      <c r="G1" s="281" t="s">
+      <c r="F1" s="274"/>
+      <c r="G1" s="275" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="282"/>
-      <c r="I1" s="283" t="s">
+      <c r="H1" s="276"/>
+      <c r="I1" s="277" t="s">
         <v>207</v>
       </c>
-      <c r="J1" s="284"/>
-      <c r="K1" s="287" t="s">
+      <c r="J1" s="278"/>
+      <c r="K1" s="281" t="s">
         <v>208</v>
       </c>
-      <c r="L1" s="288"/>
-      <c r="M1" s="288"/>
-      <c r="N1" s="289"/>
-      <c r="O1" s="285" t="s">
+      <c r="L1" s="282"/>
+      <c r="M1" s="282"/>
+      <c r="N1" s="283"/>
+      <c r="O1" s="279" t="s">
         <v>316</v>
       </c>
-      <c r="P1" s="286"/>
+      <c r="P1" s="280"/>
     </row>
     <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="228"/>
-      <c r="D2" s="228"/>
-      <c r="E2" s="270"/>
-      <c r="F2" s="271"/>
-      <c r="G2" s="272"/>
-      <c r="H2" s="273"/>
-      <c r="I2" s="274"/>
-      <c r="J2" s="275"/>
-      <c r="K2" s="276"/>
-      <c r="L2" s="277"/>
-      <c r="M2" s="276"/>
-      <c r="N2" s="277"/>
-      <c r="O2" s="276"/>
-      <c r="P2" s="278"/>
+      <c r="C2" s="210"/>
+      <c r="D2" s="210"/>
+      <c r="E2" s="284"/>
+      <c r="F2" s="285"/>
+      <c r="G2" s="286"/>
+      <c r="H2" s="287"/>
+      <c r="I2" s="288"/>
+      <c r="J2" s="289"/>
+      <c r="K2" s="270"/>
+      <c r="L2" s="271"/>
+      <c r="M2" s="270"/>
+      <c r="N2" s="271"/>
+      <c r="O2" s="270"/>
+      <c r="P2" s="272"/>
     </row>
     <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -48587,6 +48587,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="E1:F1"/>
@@ -48595,11 +48600,6 @@
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="K1:N1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:P35">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -49083,51 +49083,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="298" t="s">
+      <c r="C1" s="293" t="s">
         <v>210</v>
       </c>
-      <c r="D1" s="299"/>
-      <c r="E1" s="299"/>
-      <c r="F1" s="299"/>
-      <c r="G1" s="299"/>
-      <c r="H1" s="299"/>
-      <c r="I1" s="300"/>
+      <c r="D1" s="294"/>
+      <c r="E1" s="294"/>
+      <c r="F1" s="294"/>
+      <c r="G1" s="294"/>
+      <c r="H1" s="294"/>
+      <c r="I1" s="295"/>
       <c r="J1" s="135" t="s">
         <v>203</v>
       </c>
       <c r="K1" s="136" t="s">
         <v>202</v>
       </c>
-      <c r="L1" s="292" t="s">
+      <c r="L1" s="326" t="s">
         <v>297</v>
       </c>
-      <c r="M1" s="296"/>
-      <c r="N1" s="296"/>
-      <c r="O1" s="296"/>
-      <c r="P1" s="296"/>
-      <c r="Q1" s="296"/>
-      <c r="R1" s="296"/>
-      <c r="S1" s="296"/>
-      <c r="T1" s="296"/>
-      <c r="U1" s="296"/>
-      <c r="V1" s="296"/>
-      <c r="W1" s="296"/>
-      <c r="X1" s="296"/>
-      <c r="Y1" s="296"/>
-      <c r="Z1" s="296"/>
-      <c r="AA1" s="296"/>
-      <c r="AB1" s="296"/>
-      <c r="AC1" s="296"/>
-      <c r="AD1" s="296"/>
-      <c r="AE1" s="296"/>
-      <c r="AF1" s="296"/>
-      <c r="AG1" s="297"/>
-      <c r="AH1" s="292" t="s">
+      <c r="M1" s="329"/>
+      <c r="N1" s="329"/>
+      <c r="O1" s="329"/>
+      <c r="P1" s="329"/>
+      <c r="Q1" s="329"/>
+      <c r="R1" s="329"/>
+      <c r="S1" s="329"/>
+      <c r="T1" s="329"/>
+      <c r="U1" s="329"/>
+      <c r="V1" s="329"/>
+      <c r="W1" s="329"/>
+      <c r="X1" s="329"/>
+      <c r="Y1" s="329"/>
+      <c r="Z1" s="329"/>
+      <c r="AA1" s="329"/>
+      <c r="AB1" s="329"/>
+      <c r="AC1" s="329"/>
+      <c r="AD1" s="329"/>
+      <c r="AE1" s="329"/>
+      <c r="AF1" s="329"/>
+      <c r="AG1" s="330"/>
+      <c r="AH1" s="326" t="s">
         <v>183</v>
       </c>
-      <c r="AI1" s="293"/>
-      <c r="AJ1" s="293"/>
-      <c r="AK1" s="294"/>
+      <c r="AI1" s="327"/>
+      <c r="AJ1" s="327"/>
+      <c r="AK1" s="328"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="132"/>
@@ -54315,15 +54315,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="322" t="s">
+      <c r="K80" s="317" t="s">
         <v>183</v>
       </c>
-      <c r="L80" s="323"/>
-      <c r="M80" s="324"/>
+      <c r="L80" s="318"/>
+      <c r="M80" s="319"/>
       <c r="O80" s="157"/>
       <c r="P80" s="157"/>
-      <c r="W80" s="295"/>
-      <c r="X80" s="295"/>
+      <c r="W80" s="292"/>
+      <c r="X80" s="292"/>
       <c r="Y80" s="89" t="s">
         <v>220</v>
       </c>
@@ -54373,15 +54373,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="325"/>
-      <c r="L81" s="326"/>
-      <c r="M81" s="327"/>
+      <c r="K81" s="320"/>
+      <c r="L81" s="321"/>
+      <c r="M81" s="322"/>
       <c r="O81" s="157"/>
       <c r="P81" s="157"/>
-      <c r="W81" s="295" t="s">
+      <c r="W81" s="292" t="s">
         <v>217</v>
       </c>
-      <c r="X81" s="295"/>
+      <c r="X81" s="292"/>
       <c r="Y81" s="89">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -54437,15 +54437,15 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="325"/>
-      <c r="L82" s="326"/>
-      <c r="M82" s="327"/>
+      <c r="K82" s="320"/>
+      <c r="L82" s="321"/>
+      <c r="M82" s="322"/>
       <c r="O82" s="157"/>
       <c r="P82" s="157"/>
-      <c r="W82" s="295" t="s">
+      <c r="W82" s="292" t="s">
         <v>218</v>
       </c>
-      <c r="X82" s="295"/>
+      <c r="X82" s="292"/>
       <c r="Y82" s="89">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -54501,15 +54501,15 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="328"/>
-      <c r="L83" s="329"/>
-      <c r="M83" s="330"/>
+      <c r="K83" s="323"/>
+      <c r="L83" s="324"/>
+      <c r="M83" s="325"/>
       <c r="O83" s="157"/>
       <c r="P83" s="157"/>
-      <c r="W83" s="295" t="s">
+      <c r="W83" s="292" t="s">
         <v>219</v>
       </c>
-      <c r="X83" s="295"/>
+      <c r="X83" s="292"/>
       <c r="Y83" s="89">
         <f>COUNTIF(J16:J20,3)</f>
         <v>1</v>
@@ -54565,17 +54565,17 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="313" t="s">
+      <c r="K84" s="308" t="s">
         <v>294</v>
       </c>
-      <c r="L84" s="314"/>
-      <c r="M84" s="315"/>
+      <c r="L84" s="309"/>
+      <c r="M84" s="310"/>
       <c r="O84" s="165"/>
       <c r="P84" s="165"/>
-      <c r="W84" s="295" t="s">
+      <c r="W84" s="292" t="s">
         <v>103</v>
       </c>
-      <c r="X84" s="295"/>
+      <c r="X84" s="292"/>
       <c r="Y84" s="89">
         <f>COUNTIF(J21:J40,3)+COUNTIF(I3:I40,3)+COUNTIF(H3:H40,3)+COUNTIF(G3:G40,3)+COUNTIF(F3:F40,3)+COUNTIF(E3:E40,3)</f>
         <v>123</v>
@@ -54631,9 +54631,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="316"/>
-      <c r="L85" s="317"/>
-      <c r="M85" s="318"/>
+      <c r="K85" s="311"/>
+      <c r="L85" s="312"/>
+      <c r="M85" s="313"/>
       <c r="O85" s="165"/>
       <c r="P85" s="165"/>
     </row>
@@ -54667,9 +54667,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="316"/>
-      <c r="L86" s="317"/>
-      <c r="M86" s="318"/>
+      <c r="K86" s="311"/>
+      <c r="L86" s="312"/>
+      <c r="M86" s="313"/>
       <c r="O86" s="165"/>
       <c r="P86" s="165"/>
     </row>
@@ -54703,9 +54703,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="316"/>
-      <c r="L87" s="317"/>
-      <c r="M87" s="318"/>
+      <c r="K87" s="311"/>
+      <c r="L87" s="312"/>
+      <c r="M87" s="313"/>
       <c r="O87" s="165"/>
       <c r="P87" s="165"/>
     </row>
@@ -54739,9 +54739,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="316"/>
-      <c r="L88" s="317"/>
-      <c r="M88" s="318"/>
+      <c r="K88" s="311"/>
+      <c r="L88" s="312"/>
+      <c r="M88" s="313"/>
       <c r="O88" s="165"/>
       <c r="P88" s="165"/>
     </row>
@@ -54775,9 +54775,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="316"/>
-      <c r="L89" s="317"/>
-      <c r="M89" s="318"/>
+      <c r="K89" s="311"/>
+      <c r="L89" s="312"/>
+      <c r="M89" s="313"/>
       <c r="O89" s="165"/>
       <c r="P89" s="165"/>
     </row>
@@ -54811,9 +54811,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="316"/>
-      <c r="L90" s="317"/>
-      <c r="M90" s="318"/>
+      <c r="K90" s="311"/>
+      <c r="L90" s="312"/>
+      <c r="M90" s="313"/>
       <c r="O90" s="165"/>
       <c r="P90" s="165"/>
     </row>
@@ -54847,9 +54847,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="316"/>
-      <c r="L91" s="317"/>
-      <c r="M91" s="318"/>
+      <c r="K91" s="311"/>
+      <c r="L91" s="312"/>
+      <c r="M91" s="313"/>
       <c r="O91" s="165"/>
       <c r="P91" s="165"/>
     </row>
@@ -54883,9 +54883,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="316"/>
-      <c r="L92" s="317"/>
-      <c r="M92" s="318"/>
+      <c r="K92" s="311"/>
+      <c r="L92" s="312"/>
+      <c r="M92" s="313"/>
       <c r="O92" s="165"/>
       <c r="P92" s="165"/>
     </row>
@@ -54919,9 +54919,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="316"/>
-      <c r="L93" s="317"/>
-      <c r="M93" s="318"/>
+      <c r="K93" s="311"/>
+      <c r="L93" s="312"/>
+      <c r="M93" s="313"/>
       <c r="O93" s="165"/>
       <c r="P93" s="165"/>
     </row>
@@ -54955,9 +54955,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="316"/>
-      <c r="L94" s="317"/>
-      <c r="M94" s="318"/>
+      <c r="K94" s="311"/>
+      <c r="L94" s="312"/>
+      <c r="M94" s="313"/>
       <c r="O94" s="165"/>
       <c r="P94" s="165"/>
     </row>
@@ -54991,9 +54991,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="316"/>
-      <c r="L95" s="317"/>
-      <c r="M95" s="318"/>
+      <c r="K95" s="311"/>
+      <c r="L95" s="312"/>
+      <c r="M95" s="313"/>
       <c r="O95" s="165"/>
       <c r="P95" s="165"/>
     </row>
@@ -55027,9 +55027,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="316"/>
-      <c r="L96" s="317"/>
-      <c r="M96" s="318"/>
+      <c r="K96" s="311"/>
+      <c r="L96" s="312"/>
+      <c r="M96" s="313"/>
       <c r="O96" s="165"/>
       <c r="P96" s="165"/>
     </row>
@@ -55063,9 +55063,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="316"/>
-      <c r="L97" s="317"/>
-      <c r="M97" s="318"/>
+      <c r="K97" s="311"/>
+      <c r="L97" s="312"/>
+      <c r="M97" s="313"/>
       <c r="O97" s="165"/>
       <c r="P97" s="165"/>
     </row>
@@ -55099,9 +55099,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="316"/>
-      <c r="L98" s="317"/>
-      <c r="M98" s="318"/>
+      <c r="K98" s="311"/>
+      <c r="L98" s="312"/>
+      <c r="M98" s="313"/>
       <c r="O98" s="165"/>
       <c r="P98" s="165"/>
     </row>
@@ -55135,9 +55135,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="316"/>
-      <c r="L99" s="317"/>
-      <c r="M99" s="318"/>
+      <c r="K99" s="311"/>
+      <c r="L99" s="312"/>
+      <c r="M99" s="313"/>
       <c r="O99" s="165"/>
       <c r="P99" s="165"/>
     </row>
@@ -55171,9 +55171,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="316"/>
-      <c r="L100" s="317"/>
-      <c r="M100" s="318"/>
+      <c r="K100" s="311"/>
+      <c r="L100" s="312"/>
+      <c r="M100" s="313"/>
       <c r="O100" s="165"/>
       <c r="P100" s="165"/>
     </row>
@@ -55207,9 +55207,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="316"/>
-      <c r="L101" s="317"/>
-      <c r="M101" s="318"/>
+      <c r="K101" s="311"/>
+      <c r="L101" s="312"/>
+      <c r="M101" s="313"/>
       <c r="O101" s="165"/>
       <c r="P101" s="165"/>
     </row>
@@ -55243,9 +55243,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="316"/>
-      <c r="L102" s="317"/>
-      <c r="M102" s="318"/>
+      <c r="K102" s="311"/>
+      <c r="L102" s="312"/>
+      <c r="M102" s="313"/>
       <c r="O102" s="165"/>
       <c r="P102" s="165"/>
     </row>
@@ -55279,9 +55279,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="316"/>
-      <c r="L103" s="317"/>
-      <c r="M103" s="318"/>
+      <c r="K103" s="311"/>
+      <c r="L103" s="312"/>
+      <c r="M103" s="313"/>
       <c r="O103" s="165"/>
       <c r="P103" s="165"/>
     </row>
@@ -55315,9 +55315,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="316"/>
-      <c r="L104" s="317"/>
-      <c r="M104" s="318"/>
+      <c r="K104" s="311"/>
+      <c r="L104" s="312"/>
+      <c r="M104" s="313"/>
       <c r="O104" s="165"/>
       <c r="P104" s="165"/>
     </row>
@@ -55351,9 +55351,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="319"/>
-      <c r="L105" s="320"/>
-      <c r="M105" s="321"/>
+      <c r="K105" s="314"/>
+      <c r="L105" s="315"/>
+      <c r="M105" s="316"/>
       <c r="O105" s="165"/>
       <c r="P105" s="165"/>
     </row>
@@ -55387,11 +55387,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="310" t="s">
+      <c r="K106" s="305" t="s">
         <v>296</v>
       </c>
-      <c r="L106" s="311"/>
-      <c r="M106" s="312"/>
+      <c r="L106" s="306"/>
+      <c r="M106" s="307"/>
       <c r="O106" s="150"/>
       <c r="P106" s="150"/>
     </row>
@@ -55425,11 +55425,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="310" t="s">
+      <c r="K107" s="305" t="s">
         <v>298</v>
       </c>
-      <c r="L107" s="311"/>
-      <c r="M107" s="312"/>
+      <c r="L107" s="306"/>
+      <c r="M107" s="307"/>
       <c r="O107" s="150"/>
       <c r="P107" s="150"/>
     </row>
@@ -55463,11 +55463,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="301" t="s">
+      <c r="K108" s="296" t="s">
         <v>299</v>
       </c>
-      <c r="L108" s="302"/>
-      <c r="M108" s="303"/>
+      <c r="L108" s="297"/>
+      <c r="M108" s="298"/>
       <c r="O108" s="150"/>
       <c r="P108" s="150"/>
     </row>
@@ -55501,9 +55501,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="304"/>
-      <c r="L109" s="305"/>
-      <c r="M109" s="306"/>
+      <c r="K109" s="299"/>
+      <c r="L109" s="300"/>
+      <c r="M109" s="301"/>
       <c r="O109" s="150"/>
       <c r="P109" s="150"/>
     </row>
@@ -55537,9 +55537,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="304"/>
-      <c r="L110" s="305"/>
-      <c r="M110" s="306"/>
+      <c r="K110" s="299"/>
+      <c r="L110" s="300"/>
+      <c r="M110" s="301"/>
       <c r="O110" s="150"/>
       <c r="P110" s="150"/>
     </row>
@@ -55573,9 +55573,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="304"/>
-      <c r="L111" s="305"/>
-      <c r="M111" s="306"/>
+      <c r="K111" s="299"/>
+      <c r="L111" s="300"/>
+      <c r="M111" s="301"/>
       <c r="O111" s="150"/>
       <c r="P111" s="150"/>
     </row>
@@ -55613,9 +55613,9 @@
         <f t="shared" ref="J112:J113" si="7">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="304"/>
-      <c r="L112" s="305"/>
-      <c r="M112" s="306"/>
+      <c r="K112" s="299"/>
+      <c r="L112" s="300"/>
+      <c r="M112" s="301"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="199" t="s">
@@ -55651,13 +55651,19 @@
         <f t="shared" si="7"/>
         <v>43</v>
       </c>
-      <c r="K113" s="307"/>
-      <c r="L113" s="308"/>
-      <c r="M113" s="309"/>
+      <c r="K113" s="302"/>
+      <c r="L113" s="303"/>
+      <c r="M113" s="304"/>
     </row>
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="13">
+    <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="W80:X80"/>
+    <mergeCell ref="W81:X81"/>
+    <mergeCell ref="W82:X82"/>
+    <mergeCell ref="W83:X83"/>
+    <mergeCell ref="L1:AG1"/>
     <mergeCell ref="W84:X84"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="K108:M113"/>
@@ -55665,12 +55671,6 @@
     <mergeCell ref="K107:M107"/>
     <mergeCell ref="K84:M105"/>
     <mergeCell ref="K80:M83"/>
-    <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="W80:X80"/>
-    <mergeCell ref="W81:X81"/>
-    <mergeCell ref="W82:X82"/>
-    <mergeCell ref="W83:X83"/>
-    <mergeCell ref="L1:AG1"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7715" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE6B2971-2449-4A6E-BE1C-0A3439BD0E12}"/>
+  <xr:revisionPtr revIDLastSave="7722" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3813520-7DA5-4319-A885-569B2CDDD4A9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="19" state="hidden" r:id="rId1"/>
@@ -1320,13 +1320,13 @@
     <t>Manchester City</t>
   </si>
   <si>
-    <t>Wembley</t>
-  </si>
-  <si>
     <t>Millennium Stadium, Cardiff</t>
   </si>
   <si>
     <t>16.08.2026</t>
+  </si>
+  <si>
+    <t>FA Community Shield</t>
   </si>
 </sst>
 </file>
@@ -2828,25 +2828,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="5" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2861,7 +2844,28 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2873,6 +2877,12 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2881,9 +2891,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2897,8 +2904,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2936,15 +2949,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2952,27 +2956,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="63" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3065,28 +3048,34 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="63" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3188,6 +3177,21 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3195,10 +3199,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -6242,7 +6242,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{16A9235F-D0C2-4FBB-96A5-DD76162DB85F}" type="CELLRANGE">
+                    <a:fld id="{35D4A830-08E2-42C4-A5FF-0AF22C225868}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6276,7 +6276,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{49F35749-2C2C-46BF-87A5-BA18A1F35CDE}" type="CELLRANGE">
+                    <a:fld id="{EC8FFC31-2590-4DE6-A811-0D586F02CECB}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6310,7 +6310,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FF5F0798-A9A2-4A79-B205-E8433EE29B39}" type="CELLRANGE">
+                    <a:fld id="{3A0E5781-5B4A-46C7-A0E9-8D09277711F8}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6344,7 +6344,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B4AB6BD4-B13F-4325-A472-9B4CAD9B5B57}" type="CELLRANGE">
+                    <a:fld id="{CD8C95C4-9794-4142-9121-0E3EE63BFF7E}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6378,7 +6378,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{882CC187-95E1-447C-98FE-371C2FE1A72B}" type="CELLRANGE">
+                    <a:fld id="{9F89D97A-5174-4596-98B3-5FC2ED78634C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6412,7 +6412,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E7F52F5C-BC55-41F5-AAB2-617A3833899B}" type="CELLRANGE">
+                    <a:fld id="{07A67460-A002-4340-A2D5-5E4705071212}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6446,7 +6446,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0C43E6BE-939F-496E-908C-43F2D5DC7257}" type="CELLRANGE">
+                    <a:fld id="{C433FD60-0B0B-472C-9CC3-1B2E9D2F8C52}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6480,7 +6480,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F48A94C1-6E0B-452D-9210-5B30F971ACA6}" type="CELLRANGE">
+                    <a:fld id="{976F9636-1390-474D-B1C2-7DE21721ED8A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6514,7 +6514,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{57175C35-1FBD-4A4C-B612-8B1500318B3E}" type="CELLRANGE">
+                    <a:fld id="{A7496799-FA23-4F28-98A2-000080799B13}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6548,7 +6548,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{22D48183-3C6E-42D9-AD82-B46CFA58BC1D}" type="CELLRANGE">
+                    <a:fld id="{6A69FC7E-E056-4E11-B1C8-0BDA17EEF392}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6582,7 +6582,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4A38CB32-FD4D-435E-BC17-285F10EA4462}" type="CELLRANGE">
+                    <a:fld id="{45B6AAED-7B94-4348-BD1A-5231512982F4}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6616,7 +6616,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BDC54DBB-E5E4-4EDE-8A6A-3784F22D8CF0}" type="CELLRANGE">
+                    <a:fld id="{A422FE11-D7EB-43A9-B956-3EA457F5DD7B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6665,7 +6665,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{C3FEDDC8-BFB2-4F2E-87CA-E848809673A1}" type="CELLRANGE">
+                    <a:fld id="{A97E36A0-081B-47A3-AB40-A748350DB0F1}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6724,7 +6724,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B1E68751-3BB0-4C26-A768-ECC3BC0DE0F8}" type="CELLRANGE">
+                    <a:fld id="{6BB962F4-1FF7-458F-AFE2-6DD5CFDC046E}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6758,7 +6758,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{53D1484E-7B33-46D9-AD00-EE7D352433DE}" type="CELLRANGE">
+                    <a:fld id="{91BD3B89-7FDF-4CD6-A9FF-F6CE576F5EF4}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6792,7 +6792,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A5E65CB5-6890-4119-9F6E-6385595ED030}" type="CELLRANGE">
+                    <a:fld id="{955D740D-6181-41F7-BC37-A91D0F5FDE02}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6826,7 +6826,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CA3764AD-56BC-4A3C-9394-FBD59BDB25C2}" type="CELLRANGE">
+                    <a:fld id="{81DEFBFF-70E9-428F-A526-7126029F5C15}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6860,7 +6860,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{633417D0-3B9B-4E51-8C01-9158219DADBD}" type="CELLRANGE">
+                    <a:fld id="{64AA83C9-8849-4C74-B850-715191A0BE0A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6894,7 +6894,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7483E185-9BCC-487D-9648-156BD77F2C66}" type="CELLRANGE">
+                    <a:fld id="{1E953346-59B6-48C6-8127-4D89A1F0D56D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6928,7 +6928,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6E4929DE-E9A7-4246-B380-48305C71E7B2}" type="CELLRANGE">
+                    <a:fld id="{AB2E9363-B1CF-4CB0-9526-08709FA9F9AB}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14109,30 +14109,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="205" t="s">
+      <c r="C1" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="205"/>
-      <c r="E1" s="206" t="s">
+      <c r="D1" s="200"/>
+      <c r="E1" s="201" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="206"/>
-      <c r="G1" s="205" t="s">
+      <c r="F1" s="201"/>
+      <c r="G1" s="200" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="205"/>
-      <c r="I1" s="206" t="s">
+      <c r="H1" s="200"/>
+      <c r="I1" s="201" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="206"/>
-      <c r="K1" s="205" t="s">
+      <c r="J1" s="201"/>
+      <c r="K1" s="200" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="205"/>
-      <c r="M1" s="203" t="s">
+      <c r="L1" s="200"/>
+      <c r="M1" s="198" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="204"/>
+      <c r="N1" s="199"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15839,30 +15839,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206" t="s">
+      <c r="D2" s="200"/>
+      <c r="E2" s="201" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="205" t="s">
+      <c r="F2" s="201"/>
+      <c r="G2" s="200" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="H2" s="200"/>
+      <c r="I2" s="201" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="205" t="s">
+      <c r="J2" s="201"/>
+      <c r="K2" s="200" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="202" t="s">
+      <c r="L2" s="200"/>
+      <c r="M2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="202"/>
+      <c r="N2" s="205"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17444,30 +17444,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206" t="s">
+      <c r="D2" s="200"/>
+      <c r="E2" s="201" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="205" t="s">
+      <c r="F2" s="201"/>
+      <c r="G2" s="200" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="H2" s="200"/>
+      <c r="I2" s="201" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="205" t="s">
+      <c r="J2" s="201"/>
+      <c r="K2" s="200" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="202" t="s">
+      <c r="L2" s="200"/>
+      <c r="M2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="202"/>
+      <c r="N2" s="205"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19271,30 +19271,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206" t="s">
+      <c r="D2" s="200"/>
+      <c r="E2" s="201" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="205" t="s">
+      <c r="F2" s="201"/>
+      <c r="G2" s="200" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="H2" s="200"/>
+      <c r="I2" s="201" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="205" t="s">
+      <c r="J2" s="201"/>
+      <c r="K2" s="200" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="202" t="s">
+      <c r="L2" s="200"/>
+      <c r="M2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="202"/>
+      <c r="N2" s="205"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -20961,30 +20961,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206" t="s">
+      <c r="D2" s="200"/>
+      <c r="E2" s="201" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="205" t="s">
+      <c r="F2" s="201"/>
+      <c r="G2" s="200" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="H2" s="200"/>
+      <c r="I2" s="201" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="205" t="s">
+      <c r="J2" s="201"/>
+      <c r="K2" s="200" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="202" t="s">
+      <c r="L2" s="200"/>
+      <c r="M2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="202"/>
+      <c r="N2" s="205"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -22787,30 +22787,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206" t="s">
+      <c r="D2" s="200"/>
+      <c r="E2" s="201" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="205" t="s">
+      <c r="F2" s="201"/>
+      <c r="G2" s="200" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="H2" s="200"/>
+      <c r="I2" s="201" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="205" t="s">
+      <c r="J2" s="201"/>
+      <c r="K2" s="200" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="202" t="s">
+      <c r="L2" s="200"/>
+      <c r="M2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="202"/>
+      <c r="N2" s="205"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -24659,36 +24659,36 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="196" t="s">
+      <c r="C2" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="197"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="199" t="s">
+      <c r="D2" s="203"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="200"/>
-      <c r="H2" s="201"/>
-      <c r="I2" s="196" t="s">
+      <c r="G2" s="208"/>
+      <c r="H2" s="209"/>
+      <c r="I2" s="202" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="197"/>
-      <c r="K2" s="198"/>
-      <c r="L2" s="199" t="s">
+      <c r="J2" s="203"/>
+      <c r="K2" s="204"/>
+      <c r="L2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="200"/>
-      <c r="N2" s="201"/>
-      <c r="O2" s="196" t="s">
+      <c r="M2" s="208"/>
+      <c r="N2" s="209"/>
+      <c r="O2" s="202" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="197"/>
-      <c r="Q2" s="198"/>
-      <c r="R2" s="202" t="s">
+      <c r="P2" s="203"/>
+      <c r="Q2" s="204"/>
+      <c r="R2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="202"/>
-      <c r="T2" s="202"/>
+      <c r="S2" s="205"/>
+      <c r="T2" s="205"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -27790,36 +27790,36 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="196" t="s">
+      <c r="E1" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="197"/>
-      <c r="G1" s="198"/>
-      <c r="H1" s="199" t="s">
+      <c r="F1" s="203"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="200"/>
-      <c r="J1" s="201"/>
-      <c r="K1" s="196" t="s">
+      <c r="I1" s="208"/>
+      <c r="J1" s="209"/>
+      <c r="K1" s="202" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="197"/>
-      <c r="M1" s="198"/>
-      <c r="N1" s="199" t="s">
+      <c r="L1" s="203"/>
+      <c r="M1" s="204"/>
+      <c r="N1" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="200"/>
-      <c r="P1" s="201"/>
-      <c r="Q1" s="196" t="s">
+      <c r="O1" s="208"/>
+      <c r="P1" s="209"/>
+      <c r="Q1" s="202" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="197"/>
-      <c r="S1" s="198"/>
-      <c r="T1" s="202" t="s">
+      <c r="R1" s="203"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="202"/>
-      <c r="V1" s="202"/>
+      <c r="U1" s="205"/>
+      <c r="V1" s="205"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -39217,399 +39217,399 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="208">
-        <v>1</v>
-      </c>
-      <c r="G1" s="209"/>
-      <c r="H1" s="210"/>
-      <c r="I1" s="208">
+      <c r="F1" s="210">
+        <v>1</v>
+      </c>
+      <c r="G1" s="211"/>
+      <c r="H1" s="212"/>
+      <c r="I1" s="210">
         <v>2</v>
       </c>
-      <c r="J1" s="209"/>
-      <c r="K1" s="210"/>
-      <c r="L1" s="208">
-        <v>3</v>
-      </c>
-      <c r="M1" s="209"/>
-      <c r="N1" s="210"/>
-      <c r="O1" s="208">
+      <c r="J1" s="211"/>
+      <c r="K1" s="212"/>
+      <c r="L1" s="210">
+        <v>3</v>
+      </c>
+      <c r="M1" s="211"/>
+      <c r="N1" s="212"/>
+      <c r="O1" s="210">
         <v>4</v>
       </c>
-      <c r="P1" s="209"/>
-      <c r="Q1" s="210"/>
-      <c r="R1" s="208">
+      <c r="P1" s="211"/>
+      <c r="Q1" s="212"/>
+      <c r="R1" s="210">
         <v>5</v>
       </c>
-      <c r="S1" s="209"/>
-      <c r="T1" s="210"/>
-      <c r="U1" s="208">
+      <c r="S1" s="211"/>
+      <c r="T1" s="212"/>
+      <c r="U1" s="210">
         <v>6</v>
       </c>
-      <c r="V1" s="209"/>
-      <c r="W1" s="210"/>
-      <c r="X1" s="208">
+      <c r="V1" s="211"/>
+      <c r="W1" s="212"/>
+      <c r="X1" s="210">
         <v>7</v>
       </c>
-      <c r="Y1" s="209"/>
-      <c r="Z1" s="210"/>
-      <c r="AA1" s="208">
+      <c r="Y1" s="211"/>
+      <c r="Z1" s="212"/>
+      <c r="AA1" s="210">
         <v>8</v>
       </c>
-      <c r="AB1" s="209"/>
-      <c r="AC1" s="210"/>
-      <c r="AD1" s="208">
+      <c r="AB1" s="211"/>
+      <c r="AC1" s="212"/>
+      <c r="AD1" s="210">
         <v>9</v>
       </c>
-      <c r="AE1" s="209"/>
-      <c r="AF1" s="210"/>
-      <c r="AG1" s="208">
+      <c r="AE1" s="211"/>
+      <c r="AF1" s="212"/>
+      <c r="AG1" s="210">
         <v>10</v>
       </c>
-      <c r="AH1" s="209"/>
-      <c r="AI1" s="210"/>
-      <c r="AJ1" s="208">
+      <c r="AH1" s="211"/>
+      <c r="AI1" s="212"/>
+      <c r="AJ1" s="210">
         <v>11</v>
       </c>
-      <c r="AK1" s="209"/>
-      <c r="AL1" s="210"/>
-      <c r="AM1" s="208">
+      <c r="AK1" s="211"/>
+      <c r="AL1" s="212"/>
+      <c r="AM1" s="210">
         <v>12</v>
       </c>
-      <c r="AN1" s="209"/>
-      <c r="AO1" s="210"/>
-      <c r="AP1" s="208">
+      <c r="AN1" s="211"/>
+      <c r="AO1" s="212"/>
+      <c r="AP1" s="210">
         <v>13</v>
       </c>
-      <c r="AQ1" s="209"/>
-      <c r="AR1" s="210"/>
-      <c r="AS1" s="208">
+      <c r="AQ1" s="211"/>
+      <c r="AR1" s="212"/>
+      <c r="AS1" s="210">
         <v>14</v>
       </c>
-      <c r="AT1" s="209"/>
-      <c r="AU1" s="210"/>
-      <c r="AV1" s="208">
+      <c r="AT1" s="211"/>
+      <c r="AU1" s="212"/>
+      <c r="AV1" s="210">
         <v>15</v>
       </c>
-      <c r="AW1" s="209"/>
-      <c r="AX1" s="210"/>
-      <c r="AY1" s="208">
+      <c r="AW1" s="211"/>
+      <c r="AX1" s="212"/>
+      <c r="AY1" s="210">
         <v>16</v>
       </c>
-      <c r="AZ1" s="209"/>
-      <c r="BA1" s="210"/>
-      <c r="BB1" s="208">
+      <c r="AZ1" s="211"/>
+      <c r="BA1" s="212"/>
+      <c r="BB1" s="210">
         <v>17</v>
       </c>
-      <c r="BC1" s="209"/>
-      <c r="BD1" s="210"/>
-      <c r="BE1" s="208">
+      <c r="BC1" s="211"/>
+      <c r="BD1" s="212"/>
+      <c r="BE1" s="210">
         <v>18</v>
       </c>
-      <c r="BF1" s="209"/>
-      <c r="BG1" s="210"/>
-      <c r="BH1" s="208">
+      <c r="BF1" s="211"/>
+      <c r="BG1" s="212"/>
+      <c r="BH1" s="210">
         <v>19</v>
       </c>
-      <c r="BI1" s="209"/>
-      <c r="BJ1" s="210"/>
-      <c r="BK1" s="208">
+      <c r="BI1" s="211"/>
+      <c r="BJ1" s="212"/>
+      <c r="BK1" s="210">
         <v>20</v>
       </c>
-      <c r="BL1" s="209"/>
-      <c r="BM1" s="210"/>
-      <c r="BN1" s="208">
+      <c r="BL1" s="211"/>
+      <c r="BM1" s="212"/>
+      <c r="BN1" s="210">
         <v>21</v>
       </c>
-      <c r="BO1" s="209"/>
-      <c r="BP1" s="210"/>
-      <c r="BQ1" s="208">
+      <c r="BO1" s="211"/>
+      <c r="BP1" s="212"/>
+      <c r="BQ1" s="210">
         <v>22</v>
       </c>
-      <c r="BR1" s="209"/>
-      <c r="BS1" s="210"/>
-      <c r="BT1" s="208">
+      <c r="BR1" s="211"/>
+      <c r="BS1" s="212"/>
+      <c r="BT1" s="210">
         <v>23</v>
       </c>
-      <c r="BU1" s="209"/>
-      <c r="BV1" s="210"/>
-      <c r="BW1" s="208">
+      <c r="BU1" s="211"/>
+      <c r="BV1" s="212"/>
+      <c r="BW1" s="210">
         <v>24</v>
       </c>
-      <c r="BX1" s="209"/>
-      <c r="BY1" s="210"/>
-      <c r="BZ1" s="208">
+      <c r="BX1" s="211"/>
+      <c r="BY1" s="212"/>
+      <c r="BZ1" s="210">
         <v>25</v>
       </c>
-      <c r="CA1" s="209"/>
-      <c r="CB1" s="210"/>
-      <c r="CC1" s="208">
+      <c r="CA1" s="211"/>
+      <c r="CB1" s="212"/>
+      <c r="CC1" s="210">
         <v>26</v>
       </c>
-      <c r="CD1" s="209"/>
-      <c r="CE1" s="210"/>
-      <c r="CF1" s="208">
+      <c r="CD1" s="211"/>
+      <c r="CE1" s="212"/>
+      <c r="CF1" s="210">
         <v>27</v>
       </c>
-      <c r="CG1" s="209"/>
-      <c r="CH1" s="210"/>
-      <c r="CI1" s="208">
+      <c r="CG1" s="211"/>
+      <c r="CH1" s="212"/>
+      <c r="CI1" s="210">
         <v>28</v>
       </c>
-      <c r="CJ1" s="209"/>
-      <c r="CK1" s="210"/>
-      <c r="CL1" s="208">
+      <c r="CJ1" s="211"/>
+      <c r="CK1" s="212"/>
+      <c r="CL1" s="210">
         <v>29</v>
       </c>
-      <c r="CM1" s="209"/>
-      <c r="CN1" s="210"/>
-      <c r="CO1" s="208">
+      <c r="CM1" s="211"/>
+      <c r="CN1" s="212"/>
+      <c r="CO1" s="210">
         <v>30</v>
       </c>
-      <c r="CP1" s="209"/>
-      <c r="CQ1" s="210"/>
-      <c r="CR1" s="208">
+      <c r="CP1" s="211"/>
+      <c r="CQ1" s="212"/>
+      <c r="CR1" s="210">
         <v>31</v>
       </c>
-      <c r="CS1" s="209"/>
-      <c r="CT1" s="210"/>
-      <c r="CU1" s="208">
+      <c r="CS1" s="211"/>
+      <c r="CT1" s="212"/>
+      <c r="CU1" s="210">
         <v>32</v>
       </c>
-      <c r="CV1" s="209"/>
-      <c r="CW1" s="210"/>
-      <c r="CX1" s="208">
+      <c r="CV1" s="211"/>
+      <c r="CW1" s="212"/>
+      <c r="CX1" s="210">
         <v>33</v>
       </c>
-      <c r="CY1" s="209"/>
-      <c r="CZ1" s="210"/>
-      <c r="DA1" s="208">
+      <c r="CY1" s="211"/>
+      <c r="CZ1" s="212"/>
+      <c r="DA1" s="210">
         <v>34</v>
       </c>
-      <c r="DB1" s="209"/>
-      <c r="DC1" s="210"/>
-      <c r="DD1" s="208">
+      <c r="DB1" s="211"/>
+      <c r="DC1" s="212"/>
+      <c r="DD1" s="210">
         <v>35</v>
       </c>
-      <c r="DE1" s="209"/>
-      <c r="DF1" s="210"/>
-      <c r="DG1" s="208">
+      <c r="DE1" s="211"/>
+      <c r="DF1" s="212"/>
+      <c r="DG1" s="210">
         <v>36</v>
       </c>
-      <c r="DH1" s="209"/>
-      <c r="DI1" s="210"/>
-      <c r="DJ1" s="208">
+      <c r="DH1" s="211"/>
+      <c r="DI1" s="212"/>
+      <c r="DJ1" s="210">
         <v>37</v>
       </c>
-      <c r="DK1" s="209"/>
-      <c r="DL1" s="210"/>
-      <c r="DM1" s="208">
+      <c r="DK1" s="211"/>
+      <c r="DL1" s="212"/>
+      <c r="DM1" s="210">
         <v>38</v>
       </c>
-      <c r="DN1" s="209"/>
-      <c r="DO1" s="210"/>
+      <c r="DN1" s="211"/>
+      <c r="DO1" s="212"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="214" t="s">
+      <c r="C2" s="213" t="s">
         <v>397</v>
       </c>
-      <c r="D2" s="214" t="s">
+      <c r="D2" s="213" t="s">
         <v>398</v>
       </c>
-      <c r="E2" s="214" t="s">
+      <c r="E2" s="213" t="s">
         <v>399</v>
       </c>
-      <c r="F2" s="211" t="s">
+      <c r="F2" s="215" t="s">
         <v>347</v>
       </c>
-      <c r="G2" s="212"/>
-      <c r="H2" s="213"/>
-      <c r="I2" s="216" t="s">
+      <c r="G2" s="216"/>
+      <c r="H2" s="217"/>
+      <c r="I2" s="219" t="s">
         <v>332</v>
       </c>
-      <c r="J2" s="217"/>
-      <c r="K2" s="218"/>
-      <c r="L2" s="211" t="s">
+      <c r="J2" s="220"/>
+      <c r="K2" s="221"/>
+      <c r="L2" s="215" t="s">
         <v>331</v>
       </c>
-      <c r="M2" s="212"/>
-      <c r="N2" s="213"/>
-      <c r="O2" s="211" t="s">
+      <c r="M2" s="216"/>
+      <c r="N2" s="217"/>
+      <c r="O2" s="215" t="s">
         <v>329</v>
       </c>
-      <c r="P2" s="212"/>
-      <c r="Q2" s="213"/>
-      <c r="R2" s="211" t="s">
+      <c r="P2" s="216"/>
+      <c r="Q2" s="217"/>
+      <c r="R2" s="215" t="s">
         <v>336</v>
       </c>
-      <c r="S2" s="212"/>
-      <c r="T2" s="213"/>
-      <c r="U2" s="211" t="s">
+      <c r="S2" s="216"/>
+      <c r="T2" s="217"/>
+      <c r="U2" s="215" t="s">
         <v>321</v>
       </c>
-      <c r="V2" s="212"/>
-      <c r="W2" s="213"/>
-      <c r="X2" s="211" t="s">
+      <c r="V2" s="216"/>
+      <c r="W2" s="217"/>
+      <c r="X2" s="215" t="s">
         <v>338</v>
       </c>
-      <c r="Y2" s="212"/>
-      <c r="Z2" s="213"/>
-      <c r="AA2" s="211" t="s">
+      <c r="Y2" s="216"/>
+      <c r="Z2" s="217"/>
+      <c r="AA2" s="215" t="s">
         <v>335</v>
       </c>
-      <c r="AB2" s="212"/>
-      <c r="AC2" s="213"/>
-      <c r="AD2" s="211" t="s">
+      <c r="AB2" s="216"/>
+      <c r="AC2" s="217"/>
+      <c r="AD2" s="215" t="s">
         <v>322</v>
       </c>
-      <c r="AE2" s="212"/>
-      <c r="AF2" s="213"/>
-      <c r="AG2" s="211" t="s">
+      <c r="AE2" s="216"/>
+      <c r="AF2" s="217"/>
+      <c r="AG2" s="215" t="s">
         <v>348</v>
       </c>
-      <c r="AH2" s="212"/>
-      <c r="AI2" s="213"/>
-      <c r="AJ2" s="211" t="s">
+      <c r="AH2" s="216"/>
+      <c r="AI2" s="217"/>
+      <c r="AJ2" s="215" t="s">
         <v>325</v>
       </c>
-      <c r="AK2" s="212"/>
-      <c r="AL2" s="213"/>
-      <c r="AM2" s="211" t="s">
+      <c r="AK2" s="216"/>
+      <c r="AL2" s="217"/>
+      <c r="AM2" s="215" t="s">
         <v>324</v>
       </c>
-      <c r="AN2" s="212"/>
-      <c r="AO2" s="213"/>
-      <c r="AP2" s="211" t="s">
+      <c r="AN2" s="216"/>
+      <c r="AO2" s="217"/>
+      <c r="AP2" s="215" t="s">
         <v>333</v>
       </c>
-      <c r="AQ2" s="212"/>
-      <c r="AR2" s="213"/>
-      <c r="AS2" s="211" t="s">
+      <c r="AQ2" s="216"/>
+      <c r="AR2" s="217"/>
+      <c r="AS2" s="215" t="s">
         <v>330</v>
       </c>
-      <c r="AT2" s="212"/>
-      <c r="AU2" s="213"/>
-      <c r="AV2" s="211" t="s">
+      <c r="AT2" s="216"/>
+      <c r="AU2" s="217"/>
+      <c r="AV2" s="215" t="s">
         <v>337</v>
       </c>
-      <c r="AW2" s="212"/>
-      <c r="AX2" s="213"/>
-      <c r="AY2" s="211" t="s">
+      <c r="AW2" s="216"/>
+      <c r="AX2" s="217"/>
+      <c r="AY2" s="215" t="s">
         <v>306</v>
       </c>
-      <c r="AZ2" s="212"/>
-      <c r="BA2" s="213"/>
-      <c r="BB2" s="211" t="s">
+      <c r="AZ2" s="216"/>
+      <c r="BA2" s="217"/>
+      <c r="BB2" s="215" t="s">
         <v>327</v>
       </c>
-      <c r="BC2" s="212"/>
-      <c r="BD2" s="213"/>
-      <c r="BE2" s="211" t="s">
+      <c r="BC2" s="216"/>
+      <c r="BD2" s="217"/>
+      <c r="BE2" s="215" t="s">
         <v>326</v>
       </c>
-      <c r="BF2" s="212"/>
-      <c r="BG2" s="213"/>
-      <c r="BH2" s="211" t="s">
+      <c r="BF2" s="216"/>
+      <c r="BG2" s="217"/>
+      <c r="BH2" s="215" t="s">
         <v>349</v>
       </c>
-      <c r="BI2" s="212"/>
-      <c r="BJ2" s="213"/>
-      <c r="BK2" s="211" t="s">
+      <c r="BI2" s="216"/>
+      <c r="BJ2" s="217"/>
+      <c r="BK2" s="215" t="s">
         <v>333</v>
       </c>
-      <c r="BL2" s="212"/>
-      <c r="BM2" s="213"/>
-      <c r="BN2" s="211" t="s">
+      <c r="BL2" s="216"/>
+      <c r="BM2" s="217"/>
+      <c r="BN2" s="215" t="s">
         <v>348</v>
       </c>
-      <c r="BO2" s="212"/>
-      <c r="BP2" s="213"/>
-      <c r="BQ2" s="211" t="s">
+      <c r="BO2" s="216"/>
+      <c r="BP2" s="217"/>
+      <c r="BQ2" s="215" t="s">
         <v>325</v>
       </c>
-      <c r="BR2" s="212"/>
-      <c r="BS2" s="213"/>
-      <c r="BT2" s="211" t="s">
+      <c r="BR2" s="216"/>
+      <c r="BS2" s="217"/>
+      <c r="BT2" s="215" t="s">
         <v>324</v>
       </c>
-      <c r="BU2" s="212"/>
-      <c r="BV2" s="213"/>
-      <c r="BW2" s="211" t="s">
+      <c r="BU2" s="216"/>
+      <c r="BV2" s="217"/>
+      <c r="BW2" s="215" t="s">
         <v>322</v>
       </c>
-      <c r="BX2" s="212"/>
-      <c r="BY2" s="213"/>
-      <c r="BZ2" s="211" t="s">
+      <c r="BX2" s="216"/>
+      <c r="BY2" s="217"/>
+      <c r="BZ2" s="215" t="s">
         <v>349</v>
       </c>
-      <c r="CA2" s="212"/>
-      <c r="CB2" s="213"/>
-      <c r="CC2" s="211" t="s">
+      <c r="CA2" s="216"/>
+      <c r="CB2" s="217"/>
+      <c r="CC2" s="215" t="s">
         <v>326</v>
       </c>
-      <c r="CD2" s="212"/>
-      <c r="CE2" s="213"/>
-      <c r="CF2" s="211" t="s">
+      <c r="CD2" s="216"/>
+      <c r="CE2" s="217"/>
+      <c r="CF2" s="215" t="s">
         <v>306</v>
       </c>
-      <c r="CG2" s="212"/>
-      <c r="CH2" s="213"/>
-      <c r="CI2" s="211" t="s">
+      <c r="CG2" s="216"/>
+      <c r="CH2" s="217"/>
+      <c r="CI2" s="215" t="s">
         <v>327</v>
       </c>
-      <c r="CJ2" s="212"/>
-      <c r="CK2" s="213"/>
-      <c r="CL2" s="211" t="s">
+      <c r="CJ2" s="216"/>
+      <c r="CK2" s="217"/>
+      <c r="CL2" s="215" t="s">
         <v>331</v>
       </c>
-      <c r="CM2" s="212"/>
-      <c r="CN2" s="213"/>
-      <c r="CO2" s="211" t="s">
+      <c r="CM2" s="216"/>
+      <c r="CN2" s="217"/>
+      <c r="CO2" s="215" t="s">
         <v>329</v>
       </c>
-      <c r="CP2" s="212"/>
-      <c r="CQ2" s="213"/>
-      <c r="CR2" s="211" t="s">
+      <c r="CP2" s="216"/>
+      <c r="CQ2" s="217"/>
+      <c r="CR2" s="215" t="s">
         <v>347</v>
       </c>
-      <c r="CS2" s="212"/>
-      <c r="CT2" s="213"/>
-      <c r="CU2" s="211" t="s">
+      <c r="CS2" s="216"/>
+      <c r="CT2" s="217"/>
+      <c r="CU2" s="215" t="s">
         <v>332</v>
       </c>
-      <c r="CV2" s="212"/>
-      <c r="CW2" s="213"/>
-      <c r="CX2" s="211" t="s">
+      <c r="CV2" s="216"/>
+      <c r="CW2" s="217"/>
+      <c r="CX2" s="215" t="s">
         <v>337</v>
       </c>
-      <c r="CY2" s="212"/>
-      <c r="CZ2" s="213"/>
-      <c r="DA2" s="211" t="s">
+      <c r="CY2" s="216"/>
+      <c r="CZ2" s="217"/>
+      <c r="DA2" s="215" t="s">
         <v>330</v>
       </c>
-      <c r="DB2" s="212"/>
-      <c r="DC2" s="213"/>
-      <c r="DD2" s="211" t="s">
+      <c r="DB2" s="216"/>
+      <c r="DC2" s="217"/>
+      <c r="DD2" s="215" t="s">
         <v>321</v>
       </c>
-      <c r="DE2" s="212"/>
-      <c r="DF2" s="213"/>
-      <c r="DG2" s="211" t="s">
+      <c r="DE2" s="216"/>
+      <c r="DF2" s="217"/>
+      <c r="DG2" s="215" t="s">
         <v>338</v>
       </c>
-      <c r="DH2" s="212"/>
-      <c r="DI2" s="213"/>
-      <c r="DJ2" s="211" t="s">
+      <c r="DH2" s="216"/>
+      <c r="DI2" s="217"/>
+      <c r="DJ2" s="215" t="s">
         <v>335</v>
       </c>
-      <c r="DK2" s="212"/>
-      <c r="DL2" s="213"/>
-      <c r="DM2" s="211" t="s">
+      <c r="DK2" s="216"/>
+      <c r="DL2" s="217"/>
+      <c r="DM2" s="215" t="s">
         <v>336</v>
       </c>
-      <c r="DN2" s="212"/>
-      <c r="DO2" s="213"/>
+      <c r="DN2" s="216"/>
+      <c r="DO2" s="217"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -39618,9 +39618,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="219"/>
-      <c r="D3" s="219"/>
-      <c r="E3" s="215"/>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="218"/>
       <c r="F3" s="160" t="s">
         <v>394</v>
       </c>
@@ -45387,6 +45387,69 @@
     </row>
   </sheetData>
   <mergeCells count="79">
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
     <mergeCell ref="BE1:BG1"/>
     <mergeCell ref="C2:C3"/>
@@ -45403,69 +45466,6 @@
     <mergeCell ref="X1:Z1"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO40">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -45501,122 +45501,122 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="229" t="s">
+      <c r="C1" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="D1" s="229" t="s">
+      <c r="D1" s="234" t="s">
         <v>398</v>
       </c>
-      <c r="E1" s="229" t="s">
+      <c r="E1" s="234" t="s">
         <v>399</v>
       </c>
-      <c r="F1" s="220" t="s">
+      <c r="F1" s="225" t="s">
         <v>303</v>
       </c>
-      <c r="G1" s="221"/>
-      <c r="H1" s="221"/>
-      <c r="I1" s="221"/>
-      <c r="J1" s="221"/>
-      <c r="K1" s="221"/>
-      <c r="L1" s="221"/>
-      <c r="M1" s="221"/>
-      <c r="N1" s="221"/>
-      <c r="O1" s="221"/>
-      <c r="P1" s="221"/>
-      <c r="Q1" s="221"/>
-      <c r="R1" s="221"/>
-      <c r="S1" s="221"/>
-      <c r="T1" s="221"/>
-      <c r="U1" s="221"/>
-      <c r="V1" s="221"/>
-      <c r="W1" s="221"/>
-      <c r="X1" s="221"/>
-      <c r="Y1" s="221"/>
-      <c r="Z1" s="221"/>
-      <c r="AA1" s="221"/>
-      <c r="AB1" s="221"/>
-      <c r="AC1" s="222"/>
-      <c r="AD1" s="235" t="s">
+      <c r="G1" s="226"/>
+      <c r="H1" s="226"/>
+      <c r="I1" s="226"/>
+      <c r="J1" s="226"/>
+      <c r="K1" s="226"/>
+      <c r="L1" s="226"/>
+      <c r="M1" s="226"/>
+      <c r="N1" s="226"/>
+      <c r="O1" s="226"/>
+      <c r="P1" s="226"/>
+      <c r="Q1" s="226"/>
+      <c r="R1" s="226"/>
+      <c r="S1" s="226"/>
+      <c r="T1" s="226"/>
+      <c r="U1" s="226"/>
+      <c r="V1" s="226"/>
+      <c r="W1" s="226"/>
+      <c r="X1" s="226"/>
+      <c r="Y1" s="226"/>
+      <c r="Z1" s="226"/>
+      <c r="AA1" s="226"/>
+      <c r="AB1" s="226"/>
+      <c r="AC1" s="227"/>
+      <c r="AD1" s="237" t="s">
         <v>282</v>
       </c>
-      <c r="AE1" s="236"/>
-      <c r="AF1" s="236"/>
-      <c r="AG1" s="236"/>
-      <c r="AH1" s="236"/>
-      <c r="AI1" s="237"/>
-      <c r="AJ1" s="220" t="s">
+      <c r="AE1" s="238"/>
+      <c r="AF1" s="238"/>
+      <c r="AG1" s="238"/>
+      <c r="AH1" s="238"/>
+      <c r="AI1" s="239"/>
+      <c r="AJ1" s="225" t="s">
         <v>283</v>
       </c>
-      <c r="AK1" s="221"/>
-      <c r="AL1" s="221"/>
-      <c r="AM1" s="221"/>
-      <c r="AN1" s="221"/>
-      <c r="AO1" s="222"/>
-      <c r="AP1" s="223" t="s">
+      <c r="AK1" s="226"/>
+      <c r="AL1" s="226"/>
+      <c r="AM1" s="226"/>
+      <c r="AN1" s="226"/>
+      <c r="AO1" s="227"/>
+      <c r="AP1" s="228" t="s">
         <v>284</v>
       </c>
-      <c r="AQ1" s="224"/>
-      <c r="AR1" s="224"/>
-      <c r="AS1" s="224"/>
-      <c r="AT1" s="224"/>
-      <c r="AU1" s="225"/>
-      <c r="AV1" s="226" t="s">
+      <c r="AQ1" s="229"/>
+      <c r="AR1" s="229"/>
+      <c r="AS1" s="229"/>
+      <c r="AT1" s="229"/>
+      <c r="AU1" s="230"/>
+      <c r="AV1" s="231" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="227"/>
-      <c r="AX1" s="228"/>
+      <c r="AW1" s="232"/>
+      <c r="AX1" s="233"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="230"/>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="233"/>
-      <c r="H2" s="234"/>
-      <c r="I2" s="232"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="232"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="234"/>
-      <c r="O2" s="232"/>
-      <c r="P2" s="233"/>
-      <c r="Q2" s="234"/>
-      <c r="R2" s="232"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="234"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="234"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="233"/>
-      <c r="Z2" s="234"/>
-      <c r="AA2" s="232"/>
-      <c r="AB2" s="233"/>
-      <c r="AC2" s="233"/>
-      <c r="AD2" s="232"/>
-      <c r="AE2" s="233"/>
-      <c r="AF2" s="234"/>
-      <c r="AG2" s="232"/>
-      <c r="AH2" s="233"/>
-      <c r="AI2" s="234"/>
-      <c r="AJ2" s="232"/>
-      <c r="AK2" s="233"/>
-      <c r="AL2" s="234"/>
-      <c r="AM2" s="232"/>
-      <c r="AN2" s="233"/>
-      <c r="AO2" s="234"/>
-      <c r="AP2" s="232"/>
-      <c r="AQ2" s="233"/>
-      <c r="AR2" s="234"/>
-      <c r="AS2" s="232"/>
-      <c r="AT2" s="233"/>
-      <c r="AU2" s="234"/>
-      <c r="AV2" s="232"/>
-      <c r="AW2" s="233"/>
-      <c r="AX2" s="234"/>
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="222"/>
+      <c r="G2" s="223"/>
+      <c r="H2" s="224"/>
+      <c r="I2" s="222"/>
+      <c r="J2" s="223"/>
+      <c r="K2" s="224"/>
+      <c r="L2" s="222"/>
+      <c r="M2" s="223"/>
+      <c r="N2" s="224"/>
+      <c r="O2" s="222"/>
+      <c r="P2" s="223"/>
+      <c r="Q2" s="224"/>
+      <c r="R2" s="222"/>
+      <c r="S2" s="223"/>
+      <c r="T2" s="224"/>
+      <c r="U2" s="222"/>
+      <c r="V2" s="223"/>
+      <c r="W2" s="224"/>
+      <c r="X2" s="222"/>
+      <c r="Y2" s="223"/>
+      <c r="Z2" s="224"/>
+      <c r="AA2" s="222"/>
+      <c r="AB2" s="223"/>
+      <c r="AC2" s="223"/>
+      <c r="AD2" s="222"/>
+      <c r="AE2" s="223"/>
+      <c r="AF2" s="224"/>
+      <c r="AG2" s="222"/>
+      <c r="AH2" s="223"/>
+      <c r="AI2" s="224"/>
+      <c r="AJ2" s="222"/>
+      <c r="AK2" s="223"/>
+      <c r="AL2" s="224"/>
+      <c r="AM2" s="222"/>
+      <c r="AN2" s="223"/>
+      <c r="AO2" s="224"/>
+      <c r="AP2" s="222"/>
+      <c r="AQ2" s="223"/>
+      <c r="AR2" s="224"/>
+      <c r="AS2" s="222"/>
+      <c r="AT2" s="223"/>
+      <c r="AU2" s="224"/>
+      <c r="AV2" s="222"/>
+      <c r="AW2" s="223"/>
+      <c r="AX2" s="224"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -45625,9 +45625,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="231"/>
-      <c r="D3" s="231"/>
-      <c r="E3" s="231"/>
+      <c r="C3" s="236"/>
+      <c r="D3" s="236"/>
+      <c r="E3" s="236"/>
       <c r="F3" s="170" t="s">
         <v>394</v>
       </c>
@@ -48353,13 +48353,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -48376,6 +48369,13 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW31">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -55661,70 +55661,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="229" t="s">
+      <c r="C1" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="D1" s="229" t="s">
+      <c r="D1" s="234" t="s">
         <v>398</v>
       </c>
-      <c r="E1" s="229" t="s">
+      <c r="E1" s="234" t="s">
         <v>399</v>
       </c>
-      <c r="F1" s="269" t="s">
+      <c r="F1" s="264" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="270"/>
-      <c r="H1" s="271"/>
-      <c r="I1" s="272" t="s">
+      <c r="G1" s="265"/>
+      <c r="H1" s="266"/>
+      <c r="I1" s="267" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="273"/>
-      <c r="K1" s="274"/>
-      <c r="L1" s="239" t="s">
+      <c r="J1" s="268"/>
+      <c r="K1" s="269"/>
+      <c r="L1" s="271" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="240"/>
-      <c r="N1" s="241"/>
-      <c r="O1" s="242" t="s">
+      <c r="M1" s="272"/>
+      <c r="N1" s="273"/>
+      <c r="O1" s="274" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="243"/>
-      <c r="Q1" s="244"/>
-      <c r="R1" s="245" t="s">
+      <c r="P1" s="275"/>
+      <c r="Q1" s="276"/>
+      <c r="R1" s="240" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="246"/>
-      <c r="T1" s="247"/>
-      <c r="U1" s="248" t="s">
+      <c r="S1" s="241"/>
+      <c r="T1" s="242"/>
+      <c r="U1" s="243" t="s">
         <v>307</v>
       </c>
-      <c r="V1" s="249"/>
-      <c r="W1" s="250"/>
+      <c r="V1" s="244"/>
+      <c r="W1" s="245"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="230"/>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="252"/>
-      <c r="H2" s="253"/>
-      <c r="I2" s="266"/>
-      <c r="J2" s="267"/>
-      <c r="K2" s="268"/>
-      <c r="L2" s="263"/>
-      <c r="M2" s="264"/>
-      <c r="N2" s="265"/>
-      <c r="O2" s="260"/>
-      <c r="P2" s="261"/>
-      <c r="Q2" s="262"/>
-      <c r="R2" s="257"/>
-      <c r="S2" s="258"/>
-      <c r="T2" s="259"/>
-      <c r="U2" s="254"/>
-      <c r="V2" s="255"/>
-      <c r="W2" s="256"/>
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="262"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="258"/>
+      <c r="M2" s="259"/>
+      <c r="N2" s="260"/>
+      <c r="O2" s="255"/>
+      <c r="P2" s="256"/>
+      <c r="Q2" s="257"/>
+      <c r="R2" s="252"/>
+      <c r="S2" s="253"/>
+      <c r="T2" s="254"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="250"/>
+      <c r="W2" s="251"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -55733,9 +55733,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="238"/>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
+      <c r="C3" s="270"/>
+      <c r="D3" s="270"/>
+      <c r="E3" s="270"/>
       <c r="F3" s="189" t="s">
         <v>394</v>
       </c>
@@ -57162,6 +57162,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -57172,11 +57177,6 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W31">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -57207,70 +57207,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="229" t="s">
+      <c r="C1" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="D1" s="229" t="s">
+      <c r="D1" s="234" t="s">
         <v>398</v>
       </c>
-      <c r="E1" s="229" t="s">
+      <c r="E1" s="234" t="s">
         <v>399</v>
       </c>
-      <c r="F1" s="269" t="s">
+      <c r="F1" s="264" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="270"/>
-      <c r="H1" s="271"/>
-      <c r="I1" s="272" t="s">
+      <c r="G1" s="265"/>
+      <c r="H1" s="266"/>
+      <c r="I1" s="267" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="273"/>
-      <c r="K1" s="274"/>
-      <c r="L1" s="239" t="s">
+      <c r="J1" s="268"/>
+      <c r="K1" s="269"/>
+      <c r="L1" s="271" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="240"/>
-      <c r="N1" s="241"/>
-      <c r="O1" s="242" t="s">
+      <c r="M1" s="272"/>
+      <c r="N1" s="273"/>
+      <c r="O1" s="274" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="243"/>
-      <c r="Q1" s="244"/>
-      <c r="R1" s="245" t="s">
+      <c r="P1" s="275"/>
+      <c r="Q1" s="276"/>
+      <c r="R1" s="240" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="246"/>
-      <c r="T1" s="247"/>
-      <c r="U1" s="248" t="s">
+      <c r="S1" s="241"/>
+      <c r="T1" s="242"/>
+      <c r="U1" s="243" t="s">
         <v>307</v>
       </c>
-      <c r="V1" s="249"/>
-      <c r="W1" s="250"/>
+      <c r="V1" s="244"/>
+      <c r="W1" s="245"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="230"/>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="252"/>
-      <c r="H2" s="253"/>
-      <c r="I2" s="266"/>
-      <c r="J2" s="267"/>
-      <c r="K2" s="268"/>
-      <c r="L2" s="263"/>
-      <c r="M2" s="264"/>
-      <c r="N2" s="265"/>
-      <c r="O2" s="260"/>
-      <c r="P2" s="261"/>
-      <c r="Q2" s="262"/>
-      <c r="R2" s="257"/>
-      <c r="S2" s="258"/>
-      <c r="T2" s="259"/>
-      <c r="U2" s="254"/>
-      <c r="V2" s="255"/>
-      <c r="W2" s="256"/>
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="247"/>
+      <c r="H2" s="248"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="262"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="258"/>
+      <c r="M2" s="259"/>
+      <c r="N2" s="260"/>
+      <c r="O2" s="255"/>
+      <c r="P2" s="256"/>
+      <c r="Q2" s="257"/>
+      <c r="R2" s="252"/>
+      <c r="S2" s="253"/>
+      <c r="T2" s="254"/>
+      <c r="U2" s="249"/>
+      <c r="V2" s="250"/>
+      <c r="W2" s="251"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -57279,9 +57279,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="238"/>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
+      <c r="C3" s="270"/>
+      <c r="D3" s="270"/>
+      <c r="E3" s="270"/>
       <c r="F3" s="189" t="s">
         <v>394</v>
       </c>
@@ -58708,11 +58708,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -58723,6 +58718,11 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W31">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -58750,11 +58750,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C1" s="275" t="s">
+      <c r="C1" s="277" t="s">
         <v>341</v>
       </c>
-      <c r="D1" s="276"/>
-      <c r="E1" s="276"/>
+      <c r="D1" s="278"/>
+      <c r="E1" s="278"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -59251,51 +59251,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="283" t="s">
+      <c r="C1" s="280" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="285"/>
+      <c r="D1" s="281"/>
+      <c r="E1" s="281"/>
+      <c r="F1" s="281"/>
+      <c r="G1" s="281"/>
+      <c r="H1" s="281"/>
+      <c r="I1" s="282"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="277" t="s">
+      <c r="L1" s="313" t="s">
         <v>288</v>
       </c>
-      <c r="M1" s="281"/>
-      <c r="N1" s="281"/>
-      <c r="O1" s="281"/>
-      <c r="P1" s="281"/>
-      <c r="Q1" s="281"/>
-      <c r="R1" s="281"/>
-      <c r="S1" s="281"/>
-      <c r="T1" s="281"/>
-      <c r="U1" s="281"/>
-      <c r="V1" s="281"/>
-      <c r="W1" s="281"/>
-      <c r="X1" s="281"/>
-      <c r="Y1" s="281"/>
-      <c r="Z1" s="281"/>
-      <c r="AA1" s="281"/>
-      <c r="AB1" s="281"/>
-      <c r="AC1" s="281"/>
-      <c r="AD1" s="281"/>
-      <c r="AE1" s="281"/>
-      <c r="AF1" s="281"/>
-      <c r="AG1" s="282"/>
-      <c r="AH1" s="277" t="s">
+      <c r="M1" s="316"/>
+      <c r="N1" s="316"/>
+      <c r="O1" s="316"/>
+      <c r="P1" s="316"/>
+      <c r="Q1" s="316"/>
+      <c r="R1" s="316"/>
+      <c r="S1" s="316"/>
+      <c r="T1" s="316"/>
+      <c r="U1" s="316"/>
+      <c r="V1" s="316"/>
+      <c r="W1" s="316"/>
+      <c r="X1" s="316"/>
+      <c r="Y1" s="316"/>
+      <c r="Z1" s="316"/>
+      <c r="AA1" s="316"/>
+      <c r="AB1" s="316"/>
+      <c r="AC1" s="316"/>
+      <c r="AD1" s="316"/>
+      <c r="AE1" s="316"/>
+      <c r="AF1" s="316"/>
+      <c r="AG1" s="317"/>
+      <c r="AH1" s="313" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="278"/>
-      <c r="AJ1" s="278"/>
-      <c r="AK1" s="279"/>
+      <c r="AI1" s="314"/>
+      <c r="AJ1" s="314"/>
+      <c r="AK1" s="315"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -64483,15 +64483,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="307" t="s">
+      <c r="K80" s="304" t="s">
         <v>175</v>
       </c>
-      <c r="L80" s="308"/>
-      <c r="M80" s="309"/>
+      <c r="L80" s="305"/>
+      <c r="M80" s="306"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="280"/>
-      <c r="X80" s="280"/>
+      <c r="W80" s="279"/>
+      <c r="X80" s="279"/>
       <c r="Y80" s="70" t="s">
         <v>212</v>
       </c>
@@ -64541,15 +64541,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="310"/>
-      <c r="L81" s="311"/>
-      <c r="M81" s="312"/>
+      <c r="K81" s="307"/>
+      <c r="L81" s="308"/>
+      <c r="M81" s="309"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="280" t="s">
+      <c r="W81" s="279" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="280"/>
+      <c r="X81" s="279"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -64605,15 +64605,15 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="310"/>
-      <c r="L82" s="311"/>
-      <c r="M82" s="312"/>
+      <c r="K82" s="307"/>
+      <c r="L82" s="308"/>
+      <c r="M82" s="309"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="280" t="s">
+      <c r="W82" s="279" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="280"/>
+      <c r="X82" s="279"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -64669,15 +64669,15 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="313"/>
-      <c r="L83" s="314"/>
-      <c r="M83" s="315"/>
+      <c r="K83" s="310"/>
+      <c r="L83" s="311"/>
+      <c r="M83" s="312"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="280" t="s">
+      <c r="W83" s="279" t="s">
         <v>211</v>
       </c>
-      <c r="X83" s="280"/>
+      <c r="X83" s="279"/>
       <c r="Y83" s="70">
         <f>COUNTIF(J16:J20,3)</f>
         <v>1</v>
@@ -64733,17 +64733,17 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="298" t="s">
+      <c r="K84" s="295" t="s">
         <v>285</v>
       </c>
-      <c r="L84" s="299"/>
-      <c r="M84" s="300"/>
+      <c r="L84" s="296"/>
+      <c r="M84" s="297"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="280" t="s">
+      <c r="W84" s="279" t="s">
         <v>97</v>
       </c>
-      <c r="X84" s="280"/>
+      <c r="X84" s="279"/>
       <c r="Y84" s="70">
         <f>COUNTIF(J21:J40,3)+COUNTIF(I3:I40,3)+COUNTIF(H3:H40,3)+COUNTIF(G3:G40,3)+COUNTIF(F3:F40,3)+COUNTIF(E3:E40,3)</f>
         <v>123</v>
@@ -64799,9 +64799,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="301"/>
-      <c r="L85" s="302"/>
-      <c r="M85" s="303"/>
+      <c r="K85" s="298"/>
+      <c r="L85" s="299"/>
+      <c r="M85" s="300"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -64835,9 +64835,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="301"/>
-      <c r="L86" s="302"/>
-      <c r="M86" s="303"/>
+      <c r="K86" s="298"/>
+      <c r="L86" s="299"/>
+      <c r="M86" s="300"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -64871,9 +64871,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="301"/>
-      <c r="L87" s="302"/>
-      <c r="M87" s="303"/>
+      <c r="K87" s="298"/>
+      <c r="L87" s="299"/>
+      <c r="M87" s="300"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -64907,9 +64907,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="301"/>
-      <c r="L88" s="302"/>
-      <c r="M88" s="303"/>
+      <c r="K88" s="298"/>
+      <c r="L88" s="299"/>
+      <c r="M88" s="300"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -64943,9 +64943,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="301"/>
-      <c r="L89" s="302"/>
-      <c r="M89" s="303"/>
+      <c r="K89" s="298"/>
+      <c r="L89" s="299"/>
+      <c r="M89" s="300"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -64979,9 +64979,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="301"/>
-      <c r="L90" s="302"/>
-      <c r="M90" s="303"/>
+      <c r="K90" s="298"/>
+      <c r="L90" s="299"/>
+      <c r="M90" s="300"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -65015,9 +65015,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="301"/>
-      <c r="L91" s="302"/>
-      <c r="M91" s="303"/>
+      <c r="K91" s="298"/>
+      <c r="L91" s="299"/>
+      <c r="M91" s="300"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -65051,9 +65051,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="301"/>
-      <c r="L92" s="302"/>
-      <c r="M92" s="303"/>
+      <c r="K92" s="298"/>
+      <c r="L92" s="299"/>
+      <c r="M92" s="300"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -65087,9 +65087,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="301"/>
-      <c r="L93" s="302"/>
-      <c r="M93" s="303"/>
+      <c r="K93" s="298"/>
+      <c r="L93" s="299"/>
+      <c r="M93" s="300"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -65123,9 +65123,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="301"/>
-      <c r="L94" s="302"/>
-      <c r="M94" s="303"/>
+      <c r="K94" s="298"/>
+      <c r="L94" s="299"/>
+      <c r="M94" s="300"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -65159,9 +65159,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="301"/>
-      <c r="L95" s="302"/>
-      <c r="M95" s="303"/>
+      <c r="K95" s="298"/>
+      <c r="L95" s="299"/>
+      <c r="M95" s="300"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -65195,9 +65195,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="301"/>
-      <c r="L96" s="302"/>
-      <c r="M96" s="303"/>
+      <c r="K96" s="298"/>
+      <c r="L96" s="299"/>
+      <c r="M96" s="300"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -65231,9 +65231,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="301"/>
-      <c r="L97" s="302"/>
-      <c r="M97" s="303"/>
+      <c r="K97" s="298"/>
+      <c r="L97" s="299"/>
+      <c r="M97" s="300"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -65267,9 +65267,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="301"/>
-      <c r="L98" s="302"/>
-      <c r="M98" s="303"/>
+      <c r="K98" s="298"/>
+      <c r="L98" s="299"/>
+      <c r="M98" s="300"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -65303,9 +65303,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="301"/>
-      <c r="L99" s="302"/>
-      <c r="M99" s="303"/>
+      <c r="K99" s="298"/>
+      <c r="L99" s="299"/>
+      <c r="M99" s="300"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -65339,9 +65339,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="301"/>
-      <c r="L100" s="302"/>
-      <c r="M100" s="303"/>
+      <c r="K100" s="298"/>
+      <c r="L100" s="299"/>
+      <c r="M100" s="300"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -65375,9 +65375,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="301"/>
-      <c r="L101" s="302"/>
-      <c r="M101" s="303"/>
+      <c r="K101" s="298"/>
+      <c r="L101" s="299"/>
+      <c r="M101" s="300"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -65411,9 +65411,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="301"/>
-      <c r="L102" s="302"/>
-      <c r="M102" s="303"/>
+      <c r="K102" s="298"/>
+      <c r="L102" s="299"/>
+      <c r="M102" s="300"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -65447,9 +65447,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="301"/>
-      <c r="L103" s="302"/>
-      <c r="M103" s="303"/>
+      <c r="K103" s="298"/>
+      <c r="L103" s="299"/>
+      <c r="M103" s="300"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -65483,9 +65483,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="301"/>
-      <c r="L104" s="302"/>
-      <c r="M104" s="303"/>
+      <c r="K104" s="298"/>
+      <c r="L104" s="299"/>
+      <c r="M104" s="300"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -65519,9 +65519,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="304"/>
-      <c r="L105" s="305"/>
-      <c r="M105" s="306"/>
+      <c r="K105" s="301"/>
+      <c r="L105" s="302"/>
+      <c r="M105" s="303"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -65555,11 +65555,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="295" t="s">
+      <c r="K106" s="292" t="s">
         <v>287</v>
       </c>
-      <c r="L106" s="296"/>
-      <c r="M106" s="297"/>
+      <c r="L106" s="293"/>
+      <c r="M106" s="294"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -65593,11 +65593,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="295" t="s">
+      <c r="K107" s="292" t="s">
         <v>289</v>
       </c>
-      <c r="L107" s="296"/>
-      <c r="M107" s="297"/>
+      <c r="L107" s="293"/>
+      <c r="M107" s="294"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -65631,11 +65631,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="286" t="s">
+      <c r="K108" s="283" t="s">
         <v>290</v>
       </c>
-      <c r="L108" s="287"/>
-      <c r="M108" s="288"/>
+      <c r="L108" s="284"/>
+      <c r="M108" s="285"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -65669,9 +65669,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="289"/>
-      <c r="L109" s="290"/>
-      <c r="M109" s="291"/>
+      <c r="K109" s="286"/>
+      <c r="L109" s="287"/>
+      <c r="M109" s="288"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -65705,9 +65705,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="289"/>
-      <c r="L110" s="290"/>
-      <c r="M110" s="291"/>
+      <c r="K110" s="286"/>
+      <c r="L110" s="287"/>
+      <c r="M110" s="288"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -65741,9 +65741,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="289"/>
-      <c r="L111" s="290"/>
-      <c r="M111" s="291"/>
+      <c r="K111" s="286"/>
+      <c r="L111" s="287"/>
+      <c r="M111" s="288"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -65781,9 +65781,9 @@
         <f t="shared" ref="J112:J113" si="7">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="289"/>
-      <c r="L112" s="290"/>
-      <c r="M112" s="291"/>
+      <c r="K112" s="286"/>
+      <c r="L112" s="287"/>
+      <c r="M112" s="288"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="156" t="s">
@@ -65819,13 +65819,19 @@
         <f t="shared" si="7"/>
         <v>43</v>
       </c>
-      <c r="K113" s="292"/>
-      <c r="L113" s="293"/>
-      <c r="M113" s="294"/>
+      <c r="K113" s="289"/>
+      <c r="L113" s="290"/>
+      <c r="M113" s="291"/>
     </row>
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="13">
+    <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="W80:X80"/>
+    <mergeCell ref="W81:X81"/>
+    <mergeCell ref="W82:X82"/>
+    <mergeCell ref="W83:X83"/>
+    <mergeCell ref="L1:AG1"/>
     <mergeCell ref="W84:X84"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="K108:M113"/>
@@ -65833,12 +65839,6 @@
     <mergeCell ref="K107:M107"/>
     <mergeCell ref="K84:M105"/>
     <mergeCell ref="K80:M83"/>
-    <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="W80:X80"/>
-    <mergeCell ref="W81:X81"/>
-    <mergeCell ref="W82:X82"/>
-    <mergeCell ref="W83:X83"/>
-    <mergeCell ref="L1:AG1"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -65912,24 +65912,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="196" t="s">
+      <c r="A1" s="202" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="316"/>
-      <c r="C1" s="317" t="s">
+      <c r="B1" s="318"/>
+      <c r="C1" s="319" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="202"/>
-      <c r="E1" s="318"/>
-      <c r="H1" s="196" t="s">
+      <c r="D1" s="205"/>
+      <c r="E1" s="320"/>
+      <c r="H1" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="316"/>
-      <c r="J1" s="317" t="s">
+      <c r="I1" s="318"/>
+      <c r="J1" s="319" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="202"/>
-      <c r="L1" s="318"/>
+      <c r="K1" s="205"/>
+      <c r="L1" s="320"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -67007,38 +67007,38 @@
     <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="320" t="s">
+      <c r="A1" s="197" t="s">
         <v>408</v>
       </c>
-      <c r="B1" s="320"/>
-      <c r="C1" s="320"/>
-      <c r="D1" s="320"/>
-      <c r="E1" s="320"/>
-      <c r="F1" s="320" t="s">
+      <c r="B1" s="197"/>
+      <c r="C1" s="197"/>
+      <c r="D1" s="197"/>
+      <c r="E1" s="197"/>
+      <c r="F1" s="197" t="s">
         <v>409</v>
       </c>
-      <c r="G1" s="320"/>
-      <c r="H1" s="320"/>
-      <c r="I1" s="320"/>
-      <c r="J1" s="320"/>
+      <c r="G1" s="197"/>
+      <c r="H1" s="197"/>
+      <c r="I1" s="197"/>
+      <c r="J1" s="197"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="320"/>
-      <c r="B2" s="320"/>
-      <c r="C2" s="320"/>
-      <c r="D2" s="320"/>
-      <c r="E2" s="320"/>
-      <c r="F2" s="320"/>
-      <c r="G2" s="320"/>
-      <c r="H2" s="320"/>
-      <c r="I2" s="320"/>
-      <c r="J2" s="320"/>
+      <c r="A2" s="197"/>
+      <c r="B2" s="197"/>
+      <c r="C2" s="197"/>
+      <c r="D2" s="197"/>
+      <c r="E2" s="197"/>
+      <c r="F2" s="197"/>
+      <c r="G2" s="197"/>
+      <c r="H2" s="197"/>
+      <c r="I2" s="197"/>
+      <c r="J2" s="197"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -67076,7 +67076,7 @@
       <c r="A4" t="s">
         <v>400</v>
       </c>
-      <c r="B4" s="319">
+      <c r="B4" s="196">
         <v>0.875</v>
       </c>
       <c r="C4" t="s">
@@ -67089,13 +67089,13 @@
         <v>406</v>
       </c>
       <c r="F4" t="s">
+        <v>414</v>
+      </c>
+      <c r="G4" s="196" t="s">
+        <v>411</v>
+      </c>
+      <c r="H4" t="s">
         <v>415</v>
-      </c>
-      <c r="G4" s="319" t="s">
-        <v>411</v>
-      </c>
-      <c r="H4" t="s">
-        <v>414</v>
       </c>
       <c r="I4" t="s">
         <v>412</v>
@@ -67136,9 +67136,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="207"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="207"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -67162,36 +67162,36 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="196" t="s">
+      <c r="E2" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="197"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="199" t="s">
+      <c r="F2" s="203"/>
+      <c r="G2" s="204"/>
+      <c r="H2" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="200"/>
-      <c r="J2" s="201"/>
-      <c r="K2" s="196" t="s">
+      <c r="I2" s="208"/>
+      <c r="J2" s="209"/>
+      <c r="K2" s="202" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="197"/>
-      <c r="M2" s="198"/>
-      <c r="N2" s="199" t="s">
+      <c r="L2" s="203"/>
+      <c r="M2" s="204"/>
+      <c r="N2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="200"/>
-      <c r="P2" s="201"/>
-      <c r="Q2" s="196" t="s">
+      <c r="O2" s="208"/>
+      <c r="P2" s="209"/>
+      <c r="Q2" s="202" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="197"/>
-      <c r="S2" s="198"/>
-      <c r="T2" s="202" t="s">
+      <c r="R2" s="203"/>
+      <c r="S2" s="204"/>
+      <c r="T2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="202"/>
-      <c r="V2" s="202"/>
+      <c r="U2" s="205"/>
+      <c r="V2" s="205"/>
       <c r="Z2" s="125">
         <v>46255</v>
       </c>
@@ -70532,30 +70532,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="205" t="s">
+      <c r="D2" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="205"/>
-      <c r="F2" s="206" t="s">
+      <c r="E2" s="200"/>
+      <c r="F2" s="201" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="206"/>
-      <c r="H2" s="205" t="s">
+      <c r="G2" s="201"/>
+      <c r="H2" s="200" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="205"/>
-      <c r="J2" s="206" t="s">
+      <c r="I2" s="200"/>
+      <c r="J2" s="201" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="206"/>
-      <c r="L2" s="205" t="s">
+      <c r="K2" s="201"/>
+      <c r="L2" s="200" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="205"/>
-      <c r="N2" s="202" t="s">
+      <c r="M2" s="200"/>
+      <c r="N2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="202"/>
+      <c r="O2" s="205"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -72552,30 +72552,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="205" t="s">
+      <c r="D2" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="205"/>
-      <c r="F2" s="206" t="s">
+      <c r="E2" s="200"/>
+      <c r="F2" s="201" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="206"/>
-      <c r="H2" s="205" t="s">
+      <c r="G2" s="201"/>
+      <c r="H2" s="200" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="205"/>
-      <c r="J2" s="206" t="s">
+      <c r="I2" s="200"/>
+      <c r="J2" s="201" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="206"/>
-      <c r="L2" s="205" t="s">
+      <c r="K2" s="201"/>
+      <c r="L2" s="200" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="205"/>
-      <c r="N2" s="202" t="s">
+      <c r="M2" s="200"/>
+      <c r="N2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="202"/>
+      <c r="O2" s="205"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -74509,30 +74509,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="205" t="s">
+      <c r="D2" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="205"/>
-      <c r="F2" s="206" t="s">
+      <c r="E2" s="200"/>
+      <c r="F2" s="201" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="206"/>
-      <c r="H2" s="205" t="s">
+      <c r="G2" s="201"/>
+      <c r="H2" s="200" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="205"/>
-      <c r="J2" s="206" t="s">
+      <c r="I2" s="200"/>
+      <c r="J2" s="201" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="206"/>
-      <c r="L2" s="205" t="s">
+      <c r="K2" s="201"/>
+      <c r="L2" s="200" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="205"/>
-      <c r="N2" s="202" t="s">
+      <c r="M2" s="200"/>
+      <c r="N2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="202"/>
+      <c r="O2" s="205"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -76557,30 +76557,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="205" t="s">
+      <c r="D2" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="205"/>
-      <c r="F2" s="206" t="s">
+      <c r="E2" s="200"/>
+      <c r="F2" s="201" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="206"/>
-      <c r="H2" s="205" t="s">
+      <c r="G2" s="201"/>
+      <c r="H2" s="200" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="205"/>
-      <c r="J2" s="206" t="s">
+      <c r="I2" s="200"/>
+      <c r="J2" s="201" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="206"/>
-      <c r="L2" s="205" t="s">
+      <c r="K2" s="201"/>
+      <c r="L2" s="200" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="205"/>
-      <c r="N2" s="202" t="s">
+      <c r="M2" s="200"/>
+      <c r="N2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="202"/>
+      <c r="O2" s="205"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -78265,30 +78265,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206" t="s">
+      <c r="D2" s="200"/>
+      <c r="E2" s="201" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="205" t="s">
+      <c r="F2" s="201"/>
+      <c r="G2" s="200" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="H2" s="200"/>
+      <c r="I2" s="201" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="205" t="s">
+      <c r="J2" s="201"/>
+      <c r="K2" s="200" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="202" t="s">
+      <c r="L2" s="200"/>
+      <c r="M2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="202"/>
+      <c r="N2" s="205"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7814" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B100A38E-C445-495B-8F1B-AAB2EDF6B4AD}"/>
+  <xr:revisionPtr revIDLastSave="7817" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B234472-1F69-43DB-8C67-605A3ACDBA0C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2244" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2245" uniqueCount="442">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -2914,6 +2914,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2923,16 +2932,10 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
@@ -2947,8 +2950,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2986,15 +2995,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3002,27 +3002,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3115,28 +3094,34 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3237,6 +3222,21 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6303,7 +6303,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6E60E86B-60C1-4888-9952-FE5BA26E9738}" type="CELLRANGE">
+                    <a:fld id="{B437EF68-25A2-48C5-94FC-75BD5DC828BC}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6337,7 +6337,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BEE68E24-2132-4950-B2FB-64A5BF68633D}" type="CELLRANGE">
+                    <a:fld id="{9D53D9E3-7404-4232-939A-B6533E35635A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6371,7 +6371,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AB272EA7-3CC5-4D4A-9EFF-613745C5226D}" type="CELLRANGE">
+                    <a:fld id="{6F80CE62-244D-4457-B91A-17630F2B5CA7}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6405,7 +6405,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EEF8DEB7-D91C-4612-BF77-1455FB044DF5}" type="CELLRANGE">
+                    <a:fld id="{1A2C04F2-7BE4-479B-B897-7F305AE52EE6}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6439,7 +6439,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B2E51D23-8E1D-40CB-8B5E-EEA290550889}" type="CELLRANGE">
+                    <a:fld id="{DC8FCAA1-8BB9-47BC-885C-F805BE89C9ED}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6473,7 +6473,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4454D524-9A99-40F5-909B-10C745BAFC9F}" type="CELLRANGE">
+                    <a:fld id="{65F9ADCB-6118-491C-BE4E-90E7FC32967F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6507,7 +6507,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FC4E38AA-E47D-4954-9478-F0724811360B}" type="CELLRANGE">
+                    <a:fld id="{56BF2A5B-937E-4EAA-B19C-158D7E0B97A9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6541,7 +6541,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DE2392FF-03BE-4612-8C52-965AEF5CEC4B}" type="CELLRANGE">
+                    <a:fld id="{0B27818C-A77B-4FF2-827C-FA8E31DFD654}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6575,7 +6575,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{876E69E0-900F-4367-88D7-455230C41E66}" type="CELLRANGE">
+                    <a:fld id="{2A8043BF-E94B-4753-B457-12FF1EB4DCED}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6609,7 +6609,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8D7B3A2C-98C7-4156-9DF9-85D82F7B0A3B}" type="CELLRANGE">
+                    <a:fld id="{25EE1D23-6312-4821-A94A-7D2B1F290296}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6643,7 +6643,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DF82337D-4DAF-4EE6-852D-15548E51DC3D}" type="CELLRANGE">
+                    <a:fld id="{C2091993-D565-43A8-B2A2-267189CF10C1}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6677,7 +6677,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B6A25747-276A-4A83-96F5-53199413F546}" type="CELLRANGE">
+                    <a:fld id="{7755AF6F-06C5-4802-9435-7DE7A2544988}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6726,7 +6726,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{D97BBECD-FDC3-426F-A723-163874A9E7AF}" type="CELLRANGE">
+                    <a:fld id="{6573CAB2-ACCF-4C97-9D5A-12F97F63E8A2}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6785,7 +6785,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{565FC84A-C163-48A5-B9CE-F9BD37F195EA}" type="CELLRANGE">
+                    <a:fld id="{4A449499-E58C-4340-B8CD-BE5D759F422F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6819,7 +6819,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6A8D5C6E-5C1E-415D-9734-D969120828A1}" type="CELLRANGE">
+                    <a:fld id="{C7AEB7D4-A68B-476B-8D80-4C8BE70B5D07}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6853,7 +6853,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3707A0CD-96ED-4CF1-B11A-23B5C2A76DE1}" type="CELLRANGE">
+                    <a:fld id="{9A83A389-9B3E-476D-BACF-D93D8E01BA4D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6887,7 +6887,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1E4E08BD-3E16-4E7B-A7EB-4D9211C81780}" type="CELLRANGE">
+                    <a:fld id="{2F9B23E5-134D-438E-8905-77E2A6DCDEB5}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6921,7 +6921,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3CDF423E-FAA0-43D4-B51A-D249C071B07A}" type="CELLRANGE">
+                    <a:fld id="{07074D4D-DB33-4082-ABAC-AD95D68072B2}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6955,7 +6955,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6B2652D2-77AA-4E4F-AC4A-F86F66249E91}" type="CELLRANGE">
+                    <a:fld id="{3FD3C3A4-75E6-40DD-BED4-2E952A952700}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6989,7 +6989,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BC5FB907-A922-46F2-9060-61E3FB72A7A0}" type="CELLRANGE">
+                    <a:fld id="{C11CB376-6248-4574-92BB-DDDF40063128}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7023,7 +7023,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F20E971C-9FEF-4430-9918-6ABF925D3A1E}" type="CELLRANGE">
+                    <a:fld id="{B29C8EEA-66FB-408A-8E24-B40A0E5CA0B9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -23405,15 +23405,15 @@
         <v>0</v>
       </c>
       <c r="R5" s="2">
-        <f t="shared" ref="R5:R41" si="1">SUM(C5,F5,I5,L5,O5)</f>
+        <f t="shared" ref="R5:R16" si="1">SUM(C5,F5,I5,L5,O5)</f>
         <v>0</v>
       </c>
       <c r="S5" s="2">
-        <f t="shared" ref="S5:S41" si="2">SUM(D5,G5,J5,M5,P5)</f>
+        <f t="shared" ref="S5:S16" si="2">SUM(D5,G5,J5,M5,P5)</f>
         <v>0</v>
       </c>
       <c r="T5" s="2">
-        <f t="shared" ref="T5:T41" si="3">SUM(E5,H5,K5,N5,Q5)</f>
+        <f t="shared" ref="T5:T16" si="3">SUM(E5,H5,K5,N5,Q5)</f>
         <v>0</v>
       </c>
       <c r="V5" s="55"/>
@@ -37803,196 +37803,196 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="208">
-        <v>1</v>
-      </c>
-      <c r="G1" s="209"/>
-      <c r="H1" s="210"/>
-      <c r="I1" s="208">
+      <c r="F1" s="211">
+        <v>1</v>
+      </c>
+      <c r="G1" s="212"/>
+      <c r="H1" s="213"/>
+      <c r="I1" s="211">
         <v>2</v>
       </c>
-      <c r="J1" s="209"/>
-      <c r="K1" s="210"/>
-      <c r="L1" s="208">
-        <v>3</v>
-      </c>
-      <c r="M1" s="209"/>
-      <c r="N1" s="210"/>
-      <c r="O1" s="208">
+      <c r="J1" s="212"/>
+      <c r="K1" s="213"/>
+      <c r="L1" s="211">
+        <v>3</v>
+      </c>
+      <c r="M1" s="212"/>
+      <c r="N1" s="213"/>
+      <c r="O1" s="211">
         <v>4</v>
       </c>
-      <c r="P1" s="209"/>
-      <c r="Q1" s="210"/>
-      <c r="R1" s="208">
+      <c r="P1" s="212"/>
+      <c r="Q1" s="213"/>
+      <c r="R1" s="211">
         <v>5</v>
       </c>
-      <c r="S1" s="209"/>
-      <c r="T1" s="210"/>
-      <c r="U1" s="208">
+      <c r="S1" s="212"/>
+      <c r="T1" s="213"/>
+      <c r="U1" s="211">
         <v>6</v>
       </c>
-      <c r="V1" s="209"/>
-      <c r="W1" s="210"/>
-      <c r="X1" s="208">
+      <c r="V1" s="212"/>
+      <c r="W1" s="213"/>
+      <c r="X1" s="211">
         <v>7</v>
       </c>
-      <c r="Y1" s="209"/>
-      <c r="Z1" s="210"/>
-      <c r="AA1" s="208">
+      <c r="Y1" s="212"/>
+      <c r="Z1" s="213"/>
+      <c r="AA1" s="211">
         <v>8</v>
       </c>
-      <c r="AB1" s="209"/>
-      <c r="AC1" s="210"/>
-      <c r="AD1" s="208">
+      <c r="AB1" s="212"/>
+      <c r="AC1" s="213"/>
+      <c r="AD1" s="211">
         <v>9</v>
       </c>
-      <c r="AE1" s="209"/>
-      <c r="AF1" s="210"/>
-      <c r="AG1" s="208">
+      <c r="AE1" s="212"/>
+      <c r="AF1" s="213"/>
+      <c r="AG1" s="211">
         <v>10</v>
       </c>
-      <c r="AH1" s="209"/>
-      <c r="AI1" s="210"/>
-      <c r="AJ1" s="208">
+      <c r="AH1" s="212"/>
+      <c r="AI1" s="213"/>
+      <c r="AJ1" s="211">
         <v>11</v>
       </c>
-      <c r="AK1" s="209"/>
-      <c r="AL1" s="210"/>
-      <c r="AM1" s="208">
+      <c r="AK1" s="212"/>
+      <c r="AL1" s="213"/>
+      <c r="AM1" s="211">
         <v>12</v>
       </c>
-      <c r="AN1" s="209"/>
-      <c r="AO1" s="210"/>
-      <c r="AP1" s="208">
+      <c r="AN1" s="212"/>
+      <c r="AO1" s="213"/>
+      <c r="AP1" s="211">
         <v>13</v>
       </c>
-      <c r="AQ1" s="209"/>
-      <c r="AR1" s="210"/>
-      <c r="AS1" s="208">
+      <c r="AQ1" s="212"/>
+      <c r="AR1" s="213"/>
+      <c r="AS1" s="211">
         <v>14</v>
       </c>
-      <c r="AT1" s="209"/>
-      <c r="AU1" s="210"/>
-      <c r="AV1" s="208">
+      <c r="AT1" s="212"/>
+      <c r="AU1" s="213"/>
+      <c r="AV1" s="211">
         <v>15</v>
       </c>
-      <c r="AW1" s="209"/>
-      <c r="AX1" s="210"/>
-      <c r="AY1" s="208">
+      <c r="AW1" s="212"/>
+      <c r="AX1" s="213"/>
+      <c r="AY1" s="211">
         <v>16</v>
       </c>
-      <c r="AZ1" s="209"/>
-      <c r="BA1" s="210"/>
-      <c r="BB1" s="208">
+      <c r="AZ1" s="212"/>
+      <c r="BA1" s="213"/>
+      <c r="BB1" s="211">
         <v>17</v>
       </c>
-      <c r="BC1" s="209"/>
-      <c r="BD1" s="210"/>
-      <c r="BE1" s="208">
+      <c r="BC1" s="212"/>
+      <c r="BD1" s="213"/>
+      <c r="BE1" s="211">
         <v>18</v>
       </c>
-      <c r="BF1" s="209"/>
-      <c r="BG1" s="210"/>
-      <c r="BH1" s="208">
+      <c r="BF1" s="212"/>
+      <c r="BG1" s="213"/>
+      <c r="BH1" s="211">
         <v>19</v>
       </c>
-      <c r="BI1" s="209"/>
-      <c r="BJ1" s="210"/>
-      <c r="BK1" s="208">
+      <c r="BI1" s="212"/>
+      <c r="BJ1" s="213"/>
+      <c r="BK1" s="211">
         <v>20</v>
       </c>
-      <c r="BL1" s="209"/>
-      <c r="BM1" s="210"/>
-      <c r="BN1" s="208">
+      <c r="BL1" s="212"/>
+      <c r="BM1" s="213"/>
+      <c r="BN1" s="211">
         <v>21</v>
       </c>
-      <c r="BO1" s="209"/>
-      <c r="BP1" s="210"/>
-      <c r="BQ1" s="208">
+      <c r="BO1" s="212"/>
+      <c r="BP1" s="213"/>
+      <c r="BQ1" s="211">
         <v>22</v>
       </c>
-      <c r="BR1" s="209"/>
-      <c r="BS1" s="210"/>
-      <c r="BT1" s="208">
+      <c r="BR1" s="212"/>
+      <c r="BS1" s="213"/>
+      <c r="BT1" s="211">
         <v>23</v>
       </c>
-      <c r="BU1" s="209"/>
-      <c r="BV1" s="210"/>
-      <c r="BW1" s="208">
+      <c r="BU1" s="212"/>
+      <c r="BV1" s="213"/>
+      <c r="BW1" s="211">
         <v>24</v>
       </c>
-      <c r="BX1" s="209"/>
-      <c r="BY1" s="210"/>
-      <c r="BZ1" s="208">
+      <c r="BX1" s="212"/>
+      <c r="BY1" s="213"/>
+      <c r="BZ1" s="211">
         <v>25</v>
       </c>
-      <c r="CA1" s="209"/>
-      <c r="CB1" s="210"/>
-      <c r="CC1" s="208">
+      <c r="CA1" s="212"/>
+      <c r="CB1" s="213"/>
+      <c r="CC1" s="211">
         <v>26</v>
       </c>
-      <c r="CD1" s="209"/>
-      <c r="CE1" s="210"/>
-      <c r="CF1" s="208">
+      <c r="CD1" s="212"/>
+      <c r="CE1" s="213"/>
+      <c r="CF1" s="211">
         <v>27</v>
       </c>
-      <c r="CG1" s="209"/>
-      <c r="CH1" s="210"/>
-      <c r="CI1" s="208">
+      <c r="CG1" s="212"/>
+      <c r="CH1" s="213"/>
+      <c r="CI1" s="211">
         <v>28</v>
       </c>
-      <c r="CJ1" s="209"/>
-      <c r="CK1" s="210"/>
-      <c r="CL1" s="208">
+      <c r="CJ1" s="212"/>
+      <c r="CK1" s="213"/>
+      <c r="CL1" s="211">
         <v>29</v>
       </c>
-      <c r="CM1" s="209"/>
-      <c r="CN1" s="210"/>
-      <c r="CO1" s="208">
+      <c r="CM1" s="212"/>
+      <c r="CN1" s="213"/>
+      <c r="CO1" s="211">
         <v>30</v>
       </c>
-      <c r="CP1" s="209"/>
-      <c r="CQ1" s="210"/>
-      <c r="CR1" s="208">
+      <c r="CP1" s="212"/>
+      <c r="CQ1" s="213"/>
+      <c r="CR1" s="211">
         <v>31</v>
       </c>
-      <c r="CS1" s="209"/>
-      <c r="CT1" s="210"/>
-      <c r="CU1" s="208">
+      <c r="CS1" s="212"/>
+      <c r="CT1" s="213"/>
+      <c r="CU1" s="211">
         <v>32</v>
       </c>
-      <c r="CV1" s="209"/>
-      <c r="CW1" s="210"/>
-      <c r="CX1" s="208">
+      <c r="CV1" s="212"/>
+      <c r="CW1" s="213"/>
+      <c r="CX1" s="211">
         <v>33</v>
       </c>
-      <c r="CY1" s="209"/>
-      <c r="CZ1" s="210"/>
-      <c r="DA1" s="208">
+      <c r="CY1" s="212"/>
+      <c r="CZ1" s="213"/>
+      <c r="DA1" s="211">
         <v>34</v>
       </c>
-      <c r="DB1" s="209"/>
-      <c r="DC1" s="210"/>
-      <c r="DD1" s="208">
+      <c r="DB1" s="212"/>
+      <c r="DC1" s="213"/>
+      <c r="DD1" s="211">
         <v>35</v>
       </c>
-      <c r="DE1" s="209"/>
-      <c r="DF1" s="210"/>
-      <c r="DG1" s="208">
+      <c r="DE1" s="212"/>
+      <c r="DF1" s="213"/>
+      <c r="DG1" s="211">
         <v>36</v>
       </c>
-      <c r="DH1" s="209"/>
-      <c r="DI1" s="210"/>
-      <c r="DJ1" s="208">
+      <c r="DH1" s="212"/>
+      <c r="DI1" s="213"/>
+      <c r="DJ1" s="211">
         <v>37</v>
       </c>
-      <c r="DK1" s="209"/>
-      <c r="DL1" s="210"/>
-      <c r="DM1" s="208">
+      <c r="DK1" s="212"/>
+      <c r="DL1" s="213"/>
+      <c r="DM1" s="211">
         <v>38</v>
       </c>
-      <c r="DN1" s="209"/>
-      <c r="DO1" s="210"/>
+      <c r="DN1" s="212"/>
+      <c r="DO1" s="213"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -38006,196 +38006,196 @@
       <c r="E2" s="214" t="s">
         <v>399</v>
       </c>
-      <c r="F2" s="211" t="s">
+      <c r="F2" s="208" t="s">
         <v>347</v>
       </c>
-      <c r="G2" s="212"/>
-      <c r="H2" s="213"/>
-      <c r="I2" s="216" t="s">
+      <c r="G2" s="209"/>
+      <c r="H2" s="210"/>
+      <c r="I2" s="217" t="s">
         <v>332</v>
       </c>
-      <c r="J2" s="217"/>
-      <c r="K2" s="218"/>
-      <c r="L2" s="211" t="s">
+      <c r="J2" s="218"/>
+      <c r="K2" s="219"/>
+      <c r="L2" s="208" t="s">
         <v>331</v>
       </c>
-      <c r="M2" s="212"/>
-      <c r="N2" s="213"/>
-      <c r="O2" s="211" t="s">
+      <c r="M2" s="209"/>
+      <c r="N2" s="210"/>
+      <c r="O2" s="208" t="s">
         <v>329</v>
       </c>
-      <c r="P2" s="212"/>
-      <c r="Q2" s="213"/>
-      <c r="R2" s="211" t="s">
+      <c r="P2" s="209"/>
+      <c r="Q2" s="210"/>
+      <c r="R2" s="208" t="s">
         <v>336</v>
       </c>
-      <c r="S2" s="212"/>
-      <c r="T2" s="213"/>
-      <c r="U2" s="211" t="s">
+      <c r="S2" s="209"/>
+      <c r="T2" s="210"/>
+      <c r="U2" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="V2" s="212"/>
-      <c r="W2" s="213"/>
-      <c r="X2" s="211" t="s">
+      <c r="V2" s="209"/>
+      <c r="W2" s="210"/>
+      <c r="X2" s="208" t="s">
         <v>338</v>
       </c>
-      <c r="Y2" s="212"/>
-      <c r="Z2" s="213"/>
-      <c r="AA2" s="211" t="s">
+      <c r="Y2" s="209"/>
+      <c r="Z2" s="210"/>
+      <c r="AA2" s="208" t="s">
         <v>335</v>
       </c>
-      <c r="AB2" s="212"/>
-      <c r="AC2" s="213"/>
-      <c r="AD2" s="211" t="s">
+      <c r="AB2" s="209"/>
+      <c r="AC2" s="210"/>
+      <c r="AD2" s="208" t="s">
         <v>322</v>
       </c>
-      <c r="AE2" s="212"/>
-      <c r="AF2" s="213"/>
-      <c r="AG2" s="211" t="s">
+      <c r="AE2" s="209"/>
+      <c r="AF2" s="210"/>
+      <c r="AG2" s="208" t="s">
         <v>348</v>
       </c>
-      <c r="AH2" s="212"/>
-      <c r="AI2" s="213"/>
-      <c r="AJ2" s="211" t="s">
+      <c r="AH2" s="209"/>
+      <c r="AI2" s="210"/>
+      <c r="AJ2" s="208" t="s">
         <v>325</v>
       </c>
-      <c r="AK2" s="212"/>
-      <c r="AL2" s="213"/>
-      <c r="AM2" s="211" t="s">
+      <c r="AK2" s="209"/>
+      <c r="AL2" s="210"/>
+      <c r="AM2" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="AN2" s="212"/>
-      <c r="AO2" s="213"/>
-      <c r="AP2" s="211" t="s">
+      <c r="AN2" s="209"/>
+      <c r="AO2" s="210"/>
+      <c r="AP2" s="208" t="s">
         <v>333</v>
       </c>
-      <c r="AQ2" s="212"/>
-      <c r="AR2" s="213"/>
-      <c r="AS2" s="211" t="s">
+      <c r="AQ2" s="209"/>
+      <c r="AR2" s="210"/>
+      <c r="AS2" s="208" t="s">
         <v>330</v>
       </c>
-      <c r="AT2" s="212"/>
-      <c r="AU2" s="213"/>
-      <c r="AV2" s="211" t="s">
+      <c r="AT2" s="209"/>
+      <c r="AU2" s="210"/>
+      <c r="AV2" s="208" t="s">
         <v>337</v>
       </c>
-      <c r="AW2" s="212"/>
-      <c r="AX2" s="213"/>
-      <c r="AY2" s="211" t="s">
+      <c r="AW2" s="209"/>
+      <c r="AX2" s="210"/>
+      <c r="AY2" s="208" t="s">
         <v>306</v>
       </c>
-      <c r="AZ2" s="212"/>
-      <c r="BA2" s="213"/>
-      <c r="BB2" s="211" t="s">
+      <c r="AZ2" s="209"/>
+      <c r="BA2" s="210"/>
+      <c r="BB2" s="208" t="s">
         <v>327</v>
       </c>
-      <c r="BC2" s="212"/>
-      <c r="BD2" s="213"/>
-      <c r="BE2" s="211" t="s">
+      <c r="BC2" s="209"/>
+      <c r="BD2" s="210"/>
+      <c r="BE2" s="208" t="s">
         <v>326</v>
       </c>
-      <c r="BF2" s="212"/>
-      <c r="BG2" s="213"/>
-      <c r="BH2" s="211" t="s">
+      <c r="BF2" s="209"/>
+      <c r="BG2" s="210"/>
+      <c r="BH2" s="208" t="s">
         <v>349</v>
       </c>
-      <c r="BI2" s="212"/>
-      <c r="BJ2" s="213"/>
-      <c r="BK2" s="211" t="s">
+      <c r="BI2" s="209"/>
+      <c r="BJ2" s="210"/>
+      <c r="BK2" s="208" t="s">
         <v>333</v>
       </c>
-      <c r="BL2" s="212"/>
-      <c r="BM2" s="213"/>
-      <c r="BN2" s="211" t="s">
+      <c r="BL2" s="209"/>
+      <c r="BM2" s="210"/>
+      <c r="BN2" s="208" t="s">
         <v>348</v>
       </c>
-      <c r="BO2" s="212"/>
-      <c r="BP2" s="213"/>
-      <c r="BQ2" s="211" t="s">
+      <c r="BO2" s="209"/>
+      <c r="BP2" s="210"/>
+      <c r="BQ2" s="208" t="s">
         <v>325</v>
       </c>
-      <c r="BR2" s="212"/>
-      <c r="BS2" s="213"/>
-      <c r="BT2" s="211" t="s">
+      <c r="BR2" s="209"/>
+      <c r="BS2" s="210"/>
+      <c r="BT2" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="BU2" s="212"/>
-      <c r="BV2" s="213"/>
-      <c r="BW2" s="211" t="s">
+      <c r="BU2" s="209"/>
+      <c r="BV2" s="210"/>
+      <c r="BW2" s="208" t="s">
         <v>322</v>
       </c>
-      <c r="BX2" s="212"/>
-      <c r="BY2" s="213"/>
-      <c r="BZ2" s="211" t="s">
+      <c r="BX2" s="209"/>
+      <c r="BY2" s="210"/>
+      <c r="BZ2" s="208" t="s">
         <v>349</v>
       </c>
-      <c r="CA2" s="212"/>
-      <c r="CB2" s="213"/>
-      <c r="CC2" s="211" t="s">
+      <c r="CA2" s="209"/>
+      <c r="CB2" s="210"/>
+      <c r="CC2" s="208" t="s">
         <v>326</v>
       </c>
-      <c r="CD2" s="212"/>
-      <c r="CE2" s="213"/>
-      <c r="CF2" s="211" t="s">
+      <c r="CD2" s="209"/>
+      <c r="CE2" s="210"/>
+      <c r="CF2" s="208" t="s">
         <v>306</v>
       </c>
-      <c r="CG2" s="212"/>
-      <c r="CH2" s="213"/>
-      <c r="CI2" s="211" t="s">
+      <c r="CG2" s="209"/>
+      <c r="CH2" s="210"/>
+      <c r="CI2" s="208" t="s">
         <v>327</v>
       </c>
-      <c r="CJ2" s="212"/>
-      <c r="CK2" s="213"/>
-      <c r="CL2" s="211" t="s">
+      <c r="CJ2" s="209"/>
+      <c r="CK2" s="210"/>
+      <c r="CL2" s="208" t="s">
         <v>331</v>
       </c>
-      <c r="CM2" s="212"/>
-      <c r="CN2" s="213"/>
-      <c r="CO2" s="211" t="s">
+      <c r="CM2" s="209"/>
+      <c r="CN2" s="210"/>
+      <c r="CO2" s="208" t="s">
         <v>329</v>
       </c>
-      <c r="CP2" s="212"/>
-      <c r="CQ2" s="213"/>
-      <c r="CR2" s="211" t="s">
+      <c r="CP2" s="209"/>
+      <c r="CQ2" s="210"/>
+      <c r="CR2" s="208" t="s">
         <v>347</v>
       </c>
-      <c r="CS2" s="212"/>
-      <c r="CT2" s="213"/>
-      <c r="CU2" s="211" t="s">
+      <c r="CS2" s="209"/>
+      <c r="CT2" s="210"/>
+      <c r="CU2" s="208" t="s">
         <v>332</v>
       </c>
-      <c r="CV2" s="212"/>
-      <c r="CW2" s="213"/>
-      <c r="CX2" s="211" t="s">
+      <c r="CV2" s="209"/>
+      <c r="CW2" s="210"/>
+      <c r="CX2" s="208" t="s">
         <v>337</v>
       </c>
-      <c r="CY2" s="212"/>
-      <c r="CZ2" s="213"/>
-      <c r="DA2" s="211" t="s">
+      <c r="CY2" s="209"/>
+      <c r="CZ2" s="210"/>
+      <c r="DA2" s="208" t="s">
         <v>330</v>
       </c>
-      <c r="DB2" s="212"/>
-      <c r="DC2" s="213"/>
-      <c r="DD2" s="211" t="s">
+      <c r="DB2" s="209"/>
+      <c r="DC2" s="210"/>
+      <c r="DD2" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="DE2" s="212"/>
-      <c r="DF2" s="213"/>
-      <c r="DG2" s="211" t="s">
+      <c r="DE2" s="209"/>
+      <c r="DF2" s="210"/>
+      <c r="DG2" s="208" t="s">
         <v>338</v>
       </c>
-      <c r="DH2" s="212"/>
-      <c r="DI2" s="213"/>
-      <c r="DJ2" s="211" t="s">
+      <c r="DH2" s="209"/>
+      <c r="DI2" s="210"/>
+      <c r="DJ2" s="208" t="s">
         <v>335</v>
       </c>
-      <c r="DK2" s="212"/>
-      <c r="DL2" s="213"/>
-      <c r="DM2" s="211" t="s">
+      <c r="DK2" s="209"/>
+      <c r="DL2" s="210"/>
+      <c r="DM2" s="208" t="s">
         <v>336</v>
       </c>
-      <c r="DN2" s="212"/>
-      <c r="DO2" s="213"/>
+      <c r="DN2" s="209"/>
+      <c r="DO2" s="210"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38204,9 +38204,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="219"/>
-      <c r="D3" s="219"/>
-      <c r="E3" s="215"/>
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="216"/>
       <c r="F3" s="160" t="s">
         <v>394</v>
       </c>
@@ -38694,15 +38694,15 @@
         <v>196</v>
       </c>
       <c r="C5" s="58">
-        <f t="shared" ref="C5:C41" si="1">SUM(F5,I5,L5,O5,R5,U5,X5,AA5,AD5,AG5,AJ5,AM5,AP5,AS5,AV5,AY5,BB5,BE5,BH5,BK5,BN5,BQ5,BT5,BW5,BZ5,CC5,CF5,CI5,CL5,CO5,CR5,CU5,CX5,DA5,DD5,DG5,DJ5,DM5)</f>
+        <f t="shared" ref="C5:C17" si="1">SUM(F5,I5,L5,O5,R5,U5,X5,AA5,AD5,AG5,AJ5,AM5,AP5,AS5,AV5,AY5,BB5,BE5,BH5,BK5,BN5,BQ5,BT5,BW5,BZ5,CC5,CF5,CI5,CL5,CO5,CR5,CU5,CX5,DA5,DD5,DG5,DJ5,DM5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="58">
-        <f t="shared" ref="D5:D41" si="2">SUM(G5,J5,M5,P5,S5,V5,Y5,AB5,AE5,AH5,AK5,AN5,AQ5,AT5,AW5,AZ5,BC5,BF5,BI5,BL5,BO5,BR5,BU5,BX5,CA5,CD5,CG5,CJ5,CM5,CP5,CS5,CV5,CY5,DB5,DE5,DH5,DK5,DN5)</f>
+        <f t="shared" ref="D5:D17" si="2">SUM(G5,J5,M5,P5,S5,V5,Y5,AB5,AE5,AH5,AK5,AN5,AQ5,AT5,AW5,AZ5,BC5,BF5,BI5,BL5,BO5,BR5,BU5,BX5,CA5,CD5,CG5,CJ5,CM5,CP5,CS5,CV5,CY5,DB5,DE5,DH5,DK5,DN5)</f>
         <v>0</v>
       </c>
       <c r="E5" s="58">
-        <f t="shared" ref="E5:E41" si="3">SUM(H5,K5,N5,Q5,T5,W5,Z5,AC5,AF5,AI5,AL5,AO5,AR5,AU5,AX5,BA5,BD5,BG5,BJ5,BM5,BP5,BS5,BV5,BY5,CB5,CE5,CH5,CK5,CN5,CQ5,CT5,CW5,CZ5,DC5,DF5,DI5,DL5,DO5)</f>
+        <f t="shared" ref="E5:E17" si="3">SUM(H5,K5,N5,Q5,T5,W5,Z5,AC5,AF5,AI5,AL5,AO5,AR5,AU5,AX5,BA5,BD5,BG5,BJ5,BM5,BP5,BS5,BV5,BY5,CB5,CE5,CH5,CK5,CN5,CQ5,CT5,CW5,CZ5,DC5,DF5,DI5,DL5,DO5)</f>
         <v>0</v>
       </c>
       <c r="F5" s="52"/>
@@ -44149,6 +44149,69 @@
     </row>
   </sheetData>
   <mergeCells count="79">
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -44165,69 +44228,6 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO41">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -44263,41 +44263,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="229" t="s">
+      <c r="C1" s="232" t="s">
         <v>397</v>
       </c>
-      <c r="D1" s="229" t="s">
+      <c r="D1" s="232" t="s">
         <v>398</v>
       </c>
-      <c r="E1" s="229" t="s">
+      <c r="E1" s="232" t="s">
         <v>399</v>
       </c>
-      <c r="F1" s="220" t="s">
+      <c r="F1" s="223" t="s">
         <v>303</v>
       </c>
-      <c r="G1" s="221"/>
-      <c r="H1" s="221"/>
-      <c r="I1" s="221"/>
-      <c r="J1" s="221"/>
-      <c r="K1" s="221"/>
-      <c r="L1" s="221"/>
-      <c r="M1" s="221"/>
-      <c r="N1" s="221"/>
-      <c r="O1" s="221"/>
-      <c r="P1" s="221"/>
-      <c r="Q1" s="221"/>
-      <c r="R1" s="221"/>
-      <c r="S1" s="221"/>
-      <c r="T1" s="221"/>
-      <c r="U1" s="221"/>
-      <c r="V1" s="221"/>
-      <c r="W1" s="221"/>
-      <c r="X1" s="221"/>
-      <c r="Y1" s="221"/>
-      <c r="Z1" s="221"/>
-      <c r="AA1" s="221"/>
-      <c r="AB1" s="221"/>
-      <c r="AC1" s="222"/>
+      <c r="G1" s="224"/>
+      <c r="H1" s="224"/>
+      <c r="I1" s="224"/>
+      <c r="J1" s="224"/>
+      <c r="K1" s="224"/>
+      <c r="L1" s="224"/>
+      <c r="M1" s="224"/>
+      <c r="N1" s="224"/>
+      <c r="O1" s="224"/>
+      <c r="P1" s="224"/>
+      <c r="Q1" s="224"/>
+      <c r="R1" s="224"/>
+      <c r="S1" s="224"/>
+      <c r="T1" s="224"/>
+      <c r="U1" s="224"/>
+      <c r="V1" s="224"/>
+      <c r="W1" s="224"/>
+      <c r="X1" s="224"/>
+      <c r="Y1" s="224"/>
+      <c r="Z1" s="224"/>
+      <c r="AA1" s="224"/>
+      <c r="AB1" s="224"/>
+      <c r="AC1" s="225"/>
       <c r="AD1" s="235" t="s">
         <v>282</v>
       </c>
@@ -44306,79 +44306,79 @@
       <c r="AG1" s="236"/>
       <c r="AH1" s="236"/>
       <c r="AI1" s="237"/>
-      <c r="AJ1" s="220" t="s">
+      <c r="AJ1" s="223" t="s">
         <v>283</v>
       </c>
-      <c r="AK1" s="221"/>
-      <c r="AL1" s="221"/>
-      <c r="AM1" s="221"/>
-      <c r="AN1" s="221"/>
-      <c r="AO1" s="222"/>
-      <c r="AP1" s="223" t="s">
+      <c r="AK1" s="224"/>
+      <c r="AL1" s="224"/>
+      <c r="AM1" s="224"/>
+      <c r="AN1" s="224"/>
+      <c r="AO1" s="225"/>
+      <c r="AP1" s="226" t="s">
         <v>284</v>
       </c>
-      <c r="AQ1" s="224"/>
-      <c r="AR1" s="224"/>
-      <c r="AS1" s="224"/>
-      <c r="AT1" s="224"/>
-      <c r="AU1" s="225"/>
-      <c r="AV1" s="226" t="s">
+      <c r="AQ1" s="227"/>
+      <c r="AR1" s="227"/>
+      <c r="AS1" s="227"/>
+      <c r="AT1" s="227"/>
+      <c r="AU1" s="228"/>
+      <c r="AV1" s="229" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="227"/>
-      <c r="AX1" s="228"/>
+      <c r="AW1" s="230"/>
+      <c r="AX1" s="231"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="230"/>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="233"/>
-      <c r="H2" s="234"/>
-      <c r="I2" s="232"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="232"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="234"/>
-      <c r="O2" s="232"/>
-      <c r="P2" s="233"/>
-      <c r="Q2" s="234"/>
-      <c r="R2" s="232"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="234"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="234"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="233"/>
-      <c r="Z2" s="234"/>
-      <c r="AA2" s="232"/>
-      <c r="AB2" s="233"/>
-      <c r="AC2" s="233"/>
-      <c r="AD2" s="232"/>
-      <c r="AE2" s="233"/>
-      <c r="AF2" s="234"/>
-      <c r="AG2" s="232"/>
-      <c r="AH2" s="233"/>
-      <c r="AI2" s="234"/>
-      <c r="AJ2" s="232"/>
-      <c r="AK2" s="233"/>
-      <c r="AL2" s="234"/>
-      <c r="AM2" s="232"/>
-      <c r="AN2" s="233"/>
-      <c r="AO2" s="234"/>
-      <c r="AP2" s="232"/>
-      <c r="AQ2" s="233"/>
-      <c r="AR2" s="234"/>
-      <c r="AS2" s="232"/>
-      <c r="AT2" s="233"/>
-      <c r="AU2" s="234"/>
-      <c r="AV2" s="232"/>
-      <c r="AW2" s="233"/>
-      <c r="AX2" s="234"/>
+      <c r="C2" s="233"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="220"/>
+      <c r="G2" s="221"/>
+      <c r="H2" s="222"/>
+      <c r="I2" s="220"/>
+      <c r="J2" s="221"/>
+      <c r="K2" s="222"/>
+      <c r="L2" s="220"/>
+      <c r="M2" s="221"/>
+      <c r="N2" s="222"/>
+      <c r="O2" s="220"/>
+      <c r="P2" s="221"/>
+      <c r="Q2" s="222"/>
+      <c r="R2" s="220"/>
+      <c r="S2" s="221"/>
+      <c r="T2" s="222"/>
+      <c r="U2" s="220"/>
+      <c r="V2" s="221"/>
+      <c r="W2" s="222"/>
+      <c r="X2" s="220"/>
+      <c r="Y2" s="221"/>
+      <c r="Z2" s="222"/>
+      <c r="AA2" s="220"/>
+      <c r="AB2" s="221"/>
+      <c r="AC2" s="221"/>
+      <c r="AD2" s="220"/>
+      <c r="AE2" s="221"/>
+      <c r="AF2" s="222"/>
+      <c r="AG2" s="220"/>
+      <c r="AH2" s="221"/>
+      <c r="AI2" s="222"/>
+      <c r="AJ2" s="220"/>
+      <c r="AK2" s="221"/>
+      <c r="AL2" s="222"/>
+      <c r="AM2" s="220"/>
+      <c r="AN2" s="221"/>
+      <c r="AO2" s="222"/>
+      <c r="AP2" s="220"/>
+      <c r="AQ2" s="221"/>
+      <c r="AR2" s="222"/>
+      <c r="AS2" s="220"/>
+      <c r="AT2" s="221"/>
+      <c r="AU2" s="222"/>
+      <c r="AV2" s="220"/>
+      <c r="AW2" s="221"/>
+      <c r="AX2" s="222"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -44387,9 +44387,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="231"/>
-      <c r="D3" s="231"/>
-      <c r="E3" s="231"/>
+      <c r="C3" s="234"/>
+      <c r="D3" s="234"/>
+      <c r="E3" s="234"/>
       <c r="F3" s="170" t="s">
         <v>394</v>
       </c>
@@ -44599,15 +44599,15 @@
         <v>196</v>
       </c>
       <c r="C5" s="58">
-        <f t="shared" ref="C5:C41" si="1">SUM(F5,I5,L5,O5,R5,X5,AA5,AD5,U5,AG5,AJ5,AM5,AP5,AS5,AV5)</f>
+        <f t="shared" ref="C5:C17" si="1">SUM(F5,I5,L5,O5,R5,X5,AA5,AD5,U5,AG5,AJ5,AM5,AP5,AS5,AV5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="58">
-        <f t="shared" ref="D5:D41" si="2">SUM(G5,J5,M5,P5,S5,Y5,AB5,AE5,V5,AH5,AK5,AN5,AQ5,AT5,AW5)</f>
+        <f t="shared" ref="D5:D17" si="2">SUM(G5,J5,M5,P5,S5,Y5,AB5,AE5,V5,AH5,AK5,AN5,AQ5,AT5,AW5)</f>
         <v>0</v>
       </c>
       <c r="E5" s="58">
-        <f t="shared" ref="E5:E41" si="3">SUM(H5,K5,N5,Q5,T5,Z5,AC5,AF5,W5,AI5,AL5,AO5,AR5,AU5,AX5)</f>
+        <f t="shared" ref="E5:E17" si="3">SUM(H5,K5,N5,Q5,T5,Z5,AC5,AF5,W5,AI5,AL5,AO5,AR5,AU5,AX5)</f>
         <v>0</v>
       </c>
       <c r="F5" s="52"/>
@@ -47180,13 +47180,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -47203,6 +47196,13 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW32">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -47237,70 +47237,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="229" t="s">
+      <c r="C1" s="232" t="s">
         <v>397</v>
       </c>
-      <c r="D1" s="229" t="s">
+      <c r="D1" s="232" t="s">
         <v>398</v>
       </c>
-      <c r="E1" s="229" t="s">
+      <c r="E1" s="232" t="s">
         <v>399</v>
       </c>
-      <c r="F1" s="269" t="s">
+      <c r="F1" s="262" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="270"/>
-      <c r="H1" s="271"/>
-      <c r="I1" s="272" t="s">
+      <c r="G1" s="263"/>
+      <c r="H1" s="264"/>
+      <c r="I1" s="265" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="273"/>
-      <c r="K1" s="274"/>
-      <c r="L1" s="239" t="s">
+      <c r="J1" s="266"/>
+      <c r="K1" s="267"/>
+      <c r="L1" s="269" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="240"/>
-      <c r="N1" s="241"/>
-      <c r="O1" s="242" t="s">
+      <c r="M1" s="270"/>
+      <c r="N1" s="271"/>
+      <c r="O1" s="272" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="243"/>
-      <c r="Q1" s="244"/>
-      <c r="R1" s="245" t="s">
+      <c r="P1" s="273"/>
+      <c r="Q1" s="274"/>
+      <c r="R1" s="238" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="246"/>
-      <c r="T1" s="247"/>
-      <c r="U1" s="248" t="s">
+      <c r="S1" s="239"/>
+      <c r="T1" s="240"/>
+      <c r="U1" s="241" t="s">
         <v>307</v>
       </c>
-      <c r="V1" s="249"/>
-      <c r="W1" s="250"/>
+      <c r="V1" s="242"/>
+      <c r="W1" s="243"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="230"/>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="252"/>
-      <c r="H2" s="253"/>
-      <c r="I2" s="266"/>
-      <c r="J2" s="267"/>
-      <c r="K2" s="268"/>
-      <c r="L2" s="263"/>
-      <c r="M2" s="264"/>
-      <c r="N2" s="265"/>
-      <c r="O2" s="260"/>
-      <c r="P2" s="261"/>
-      <c r="Q2" s="262"/>
-      <c r="R2" s="257"/>
-      <c r="S2" s="258"/>
-      <c r="T2" s="259"/>
-      <c r="U2" s="254"/>
-      <c r="V2" s="255"/>
-      <c r="W2" s="256"/>
+      <c r="C2" s="233"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="244"/>
+      <c r="G2" s="245"/>
+      <c r="H2" s="246"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="260"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="256"/>
+      <c r="M2" s="257"/>
+      <c r="N2" s="258"/>
+      <c r="O2" s="253"/>
+      <c r="P2" s="254"/>
+      <c r="Q2" s="255"/>
+      <c r="R2" s="250"/>
+      <c r="S2" s="251"/>
+      <c r="T2" s="252"/>
+      <c r="U2" s="247"/>
+      <c r="V2" s="248"/>
+      <c r="W2" s="249"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -47309,9 +47309,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="238"/>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
+      <c r="C3" s="268"/>
+      <c r="D3" s="268"/>
+      <c r="E3" s="268"/>
       <c r="F3" s="189" t="s">
         <v>394</v>
       </c>
@@ -47413,7 +47413,7 @@
         <v>196</v>
       </c>
       <c r="C5" s="58">
-        <f t="shared" ref="C5:C17" si="1">SUM(F5,I5,L5,O5,R5,U5)</f>
+        <f t="shared" ref="C5" si="1">SUM(F5,I5,L5,O5,R5,U5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="58">
@@ -47459,7 +47459,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="58">
-        <f t="shared" ref="E6:E41" si="4">SUM(H6,K6,N6,Q6,T6,W6)</f>
+        <f t="shared" ref="E6:E40" si="4">SUM(H6,K6,N6,Q6,T6,W6)</f>
         <v>0</v>
       </c>
       <c r="F6" s="52"/>
@@ -48781,11 +48781,11 @@
         <v>302</v>
       </c>
       <c r="C41" s="164">
-        <f t="shared" ref="C30:C41" si="5">SUM(F41,I41,L41,O41,R41,U41)</f>
+        <f t="shared" ref="C41" si="5">SUM(F41,I41,L41,O41,R41,U41)</f>
         <v>0</v>
       </c>
       <c r="D41" s="192">
-        <f t="shared" ref="D30:E41" si="6">SUM(G41,J41,M41,P41,S41,V41)</f>
+        <f t="shared" ref="D41:E41" si="6">SUM(G41,J41,M41,P41,S41,V41)</f>
         <v>0</v>
       </c>
       <c r="E41" s="192">
@@ -48887,6 +48887,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -48897,11 +48902,6 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -49342,15 +49342,15 @@
         <v>0</v>
       </c>
       <c r="J7" s="25">
-        <f t="shared" ref="J7:J43" si="0">G7+C7</f>
+        <f t="shared" ref="J7:J19" si="0">G7+C7</f>
         <v>131</v>
       </c>
       <c r="K7" s="25">
-        <f t="shared" ref="K7:K43" si="1">H7+D7</f>
+        <f t="shared" ref="K7:K19" si="1">H7+D7</f>
         <v>7</v>
       </c>
       <c r="L7" s="25">
-        <f t="shared" ref="L7:L43" si="2">I7+E7</f>
+        <f t="shared" ref="L7:L19" si="2">I7+E7</f>
         <v>2</v>
       </c>
       <c r="N7" s="45" t="s">
@@ -49379,15 +49379,15 @@
         <v>0</v>
       </c>
       <c r="V7" s="26">
-        <f t="shared" ref="V7:V42" si="3">S7+O7</f>
+        <f t="shared" ref="V7:V19" si="3">S7+O7</f>
         <v>37</v>
       </c>
       <c r="W7" s="26">
-        <f t="shared" ref="W7:W42" si="4">T7+P7</f>
+        <f t="shared" ref="W7:W19" si="4">T7+P7</f>
         <v>1</v>
       </c>
       <c r="X7" s="26">
-        <f t="shared" ref="X7:X42" si="5">U7+Q7</f>
+        <f t="shared" ref="X7:X19" si="5">U7+Q7</f>
         <v>0</v>
       </c>
       <c r="Z7" s="23" t="s">
@@ -49416,15 +49416,15 @@
         <v>0</v>
       </c>
       <c r="AH7" s="24">
-        <f t="shared" ref="AH7:AH43" si="6">AE7+AA7</f>
+        <f t="shared" ref="AH7:AH19" si="6">AE7+AA7</f>
         <v>5</v>
       </c>
       <c r="AI7" s="24">
-        <f t="shared" ref="AI7:AI43" si="7">AF7+AB7</f>
+        <f t="shared" ref="AI7:AI19" si="7">AF7+AB7</f>
         <v>0</v>
       </c>
       <c r="AJ7" s="24">
-        <f t="shared" ref="AJ7:AJ43" si="8">AG7+AC7</f>
+        <f t="shared" ref="AJ7:AJ19" si="8">AG7+AC7</f>
         <v>0</v>
       </c>
       <c r="AL7" s="63" t="s">
@@ -49453,15 +49453,15 @@
         <v>0</v>
       </c>
       <c r="AT7" s="18">
-        <f t="shared" ref="AT7:AT43" si="9">AQ7+AM7</f>
+        <f t="shared" ref="AT7:AT19" si="9">AQ7+AM7</f>
         <v>10</v>
       </c>
       <c r="AU7" s="18">
-        <f t="shared" ref="AU7:AU43" si="10">AR7+AN7</f>
+        <f t="shared" ref="AU7:AU19" si="10">AR7+AN7</f>
         <v>0</v>
       </c>
       <c r="AV7" s="18">
-        <f t="shared" ref="AV7:AV43" si="11">AS7+AO7</f>
+        <f t="shared" ref="AV7:AV19" si="11">AS7+AO7</f>
         <v>1</v>
       </c>
       <c r="AX7" s="32" t="s">
@@ -49490,15 +49490,15 @@
         <v>0</v>
       </c>
       <c r="BF7" s="33">
-        <f t="shared" ref="BF7:BF43" si="12">BC7+AY7</f>
+        <f t="shared" ref="BF7:BF19" si="12">BC7+AY7</f>
         <v>1</v>
       </c>
       <c r="BG7" s="33">
-        <f t="shared" ref="BG7:BG43" si="13">BD7+AZ7</f>
+        <f t="shared" ref="BG7:BG19" si="13">BD7+AZ7</f>
         <v>0</v>
       </c>
       <c r="BH7" s="33">
-        <f t="shared" ref="BH7:BH43" si="14">BE7+BA7</f>
+        <f t="shared" ref="BH7:BH19" si="14">BE7+BA7</f>
         <v>0</v>
       </c>
     </row>
@@ -56373,70 +56373,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="229" t="s">
+      <c r="C1" s="232" t="s">
         <v>397</v>
       </c>
-      <c r="D1" s="229" t="s">
+      <c r="D1" s="232" t="s">
         <v>398</v>
       </c>
-      <c r="E1" s="229" t="s">
+      <c r="E1" s="232" t="s">
         <v>399</v>
       </c>
-      <c r="F1" s="269" t="s">
+      <c r="F1" s="262" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="270"/>
-      <c r="H1" s="271"/>
-      <c r="I1" s="272" t="s">
+      <c r="G1" s="263"/>
+      <c r="H1" s="264"/>
+      <c r="I1" s="265" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="273"/>
-      <c r="K1" s="274"/>
-      <c r="L1" s="239" t="s">
+      <c r="J1" s="266"/>
+      <c r="K1" s="267"/>
+      <c r="L1" s="269" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="240"/>
-      <c r="N1" s="241"/>
-      <c r="O1" s="242" t="s">
+      <c r="M1" s="270"/>
+      <c r="N1" s="271"/>
+      <c r="O1" s="272" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="243"/>
-      <c r="Q1" s="244"/>
-      <c r="R1" s="245" t="s">
+      <c r="P1" s="273"/>
+      <c r="Q1" s="274"/>
+      <c r="R1" s="238" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="246"/>
-      <c r="T1" s="247"/>
-      <c r="U1" s="248" t="s">
+      <c r="S1" s="239"/>
+      <c r="T1" s="240"/>
+      <c r="U1" s="241" t="s">
         <v>307</v>
       </c>
-      <c r="V1" s="249"/>
-      <c r="W1" s="250"/>
+      <c r="V1" s="242"/>
+      <c r="W1" s="243"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="230"/>
-      <c r="D2" s="230"/>
-      <c r="E2" s="230"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="252"/>
-      <c r="H2" s="253"/>
-      <c r="I2" s="266"/>
-      <c r="J2" s="267"/>
-      <c r="K2" s="268"/>
-      <c r="L2" s="263"/>
-      <c r="M2" s="264"/>
-      <c r="N2" s="265"/>
-      <c r="O2" s="260"/>
-      <c r="P2" s="261"/>
-      <c r="Q2" s="262"/>
-      <c r="R2" s="257"/>
-      <c r="S2" s="258"/>
-      <c r="T2" s="259"/>
-      <c r="U2" s="254"/>
-      <c r="V2" s="255"/>
-      <c r="W2" s="256"/>
+      <c r="C2" s="233"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="244"/>
+      <c r="G2" s="245"/>
+      <c r="H2" s="246"/>
+      <c r="I2" s="259"/>
+      <c r="J2" s="260"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="256"/>
+      <c r="M2" s="257"/>
+      <c r="N2" s="258"/>
+      <c r="O2" s="253"/>
+      <c r="P2" s="254"/>
+      <c r="Q2" s="255"/>
+      <c r="R2" s="250"/>
+      <c r="S2" s="251"/>
+      <c r="T2" s="252"/>
+      <c r="U2" s="247"/>
+      <c r="V2" s="248"/>
+      <c r="W2" s="249"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -56445,9 +56445,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="238"/>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
+      <c r="C3" s="268"/>
+      <c r="D3" s="268"/>
+      <c r="E3" s="268"/>
       <c r="F3" s="189" t="s">
         <v>394</v>
       </c>
@@ -56549,7 +56549,7 @@
         <v>196</v>
       </c>
       <c r="C5" s="58">
-        <f t="shared" ref="C5:E21" si="1">SUM(F5,I5,L5,O5,R5,U5)</f>
+        <f t="shared" ref="C5:E17" si="1">SUM(F5,I5,L5,O5,R5,U5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="58">
@@ -58023,11 +58023,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -58038,6 +58033,11 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -58577,51 +58577,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="283" t="s">
+      <c r="C1" s="278" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="285"/>
+      <c r="D1" s="279"/>
+      <c r="E1" s="279"/>
+      <c r="F1" s="279"/>
+      <c r="G1" s="279"/>
+      <c r="H1" s="279"/>
+      <c r="I1" s="280"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="277" t="s">
+      <c r="L1" s="311" t="s">
         <v>288</v>
       </c>
-      <c r="M1" s="281"/>
-      <c r="N1" s="281"/>
-      <c r="O1" s="281"/>
-      <c r="P1" s="281"/>
-      <c r="Q1" s="281"/>
-      <c r="R1" s="281"/>
-      <c r="S1" s="281"/>
-      <c r="T1" s="281"/>
-      <c r="U1" s="281"/>
-      <c r="V1" s="281"/>
-      <c r="W1" s="281"/>
-      <c r="X1" s="281"/>
-      <c r="Y1" s="281"/>
-      <c r="Z1" s="281"/>
-      <c r="AA1" s="281"/>
-      <c r="AB1" s="281"/>
-      <c r="AC1" s="281"/>
-      <c r="AD1" s="281"/>
-      <c r="AE1" s="281"/>
-      <c r="AF1" s="281"/>
-      <c r="AG1" s="282"/>
-      <c r="AH1" s="277" t="s">
+      <c r="M1" s="314"/>
+      <c r="N1" s="314"/>
+      <c r="O1" s="314"/>
+      <c r="P1" s="314"/>
+      <c r="Q1" s="314"/>
+      <c r="R1" s="314"/>
+      <c r="S1" s="314"/>
+      <c r="T1" s="314"/>
+      <c r="U1" s="314"/>
+      <c r="V1" s="314"/>
+      <c r="W1" s="314"/>
+      <c r="X1" s="314"/>
+      <c r="Y1" s="314"/>
+      <c r="Z1" s="314"/>
+      <c r="AA1" s="314"/>
+      <c r="AB1" s="314"/>
+      <c r="AC1" s="314"/>
+      <c r="AD1" s="314"/>
+      <c r="AE1" s="314"/>
+      <c r="AF1" s="314"/>
+      <c r="AG1" s="315"/>
+      <c r="AH1" s="311" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="278"/>
-      <c r="AJ1" s="278"/>
-      <c r="AK1" s="279"/>
+      <c r="AI1" s="312"/>
+      <c r="AJ1" s="312"/>
+      <c r="AK1" s="313"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -63809,15 +63809,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="307" t="s">
+      <c r="K80" s="302" t="s">
         <v>175</v>
       </c>
-      <c r="L80" s="308"/>
-      <c r="M80" s="309"/>
+      <c r="L80" s="303"/>
+      <c r="M80" s="304"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="280"/>
-      <c r="X80" s="280"/>
+      <c r="W80" s="277"/>
+      <c r="X80" s="277"/>
       <c r="Y80" s="70" t="s">
         <v>212</v>
       </c>
@@ -63867,15 +63867,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="310"/>
-      <c r="L81" s="311"/>
-      <c r="M81" s="312"/>
+      <c r="K81" s="305"/>
+      <c r="L81" s="306"/>
+      <c r="M81" s="307"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="280" t="s">
+      <c r="W81" s="277" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="280"/>
+      <c r="X81" s="277"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -63931,15 +63931,15 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="310"/>
-      <c r="L82" s="311"/>
-      <c r="M82" s="312"/>
+      <c r="K82" s="305"/>
+      <c r="L82" s="306"/>
+      <c r="M82" s="307"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="280" t="s">
+      <c r="W82" s="277" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="280"/>
+      <c r="X82" s="277"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -63995,15 +63995,15 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="313"/>
-      <c r="L83" s="314"/>
-      <c r="M83" s="315"/>
+      <c r="K83" s="308"/>
+      <c r="L83" s="309"/>
+      <c r="M83" s="310"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="280" t="s">
+      <c r="W83" s="277" t="s">
         <v>211</v>
       </c>
-      <c r="X83" s="280"/>
+      <c r="X83" s="277"/>
       <c r="Y83" s="70">
         <f>COUNTIF(J16:J20,3)</f>
         <v>1</v>
@@ -64059,17 +64059,17 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="298" t="s">
+      <c r="K84" s="293" t="s">
         <v>285</v>
       </c>
-      <c r="L84" s="299"/>
-      <c r="M84" s="300"/>
+      <c r="L84" s="294"/>
+      <c r="M84" s="295"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="280" t="s">
+      <c r="W84" s="277" t="s">
         <v>97</v>
       </c>
-      <c r="X84" s="280"/>
+      <c r="X84" s="277"/>
       <c r="Y84" s="70">
         <f>COUNTIF(J21:J40,3)+COUNTIF(I3:I40,3)+COUNTIF(H3:H40,3)+COUNTIF(G3:G40,3)+COUNTIF(F3:F40,3)+COUNTIF(E3:E40,3)</f>
         <v>123</v>
@@ -64125,9 +64125,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="301"/>
-      <c r="L85" s="302"/>
-      <c r="M85" s="303"/>
+      <c r="K85" s="296"/>
+      <c r="L85" s="297"/>
+      <c r="M85" s="298"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -64161,9 +64161,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="301"/>
-      <c r="L86" s="302"/>
-      <c r="M86" s="303"/>
+      <c r="K86" s="296"/>
+      <c r="L86" s="297"/>
+      <c r="M86" s="298"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -64197,9 +64197,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="301"/>
-      <c r="L87" s="302"/>
-      <c r="M87" s="303"/>
+      <c r="K87" s="296"/>
+      <c r="L87" s="297"/>
+      <c r="M87" s="298"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -64233,9 +64233,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="301"/>
-      <c r="L88" s="302"/>
-      <c r="M88" s="303"/>
+      <c r="K88" s="296"/>
+      <c r="L88" s="297"/>
+      <c r="M88" s="298"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -64269,9 +64269,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="301"/>
-      <c r="L89" s="302"/>
-      <c r="M89" s="303"/>
+      <c r="K89" s="296"/>
+      <c r="L89" s="297"/>
+      <c r="M89" s="298"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -64305,9 +64305,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="301"/>
-      <c r="L90" s="302"/>
-      <c r="M90" s="303"/>
+      <c r="K90" s="296"/>
+      <c r="L90" s="297"/>
+      <c r="M90" s="298"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -64341,9 +64341,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="301"/>
-      <c r="L91" s="302"/>
-      <c r="M91" s="303"/>
+      <c r="K91" s="296"/>
+      <c r="L91" s="297"/>
+      <c r="M91" s="298"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -64377,9 +64377,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="301"/>
-      <c r="L92" s="302"/>
-      <c r="M92" s="303"/>
+      <c r="K92" s="296"/>
+      <c r="L92" s="297"/>
+      <c r="M92" s="298"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -64413,9 +64413,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="301"/>
-      <c r="L93" s="302"/>
-      <c r="M93" s="303"/>
+      <c r="K93" s="296"/>
+      <c r="L93" s="297"/>
+      <c r="M93" s="298"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -64449,9 +64449,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="301"/>
-      <c r="L94" s="302"/>
-      <c r="M94" s="303"/>
+      <c r="K94" s="296"/>
+      <c r="L94" s="297"/>
+      <c r="M94" s="298"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -64485,9 +64485,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="301"/>
-      <c r="L95" s="302"/>
-      <c r="M95" s="303"/>
+      <c r="K95" s="296"/>
+      <c r="L95" s="297"/>
+      <c r="M95" s="298"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -64521,9 +64521,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="301"/>
-      <c r="L96" s="302"/>
-      <c r="M96" s="303"/>
+      <c r="K96" s="296"/>
+      <c r="L96" s="297"/>
+      <c r="M96" s="298"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -64557,9 +64557,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="301"/>
-      <c r="L97" s="302"/>
-      <c r="M97" s="303"/>
+      <c r="K97" s="296"/>
+      <c r="L97" s="297"/>
+      <c r="M97" s="298"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -64593,9 +64593,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="301"/>
-      <c r="L98" s="302"/>
-      <c r="M98" s="303"/>
+      <c r="K98" s="296"/>
+      <c r="L98" s="297"/>
+      <c r="M98" s="298"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -64629,9 +64629,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="301"/>
-      <c r="L99" s="302"/>
-      <c r="M99" s="303"/>
+      <c r="K99" s="296"/>
+      <c r="L99" s="297"/>
+      <c r="M99" s="298"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -64665,9 +64665,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="301"/>
-      <c r="L100" s="302"/>
-      <c r="M100" s="303"/>
+      <c r="K100" s="296"/>
+      <c r="L100" s="297"/>
+      <c r="M100" s="298"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -64701,9 +64701,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="301"/>
-      <c r="L101" s="302"/>
-      <c r="M101" s="303"/>
+      <c r="K101" s="296"/>
+      <c r="L101" s="297"/>
+      <c r="M101" s="298"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -64737,9 +64737,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="301"/>
-      <c r="L102" s="302"/>
-      <c r="M102" s="303"/>
+      <c r="K102" s="296"/>
+      <c r="L102" s="297"/>
+      <c r="M102" s="298"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -64773,9 +64773,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="301"/>
-      <c r="L103" s="302"/>
-      <c r="M103" s="303"/>
+      <c r="K103" s="296"/>
+      <c r="L103" s="297"/>
+      <c r="M103" s="298"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -64809,9 +64809,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="301"/>
-      <c r="L104" s="302"/>
-      <c r="M104" s="303"/>
+      <c r="K104" s="296"/>
+      <c r="L104" s="297"/>
+      <c r="M104" s="298"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -64845,9 +64845,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="304"/>
-      <c r="L105" s="305"/>
-      <c r="M105" s="306"/>
+      <c r="K105" s="299"/>
+      <c r="L105" s="300"/>
+      <c r="M105" s="301"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -64881,11 +64881,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="295" t="s">
+      <c r="K106" s="290" t="s">
         <v>287</v>
       </c>
-      <c r="L106" s="296"/>
-      <c r="M106" s="297"/>
+      <c r="L106" s="291"/>
+      <c r="M106" s="292"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -64919,11 +64919,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="295" t="s">
+      <c r="K107" s="290" t="s">
         <v>289</v>
       </c>
-      <c r="L107" s="296"/>
-      <c r="M107" s="297"/>
+      <c r="L107" s="291"/>
+      <c r="M107" s="292"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -64957,11 +64957,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="286" t="s">
+      <c r="K108" s="281" t="s">
         <v>290</v>
       </c>
-      <c r="L108" s="287"/>
-      <c r="M108" s="288"/>
+      <c r="L108" s="282"/>
+      <c r="M108" s="283"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -64995,9 +64995,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="289"/>
-      <c r="L109" s="290"/>
-      <c r="M109" s="291"/>
+      <c r="K109" s="284"/>
+      <c r="L109" s="285"/>
+      <c r="M109" s="286"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -65031,9 +65031,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="289"/>
-      <c r="L110" s="290"/>
-      <c r="M110" s="291"/>
+      <c r="K110" s="284"/>
+      <c r="L110" s="285"/>
+      <c r="M110" s="286"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -65067,9 +65067,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="289"/>
-      <c r="L111" s="290"/>
-      <c r="M111" s="291"/>
+      <c r="K111" s="284"/>
+      <c r="L111" s="285"/>
+      <c r="M111" s="286"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -65107,9 +65107,9 @@
         <f t="shared" ref="J112:J113" si="7">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="289"/>
-      <c r="L112" s="290"/>
-      <c r="M112" s="291"/>
+      <c r="K112" s="284"/>
+      <c r="L112" s="285"/>
+      <c r="M112" s="286"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="156" t="s">
@@ -65145,13 +65145,19 @@
         <f t="shared" si="7"/>
         <v>43</v>
       </c>
-      <c r="K113" s="292"/>
-      <c r="L113" s="293"/>
-      <c r="M113" s="294"/>
+      <c r="K113" s="287"/>
+      <c r="L113" s="288"/>
+      <c r="M113" s="289"/>
     </row>
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="13">
+    <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="W80:X80"/>
+    <mergeCell ref="W81:X81"/>
+    <mergeCell ref="W82:X82"/>
+    <mergeCell ref="W83:X83"/>
+    <mergeCell ref="L1:AG1"/>
     <mergeCell ref="W84:X84"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="K108:M113"/>
@@ -65159,12 +65165,6 @@
     <mergeCell ref="K107:M107"/>
     <mergeCell ref="K84:M105"/>
     <mergeCell ref="K80:M83"/>
-    <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="W80:X80"/>
-    <mergeCell ref="W81:X81"/>
-    <mergeCell ref="W82:X82"/>
-    <mergeCell ref="W83:X83"/>
-    <mergeCell ref="L1:AG1"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -65521,7 +65521,7 @@
         <v>6</v>
       </c>
       <c r="M8" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="N8" s="195">
         <v>1</v>
@@ -65536,10 +65536,10 @@
         <v>0</v>
       </c>
       <c r="R8" s="195">
+        <v>3</v>
+      </c>
+      <c r="S8" s="195">
         <v>2</v>
-      </c>
-      <c r="S8" s="195">
-        <v>1</v>
       </c>
       <c r="T8" s="195">
         <v>1</v>
@@ -65553,7 +65553,7 @@
         <v>7</v>
       </c>
       <c r="M9" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="N9" s="195">
         <v>1</v>
@@ -65585,7 +65585,7 @@
         <v>8</v>
       </c>
       <c r="M10" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="N10" s="195">
         <v>1</v>
@@ -65600,10 +65600,10 @@
         <v>0</v>
       </c>
       <c r="R10" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S10" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" s="195">
         <v>1</v>
@@ -65617,31 +65617,31 @@
         <v>9</v>
       </c>
       <c r="M11" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="N11" s="195">
         <v>1</v>
       </c>
       <c r="O11" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="195">
         <v>0</v>
       </c>
       <c r="R11" s="195">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S11" s="195">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T11" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" s="195">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -65649,7 +65649,7 @@
         <v>10</v>
       </c>
       <c r="M12" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="N12" s="195">
         <v>1</v>
@@ -65681,31 +65681,31 @@
         <v>11</v>
       </c>
       <c r="M13" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="N13" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="195">
         <v>0</v>
       </c>
       <c r="P13" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="195">
         <v>0</v>
       </c>
       <c r="R13" s="195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S13" s="195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T13" s="195">
         <v>0</v>
       </c>
       <c r="U13" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -65716,7 +65716,7 @@
         <v>425</v>
       </c>
       <c r="N14" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="195">
         <v>0</v>
@@ -65725,16 +65725,16 @@
         <v>0</v>
       </c>
       <c r="Q14" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S14" s="195">
-        <v>0</v>
-      </c>
-      <c r="T14" s="195">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="T14" s="195" t="s">
+        <v>435</v>
       </c>
       <c r="U14" s="195">
         <v>0</v>
@@ -67187,7 +67187,7 @@
       <c r="U2" s="199"/>
       <c r="V2" s="199"/>
       <c r="Z2" s="125">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -67414,15 +67414,15 @@
         <v>0</v>
       </c>
       <c r="T5" s="2">
-        <f t="shared" ref="T5:T41" si="2">SUM(E5,H5,K5,N5,Q5)</f>
+        <f t="shared" ref="T5:T17" si="2">SUM(E5,H5,K5,N5,Q5)</f>
         <v>184</v>
       </c>
       <c r="U5" s="2">
-        <f t="shared" ref="U5:U41" si="3">SUM(F5,I5,L5,O5,R5)</f>
+        <f t="shared" ref="U5:U17" si="3">SUM(F5,I5,L5,O5,R5)</f>
         <v>8</v>
       </c>
       <c r="V5" s="2">
-        <f t="shared" ref="V5:V41" si="4">SUM(G5,J5,M5,P5,S5)</f>
+        <f t="shared" ref="V5:V17" si="4">SUM(G5,J5,M5,P5,S5)</f>
         <v>3</v>
       </c>
     </row>

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7817" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B234472-1F69-43DB-8C67-605A3ACDBA0C}"/>
+  <xr:revisionPtr revIDLastSave="7821" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C3000F7-68B2-4D6B-9A9D-17DE1BF985B0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="19" state="hidden" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2245" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2245" uniqueCount="443">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -1392,9 +1392,6 @@
     <t>−2</t>
   </si>
   <si>
-    <t>−3</t>
-  </si>
-  <si>
     <t>−4</t>
   </si>
   <si>
@@ -1405,6 +1402,12 @@
   </si>
   <si>
     <t>KONSA Ezri</t>
+  </si>
+  <si>
+    <t>Ipswitch Town</t>
+  </si>
+  <si>
+    <t>−5</t>
   </si>
 </sst>
 </file>
@@ -2878,78 +2881,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3003,6 +2934,78 @@
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6303,7 +6306,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B437EF68-25A2-48C5-94FC-75BD5DC828BC}" type="CELLRANGE">
+                    <a:fld id="{81AC17A7-D0DB-41A7-A8BD-682BF5C70B16}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6337,7 +6340,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9D53D9E3-7404-4232-939A-B6533E35635A}" type="CELLRANGE">
+                    <a:fld id="{2608D685-72B0-4DFB-B949-DDBCFEAB54E1}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6371,7 +6374,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6F80CE62-244D-4457-B91A-17630F2B5CA7}" type="CELLRANGE">
+                    <a:fld id="{F0BE18A7-E11D-4369-9E4B-8739DEE606D4}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6405,7 +6408,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1A2C04F2-7BE4-479B-B897-7F305AE52EE6}" type="CELLRANGE">
+                    <a:fld id="{36C0696B-AE85-464E-8107-8867E5F26DC4}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6439,7 +6442,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DC8FCAA1-8BB9-47BC-885C-F805BE89C9ED}" type="CELLRANGE">
+                    <a:fld id="{002A6D39-AB06-490D-AFC2-1B5E0DFB4B91}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6473,7 +6476,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{65F9ADCB-6118-491C-BE4E-90E7FC32967F}" type="CELLRANGE">
+                    <a:fld id="{B6BC8544-3537-4B68-B951-BF019E7E967A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6507,7 +6510,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{56BF2A5B-937E-4EAA-B19C-158D7E0B97A9}" type="CELLRANGE">
+                    <a:fld id="{0644143A-23C9-4FBA-B0D2-732EE0CF4DDD}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6541,7 +6544,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0B27818C-A77B-4FF2-827C-FA8E31DFD654}" type="CELLRANGE">
+                    <a:fld id="{DACE080B-7ACB-49E5-BABF-4A3B806BD266}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6575,7 +6578,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2A8043BF-E94B-4753-B457-12FF1EB4DCED}" type="CELLRANGE">
+                    <a:fld id="{91D4642C-BD38-49B7-808B-C6F052BF8838}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6609,7 +6612,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{25EE1D23-6312-4821-A94A-7D2B1F290296}" type="CELLRANGE">
+                    <a:fld id="{DAEB6BB9-9DC5-4181-983B-4D597F922252}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6643,7 +6646,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C2091993-D565-43A8-B2A2-267189CF10C1}" type="CELLRANGE">
+                    <a:fld id="{D95090CC-6862-4CDB-A0A2-D81F098AE4AD}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6677,7 +6680,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7755AF6F-06C5-4802-9435-7DE7A2544988}" type="CELLRANGE">
+                    <a:fld id="{F029F32D-2866-43F4-92C6-10350B1CEAC0}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6726,7 +6729,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{6573CAB2-ACCF-4C97-9D5A-12F97F63E8A2}" type="CELLRANGE">
+                    <a:fld id="{704AD6E8-D892-4BE7-9A9A-C0BD7A08B876}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6785,7 +6788,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4A449499-E58C-4340-B8CD-BE5D759F422F}" type="CELLRANGE">
+                    <a:fld id="{23958310-BEE2-4B12-B8BB-DEE56694B608}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6819,7 +6822,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C7AEB7D4-A68B-476B-8D80-4C8BE70B5D07}" type="CELLRANGE">
+                    <a:fld id="{05A610F4-D843-4CCE-AE35-EC1EDA59A1E9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6853,7 +6856,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9A83A389-9B3E-476D-BACF-D93D8E01BA4D}" type="CELLRANGE">
+                    <a:fld id="{2F72991E-1815-4951-B46C-FE44BD5FA44D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6887,7 +6890,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2F9B23E5-134D-438E-8905-77E2A6DCDEB5}" type="CELLRANGE">
+                    <a:fld id="{A8B6EE8A-B587-49DB-9ABF-77539CF665F3}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6921,7 +6924,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{07074D4D-DB33-4082-ABAC-AD95D68072B2}" type="CELLRANGE">
+                    <a:fld id="{B7725022-F3B0-4E20-B904-E2C9BA187A5F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6955,7 +6958,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3FD3C3A4-75E6-40DD-BED4-2E952A952700}" type="CELLRANGE">
+                    <a:fld id="{E75E853D-4397-4B00-8BF7-C788AF2DA41E}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6989,7 +6992,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C11CB376-6248-4574-92BB-DDDF40063128}" type="CELLRANGE">
+                    <a:fld id="{165F05A8-179B-4470-AC04-805CCBB74702}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7023,7 +7026,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B29C8EEA-66FB-408A-8E24-B40A0E5CA0B9}" type="CELLRANGE">
+                    <a:fld id="{BCA4F555-BFDA-469E-921A-6A64CC42E84D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14219,30 +14222,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="206" t="s">
+      <c r="C1" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="206"/>
-      <c r="E1" s="207" t="s">
+      <c r="D1" s="216"/>
+      <c r="E1" s="217" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="207"/>
-      <c r="G1" s="206" t="s">
+      <c r="F1" s="217"/>
+      <c r="G1" s="216" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="206"/>
-      <c r="I1" s="207" t="s">
+      <c r="H1" s="216"/>
+      <c r="I1" s="217" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="207"/>
-      <c r="K1" s="206" t="s">
+      <c r="J1" s="217"/>
+      <c r="K1" s="216" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="206"/>
-      <c r="M1" s="204" t="s">
+      <c r="L1" s="216"/>
+      <c r="M1" s="214" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="205"/>
+      <c r="N1" s="215"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15949,30 +15952,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="216"/>
+      <c r="E2" s="217" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="217"/>
+      <c r="G2" s="216" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="216"/>
+      <c r="I2" s="217" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="217"/>
+      <c r="K2" s="216" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="199" t="s">
+      <c r="L2" s="216"/>
+      <c r="M2" s="221" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="199"/>
+      <c r="N2" s="221"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17776,30 +17779,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="216"/>
+      <c r="E2" s="217" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="217"/>
+      <c r="G2" s="216" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="216"/>
+      <c r="I2" s="217" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="217"/>
+      <c r="K2" s="216" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="199" t="s">
+      <c r="L2" s="216"/>
+      <c r="M2" s="221" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="199"/>
+      <c r="N2" s="221"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19466,30 +19469,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="216"/>
+      <c r="E2" s="217" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="217"/>
+      <c r="G2" s="216" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="216"/>
+      <c r="I2" s="217" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="217"/>
+      <c r="K2" s="216" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="199" t="s">
+      <c r="L2" s="216"/>
+      <c r="M2" s="221" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="199"/>
+      <c r="N2" s="221"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21292,30 +21295,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="216"/>
+      <c r="E2" s="217" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="217"/>
+      <c r="G2" s="216" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="216"/>
+      <c r="I2" s="217" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="217"/>
+      <c r="K2" s="216" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="199" t="s">
+      <c r="L2" s="216"/>
+      <c r="M2" s="221" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="199"/>
+      <c r="N2" s="221"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23164,36 +23167,36 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="196" t="s">
+      <c r="C2" s="218" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="197"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="201" t="s">
+      <c r="D2" s="219"/>
+      <c r="E2" s="220"/>
+      <c r="F2" s="223" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="202"/>
-      <c r="H2" s="203"/>
-      <c r="I2" s="196" t="s">
+      <c r="G2" s="224"/>
+      <c r="H2" s="225"/>
+      <c r="I2" s="218" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="197"/>
-      <c r="K2" s="198"/>
-      <c r="L2" s="201" t="s">
+      <c r="J2" s="219"/>
+      <c r="K2" s="220"/>
+      <c r="L2" s="223" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="202"/>
-      <c r="N2" s="203"/>
-      <c r="O2" s="196" t="s">
+      <c r="M2" s="224"/>
+      <c r="N2" s="225"/>
+      <c r="O2" s="218" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="197"/>
-      <c r="Q2" s="198"/>
-      <c r="R2" s="199" t="s">
+      <c r="P2" s="219"/>
+      <c r="Q2" s="220"/>
+      <c r="R2" s="221" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="199"/>
-      <c r="T2" s="199"/>
+      <c r="S2" s="221"/>
+      <c r="T2" s="221"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -24395,7 +24398,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="149" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C18" s="6">
         <f>'Premier League'!C18</f>
@@ -26376,36 +26379,36 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="196" t="s">
+      <c r="E1" s="218" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="197"/>
-      <c r="G1" s="198"/>
-      <c r="H1" s="201" t="s">
+      <c r="F1" s="219"/>
+      <c r="G1" s="220"/>
+      <c r="H1" s="223" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="202"/>
-      <c r="J1" s="203"/>
-      <c r="K1" s="196" t="s">
+      <c r="I1" s="224"/>
+      <c r="J1" s="225"/>
+      <c r="K1" s="218" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="197"/>
-      <c r="M1" s="198"/>
-      <c r="N1" s="201" t="s">
+      <c r="L1" s="219"/>
+      <c r="M1" s="220"/>
+      <c r="N1" s="223" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="202"/>
-      <c r="P1" s="203"/>
-      <c r="Q1" s="196" t="s">
+      <c r="O1" s="224"/>
+      <c r="P1" s="225"/>
+      <c r="Q1" s="218" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="197"/>
-      <c r="S1" s="198"/>
-      <c r="T1" s="199" t="s">
+      <c r="R1" s="219"/>
+      <c r="S1" s="220"/>
+      <c r="T1" s="221" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="199"/>
-      <c r="V1" s="199"/>
+      <c r="U1" s="221"/>
+      <c r="V1" s="221"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37803,399 +37806,399 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="211">
-        <v>1</v>
-      </c>
-      <c r="G1" s="212"/>
-      <c r="H1" s="213"/>
-      <c r="I1" s="211">
+      <c r="F1" s="229">
+        <v>1</v>
+      </c>
+      <c r="G1" s="230"/>
+      <c r="H1" s="231"/>
+      <c r="I1" s="229">
         <v>2</v>
       </c>
-      <c r="J1" s="212"/>
-      <c r="K1" s="213"/>
-      <c r="L1" s="211">
-        <v>3</v>
-      </c>
-      <c r="M1" s="212"/>
-      <c r="N1" s="213"/>
-      <c r="O1" s="211">
+      <c r="J1" s="230"/>
+      <c r="K1" s="231"/>
+      <c r="L1" s="229">
+        <v>3</v>
+      </c>
+      <c r="M1" s="230"/>
+      <c r="N1" s="231"/>
+      <c r="O1" s="229">
         <v>4</v>
       </c>
-      <c r="P1" s="212"/>
-      <c r="Q1" s="213"/>
-      <c r="R1" s="211">
+      <c r="P1" s="230"/>
+      <c r="Q1" s="231"/>
+      <c r="R1" s="229">
         <v>5</v>
       </c>
-      <c r="S1" s="212"/>
-      <c r="T1" s="213"/>
-      <c r="U1" s="211">
+      <c r="S1" s="230"/>
+      <c r="T1" s="231"/>
+      <c r="U1" s="229">
         <v>6</v>
       </c>
-      <c r="V1" s="212"/>
-      <c r="W1" s="213"/>
-      <c r="X1" s="211">
+      <c r="V1" s="230"/>
+      <c r="W1" s="231"/>
+      <c r="X1" s="229">
         <v>7</v>
       </c>
-      <c r="Y1" s="212"/>
-      <c r="Z1" s="213"/>
-      <c r="AA1" s="211">
+      <c r="Y1" s="230"/>
+      <c r="Z1" s="231"/>
+      <c r="AA1" s="229">
         <v>8</v>
       </c>
-      <c r="AB1" s="212"/>
-      <c r="AC1" s="213"/>
-      <c r="AD1" s="211">
+      <c r="AB1" s="230"/>
+      <c r="AC1" s="231"/>
+      <c r="AD1" s="229">
         <v>9</v>
       </c>
-      <c r="AE1" s="212"/>
-      <c r="AF1" s="213"/>
-      <c r="AG1" s="211">
+      <c r="AE1" s="230"/>
+      <c r="AF1" s="231"/>
+      <c r="AG1" s="229">
         <v>10</v>
       </c>
-      <c r="AH1" s="212"/>
-      <c r="AI1" s="213"/>
-      <c r="AJ1" s="211">
+      <c r="AH1" s="230"/>
+      <c r="AI1" s="231"/>
+      <c r="AJ1" s="229">
         <v>11</v>
       </c>
-      <c r="AK1" s="212"/>
-      <c r="AL1" s="213"/>
-      <c r="AM1" s="211">
+      <c r="AK1" s="230"/>
+      <c r="AL1" s="231"/>
+      <c r="AM1" s="229">
         <v>12</v>
       </c>
-      <c r="AN1" s="212"/>
-      <c r="AO1" s="213"/>
-      <c r="AP1" s="211">
+      <c r="AN1" s="230"/>
+      <c r="AO1" s="231"/>
+      <c r="AP1" s="229">
         <v>13</v>
       </c>
-      <c r="AQ1" s="212"/>
-      <c r="AR1" s="213"/>
-      <c r="AS1" s="211">
+      <c r="AQ1" s="230"/>
+      <c r="AR1" s="231"/>
+      <c r="AS1" s="229">
         <v>14</v>
       </c>
-      <c r="AT1" s="212"/>
-      <c r="AU1" s="213"/>
-      <c r="AV1" s="211">
+      <c r="AT1" s="230"/>
+      <c r="AU1" s="231"/>
+      <c r="AV1" s="229">
         <v>15</v>
       </c>
-      <c r="AW1" s="212"/>
-      <c r="AX1" s="213"/>
-      <c r="AY1" s="211">
+      <c r="AW1" s="230"/>
+      <c r="AX1" s="231"/>
+      <c r="AY1" s="229">
         <v>16</v>
       </c>
-      <c r="AZ1" s="212"/>
-      <c r="BA1" s="213"/>
-      <c r="BB1" s="211">
+      <c r="AZ1" s="230"/>
+      <c r="BA1" s="231"/>
+      <c r="BB1" s="229">
         <v>17</v>
       </c>
-      <c r="BC1" s="212"/>
-      <c r="BD1" s="213"/>
-      <c r="BE1" s="211">
+      <c r="BC1" s="230"/>
+      <c r="BD1" s="231"/>
+      <c r="BE1" s="229">
         <v>18</v>
       </c>
-      <c r="BF1" s="212"/>
-      <c r="BG1" s="213"/>
-      <c r="BH1" s="211">
+      <c r="BF1" s="230"/>
+      <c r="BG1" s="231"/>
+      <c r="BH1" s="229">
         <v>19</v>
       </c>
-      <c r="BI1" s="212"/>
-      <c r="BJ1" s="213"/>
-      <c r="BK1" s="211">
+      <c r="BI1" s="230"/>
+      <c r="BJ1" s="231"/>
+      <c r="BK1" s="229">
         <v>20</v>
       </c>
-      <c r="BL1" s="212"/>
-      <c r="BM1" s="213"/>
-      <c r="BN1" s="211">
+      <c r="BL1" s="230"/>
+      <c r="BM1" s="231"/>
+      <c r="BN1" s="229">
         <v>21</v>
       </c>
-      <c r="BO1" s="212"/>
-      <c r="BP1" s="213"/>
-      <c r="BQ1" s="211">
+      <c r="BO1" s="230"/>
+      <c r="BP1" s="231"/>
+      <c r="BQ1" s="229">
         <v>22</v>
       </c>
-      <c r="BR1" s="212"/>
-      <c r="BS1" s="213"/>
-      <c r="BT1" s="211">
+      <c r="BR1" s="230"/>
+      <c r="BS1" s="231"/>
+      <c r="BT1" s="229">
         <v>23</v>
       </c>
-      <c r="BU1" s="212"/>
-      <c r="BV1" s="213"/>
-      <c r="BW1" s="211">
+      <c r="BU1" s="230"/>
+      <c r="BV1" s="231"/>
+      <c r="BW1" s="229">
         <v>24</v>
       </c>
-      <c r="BX1" s="212"/>
-      <c r="BY1" s="213"/>
-      <c r="BZ1" s="211">
+      <c r="BX1" s="230"/>
+      <c r="BY1" s="231"/>
+      <c r="BZ1" s="229">
         <v>25</v>
       </c>
-      <c r="CA1" s="212"/>
-      <c r="CB1" s="213"/>
-      <c r="CC1" s="211">
+      <c r="CA1" s="230"/>
+      <c r="CB1" s="231"/>
+      <c r="CC1" s="229">
         <v>26</v>
       </c>
-      <c r="CD1" s="212"/>
-      <c r="CE1" s="213"/>
-      <c r="CF1" s="211">
+      <c r="CD1" s="230"/>
+      <c r="CE1" s="231"/>
+      <c r="CF1" s="229">
         <v>27</v>
       </c>
-      <c r="CG1" s="212"/>
-      <c r="CH1" s="213"/>
-      <c r="CI1" s="211">
+      <c r="CG1" s="230"/>
+      <c r="CH1" s="231"/>
+      <c r="CI1" s="229">
         <v>28</v>
       </c>
-      <c r="CJ1" s="212"/>
-      <c r="CK1" s="213"/>
-      <c r="CL1" s="211">
+      <c r="CJ1" s="230"/>
+      <c r="CK1" s="231"/>
+      <c r="CL1" s="229">
         <v>29</v>
       </c>
-      <c r="CM1" s="212"/>
-      <c r="CN1" s="213"/>
-      <c r="CO1" s="211">
+      <c r="CM1" s="230"/>
+      <c r="CN1" s="231"/>
+      <c r="CO1" s="229">
         <v>30</v>
       </c>
-      <c r="CP1" s="212"/>
-      <c r="CQ1" s="213"/>
-      <c r="CR1" s="211">
+      <c r="CP1" s="230"/>
+      <c r="CQ1" s="231"/>
+      <c r="CR1" s="229">
         <v>31</v>
       </c>
-      <c r="CS1" s="212"/>
-      <c r="CT1" s="213"/>
-      <c r="CU1" s="211">
+      <c r="CS1" s="230"/>
+      <c r="CT1" s="231"/>
+      <c r="CU1" s="229">
         <v>32</v>
       </c>
-      <c r="CV1" s="212"/>
-      <c r="CW1" s="213"/>
-      <c r="CX1" s="211">
+      <c r="CV1" s="230"/>
+      <c r="CW1" s="231"/>
+      <c r="CX1" s="229">
         <v>33</v>
       </c>
-      <c r="CY1" s="212"/>
-      <c r="CZ1" s="213"/>
-      <c r="DA1" s="211">
+      <c r="CY1" s="230"/>
+      <c r="CZ1" s="231"/>
+      <c r="DA1" s="229">
         <v>34</v>
       </c>
-      <c r="DB1" s="212"/>
-      <c r="DC1" s="213"/>
-      <c r="DD1" s="211">
+      <c r="DB1" s="230"/>
+      <c r="DC1" s="231"/>
+      <c r="DD1" s="229">
         <v>35</v>
       </c>
-      <c r="DE1" s="212"/>
-      <c r="DF1" s="213"/>
-      <c r="DG1" s="211">
+      <c r="DE1" s="230"/>
+      <c r="DF1" s="231"/>
+      <c r="DG1" s="229">
         <v>36</v>
       </c>
-      <c r="DH1" s="212"/>
-      <c r="DI1" s="213"/>
-      <c r="DJ1" s="211">
+      <c r="DH1" s="230"/>
+      <c r="DI1" s="231"/>
+      <c r="DJ1" s="229">
         <v>37</v>
       </c>
-      <c r="DK1" s="212"/>
-      <c r="DL1" s="213"/>
-      <c r="DM1" s="211">
+      <c r="DK1" s="230"/>
+      <c r="DL1" s="231"/>
+      <c r="DM1" s="229">
         <v>38</v>
       </c>
-      <c r="DN1" s="212"/>
-      <c r="DO1" s="213"/>
+      <c r="DN1" s="230"/>
+      <c r="DO1" s="231"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="214" t="s">
+      <c r="C2" s="232" t="s">
         <v>397</v>
       </c>
-      <c r="D2" s="214" t="s">
+      <c r="D2" s="232" t="s">
         <v>398</v>
       </c>
-      <c r="E2" s="214" t="s">
+      <c r="E2" s="232" t="s">
         <v>399</v>
       </c>
-      <c r="F2" s="208" t="s">
+      <c r="F2" s="226" t="s">
         <v>347</v>
       </c>
-      <c r="G2" s="209"/>
-      <c r="H2" s="210"/>
-      <c r="I2" s="217" t="s">
+      <c r="G2" s="227"/>
+      <c r="H2" s="228"/>
+      <c r="I2" s="235" t="s">
         <v>332</v>
       </c>
-      <c r="J2" s="218"/>
-      <c r="K2" s="219"/>
-      <c r="L2" s="208" t="s">
+      <c r="J2" s="236"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="226" t="s">
         <v>331</v>
       </c>
-      <c r="M2" s="209"/>
-      <c r="N2" s="210"/>
-      <c r="O2" s="208" t="s">
+      <c r="M2" s="227"/>
+      <c r="N2" s="228"/>
+      <c r="O2" s="226" t="s">
         <v>329</v>
       </c>
-      <c r="P2" s="209"/>
-      <c r="Q2" s="210"/>
-      <c r="R2" s="208" t="s">
+      <c r="P2" s="227"/>
+      <c r="Q2" s="228"/>
+      <c r="R2" s="226" t="s">
         <v>336</v>
       </c>
-      <c r="S2" s="209"/>
-      <c r="T2" s="210"/>
-      <c r="U2" s="208" t="s">
+      <c r="S2" s="227"/>
+      <c r="T2" s="228"/>
+      <c r="U2" s="226" t="s">
         <v>321</v>
       </c>
-      <c r="V2" s="209"/>
-      <c r="W2" s="210"/>
-      <c r="X2" s="208" t="s">
+      <c r="V2" s="227"/>
+      <c r="W2" s="228"/>
+      <c r="X2" s="226" t="s">
         <v>338</v>
       </c>
-      <c r="Y2" s="209"/>
-      <c r="Z2" s="210"/>
-      <c r="AA2" s="208" t="s">
+      <c r="Y2" s="227"/>
+      <c r="Z2" s="228"/>
+      <c r="AA2" s="226" t="s">
         <v>335</v>
       </c>
-      <c r="AB2" s="209"/>
-      <c r="AC2" s="210"/>
-      <c r="AD2" s="208" t="s">
+      <c r="AB2" s="227"/>
+      <c r="AC2" s="228"/>
+      <c r="AD2" s="226" t="s">
         <v>322</v>
       </c>
-      <c r="AE2" s="209"/>
-      <c r="AF2" s="210"/>
-      <c r="AG2" s="208" t="s">
+      <c r="AE2" s="227"/>
+      <c r="AF2" s="228"/>
+      <c r="AG2" s="226" t="s">
         <v>348</v>
       </c>
-      <c r="AH2" s="209"/>
-      <c r="AI2" s="210"/>
-      <c r="AJ2" s="208" t="s">
+      <c r="AH2" s="227"/>
+      <c r="AI2" s="228"/>
+      <c r="AJ2" s="226" t="s">
         <v>325</v>
       </c>
-      <c r="AK2" s="209"/>
-      <c r="AL2" s="210"/>
-      <c r="AM2" s="208" t="s">
+      <c r="AK2" s="227"/>
+      <c r="AL2" s="228"/>
+      <c r="AM2" s="226" t="s">
         <v>324</v>
       </c>
-      <c r="AN2" s="209"/>
-      <c r="AO2" s="210"/>
-      <c r="AP2" s="208" t="s">
+      <c r="AN2" s="227"/>
+      <c r="AO2" s="228"/>
+      <c r="AP2" s="226" t="s">
         <v>333</v>
       </c>
-      <c r="AQ2" s="209"/>
-      <c r="AR2" s="210"/>
-      <c r="AS2" s="208" t="s">
+      <c r="AQ2" s="227"/>
+      <c r="AR2" s="228"/>
+      <c r="AS2" s="226" t="s">
         <v>330</v>
       </c>
-      <c r="AT2" s="209"/>
-      <c r="AU2" s="210"/>
-      <c r="AV2" s="208" t="s">
+      <c r="AT2" s="227"/>
+      <c r="AU2" s="228"/>
+      <c r="AV2" s="226" t="s">
         <v>337</v>
       </c>
-      <c r="AW2" s="209"/>
-      <c r="AX2" s="210"/>
-      <c r="AY2" s="208" t="s">
+      <c r="AW2" s="227"/>
+      <c r="AX2" s="228"/>
+      <c r="AY2" s="226" t="s">
         <v>306</v>
       </c>
-      <c r="AZ2" s="209"/>
-      <c r="BA2" s="210"/>
-      <c r="BB2" s="208" t="s">
+      <c r="AZ2" s="227"/>
+      <c r="BA2" s="228"/>
+      <c r="BB2" s="226" t="s">
         <v>327</v>
       </c>
-      <c r="BC2" s="209"/>
-      <c r="BD2" s="210"/>
-      <c r="BE2" s="208" t="s">
+      <c r="BC2" s="227"/>
+      <c r="BD2" s="228"/>
+      <c r="BE2" s="226" t="s">
         <v>326</v>
       </c>
-      <c r="BF2" s="209"/>
-      <c r="BG2" s="210"/>
-      <c r="BH2" s="208" t="s">
+      <c r="BF2" s="227"/>
+      <c r="BG2" s="228"/>
+      <c r="BH2" s="226" t="s">
         <v>349</v>
       </c>
-      <c r="BI2" s="209"/>
-      <c r="BJ2" s="210"/>
-      <c r="BK2" s="208" t="s">
+      <c r="BI2" s="227"/>
+      <c r="BJ2" s="228"/>
+      <c r="BK2" s="226" t="s">
         <v>333</v>
       </c>
-      <c r="BL2" s="209"/>
-      <c r="BM2" s="210"/>
-      <c r="BN2" s="208" t="s">
+      <c r="BL2" s="227"/>
+      <c r="BM2" s="228"/>
+      <c r="BN2" s="226" t="s">
         <v>348</v>
       </c>
-      <c r="BO2" s="209"/>
-      <c r="BP2" s="210"/>
-      <c r="BQ2" s="208" t="s">
+      <c r="BO2" s="227"/>
+      <c r="BP2" s="228"/>
+      <c r="BQ2" s="226" t="s">
         <v>325</v>
       </c>
-      <c r="BR2" s="209"/>
-      <c r="BS2" s="210"/>
-      <c r="BT2" s="208" t="s">
+      <c r="BR2" s="227"/>
+      <c r="BS2" s="228"/>
+      <c r="BT2" s="226" t="s">
         <v>324</v>
       </c>
-      <c r="BU2" s="209"/>
-      <c r="BV2" s="210"/>
-      <c r="BW2" s="208" t="s">
+      <c r="BU2" s="227"/>
+      <c r="BV2" s="228"/>
+      <c r="BW2" s="226" t="s">
         <v>322</v>
       </c>
-      <c r="BX2" s="209"/>
-      <c r="BY2" s="210"/>
-      <c r="BZ2" s="208" t="s">
+      <c r="BX2" s="227"/>
+      <c r="BY2" s="228"/>
+      <c r="BZ2" s="226" t="s">
         <v>349</v>
       </c>
-      <c r="CA2" s="209"/>
-      <c r="CB2" s="210"/>
-      <c r="CC2" s="208" t="s">
+      <c r="CA2" s="227"/>
+      <c r="CB2" s="228"/>
+      <c r="CC2" s="226" t="s">
         <v>326</v>
       </c>
-      <c r="CD2" s="209"/>
-      <c r="CE2" s="210"/>
-      <c r="CF2" s="208" t="s">
+      <c r="CD2" s="227"/>
+      <c r="CE2" s="228"/>
+      <c r="CF2" s="226" t="s">
         <v>306</v>
       </c>
-      <c r="CG2" s="209"/>
-      <c r="CH2" s="210"/>
-      <c r="CI2" s="208" t="s">
+      <c r="CG2" s="227"/>
+      <c r="CH2" s="228"/>
+      <c r="CI2" s="226" t="s">
         <v>327</v>
       </c>
-      <c r="CJ2" s="209"/>
-      <c r="CK2" s="210"/>
-      <c r="CL2" s="208" t="s">
+      <c r="CJ2" s="227"/>
+      <c r="CK2" s="228"/>
+      <c r="CL2" s="226" t="s">
         <v>331</v>
       </c>
-      <c r="CM2" s="209"/>
-      <c r="CN2" s="210"/>
-      <c r="CO2" s="208" t="s">
+      <c r="CM2" s="227"/>
+      <c r="CN2" s="228"/>
+      <c r="CO2" s="226" t="s">
         <v>329</v>
       </c>
-      <c r="CP2" s="209"/>
-      <c r="CQ2" s="210"/>
-      <c r="CR2" s="208" t="s">
+      <c r="CP2" s="227"/>
+      <c r="CQ2" s="228"/>
+      <c r="CR2" s="226" t="s">
         <v>347</v>
       </c>
-      <c r="CS2" s="209"/>
-      <c r="CT2" s="210"/>
-      <c r="CU2" s="208" t="s">
+      <c r="CS2" s="227"/>
+      <c r="CT2" s="228"/>
+      <c r="CU2" s="226" t="s">
         <v>332</v>
       </c>
-      <c r="CV2" s="209"/>
-      <c r="CW2" s="210"/>
-      <c r="CX2" s="208" t="s">
+      <c r="CV2" s="227"/>
+      <c r="CW2" s="228"/>
+      <c r="CX2" s="226" t="s">
         <v>337</v>
       </c>
-      <c r="CY2" s="209"/>
-      <c r="CZ2" s="210"/>
-      <c r="DA2" s="208" t="s">
+      <c r="CY2" s="227"/>
+      <c r="CZ2" s="228"/>
+      <c r="DA2" s="226" t="s">
         <v>330</v>
       </c>
-      <c r="DB2" s="209"/>
-      <c r="DC2" s="210"/>
-      <c r="DD2" s="208" t="s">
+      <c r="DB2" s="227"/>
+      <c r="DC2" s="228"/>
+      <c r="DD2" s="226" t="s">
         <v>321</v>
       </c>
-      <c r="DE2" s="209"/>
-      <c r="DF2" s="210"/>
-      <c r="DG2" s="208" t="s">
+      <c r="DE2" s="227"/>
+      <c r="DF2" s="228"/>
+      <c r="DG2" s="226" t="s">
         <v>338</v>
       </c>
-      <c r="DH2" s="209"/>
-      <c r="DI2" s="210"/>
-      <c r="DJ2" s="208" t="s">
+      <c r="DH2" s="227"/>
+      <c r="DI2" s="228"/>
+      <c r="DJ2" s="226" t="s">
         <v>335</v>
       </c>
-      <c r="DK2" s="209"/>
-      <c r="DL2" s="210"/>
-      <c r="DM2" s="208" t="s">
+      <c r="DK2" s="227"/>
+      <c r="DL2" s="228"/>
+      <c r="DM2" s="226" t="s">
         <v>336</v>
       </c>
-      <c r="DN2" s="209"/>
-      <c r="DO2" s="210"/>
+      <c r="DN2" s="227"/>
+      <c r="DO2" s="228"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38204,9 +38207,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="215"/>
-      <c r="D3" s="215"/>
-      <c r="E3" s="216"/>
+      <c r="C3" s="233"/>
+      <c r="D3" s="233"/>
+      <c r="E3" s="234"/>
       <c r="F3" s="160" t="s">
         <v>394</v>
       </c>
@@ -40453,7 +40456,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="149" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C18" s="58">
         <f t="shared" ref="C18:C41" si="4">SUM(F18,I18,L18,O18,R18,U18,X18,AA18,AD18,AG18,AJ18,AM18,AP18,AS18,AV18,AY18,BB18,BE18,BH18,BK18,BN18,BQ18,BT18,BW18,BZ18,CC18,CF18,CI18,CL18,CO18,CR18,CU18,CX18,DA18,DD18,DG18,DJ18,DM18)</f>
@@ -44263,122 +44266,122 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="232" t="s">
+      <c r="C1" s="208" t="s">
         <v>397</v>
       </c>
-      <c r="D1" s="232" t="s">
+      <c r="D1" s="208" t="s">
         <v>398</v>
       </c>
-      <c r="E1" s="232" t="s">
+      <c r="E1" s="208" t="s">
         <v>399</v>
       </c>
-      <c r="F1" s="223" t="s">
+      <c r="F1" s="199" t="s">
         <v>303</v>
       </c>
-      <c r="G1" s="224"/>
-      <c r="H1" s="224"/>
-      <c r="I1" s="224"/>
-      <c r="J1" s="224"/>
-      <c r="K1" s="224"/>
-      <c r="L1" s="224"/>
-      <c r="M1" s="224"/>
-      <c r="N1" s="224"/>
-      <c r="O1" s="224"/>
-      <c r="P1" s="224"/>
-      <c r="Q1" s="224"/>
-      <c r="R1" s="224"/>
-      <c r="S1" s="224"/>
-      <c r="T1" s="224"/>
-      <c r="U1" s="224"/>
-      <c r="V1" s="224"/>
-      <c r="W1" s="224"/>
-      <c r="X1" s="224"/>
-      <c r="Y1" s="224"/>
-      <c r="Z1" s="224"/>
-      <c r="AA1" s="224"/>
-      <c r="AB1" s="224"/>
-      <c r="AC1" s="225"/>
-      <c r="AD1" s="235" t="s">
+      <c r="G1" s="200"/>
+      <c r="H1" s="200"/>
+      <c r="I1" s="200"/>
+      <c r="J1" s="200"/>
+      <c r="K1" s="200"/>
+      <c r="L1" s="200"/>
+      <c r="M1" s="200"/>
+      <c r="N1" s="200"/>
+      <c r="O1" s="200"/>
+      <c r="P1" s="200"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="200"/>
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="200"/>
+      <c r="Y1" s="200"/>
+      <c r="Z1" s="200"/>
+      <c r="AA1" s="200"/>
+      <c r="AB1" s="200"/>
+      <c r="AC1" s="201"/>
+      <c r="AD1" s="211" t="s">
         <v>282</v>
       </c>
-      <c r="AE1" s="236"/>
-      <c r="AF1" s="236"/>
-      <c r="AG1" s="236"/>
-      <c r="AH1" s="236"/>
-      <c r="AI1" s="237"/>
-      <c r="AJ1" s="223" t="s">
+      <c r="AE1" s="212"/>
+      <c r="AF1" s="212"/>
+      <c r="AG1" s="212"/>
+      <c r="AH1" s="212"/>
+      <c r="AI1" s="213"/>
+      <c r="AJ1" s="199" t="s">
         <v>283</v>
       </c>
-      <c r="AK1" s="224"/>
-      <c r="AL1" s="224"/>
-      <c r="AM1" s="224"/>
-      <c r="AN1" s="224"/>
-      <c r="AO1" s="225"/>
-      <c r="AP1" s="226" t="s">
+      <c r="AK1" s="200"/>
+      <c r="AL1" s="200"/>
+      <c r="AM1" s="200"/>
+      <c r="AN1" s="200"/>
+      <c r="AO1" s="201"/>
+      <c r="AP1" s="202" t="s">
         <v>284</v>
       </c>
-      <c r="AQ1" s="227"/>
-      <c r="AR1" s="227"/>
-      <c r="AS1" s="227"/>
-      <c r="AT1" s="227"/>
-      <c r="AU1" s="228"/>
-      <c r="AV1" s="229" t="s">
+      <c r="AQ1" s="203"/>
+      <c r="AR1" s="203"/>
+      <c r="AS1" s="203"/>
+      <c r="AT1" s="203"/>
+      <c r="AU1" s="204"/>
+      <c r="AV1" s="205" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="230"/>
-      <c r="AX1" s="231"/>
+      <c r="AW1" s="206"/>
+      <c r="AX1" s="207"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="220"/>
-      <c r="G2" s="221"/>
-      <c r="H2" s="222"/>
-      <c r="I2" s="220"/>
-      <c r="J2" s="221"/>
-      <c r="K2" s="222"/>
-      <c r="L2" s="220"/>
-      <c r="M2" s="221"/>
-      <c r="N2" s="222"/>
-      <c r="O2" s="220"/>
-      <c r="P2" s="221"/>
-      <c r="Q2" s="222"/>
-      <c r="R2" s="220"/>
-      <c r="S2" s="221"/>
-      <c r="T2" s="222"/>
-      <c r="U2" s="220"/>
-      <c r="V2" s="221"/>
-      <c r="W2" s="222"/>
-      <c r="X2" s="220"/>
-      <c r="Y2" s="221"/>
-      <c r="Z2" s="222"/>
-      <c r="AA2" s="220"/>
-      <c r="AB2" s="221"/>
-      <c r="AC2" s="221"/>
-      <c r="AD2" s="220"/>
-      <c r="AE2" s="221"/>
-      <c r="AF2" s="222"/>
-      <c r="AG2" s="220"/>
-      <c r="AH2" s="221"/>
-      <c r="AI2" s="222"/>
-      <c r="AJ2" s="220"/>
-      <c r="AK2" s="221"/>
-      <c r="AL2" s="222"/>
-      <c r="AM2" s="220"/>
-      <c r="AN2" s="221"/>
-      <c r="AO2" s="222"/>
-      <c r="AP2" s="220"/>
-      <c r="AQ2" s="221"/>
-      <c r="AR2" s="222"/>
-      <c r="AS2" s="220"/>
-      <c r="AT2" s="221"/>
-      <c r="AU2" s="222"/>
-      <c r="AV2" s="220"/>
-      <c r="AW2" s="221"/>
-      <c r="AX2" s="222"/>
+      <c r="C2" s="209"/>
+      <c r="D2" s="209"/>
+      <c r="E2" s="209"/>
+      <c r="F2" s="196"/>
+      <c r="G2" s="197"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="196"/>
+      <c r="J2" s="197"/>
+      <c r="K2" s="198"/>
+      <c r="L2" s="196"/>
+      <c r="M2" s="197"/>
+      <c r="N2" s="198"/>
+      <c r="O2" s="196"/>
+      <c r="P2" s="197"/>
+      <c r="Q2" s="198"/>
+      <c r="R2" s="196"/>
+      <c r="S2" s="197"/>
+      <c r="T2" s="198"/>
+      <c r="U2" s="196"/>
+      <c r="V2" s="197"/>
+      <c r="W2" s="198"/>
+      <c r="X2" s="196"/>
+      <c r="Y2" s="197"/>
+      <c r="Z2" s="198"/>
+      <c r="AA2" s="196"/>
+      <c r="AB2" s="197"/>
+      <c r="AC2" s="197"/>
+      <c r="AD2" s="196"/>
+      <c r="AE2" s="197"/>
+      <c r="AF2" s="198"/>
+      <c r="AG2" s="196"/>
+      <c r="AH2" s="197"/>
+      <c r="AI2" s="198"/>
+      <c r="AJ2" s="196"/>
+      <c r="AK2" s="197"/>
+      <c r="AL2" s="198"/>
+      <c r="AM2" s="196"/>
+      <c r="AN2" s="197"/>
+      <c r="AO2" s="198"/>
+      <c r="AP2" s="196"/>
+      <c r="AQ2" s="197"/>
+      <c r="AR2" s="198"/>
+      <c r="AS2" s="196"/>
+      <c r="AT2" s="197"/>
+      <c r="AU2" s="198"/>
+      <c r="AV2" s="196"/>
+      <c r="AW2" s="197"/>
+      <c r="AX2" s="198"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -44387,9 +44390,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="234"/>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
+      <c r="C3" s="210"/>
+      <c r="D3" s="210"/>
+      <c r="E3" s="210"/>
       <c r="F3" s="170" t="s">
         <v>394</v>
       </c>
@@ -45441,7 +45444,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="149" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C18" s="58">
         <f t="shared" ref="C18:C41" si="4">SUM(F18,I18,L18,O18,R18,X18,AA18,AD18,U18,AG18,AJ18,AM18,AP18,AS18,AV18)</f>
@@ -47237,13 +47240,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="232" t="s">
+      <c r="C1" s="208" t="s">
         <v>397</v>
       </c>
-      <c r="D1" s="232" t="s">
+      <c r="D1" s="208" t="s">
         <v>398</v>
       </c>
-      <c r="E1" s="232" t="s">
+      <c r="E1" s="208" t="s">
         <v>399</v>
       </c>
       <c r="F1" s="262" t="s">
@@ -47280,9 +47283,9 @@
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
+      <c r="C2" s="209"/>
+      <c r="D2" s="209"/>
+      <c r="E2" s="209"/>
       <c r="F2" s="244"/>
       <c r="G2" s="245"/>
       <c r="H2" s="246"/>
@@ -47904,7 +47907,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="149" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C18" s="58">
         <f t="shared" si="2"/>
@@ -51787,7 +51790,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C20" s="25">
         <v>0</v>
@@ -51824,7 +51827,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="45" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O20" s="26">
         <v>0</v>
@@ -51861,7 +51864,7 @@
         <v>0</v>
       </c>
       <c r="Z20" s="57" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AA20" s="24">
         <v>0</v>
@@ -51898,7 +51901,7 @@
         <v>0</v>
       </c>
       <c r="AL20" s="63" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AM20" s="18">
         <v>0</v>
@@ -51935,7 +51938,7 @@
         <v>0</v>
       </c>
       <c r="AX20" s="32" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AY20" s="33">
         <v>0</v>
@@ -56373,13 +56376,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="232" t="s">
+      <c r="C1" s="208" t="s">
         <v>397</v>
       </c>
-      <c r="D1" s="232" t="s">
+      <c r="D1" s="208" t="s">
         <v>398</v>
       </c>
-      <c r="E1" s="232" t="s">
+      <c r="E1" s="208" t="s">
         <v>399</v>
       </c>
       <c r="F1" s="262" t="s">
@@ -56416,10 +56419,12 @@
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="244"/>
+      <c r="C2" s="209"/>
+      <c r="D2" s="209"/>
+      <c r="E2" s="209"/>
+      <c r="F2" s="244" t="s">
+        <v>441</v>
+      </c>
       <c r="G2" s="245"/>
       <c r="H2" s="246"/>
       <c r="I2" s="259"/>
@@ -57040,7 +57045,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="149" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C18" s="58">
         <f t="shared" ref="C18:C41" si="2">SUM(F18,I18,L18,O18,R18,U18)</f>
@@ -58267,7 +58272,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="149" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="20"/>
@@ -65331,13 +65336,13 @@
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="N3" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P3" s="195">
         <v>0</v>
@@ -65346,21 +65351,21 @@
         <v>0</v>
       </c>
       <c r="R3" s="195">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S3" s="195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T3" s="195">
         <v>4</v>
       </c>
       <c r="U3" s="195">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B4" s="194">
         <v>0.875</v>
@@ -65372,7 +65377,7 @@
         <v>418</v>
       </c>
       <c r="E4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F4" t="s">
         <v>400</v>
@@ -65393,13 +65398,13 @@
         <v>2</v>
       </c>
       <c r="M4" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="N4" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P4" s="195">
         <v>0</v>
@@ -65417,7 +65422,7 @@
         <v>3</v>
       </c>
       <c r="U4" s="195">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -65425,13 +65430,13 @@
         <v>3</v>
       </c>
       <c r="M5" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N5" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P5" s="195">
         <v>0</v>
@@ -65440,16 +65445,16 @@
         <v>0</v>
       </c>
       <c r="R5" s="195">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S5" s="195">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T5" s="195">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U5" s="195">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -65457,31 +65462,31 @@
         <v>4</v>
       </c>
       <c r="M6" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="N6" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O6" s="195">
         <v>1</v>
       </c>
       <c r="P6" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="195">
         <v>0</v>
       </c>
       <c r="R6" s="195">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S6" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U6" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -65489,31 +65494,31 @@
         <v>5</v>
       </c>
       <c r="M7" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="N7" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" s="195">
         <v>1</v>
       </c>
       <c r="P7" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="195">
         <v>0</v>
       </c>
       <c r="R7" s="195">
+        <v>4</v>
+      </c>
+      <c r="S7" s="195">
         <v>2</v>
-      </c>
-      <c r="S7" s="195">
-        <v>0</v>
       </c>
       <c r="T7" s="195">
         <v>2</v>
       </c>
       <c r="U7" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -65521,16 +65526,16 @@
         <v>6</v>
       </c>
       <c r="M8" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N8" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" s="195">
         <v>1</v>
       </c>
       <c r="P8" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="195">
         <v>0</v>
@@ -65539,13 +65544,13 @@
         <v>3</v>
       </c>
       <c r="S8" s="195">
+        <v>1</v>
+      </c>
+      <c r="T8" s="195">
         <v>2</v>
       </c>
-      <c r="T8" s="195">
-        <v>1</v>
-      </c>
       <c r="U8" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -65553,16 +65558,16 @@
         <v>7</v>
       </c>
       <c r="M9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N9" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" s="195">
         <v>1</v>
       </c>
       <c r="P9" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="195">
         <v>0</v>
@@ -65577,7 +65582,7 @@
         <v>1</v>
       </c>
       <c r="U9" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -65585,10 +65590,10 @@
         <v>8</v>
       </c>
       <c r="M10" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="N10" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" s="195">
         <v>1</v>
@@ -65597,16 +65602,16 @@
         <v>0</v>
       </c>
       <c r="Q10" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="195">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S10" s="195">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T10" s="195">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U10" s="195">
         <v>3</v>
@@ -65617,7 +65622,7 @@
         <v>9</v>
       </c>
       <c r="M11" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="N11" s="195">
         <v>1</v>
@@ -65632,13 +65637,13 @@
         <v>0</v>
       </c>
       <c r="R11" s="195">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S11" s="195">
         <v>0</v>
       </c>
       <c r="T11" s="195">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U11" s="195">
         <v>3</v>
@@ -65649,31 +65654,31 @@
         <v>10</v>
       </c>
       <c r="M12" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N12" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="195">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S12" s="195">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T12" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" s="195">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -65681,19 +65686,19 @@
         <v>11</v>
       </c>
       <c r="M13" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N13" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" s="195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="195">
         <v>2</v>
@@ -65705,7 +65710,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="195">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -65713,13 +65718,13 @@
         <v>12</v>
       </c>
       <c r="M14" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N14" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" s="195">
         <v>0</v>
@@ -65728,16 +65733,16 @@
         <v>1</v>
       </c>
       <c r="R14" s="195">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S14" s="195">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T14" s="195" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="U14" s="195">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -65745,31 +65750,31 @@
         <v>13</v>
       </c>
       <c r="M15" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="N15" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15" s="195">
         <v>0</v>
       </c>
       <c r="P15" s="195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" s="195">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S15" s="195">
+        <v>4</v>
+      </c>
+      <c r="T15" s="195">
+        <v>0</v>
+      </c>
+      <c r="U15" s="195">
         <v>2</v>
-      </c>
-      <c r="T15" s="195" t="s">
-        <v>435</v>
-      </c>
-      <c r="U15" s="195">
-        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -65777,31 +65782,31 @@
         <v>14</v>
       </c>
       <c r="M16" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="N16" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O16" s="195">
         <v>0</v>
       </c>
       <c r="P16" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="195">
         <v>1</v>
       </c>
       <c r="R16" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S16" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T16" s="195" t="s">
         <v>435</v>
       </c>
       <c r="U16" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="12:21" x14ac:dyDescent="0.25">
@@ -65812,28 +65817,28 @@
         <v>432</v>
       </c>
       <c r="N17" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" s="195">
         <v>0</v>
       </c>
       <c r="P17" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="195">
         <v>1</v>
       </c>
       <c r="R17" s="195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S17" s="195">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T17" s="195" t="s">
         <v>435</v>
       </c>
       <c r="U17" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="12:21" x14ac:dyDescent="0.25">
@@ -65841,10 +65846,10 @@
         <v>16</v>
       </c>
       <c r="M18" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N18" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O18" s="195">
         <v>0</v>
@@ -65853,13 +65858,13 @@
         <v>0</v>
       </c>
       <c r="Q18" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" s="195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18" s="195">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T18" s="195" t="s">
         <v>436</v>
@@ -65873,7 +65878,7 @@
         <v>17</v>
       </c>
       <c r="M19" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="N19" s="195">
         <v>1</v>
@@ -65891,10 +65896,10 @@
         <v>0</v>
       </c>
       <c r="S19" s="195">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T19" s="195" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="U19" s="195">
         <v>0</v>
@@ -65908,7 +65913,7 @@
         <v>407</v>
       </c>
       <c r="N20" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20" s="195">
         <v>0</v>
@@ -65917,13 +65922,13 @@
         <v>0</v>
       </c>
       <c r="Q20" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20" s="195">
         <v>0</v>
       </c>
       <c r="S20" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T20" s="195" t="s">
         <v>437</v>
@@ -65937,10 +65942,10 @@
         <v>19</v>
       </c>
       <c r="M21" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="N21" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O21" s="195">
         <v>0</v>
@@ -65949,16 +65954,16 @@
         <v>0</v>
       </c>
       <c r="Q21" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" s="195">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T21" s="195" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="U21" s="195">
         <v>0</v>
@@ -65969,10 +65974,10 @@
         <v>20</v>
       </c>
       <c r="M22" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="N22" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O22" s="195">
         <v>0</v>
@@ -65981,16 +65986,16 @@
         <v>0</v>
       </c>
       <c r="Q22" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22" s="195">
         <v>0</v>
       </c>
       <c r="S22" s="195">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T22" s="195" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="U22" s="195">
         <v>0</v>
@@ -66025,23 +66030,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="196" t="s">
+      <c r="A1" s="218" t="s">
         <v>46</v>
       </c>
       <c r="B1" s="317"/>
       <c r="C1" s="318" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="199"/>
+      <c r="D1" s="221"/>
       <c r="E1" s="319"/>
-      <c r="H1" s="196" t="s">
+      <c r="H1" s="218" t="s">
         <v>47</v>
       </c>
       <c r="I1" s="317"/>
       <c r="J1" s="318" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="199"/>
+      <c r="K1" s="221"/>
       <c r="L1" s="319"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -67130,9 +67135,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
+      <c r="F1" s="222"/>
+      <c r="G1" s="222"/>
+      <c r="H1" s="222"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -67156,38 +67161,38 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="196" t="s">
+      <c r="E2" s="218" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="197"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="201" t="s">
+      <c r="F2" s="219"/>
+      <c r="G2" s="220"/>
+      <c r="H2" s="223" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="202"/>
-      <c r="J2" s="203"/>
-      <c r="K2" s="196" t="s">
+      <c r="I2" s="224"/>
+      <c r="J2" s="225"/>
+      <c r="K2" s="218" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="197"/>
-      <c r="M2" s="198"/>
-      <c r="N2" s="201" t="s">
+      <c r="L2" s="219"/>
+      <c r="M2" s="220"/>
+      <c r="N2" s="223" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="202"/>
-      <c r="P2" s="203"/>
-      <c r="Q2" s="196" t="s">
+      <c r="O2" s="224"/>
+      <c r="P2" s="225"/>
+      <c r="Q2" s="218" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="197"/>
-      <c r="S2" s="198"/>
-      <c r="T2" s="199" t="s">
+      <c r="R2" s="219"/>
+      <c r="S2" s="220"/>
+      <c r="T2" s="221" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="199"/>
-      <c r="V2" s="199"/>
+      <c r="U2" s="221"/>
+      <c r="V2" s="221"/>
       <c r="Z2" s="125">
-        <v>46259</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -68469,7 +68474,7 @@
         <v>353</v>
       </c>
       <c r="D18" s="149" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E18" s="6">
         <f>'#'!J20</f>
@@ -70612,30 +70617,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="216"/>
+      <c r="F2" s="217" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="217"/>
+      <c r="H2" s="216" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="216"/>
+      <c r="J2" s="217" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="217"/>
+      <c r="L2" s="216" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="199" t="s">
+      <c r="M2" s="216"/>
+      <c r="N2" s="221" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="199"/>
+      <c r="O2" s="221"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -72632,30 +72637,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="216"/>
+      <c r="F2" s="217" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="217"/>
+      <c r="H2" s="216" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="216"/>
+      <c r="J2" s="217" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="217"/>
+      <c r="L2" s="216" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="199" t="s">
+      <c r="M2" s="216"/>
+      <c r="N2" s="221" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="199"/>
+      <c r="O2" s="221"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -74589,30 +74594,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="216"/>
+      <c r="F2" s="217" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="217"/>
+      <c r="H2" s="216" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="216"/>
+      <c r="J2" s="217" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="217"/>
+      <c r="L2" s="216" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="199" t="s">
+      <c r="M2" s="216"/>
+      <c r="N2" s="221" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="199"/>
+      <c r="O2" s="221"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -76637,30 +76642,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="216"/>
+      <c r="F2" s="217" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="217"/>
+      <c r="H2" s="216" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="216"/>
+      <c r="J2" s="217" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="217"/>
+      <c r="L2" s="216" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="199" t="s">
+      <c r="M2" s="216"/>
+      <c r="N2" s="221" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="199"/>
+      <c r="O2" s="221"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -78345,30 +78350,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="216"/>
+      <c r="E2" s="217" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="217"/>
+      <c r="G2" s="216" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="216"/>
+      <c r="I2" s="217" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="217"/>
+      <c r="K2" s="216" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="199" t="s">
+      <c r="L2" s="216"/>
+      <c r="M2" s="221" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="199"/>
+      <c r="N2" s="221"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -80130,30 +80135,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="216"/>
+      <c r="E2" s="217" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="217"/>
+      <c r="G2" s="216" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="216"/>
+      <c r="I2" s="217" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="217"/>
+      <c r="K2" s="216" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="199" t="s">
+      <c r="L2" s="216"/>
+      <c r="M2" s="221" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="199"/>
+      <c r="N2" s="221"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7821" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C3000F7-68B2-4D6B-9A9D-17DE1BF985B0}"/>
+  <xr:revisionPtr revIDLastSave="7849" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{506C9596-0567-4D53-A0C2-9B74059E740B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1281,9 +1281,6 @@
     <t>Σ Ast</t>
   </si>
   <si>
-    <t>21.08.2026</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -1312,9 +1309,6 @@
   </si>
   <si>
     <t>Score</t>
-  </si>
-  <si>
-    <t>3-0</t>
   </si>
   <si>
     <t>Manchester City</t>
@@ -1408,6 +1402,12 @@
   </si>
   <si>
     <t>−5</t>
+  </si>
+  <si>
+    <t>1-0</t>
+  </si>
+  <si>
+    <t>06.09.2026</t>
   </si>
 </sst>
 </file>
@@ -2881,6 +2881,78 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2934,78 +3006,6 @@
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4457,28 +4457,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -4502,7 +4502,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>2</c:v>
@@ -4520,13 +4520,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0</c:v>
@@ -4538,13 +4538,13 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>0</c:v>
@@ -4711,7 +4711,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2</c:v>
@@ -6306,7 +6306,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{81AC17A7-D0DB-41A7-A8BD-682BF5C70B16}" type="CELLRANGE">
+                    <a:fld id="{EF694E91-53AF-4BE8-BC2C-7C4893FAEB76}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6340,7 +6340,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2608D685-72B0-4DFB-B949-DDBCFEAB54E1}" type="CELLRANGE">
+                    <a:fld id="{ED20685B-570B-42BF-9419-4BA737269059}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6374,7 +6374,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F0BE18A7-E11D-4369-9E4B-8739DEE606D4}" type="CELLRANGE">
+                    <a:fld id="{1697190C-FEB6-4D72-ABAB-4F14423722A8}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6408,7 +6408,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{36C0696B-AE85-464E-8107-8867E5F26DC4}" type="CELLRANGE">
+                    <a:fld id="{EA6FB649-2277-4059-A081-B161DC0FE6B7}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6442,7 +6442,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{002A6D39-AB06-490D-AFC2-1B5E0DFB4B91}" type="CELLRANGE">
+                    <a:fld id="{B30A99D4-84EA-4A6A-BA27-EF39ECB6ED16}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6476,7 +6476,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B6BC8544-3537-4B68-B951-BF019E7E967A}" type="CELLRANGE">
+                    <a:fld id="{98C86552-FF2B-4D8A-8B61-578E84526CD4}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6510,7 +6510,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0644143A-23C9-4FBA-B0D2-732EE0CF4DDD}" type="CELLRANGE">
+                    <a:fld id="{84D1840B-74E6-414D-ABF5-8CB3E1968122}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6544,7 +6544,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DACE080B-7ACB-49E5-BABF-4A3B806BD266}" type="CELLRANGE">
+                    <a:fld id="{B28BA611-D3F5-4D85-98AE-21D015434994}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6578,7 +6578,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{91D4642C-BD38-49B7-808B-C6F052BF8838}" type="CELLRANGE">
+                    <a:fld id="{65A3FD7D-3C13-4246-8584-C9FBDB95D524}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6612,7 +6612,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DAEB6BB9-9DC5-4181-983B-4D597F922252}" type="CELLRANGE">
+                    <a:fld id="{A250ABEE-621B-40F5-AC38-3264A8308B8D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6646,7 +6646,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D95090CC-6862-4CDB-A0A2-D81F098AE4AD}" type="CELLRANGE">
+                    <a:fld id="{D911C9FA-CACA-42D8-86FB-4CF33B41F1C9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6680,7 +6680,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F029F32D-2866-43F4-92C6-10350B1CEAC0}" type="CELLRANGE">
+                    <a:fld id="{446CEE18-311D-4220-8C81-BAFCE761BF51}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6729,7 +6729,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{704AD6E8-D892-4BE7-9A9A-C0BD7A08B876}" type="CELLRANGE">
+                    <a:fld id="{4E69E635-9EB5-4C96-8122-FBD29122FB01}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6788,7 +6788,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{23958310-BEE2-4B12-B8BB-DEE56694B608}" type="CELLRANGE">
+                    <a:fld id="{7D72F8FC-09DD-49FE-A4D0-EC46FEBDD7B8}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6822,7 +6822,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{05A610F4-D843-4CCE-AE35-EC1EDA59A1E9}" type="CELLRANGE">
+                    <a:fld id="{2A3919B7-6439-4876-986D-2BC1DEF0CA49}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6856,7 +6856,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2F72991E-1815-4951-B46C-FE44BD5FA44D}" type="CELLRANGE">
+                    <a:fld id="{0C607145-ABE3-47B7-A4A0-1A2F5444619D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6890,7 +6890,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A8B6EE8A-B587-49DB-9ABF-77539CF665F3}" type="CELLRANGE">
+                    <a:fld id="{45D4EABF-E6A0-44A4-A8BA-75CEB63E06B2}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6924,7 +6924,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B7725022-F3B0-4E20-B904-E2C9BA187A5F}" type="CELLRANGE">
+                    <a:fld id="{EE5C6A9B-DAEB-4188-B523-4C1850DEF1F0}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6958,7 +6958,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E75E853D-4397-4B00-8BF7-C788AF2DA41E}" type="CELLRANGE">
+                    <a:fld id="{5D3C753C-82B4-4889-8ABB-B8AFE8A5AF53}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6992,7 +6992,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{165F05A8-179B-4470-AC04-805CCBB74702}" type="CELLRANGE">
+                    <a:fld id="{CF20D458-E1A8-41A7-B3BA-785ED035D6BF}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7026,7 +7026,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BCA4F555-BFDA-469E-921A-6A64CC42E84D}" type="CELLRANGE">
+                    <a:fld id="{0A76C135-2420-4B13-8564-070D19D08D8B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7204,19 +7204,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>192</c:v>
+                  <c:v>193</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>263</c:v>
+                  <c:v>264</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>314</c:v>
+                  <c:v>315</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>236</c:v>
+                  <c:v>237</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>123</c:v>
@@ -7240,7 +7240,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>44</c:v>
@@ -7258,13 +7258,13 @@
                   <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>113</c:v>
+                  <c:v>114</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>67</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>2</c:v>
@@ -7288,7 +7288,7 @@
                   <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>82</c:v>
+                  <c:v>83</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>44</c:v>
@@ -7551,7 +7551,7 @@
                         <c:v>24</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>82</c:v>
+                        <c:v>83</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>44</c:v>
@@ -14222,30 +14222,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="216" t="s">
+      <c r="C1" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="216"/>
-      <c r="E1" s="217" t="s">
+      <c r="D1" s="206"/>
+      <c r="E1" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="217"/>
-      <c r="G1" s="216" t="s">
+      <c r="F1" s="207"/>
+      <c r="G1" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="216"/>
-      <c r="I1" s="217" t="s">
+      <c r="H1" s="206"/>
+      <c r="I1" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="217"/>
-      <c r="K1" s="216" t="s">
+      <c r="J1" s="207"/>
+      <c r="K1" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="216"/>
-      <c r="M1" s="214" t="s">
+      <c r="L1" s="206"/>
+      <c r="M1" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="215"/>
+      <c r="N1" s="205"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15952,30 +15952,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="216" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="216"/>
-      <c r="E2" s="217" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="217"/>
-      <c r="G2" s="216" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="216"/>
-      <c r="I2" s="217" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="217"/>
-      <c r="K2" s="216" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="216"/>
-      <c r="M2" s="221" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="221"/>
+      <c r="N2" s="199"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17779,30 +17779,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="216" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="216"/>
-      <c r="E2" s="217" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="217"/>
-      <c r="G2" s="216" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="216"/>
-      <c r="I2" s="217" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="217"/>
-      <c r="K2" s="216" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="216"/>
-      <c r="M2" s="221" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="221"/>
+      <c r="N2" s="199"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19469,30 +19469,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="216" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="216"/>
-      <c r="E2" s="217" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="217"/>
-      <c r="G2" s="216" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="216"/>
-      <c r="I2" s="217" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="217"/>
-      <c r="K2" s="216" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="216"/>
-      <c r="M2" s="221" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="221"/>
+      <c r="N2" s="199"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21295,30 +21295,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="216" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="216"/>
-      <c r="E2" s="217" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="217"/>
-      <c r="G2" s="216" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="216"/>
-      <c r="I2" s="217" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="217"/>
-      <c r="K2" s="216" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="216"/>
-      <c r="M2" s="221" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="221"/>
+      <c r="N2" s="199"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23167,36 +23167,36 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="218" t="s">
+      <c r="C2" s="196" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="219"/>
-      <c r="E2" s="220"/>
-      <c r="F2" s="223" t="s">
+      <c r="D2" s="197"/>
+      <c r="E2" s="198"/>
+      <c r="F2" s="201" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="224"/>
-      <c r="H2" s="225"/>
-      <c r="I2" s="218" t="s">
+      <c r="G2" s="202"/>
+      <c r="H2" s="203"/>
+      <c r="I2" s="196" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="219"/>
-      <c r="K2" s="220"/>
-      <c r="L2" s="223" t="s">
+      <c r="J2" s="197"/>
+      <c r="K2" s="198"/>
+      <c r="L2" s="201" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="224"/>
-      <c r="N2" s="225"/>
-      <c r="O2" s="218" t="s">
+      <c r="M2" s="202"/>
+      <c r="N2" s="203"/>
+      <c r="O2" s="196" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="219"/>
-      <c r="Q2" s="220"/>
-      <c r="R2" s="221" t="s">
+      <c r="P2" s="197"/>
+      <c r="Q2" s="198"/>
+      <c r="R2" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="221"/>
-      <c r="T2" s="221"/>
+      <c r="S2" s="199"/>
+      <c r="T2" s="199"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23269,7 +23269,7 @@
       </c>
       <c r="C4" s="6">
         <f>'Premier League'!C4</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="6">
         <f>'Premier League'!D4</f>
@@ -23329,7 +23329,7 @@
       </c>
       <c r="R4" s="2">
         <f>SUM(C4,F4,I4,L4,O4)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S4" s="2">
         <f t="shared" ref="S4:T4" si="0">SUM(D4,G4,J4,M4,P4)</f>
@@ -23430,7 +23430,7 @@
       </c>
       <c r="C6" s="6">
         <f>'Premier League'!C6</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6">
         <f>'Premier League'!D6</f>
@@ -23490,7 +23490,7 @@
       </c>
       <c r="R6" s="2">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S6" s="2">
         <f t="shared" si="2"/>
@@ -23511,7 +23511,7 @@
       </c>
       <c r="C7" s="6">
         <f>'Premier League'!C7</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="6">
         <f>'Premier League'!D7</f>
@@ -23571,7 +23571,7 @@
       </c>
       <c r="R7" s="2">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S7" s="2">
         <f t="shared" si="2"/>
@@ -23673,7 +23673,7 @@
       </c>
       <c r="C9" s="6">
         <f>'Premier League'!C9</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="6">
         <f>'Premier League'!D9</f>
@@ -23733,7 +23733,7 @@
       </c>
       <c r="R9" s="2">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S9" s="2">
         <f t="shared" si="2"/>
@@ -23754,11 +23754,11 @@
       </c>
       <c r="C10" s="6">
         <f>'Premier League'!C10</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="6">
         <f>'Premier League'!D10</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="6">
         <f>'Premier League'!E10</f>
@@ -23814,11 +23814,11 @@
       </c>
       <c r="R10" s="2">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S10" s="2">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T10" s="2">
         <f t="shared" si="3"/>
@@ -23835,7 +23835,7 @@
       </c>
       <c r="C11" s="6">
         <f>'Premier League'!C11</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="6">
         <f>'Premier League'!D11</f>
@@ -23895,7 +23895,7 @@
       </c>
       <c r="R11" s="2">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S11" s="2">
         <f t="shared" si="2"/>
@@ -24398,7 +24398,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="149" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C18" s="6">
         <f>'Premier League'!C18</f>
@@ -24483,7 +24483,7 @@
       </c>
       <c r="C19" s="6">
         <f>'Premier League'!C19</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="6">
         <f>'Premier League'!D19</f>
@@ -24543,7 +24543,7 @@
       </c>
       <c r="R19" s="2">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S19" s="2">
         <f t="shared" si="5"/>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="C25" s="6">
         <f>'Premier League'!C25</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="6">
         <f>'Premier League'!D25</f>
@@ -25026,7 +25026,7 @@
       </c>
       <c r="R25" s="2">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S25" s="2">
         <f t="shared" si="5"/>
@@ -25128,7 +25128,7 @@
       </c>
       <c r="C27" s="6">
         <f>'Premier League'!C27</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="6">
         <f>'Premier League'!D27</f>
@@ -25136,7 +25136,7 @@
       </c>
       <c r="E27" s="6">
         <f>'Premier League'!E27</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="4">
         <f>Europe!C27</f>
@@ -25188,7 +25188,7 @@
       </c>
       <c r="R27" s="2">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S27" s="2">
         <f t="shared" si="5"/>
@@ -25196,7 +25196,7 @@
       </c>
       <c r="T27" s="2">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V27" s="55"/>
     </row>
@@ -25452,7 +25452,7 @@
       </c>
       <c r="C31" s="6">
         <f>'Premier League'!C31</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="6">
         <f>'Premier League'!D31</f>
@@ -25512,7 +25512,7 @@
       </c>
       <c r="R31" s="2">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S31" s="2">
         <f t="shared" si="5"/>
@@ -25614,7 +25614,7 @@
       </c>
       <c r="C33" s="6">
         <f>'Premier League'!C33</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="6">
         <f>'Premier League'!D33</f>
@@ -25674,7 +25674,7 @@
       </c>
       <c r="R33" s="2">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S33" s="2">
         <f t="shared" si="5"/>
@@ -26379,36 +26379,36 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="218" t="s">
+      <c r="E1" s="196" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="219"/>
-      <c r="G1" s="220"/>
-      <c r="H1" s="223" t="s">
+      <c r="F1" s="197"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="201" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="224"/>
-      <c r="J1" s="225"/>
-      <c r="K1" s="218" t="s">
+      <c r="I1" s="202"/>
+      <c r="J1" s="203"/>
+      <c r="K1" s="196" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="219"/>
-      <c r="M1" s="220"/>
-      <c r="N1" s="223" t="s">
+      <c r="L1" s="197"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="201" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="224"/>
-      <c r="P1" s="225"/>
-      <c r="Q1" s="218" t="s">
+      <c r="O1" s="202"/>
+      <c r="P1" s="203"/>
+      <c r="Q1" s="196" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="219"/>
-      <c r="S1" s="220"/>
-      <c r="T1" s="221" t="s">
+      <c r="R1" s="197"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="221"/>
-      <c r="V1" s="221"/>
+      <c r="U1" s="199"/>
+      <c r="V1" s="199"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37806,399 +37806,399 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="229">
-        <v>1</v>
-      </c>
-      <c r="G1" s="230"/>
-      <c r="H1" s="231"/>
-      <c r="I1" s="229">
+      <c r="F1" s="211">
+        <v>1</v>
+      </c>
+      <c r="G1" s="212"/>
+      <c r="H1" s="213"/>
+      <c r="I1" s="211">
         <v>2</v>
       </c>
-      <c r="J1" s="230"/>
-      <c r="K1" s="231"/>
-      <c r="L1" s="229">
-        <v>3</v>
-      </c>
-      <c r="M1" s="230"/>
-      <c r="N1" s="231"/>
-      <c r="O1" s="229">
+      <c r="J1" s="212"/>
+      <c r="K1" s="213"/>
+      <c r="L1" s="211">
+        <v>3</v>
+      </c>
+      <c r="M1" s="212"/>
+      <c r="N1" s="213"/>
+      <c r="O1" s="211">
         <v>4</v>
       </c>
-      <c r="P1" s="230"/>
-      <c r="Q1" s="231"/>
-      <c r="R1" s="229">
+      <c r="P1" s="212"/>
+      <c r="Q1" s="213"/>
+      <c r="R1" s="211">
         <v>5</v>
       </c>
-      <c r="S1" s="230"/>
-      <c r="T1" s="231"/>
-      <c r="U1" s="229">
+      <c r="S1" s="212"/>
+      <c r="T1" s="213"/>
+      <c r="U1" s="211">
         <v>6</v>
       </c>
-      <c r="V1" s="230"/>
-      <c r="W1" s="231"/>
-      <c r="X1" s="229">
+      <c r="V1" s="212"/>
+      <c r="W1" s="213"/>
+      <c r="X1" s="211">
         <v>7</v>
       </c>
-      <c r="Y1" s="230"/>
-      <c r="Z1" s="231"/>
-      <c r="AA1" s="229">
+      <c r="Y1" s="212"/>
+      <c r="Z1" s="213"/>
+      <c r="AA1" s="211">
         <v>8</v>
       </c>
-      <c r="AB1" s="230"/>
-      <c r="AC1" s="231"/>
-      <c r="AD1" s="229">
+      <c r="AB1" s="212"/>
+      <c r="AC1" s="213"/>
+      <c r="AD1" s="211">
         <v>9</v>
       </c>
-      <c r="AE1" s="230"/>
-      <c r="AF1" s="231"/>
-      <c r="AG1" s="229">
+      <c r="AE1" s="212"/>
+      <c r="AF1" s="213"/>
+      <c r="AG1" s="211">
         <v>10</v>
       </c>
-      <c r="AH1" s="230"/>
-      <c r="AI1" s="231"/>
-      <c r="AJ1" s="229">
+      <c r="AH1" s="212"/>
+      <c r="AI1" s="213"/>
+      <c r="AJ1" s="211">
         <v>11</v>
       </c>
-      <c r="AK1" s="230"/>
-      <c r="AL1" s="231"/>
-      <c r="AM1" s="229">
+      <c r="AK1" s="212"/>
+      <c r="AL1" s="213"/>
+      <c r="AM1" s="211">
         <v>12</v>
       </c>
-      <c r="AN1" s="230"/>
-      <c r="AO1" s="231"/>
-      <c r="AP1" s="229">
+      <c r="AN1" s="212"/>
+      <c r="AO1" s="213"/>
+      <c r="AP1" s="211">
         <v>13</v>
       </c>
-      <c r="AQ1" s="230"/>
-      <c r="AR1" s="231"/>
-      <c r="AS1" s="229">
+      <c r="AQ1" s="212"/>
+      <c r="AR1" s="213"/>
+      <c r="AS1" s="211">
         <v>14</v>
       </c>
-      <c r="AT1" s="230"/>
-      <c r="AU1" s="231"/>
-      <c r="AV1" s="229">
+      <c r="AT1" s="212"/>
+      <c r="AU1" s="213"/>
+      <c r="AV1" s="211">
         <v>15</v>
       </c>
-      <c r="AW1" s="230"/>
-      <c r="AX1" s="231"/>
-      <c r="AY1" s="229">
+      <c r="AW1" s="212"/>
+      <c r="AX1" s="213"/>
+      <c r="AY1" s="211">
         <v>16</v>
       </c>
-      <c r="AZ1" s="230"/>
-      <c r="BA1" s="231"/>
-      <c r="BB1" s="229">
+      <c r="AZ1" s="212"/>
+      <c r="BA1" s="213"/>
+      <c r="BB1" s="211">
         <v>17</v>
       </c>
-      <c r="BC1" s="230"/>
-      <c r="BD1" s="231"/>
-      <c r="BE1" s="229">
+      <c r="BC1" s="212"/>
+      <c r="BD1" s="213"/>
+      <c r="BE1" s="211">
         <v>18</v>
       </c>
-      <c r="BF1" s="230"/>
-      <c r="BG1" s="231"/>
-      <c r="BH1" s="229">
+      <c r="BF1" s="212"/>
+      <c r="BG1" s="213"/>
+      <c r="BH1" s="211">
         <v>19</v>
       </c>
-      <c r="BI1" s="230"/>
-      <c r="BJ1" s="231"/>
-      <c r="BK1" s="229">
+      <c r="BI1" s="212"/>
+      <c r="BJ1" s="213"/>
+      <c r="BK1" s="211">
         <v>20</v>
       </c>
-      <c r="BL1" s="230"/>
-      <c r="BM1" s="231"/>
-      <c r="BN1" s="229">
+      <c r="BL1" s="212"/>
+      <c r="BM1" s="213"/>
+      <c r="BN1" s="211">
         <v>21</v>
       </c>
-      <c r="BO1" s="230"/>
-      <c r="BP1" s="231"/>
-      <c r="BQ1" s="229">
+      <c r="BO1" s="212"/>
+      <c r="BP1" s="213"/>
+      <c r="BQ1" s="211">
         <v>22</v>
       </c>
-      <c r="BR1" s="230"/>
-      <c r="BS1" s="231"/>
-      <c r="BT1" s="229">
+      <c r="BR1" s="212"/>
+      <c r="BS1" s="213"/>
+      <c r="BT1" s="211">
         <v>23</v>
       </c>
-      <c r="BU1" s="230"/>
-      <c r="BV1" s="231"/>
-      <c r="BW1" s="229">
+      <c r="BU1" s="212"/>
+      <c r="BV1" s="213"/>
+      <c r="BW1" s="211">
         <v>24</v>
       </c>
-      <c r="BX1" s="230"/>
-      <c r="BY1" s="231"/>
-      <c r="BZ1" s="229">
+      <c r="BX1" s="212"/>
+      <c r="BY1" s="213"/>
+      <c r="BZ1" s="211">
         <v>25</v>
       </c>
-      <c r="CA1" s="230"/>
-      <c r="CB1" s="231"/>
-      <c r="CC1" s="229">
+      <c r="CA1" s="212"/>
+      <c r="CB1" s="213"/>
+      <c r="CC1" s="211">
         <v>26</v>
       </c>
-      <c r="CD1" s="230"/>
-      <c r="CE1" s="231"/>
-      <c r="CF1" s="229">
+      <c r="CD1" s="212"/>
+      <c r="CE1" s="213"/>
+      <c r="CF1" s="211">
         <v>27</v>
       </c>
-      <c r="CG1" s="230"/>
-      <c r="CH1" s="231"/>
-      <c r="CI1" s="229">
+      <c r="CG1" s="212"/>
+      <c r="CH1" s="213"/>
+      <c r="CI1" s="211">
         <v>28</v>
       </c>
-      <c r="CJ1" s="230"/>
-      <c r="CK1" s="231"/>
-      <c r="CL1" s="229">
+      <c r="CJ1" s="212"/>
+      <c r="CK1" s="213"/>
+      <c r="CL1" s="211">
         <v>29</v>
       </c>
-      <c r="CM1" s="230"/>
-      <c r="CN1" s="231"/>
-      <c r="CO1" s="229">
+      <c r="CM1" s="212"/>
+      <c r="CN1" s="213"/>
+      <c r="CO1" s="211">
         <v>30</v>
       </c>
-      <c r="CP1" s="230"/>
-      <c r="CQ1" s="231"/>
-      <c r="CR1" s="229">
+      <c r="CP1" s="212"/>
+      <c r="CQ1" s="213"/>
+      <c r="CR1" s="211">
         <v>31</v>
       </c>
-      <c r="CS1" s="230"/>
-      <c r="CT1" s="231"/>
-      <c r="CU1" s="229">
+      <c r="CS1" s="212"/>
+      <c r="CT1" s="213"/>
+      <c r="CU1" s="211">
         <v>32</v>
       </c>
-      <c r="CV1" s="230"/>
-      <c r="CW1" s="231"/>
-      <c r="CX1" s="229">
+      <c r="CV1" s="212"/>
+      <c r="CW1" s="213"/>
+      <c r="CX1" s="211">
         <v>33</v>
       </c>
-      <c r="CY1" s="230"/>
-      <c r="CZ1" s="231"/>
-      <c r="DA1" s="229">
+      <c r="CY1" s="212"/>
+      <c r="CZ1" s="213"/>
+      <c r="DA1" s="211">
         <v>34</v>
       </c>
-      <c r="DB1" s="230"/>
-      <c r="DC1" s="231"/>
-      <c r="DD1" s="229">
+      <c r="DB1" s="212"/>
+      <c r="DC1" s="213"/>
+      <c r="DD1" s="211">
         <v>35</v>
       </c>
-      <c r="DE1" s="230"/>
-      <c r="DF1" s="231"/>
-      <c r="DG1" s="229">
+      <c r="DE1" s="212"/>
+      <c r="DF1" s="213"/>
+      <c r="DG1" s="211">
         <v>36</v>
       </c>
-      <c r="DH1" s="230"/>
-      <c r="DI1" s="231"/>
-      <c r="DJ1" s="229">
+      <c r="DH1" s="212"/>
+      <c r="DI1" s="213"/>
+      <c r="DJ1" s="211">
         <v>37</v>
       </c>
-      <c r="DK1" s="230"/>
-      <c r="DL1" s="231"/>
-      <c r="DM1" s="229">
+      <c r="DK1" s="212"/>
+      <c r="DL1" s="213"/>
+      <c r="DM1" s="211">
         <v>38</v>
       </c>
-      <c r="DN1" s="230"/>
-      <c r="DO1" s="231"/>
+      <c r="DN1" s="212"/>
+      <c r="DO1" s="213"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="214" t="s">
         <v>397</v>
       </c>
-      <c r="D2" s="232" t="s">
+      <c r="D2" s="214" t="s">
         <v>398</v>
       </c>
-      <c r="E2" s="232" t="s">
+      <c r="E2" s="214" t="s">
         <v>399</v>
       </c>
-      <c r="F2" s="226" t="s">
+      <c r="F2" s="208" t="s">
         <v>347</v>
       </c>
-      <c r="G2" s="227"/>
-      <c r="H2" s="228"/>
-      <c r="I2" s="235" t="s">
+      <c r="G2" s="209"/>
+      <c r="H2" s="210"/>
+      <c r="I2" s="217" t="s">
         <v>332</v>
       </c>
-      <c r="J2" s="236"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="226" t="s">
+      <c r="J2" s="218"/>
+      <c r="K2" s="219"/>
+      <c r="L2" s="208" t="s">
         <v>331</v>
       </c>
-      <c r="M2" s="227"/>
-      <c r="N2" s="228"/>
-      <c r="O2" s="226" t="s">
+      <c r="M2" s="209"/>
+      <c r="N2" s="210"/>
+      <c r="O2" s="208" t="s">
         <v>329</v>
       </c>
-      <c r="P2" s="227"/>
-      <c r="Q2" s="228"/>
-      <c r="R2" s="226" t="s">
+      <c r="P2" s="209"/>
+      <c r="Q2" s="210"/>
+      <c r="R2" s="208" t="s">
         <v>336</v>
       </c>
-      <c r="S2" s="227"/>
-      <c r="T2" s="228"/>
-      <c r="U2" s="226" t="s">
+      <c r="S2" s="209"/>
+      <c r="T2" s="210"/>
+      <c r="U2" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="V2" s="227"/>
-      <c r="W2" s="228"/>
-      <c r="X2" s="226" t="s">
+      <c r="V2" s="209"/>
+      <c r="W2" s="210"/>
+      <c r="X2" s="208" t="s">
         <v>338</v>
       </c>
-      <c r="Y2" s="227"/>
-      <c r="Z2" s="228"/>
-      <c r="AA2" s="226" t="s">
+      <c r="Y2" s="209"/>
+      <c r="Z2" s="210"/>
+      <c r="AA2" s="208" t="s">
         <v>335</v>
       </c>
-      <c r="AB2" s="227"/>
-      <c r="AC2" s="228"/>
-      <c r="AD2" s="226" t="s">
+      <c r="AB2" s="209"/>
+      <c r="AC2" s="210"/>
+      <c r="AD2" s="208" t="s">
         <v>322</v>
       </c>
-      <c r="AE2" s="227"/>
-      <c r="AF2" s="228"/>
-      <c r="AG2" s="226" t="s">
+      <c r="AE2" s="209"/>
+      <c r="AF2" s="210"/>
+      <c r="AG2" s="208" t="s">
         <v>348</v>
       </c>
-      <c r="AH2" s="227"/>
-      <c r="AI2" s="228"/>
-      <c r="AJ2" s="226" t="s">
+      <c r="AH2" s="209"/>
+      <c r="AI2" s="210"/>
+      <c r="AJ2" s="208" t="s">
         <v>325</v>
       </c>
-      <c r="AK2" s="227"/>
-      <c r="AL2" s="228"/>
-      <c r="AM2" s="226" t="s">
+      <c r="AK2" s="209"/>
+      <c r="AL2" s="210"/>
+      <c r="AM2" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="AN2" s="227"/>
-      <c r="AO2" s="228"/>
-      <c r="AP2" s="226" t="s">
+      <c r="AN2" s="209"/>
+      <c r="AO2" s="210"/>
+      <c r="AP2" s="208" t="s">
         <v>333</v>
       </c>
-      <c r="AQ2" s="227"/>
-      <c r="AR2" s="228"/>
-      <c r="AS2" s="226" t="s">
+      <c r="AQ2" s="209"/>
+      <c r="AR2" s="210"/>
+      <c r="AS2" s="208" t="s">
         <v>330</v>
       </c>
-      <c r="AT2" s="227"/>
-      <c r="AU2" s="228"/>
-      <c r="AV2" s="226" t="s">
+      <c r="AT2" s="209"/>
+      <c r="AU2" s="210"/>
+      <c r="AV2" s="208" t="s">
         <v>337</v>
       </c>
-      <c r="AW2" s="227"/>
-      <c r="AX2" s="228"/>
-      <c r="AY2" s="226" t="s">
+      <c r="AW2" s="209"/>
+      <c r="AX2" s="210"/>
+      <c r="AY2" s="208" t="s">
         <v>306</v>
       </c>
-      <c r="AZ2" s="227"/>
-      <c r="BA2" s="228"/>
-      <c r="BB2" s="226" t="s">
+      <c r="AZ2" s="209"/>
+      <c r="BA2" s="210"/>
+      <c r="BB2" s="208" t="s">
         <v>327</v>
       </c>
-      <c r="BC2" s="227"/>
-      <c r="BD2" s="228"/>
-      <c r="BE2" s="226" t="s">
+      <c r="BC2" s="209"/>
+      <c r="BD2" s="210"/>
+      <c r="BE2" s="208" t="s">
         <v>326</v>
       </c>
-      <c r="BF2" s="227"/>
-      <c r="BG2" s="228"/>
-      <c r="BH2" s="226" t="s">
+      <c r="BF2" s="209"/>
+      <c r="BG2" s="210"/>
+      <c r="BH2" s="208" t="s">
         <v>349</v>
       </c>
-      <c r="BI2" s="227"/>
-      <c r="BJ2" s="228"/>
-      <c r="BK2" s="226" t="s">
+      <c r="BI2" s="209"/>
+      <c r="BJ2" s="210"/>
+      <c r="BK2" s="208" t="s">
         <v>333</v>
       </c>
-      <c r="BL2" s="227"/>
-      <c r="BM2" s="228"/>
-      <c r="BN2" s="226" t="s">
+      <c r="BL2" s="209"/>
+      <c r="BM2" s="210"/>
+      <c r="BN2" s="208" t="s">
         <v>348</v>
       </c>
-      <c r="BO2" s="227"/>
-      <c r="BP2" s="228"/>
-      <c r="BQ2" s="226" t="s">
+      <c r="BO2" s="209"/>
+      <c r="BP2" s="210"/>
+      <c r="BQ2" s="208" t="s">
         <v>325</v>
       </c>
-      <c r="BR2" s="227"/>
-      <c r="BS2" s="228"/>
-      <c r="BT2" s="226" t="s">
+      <c r="BR2" s="209"/>
+      <c r="BS2" s="210"/>
+      <c r="BT2" s="208" t="s">
         <v>324</v>
       </c>
-      <c r="BU2" s="227"/>
-      <c r="BV2" s="228"/>
-      <c r="BW2" s="226" t="s">
+      <c r="BU2" s="209"/>
+      <c r="BV2" s="210"/>
+      <c r="BW2" s="208" t="s">
         <v>322</v>
       </c>
-      <c r="BX2" s="227"/>
-      <c r="BY2" s="228"/>
-      <c r="BZ2" s="226" t="s">
+      <c r="BX2" s="209"/>
+      <c r="BY2" s="210"/>
+      <c r="BZ2" s="208" t="s">
         <v>349</v>
       </c>
-      <c r="CA2" s="227"/>
-      <c r="CB2" s="228"/>
-      <c r="CC2" s="226" t="s">
+      <c r="CA2" s="209"/>
+      <c r="CB2" s="210"/>
+      <c r="CC2" s="208" t="s">
         <v>326</v>
       </c>
-      <c r="CD2" s="227"/>
-      <c r="CE2" s="228"/>
-      <c r="CF2" s="226" t="s">
+      <c r="CD2" s="209"/>
+      <c r="CE2" s="210"/>
+      <c r="CF2" s="208" t="s">
         <v>306</v>
       </c>
-      <c r="CG2" s="227"/>
-      <c r="CH2" s="228"/>
-      <c r="CI2" s="226" t="s">
+      <c r="CG2" s="209"/>
+      <c r="CH2" s="210"/>
+      <c r="CI2" s="208" t="s">
         <v>327</v>
       </c>
-      <c r="CJ2" s="227"/>
-      <c r="CK2" s="228"/>
-      <c r="CL2" s="226" t="s">
+      <c r="CJ2" s="209"/>
+      <c r="CK2" s="210"/>
+      <c r="CL2" s="208" t="s">
         <v>331</v>
       </c>
-      <c r="CM2" s="227"/>
-      <c r="CN2" s="228"/>
-      <c r="CO2" s="226" t="s">
+      <c r="CM2" s="209"/>
+      <c r="CN2" s="210"/>
+      <c r="CO2" s="208" t="s">
         <v>329</v>
       </c>
-      <c r="CP2" s="227"/>
-      <c r="CQ2" s="228"/>
-      <c r="CR2" s="226" t="s">
+      <c r="CP2" s="209"/>
+      <c r="CQ2" s="210"/>
+      <c r="CR2" s="208" t="s">
         <v>347</v>
       </c>
-      <c r="CS2" s="227"/>
-      <c r="CT2" s="228"/>
-      <c r="CU2" s="226" t="s">
+      <c r="CS2" s="209"/>
+      <c r="CT2" s="210"/>
+      <c r="CU2" s="208" t="s">
         <v>332</v>
       </c>
-      <c r="CV2" s="227"/>
-      <c r="CW2" s="228"/>
-      <c r="CX2" s="226" t="s">
+      <c r="CV2" s="209"/>
+      <c r="CW2" s="210"/>
+      <c r="CX2" s="208" t="s">
         <v>337</v>
       </c>
-      <c r="CY2" s="227"/>
-      <c r="CZ2" s="228"/>
-      <c r="DA2" s="226" t="s">
+      <c r="CY2" s="209"/>
+      <c r="CZ2" s="210"/>
+      <c r="DA2" s="208" t="s">
         <v>330</v>
       </c>
-      <c r="DB2" s="227"/>
-      <c r="DC2" s="228"/>
-      <c r="DD2" s="226" t="s">
+      <c r="DB2" s="209"/>
+      <c r="DC2" s="210"/>
+      <c r="DD2" s="208" t="s">
         <v>321</v>
       </c>
-      <c r="DE2" s="227"/>
-      <c r="DF2" s="228"/>
-      <c r="DG2" s="226" t="s">
+      <c r="DE2" s="209"/>
+      <c r="DF2" s="210"/>
+      <c r="DG2" s="208" t="s">
         <v>338</v>
       </c>
-      <c r="DH2" s="227"/>
-      <c r="DI2" s="228"/>
-      <c r="DJ2" s="226" t="s">
+      <c r="DH2" s="209"/>
+      <c r="DI2" s="210"/>
+      <c r="DJ2" s="208" t="s">
         <v>335</v>
       </c>
-      <c r="DK2" s="227"/>
-      <c r="DL2" s="228"/>
-      <c r="DM2" s="226" t="s">
+      <c r="DK2" s="209"/>
+      <c r="DL2" s="210"/>
+      <c r="DM2" s="208" t="s">
         <v>336</v>
       </c>
-      <c r="DN2" s="227"/>
-      <c r="DO2" s="228"/>
+      <c r="DN2" s="209"/>
+      <c r="DO2" s="210"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38207,9 +38207,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="233"/>
-      <c r="D3" s="233"/>
-      <c r="E3" s="234"/>
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="216"/>
       <c r="F3" s="160" t="s">
         <v>394</v>
       </c>
@@ -38562,7 +38562,7 @@
       </c>
       <c r="C4" s="58">
         <f>SUM(F4,I4,L4,O4,R4,U4,X4,AA4,AD4,AG4,AJ4,AM4,AP4,AS4,AV4,AY4,BB4,BE4,BH4,BK4,BN4,BQ4,BT4,BW4,BZ4,CC4,CF4,CI4,CL4,CO4,CR4,CU4,CX4,DA4,DD4,DG4,DJ4,DM4)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="58">
         <f t="shared" ref="D4:E4" si="0">SUM(G4,J4,M4,P4,S4,V4,Y4,AB4,AE4,AH4,AK4,AN4,AQ4,AT4,AW4,AZ4,BC4,BF4,BI4,BL4,BO4,BR4,BU4,BX4,CA4,CD4,CG4,CJ4,CM4,CP4,CS4,CV4,CY4,DB4,DE4,DH4,DK4,DN4)</f>
@@ -38577,7 +38577,9 @@
       </c>
       <c r="G4" s="36"/>
       <c r="H4" s="53"/>
-      <c r="I4" s="52"/>
+      <c r="I4" s="52">
+        <v>1</v>
+      </c>
       <c r="J4" s="36"/>
       <c r="K4" s="53"/>
       <c r="L4" s="52"/>
@@ -38832,7 +38834,7 @@
       </c>
       <c r="C6" s="58">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="58">
         <f t="shared" si="2"/>
@@ -38847,7 +38849,9 @@
       </c>
       <c r="G6" s="36"/>
       <c r="H6" s="53"/>
-      <c r="I6" s="52"/>
+      <c r="I6" s="52">
+        <v>1</v>
+      </c>
       <c r="J6" s="36"/>
       <c r="K6" s="53"/>
       <c r="L6" s="52"/>
@@ -38968,7 +38972,7 @@
       </c>
       <c r="C7" s="58">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="58">
         <f t="shared" si="2"/>
@@ -38985,7 +38989,9 @@
       <c r="H7" s="53">
         <v>1</v>
       </c>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>1</v>
+      </c>
       <c r="J7" s="36"/>
       <c r="K7" s="53"/>
       <c r="L7" s="52"/>
@@ -39242,7 +39248,7 @@
       </c>
       <c r="C9" s="58">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="58">
         <f t="shared" si="2"/>
@@ -39257,7 +39263,9 @@
       </c>
       <c r="G9" s="36"/>
       <c r="H9" s="53"/>
-      <c r="I9" s="52"/>
+      <c r="I9" s="52">
+        <v>1</v>
+      </c>
       <c r="J9" s="36"/>
       <c r="K9" s="53"/>
       <c r="L9" s="52"/>
@@ -39378,11 +39386,11 @@
       </c>
       <c r="C10" s="58">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="58">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="58">
         <f t="shared" si="3"/>
@@ -39395,8 +39403,12 @@
         <v>1</v>
       </c>
       <c r="H10" s="53"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="36"/>
+      <c r="I10" s="52">
+        <v>1</v>
+      </c>
+      <c r="J10" s="36">
+        <v>1</v>
+      </c>
       <c r="K10" s="53"/>
       <c r="L10" s="52"/>
       <c r="M10" s="36"/>
@@ -39516,7 +39528,7 @@
       </c>
       <c r="C11" s="58">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="58">
         <f t="shared" si="2"/>
@@ -39533,7 +39545,9 @@
         <v>1</v>
       </c>
       <c r="H11" s="53"/>
-      <c r="I11" s="52"/>
+      <c r="I11" s="52">
+        <v>1</v>
+      </c>
       <c r="J11" s="36"/>
       <c r="K11" s="53"/>
       <c r="L11" s="52"/>
@@ -40456,7 +40470,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="149" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C18" s="58">
         <f t="shared" ref="C18:C41" si="4">SUM(F18,I18,L18,O18,R18,U18,X18,AA18,AD18,AG18,AJ18,AM18,AP18,AS18,AV18,AY18,BB18,BE18,BH18,BK18,BN18,BQ18,BT18,BW18,BZ18,CC18,CF18,CI18,CL18,CO18,CR18,CU18,CX18,DA18,DD18,DG18,DJ18,DM18)</f>
@@ -40594,7 +40608,7 @@
       </c>
       <c r="C19" s="58">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="58">
         <f t="shared" si="5"/>
@@ -40609,7 +40623,9 @@
       </c>
       <c r="G19" s="36"/>
       <c r="H19" s="53"/>
-      <c r="I19" s="52"/>
+      <c r="I19" s="52">
+        <v>1</v>
+      </c>
       <c r="J19" s="36"/>
       <c r="K19" s="53"/>
       <c r="L19" s="52"/>
@@ -41404,7 +41420,7 @@
       </c>
       <c r="C25" s="58">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="58">
         <f t="shared" si="5"/>
@@ -41421,7 +41437,9 @@
         <v>1</v>
       </c>
       <c r="H25" s="53"/>
-      <c r="I25" s="52"/>
+      <c r="I25" s="52">
+        <v>1</v>
+      </c>
       <c r="J25" s="36"/>
       <c r="K25" s="53"/>
       <c r="L25" s="52"/>
@@ -41676,7 +41694,7 @@
       </c>
       <c r="C27" s="58">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="58">
         <f t="shared" si="5"/>
@@ -41684,7 +41702,7 @@
       </c>
       <c r="E27" s="58">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="52">
         <v>1</v>
@@ -41693,9 +41711,13 @@
       <c r="H27" s="53">
         <v>1</v>
       </c>
-      <c r="I27" s="52"/>
+      <c r="I27" s="52">
+        <v>1</v>
+      </c>
       <c r="J27" s="36"/>
-      <c r="K27" s="53"/>
+      <c r="K27" s="53">
+        <v>1</v>
+      </c>
       <c r="L27" s="52"/>
       <c r="M27" s="36"/>
       <c r="N27" s="53"/>
@@ -42218,7 +42240,7 @@
       </c>
       <c r="C31" s="58">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="58">
         <f t="shared" si="5"/>
@@ -42233,7 +42255,9 @@
       </c>
       <c r="G31" s="36"/>
       <c r="H31" s="53"/>
-      <c r="I31" s="52"/>
+      <c r="I31" s="52">
+        <v>1</v>
+      </c>
       <c r="J31" s="36"/>
       <c r="K31" s="53"/>
       <c r="L31" s="52"/>
@@ -42488,7 +42512,7 @@
       </c>
       <c r="C33" s="58">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="58">
         <f t="shared" si="5"/>
@@ -42503,7 +42527,9 @@
       </c>
       <c r="G33" s="36"/>
       <c r="H33" s="53"/>
-      <c r="I33" s="52"/>
+      <c r="I33" s="52">
+        <v>1</v>
+      </c>
       <c r="J33" s="36"/>
       <c r="K33" s="53"/>
       <c r="L33" s="52"/>
@@ -43707,15 +43733,15 @@
       </c>
       <c r="I42" s="73">
         <f t="shared" ref="I42:BT42" si="8">SUM(I4:I41)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J42" s="73">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" s="73">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="73">
         <f t="shared" si="8"/>
@@ -44266,122 +44292,122 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="208" t="s">
+      <c r="C1" s="232" t="s">
         <v>397</v>
       </c>
-      <c r="D1" s="208" t="s">
+      <c r="D1" s="232" t="s">
         <v>398</v>
       </c>
-      <c r="E1" s="208" t="s">
+      <c r="E1" s="232" t="s">
         <v>399</v>
       </c>
-      <c r="F1" s="199" t="s">
+      <c r="F1" s="223" t="s">
         <v>303</v>
       </c>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
-      <c r="J1" s="200"/>
-      <c r="K1" s="200"/>
-      <c r="L1" s="200"/>
-      <c r="M1" s="200"/>
-      <c r="N1" s="200"/>
-      <c r="O1" s="200"/>
-      <c r="P1" s="200"/>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="200"/>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="200"/>
-      <c r="Y1" s="200"/>
-      <c r="Z1" s="200"/>
-      <c r="AA1" s="200"/>
-      <c r="AB1" s="200"/>
-      <c r="AC1" s="201"/>
-      <c r="AD1" s="211" t="s">
+      <c r="G1" s="224"/>
+      <c r="H1" s="224"/>
+      <c r="I1" s="224"/>
+      <c r="J1" s="224"/>
+      <c r="K1" s="224"/>
+      <c r="L1" s="224"/>
+      <c r="M1" s="224"/>
+      <c r="N1" s="224"/>
+      <c r="O1" s="224"/>
+      <c r="P1" s="224"/>
+      <c r="Q1" s="224"/>
+      <c r="R1" s="224"/>
+      <c r="S1" s="224"/>
+      <c r="T1" s="224"/>
+      <c r="U1" s="224"/>
+      <c r="V1" s="224"/>
+      <c r="W1" s="224"/>
+      <c r="X1" s="224"/>
+      <c r="Y1" s="224"/>
+      <c r="Z1" s="224"/>
+      <c r="AA1" s="224"/>
+      <c r="AB1" s="224"/>
+      <c r="AC1" s="225"/>
+      <c r="AD1" s="235" t="s">
         <v>282</v>
       </c>
-      <c r="AE1" s="212"/>
-      <c r="AF1" s="212"/>
-      <c r="AG1" s="212"/>
-      <c r="AH1" s="212"/>
-      <c r="AI1" s="213"/>
-      <c r="AJ1" s="199" t="s">
+      <c r="AE1" s="236"/>
+      <c r="AF1" s="236"/>
+      <c r="AG1" s="236"/>
+      <c r="AH1" s="236"/>
+      <c r="AI1" s="237"/>
+      <c r="AJ1" s="223" t="s">
         <v>283</v>
       </c>
-      <c r="AK1" s="200"/>
-      <c r="AL1" s="200"/>
-      <c r="AM1" s="200"/>
-      <c r="AN1" s="200"/>
-      <c r="AO1" s="201"/>
-      <c r="AP1" s="202" t="s">
+      <c r="AK1" s="224"/>
+      <c r="AL1" s="224"/>
+      <c r="AM1" s="224"/>
+      <c r="AN1" s="224"/>
+      <c r="AO1" s="225"/>
+      <c r="AP1" s="226" t="s">
         <v>284</v>
       </c>
-      <c r="AQ1" s="203"/>
-      <c r="AR1" s="203"/>
-      <c r="AS1" s="203"/>
-      <c r="AT1" s="203"/>
-      <c r="AU1" s="204"/>
-      <c r="AV1" s="205" t="s">
+      <c r="AQ1" s="227"/>
+      <c r="AR1" s="227"/>
+      <c r="AS1" s="227"/>
+      <c r="AT1" s="227"/>
+      <c r="AU1" s="228"/>
+      <c r="AV1" s="229" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="206"/>
-      <c r="AX1" s="207"/>
+      <c r="AW1" s="230"/>
+      <c r="AX1" s="231"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="209"/>
-      <c r="D2" s="209"/>
-      <c r="E2" s="209"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="197"/>
-      <c r="H2" s="198"/>
-      <c r="I2" s="196"/>
-      <c r="J2" s="197"/>
-      <c r="K2" s="198"/>
-      <c r="L2" s="196"/>
-      <c r="M2" s="197"/>
-      <c r="N2" s="198"/>
-      <c r="O2" s="196"/>
-      <c r="P2" s="197"/>
-      <c r="Q2" s="198"/>
-      <c r="R2" s="196"/>
-      <c r="S2" s="197"/>
-      <c r="T2" s="198"/>
-      <c r="U2" s="196"/>
-      <c r="V2" s="197"/>
-      <c r="W2" s="198"/>
-      <c r="X2" s="196"/>
-      <c r="Y2" s="197"/>
-      <c r="Z2" s="198"/>
-      <c r="AA2" s="196"/>
-      <c r="AB2" s="197"/>
-      <c r="AC2" s="197"/>
-      <c r="AD2" s="196"/>
-      <c r="AE2" s="197"/>
-      <c r="AF2" s="198"/>
-      <c r="AG2" s="196"/>
-      <c r="AH2" s="197"/>
-      <c r="AI2" s="198"/>
-      <c r="AJ2" s="196"/>
-      <c r="AK2" s="197"/>
-      <c r="AL2" s="198"/>
-      <c r="AM2" s="196"/>
-      <c r="AN2" s="197"/>
-      <c r="AO2" s="198"/>
-      <c r="AP2" s="196"/>
-      <c r="AQ2" s="197"/>
-      <c r="AR2" s="198"/>
-      <c r="AS2" s="196"/>
-      <c r="AT2" s="197"/>
-      <c r="AU2" s="198"/>
-      <c r="AV2" s="196"/>
-      <c r="AW2" s="197"/>
-      <c r="AX2" s="198"/>
+      <c r="C2" s="233"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="220"/>
+      <c r="G2" s="221"/>
+      <c r="H2" s="222"/>
+      <c r="I2" s="220"/>
+      <c r="J2" s="221"/>
+      <c r="K2" s="222"/>
+      <c r="L2" s="220"/>
+      <c r="M2" s="221"/>
+      <c r="N2" s="222"/>
+      <c r="O2" s="220"/>
+      <c r="P2" s="221"/>
+      <c r="Q2" s="222"/>
+      <c r="R2" s="220"/>
+      <c r="S2" s="221"/>
+      <c r="T2" s="222"/>
+      <c r="U2" s="220"/>
+      <c r="V2" s="221"/>
+      <c r="W2" s="222"/>
+      <c r="X2" s="220"/>
+      <c r="Y2" s="221"/>
+      <c r="Z2" s="222"/>
+      <c r="AA2" s="220"/>
+      <c r="AB2" s="221"/>
+      <c r="AC2" s="221"/>
+      <c r="AD2" s="220"/>
+      <c r="AE2" s="221"/>
+      <c r="AF2" s="222"/>
+      <c r="AG2" s="220"/>
+      <c r="AH2" s="221"/>
+      <c r="AI2" s="222"/>
+      <c r="AJ2" s="220"/>
+      <c r="AK2" s="221"/>
+      <c r="AL2" s="222"/>
+      <c r="AM2" s="220"/>
+      <c r="AN2" s="221"/>
+      <c r="AO2" s="222"/>
+      <c r="AP2" s="220"/>
+      <c r="AQ2" s="221"/>
+      <c r="AR2" s="222"/>
+      <c r="AS2" s="220"/>
+      <c r="AT2" s="221"/>
+      <c r="AU2" s="222"/>
+      <c r="AV2" s="220"/>
+      <c r="AW2" s="221"/>
+      <c r="AX2" s="222"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -44390,9 +44416,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="210"/>
-      <c r="D3" s="210"/>
-      <c r="E3" s="210"/>
+      <c r="C3" s="234"/>
+      <c r="D3" s="234"/>
+      <c r="E3" s="234"/>
       <c r="F3" s="170" t="s">
         <v>394</v>
       </c>
@@ -45444,7 +45470,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="149" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C18" s="58">
         <f t="shared" ref="C18:C41" si="4">SUM(F18,I18,L18,O18,R18,X18,AA18,AD18,U18,AG18,AJ18,AM18,AP18,AS18,AV18)</f>
@@ -47240,13 +47266,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="208" t="s">
+      <c r="C1" s="232" t="s">
         <v>397</v>
       </c>
-      <c r="D1" s="208" t="s">
+      <c r="D1" s="232" t="s">
         <v>398</v>
       </c>
-      <c r="E1" s="208" t="s">
+      <c r="E1" s="232" t="s">
         <v>399</v>
       </c>
       <c r="F1" s="262" t="s">
@@ -47283,9 +47309,9 @@
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="209"/>
-      <c r="D2" s="209"/>
-      <c r="E2" s="209"/>
+      <c r="C2" s="233"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
       <c r="F2" s="244"/>
       <c r="G2" s="245"/>
       <c r="H2" s="246"/>
@@ -47907,7 +47933,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="149" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C18" s="58">
         <f t="shared" si="2"/>
@@ -49144,7 +49170,7 @@
       <c r="F6" s="25"/>
       <c r="G6" s="21">
         <f>'Apps &amp; Goals 26-27'!C4</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="21">
         <f>'Apps &amp; Goals 26-27'!D4</f>
@@ -49156,7 +49182,7 @@
       </c>
       <c r="J6" s="25">
         <f>G6+C6</f>
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K6" s="25">
         <f>H6+D6</f>
@@ -49524,7 +49550,7 @@
       <c r="F8" s="25"/>
       <c r="G8" s="21">
         <f>'Apps &amp; Goals 26-27'!C6</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="21">
         <f>'Apps &amp; Goals 26-27'!D6</f>
@@ -49536,7 +49562,7 @@
       </c>
       <c r="J8" s="25">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K8" s="25">
         <f t="shared" si="1"/>
@@ -49714,7 +49740,7 @@
       <c r="F9" s="25"/>
       <c r="G9" s="21">
         <f>'Apps &amp; Goals 26-27'!C7</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="21">
         <f>'Apps &amp; Goals 26-27'!D7</f>
@@ -49726,7 +49752,7 @@
       </c>
       <c r="J9" s="25">
         <f t="shared" si="0"/>
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K9" s="25">
         <f t="shared" si="1"/>
@@ -50094,7 +50120,7 @@
       <c r="F11" s="25"/>
       <c r="G11" s="21">
         <f>'Apps &amp; Goals 26-27'!C9</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="21">
         <f>'Apps &amp; Goals 26-27'!D9</f>
@@ -50106,7 +50132,7 @@
       </c>
       <c r="J11" s="25">
         <f t="shared" si="0"/>
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K11" s="25">
         <f t="shared" si="1"/>
@@ -50284,11 +50310,11 @@
       <c r="F12" s="25"/>
       <c r="G12" s="21">
         <f>'Apps &amp; Goals 26-27'!C10</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="21">
         <f>'Apps &amp; Goals 26-27'!D10</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="21">
         <f>'Apps &amp; Goals 26-27'!E10</f>
@@ -50296,11 +50322,11 @@
       </c>
       <c r="J12" s="25">
         <f t="shared" si="0"/>
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K12" s="25">
         <f t="shared" si="1"/>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L12" s="25">
         <f t="shared" si="2"/>
@@ -50474,7 +50500,7 @@
       <c r="F13" s="25"/>
       <c r="G13" s="21">
         <f>'Apps &amp; Goals 26-27'!C11</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="21">
         <f>'Apps &amp; Goals 26-27'!D11</f>
@@ -50486,7 +50512,7 @@
       </c>
       <c r="J13" s="25">
         <f t="shared" si="0"/>
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K13" s="25">
         <f t="shared" si="1"/>
@@ -51790,7 +51816,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C20" s="25">
         <v>0</v>
@@ -51827,7 +51853,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="45" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="O20" s="26">
         <v>0</v>
@@ -51864,7 +51890,7 @@
         <v>0</v>
       </c>
       <c r="Z20" s="57" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AA20" s="24">
         <v>0</v>
@@ -51901,7 +51927,7 @@
         <v>0</v>
       </c>
       <c r="AL20" s="63" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AM20" s="18">
         <v>0</v>
@@ -51938,7 +51964,7 @@
         <v>0</v>
       </c>
       <c r="AX20" s="32" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AY20" s="33">
         <v>0</v>
@@ -51994,7 +52020,7 @@
       <c r="F21" s="25"/>
       <c r="G21" s="21">
         <f>'Apps &amp; Goals 26-27'!C19</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" s="21">
         <f>'Apps &amp; Goals 26-27'!D19</f>
@@ -52006,7 +52032,7 @@
       </c>
       <c r="J21" s="25">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" s="25">
         <f t="shared" si="16"/>
@@ -53134,7 +53160,7 @@
       <c r="F27" s="25"/>
       <c r="G27" s="21">
         <f>'Apps &amp; Goals 26-27'!C25</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="21">
         <f>'Apps &amp; Goals 26-27'!D25</f>
@@ -53146,7 +53172,7 @@
       </c>
       <c r="J27" s="25">
         <f t="shared" si="15"/>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K27" s="25">
         <f t="shared" si="16"/>
@@ -53514,7 +53540,7 @@
       <c r="F29" s="25"/>
       <c r="G29" s="21">
         <f>'Apps &amp; Goals 26-27'!C27</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="21">
         <f>'Apps &amp; Goals 26-27'!D27</f>
@@ -53522,11 +53548,11 @@
       </c>
       <c r="I29" s="21">
         <f>'Apps &amp; Goals 26-27'!E27</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="25">
         <f t="shared" si="15"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K29" s="25">
         <f t="shared" si="16"/>
@@ -53534,7 +53560,7 @@
       </c>
       <c r="L29" s="25">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N29" s="20" t="s">
         <v>292</v>
@@ -54274,7 +54300,7 @@
       <c r="F33" s="25"/>
       <c r="G33" s="21">
         <f>'Apps &amp; Goals 26-27'!C31</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="21">
         <f>'Apps &amp; Goals 26-27'!D31</f>
@@ -54286,7 +54312,7 @@
       </c>
       <c r="J33" s="25">
         <f t="shared" si="15"/>
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K33" s="25">
         <f t="shared" si="16"/>
@@ -54654,7 +54680,7 @@
       <c r="F35" s="25"/>
       <c r="G35" s="21">
         <f>'Apps &amp; Goals 26-27'!C33</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" s="21">
         <f>'Apps &amp; Goals 26-27'!D33</f>
@@ -54666,7 +54692,7 @@
       </c>
       <c r="J35" s="25">
         <f t="shared" si="15"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K35" s="25">
         <f t="shared" si="16"/>
@@ -56376,13 +56402,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="208" t="s">
+      <c r="C1" s="232" t="s">
         <v>397</v>
       </c>
-      <c r="D1" s="208" t="s">
+      <c r="D1" s="232" t="s">
         <v>398</v>
       </c>
-      <c r="E1" s="208" t="s">
+      <c r="E1" s="232" t="s">
         <v>399</v>
       </c>
       <c r="F1" s="262" t="s">
@@ -56419,11 +56445,11 @@
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="209"/>
-      <c r="D2" s="209"/>
-      <c r="E2" s="209"/>
+      <c r="C2" s="233"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
       <c r="F2" s="244" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G2" s="245"/>
       <c r="H2" s="246"/>
@@ -57045,7 +57071,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="149" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C18" s="58">
         <f t="shared" ref="C18:C41" si="2">SUM(F18,I18,L18,O18,R18,U18)</f>
@@ -58272,7 +58298,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="149" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="20"/>
@@ -65245,14 +65271,14 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="316" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B1" s="316"/>
       <c r="C1" s="316"/>
       <c r="D1" s="316"/>
       <c r="E1" s="316"/>
       <c r="F1" s="316" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G1" s="316"/>
       <c r="H1" s="316"/>
@@ -65271,13 +65297,13 @@
       <c r="I2" s="316"/>
       <c r="J2" s="316"/>
       <c r="L2" t="s">
+        <v>411</v>
+      </c>
+      <c r="M2" t="s">
+        <v>412</v>
+      </c>
+      <c r="N2" t="s">
         <v>413</v>
-      </c>
-      <c r="M2" t="s">
-        <v>414</v>
-      </c>
-      <c r="N2" t="s">
-        <v>415</v>
       </c>
       <c r="O2" t="s">
         <v>212</v>
@@ -65298,45 +65324,45 @@
         <v>139</v>
       </c>
       <c r="U2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>400</v>
+      </c>
+      <c r="B3" t="s">
         <v>401</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>402</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>403</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>404</v>
       </c>
-      <c r="E3" t="s">
-        <v>405</v>
-      </c>
       <c r="F3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I3" t="s">
+        <v>403</v>
+      </c>
+      <c r="J3" t="s">
+        <v>404</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3" t="s">
         <v>410</v>
-      </c>
-      <c r="H3" t="s">
-        <v>403</v>
-      </c>
-      <c r="I3" t="s">
-        <v>404</v>
-      </c>
-      <c r="J3" t="s">
-        <v>405</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3" t="s">
-        <v>412</v>
       </c>
       <c r="N3" s="195">
         <v>2</v>
@@ -65365,40 +65391,40 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B4" s="194">
-        <v>0.875</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E4" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="F4" t="s">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="G4" s="194" t="s">
-        <v>411</v>
+        <v>441</v>
       </c>
       <c r="H4" t="s">
         <v>4</v>
       </c>
       <c r="I4" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="J4" t="s">
-        <v>406</v>
+        <v>437</v>
       </c>
       <c r="L4">
         <v>2</v>
       </c>
       <c r="M4" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="N4" s="195">
         <v>2</v>
@@ -65413,13 +65439,13 @@
         <v>0</v>
       </c>
       <c r="R4" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S4" s="195">
         <v>0</v>
       </c>
       <c r="T4" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U4" s="195">
         <v>6</v>
@@ -65430,7 +65456,7 @@
         <v>3</v>
       </c>
       <c r="M5" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N5" s="195">
         <v>2</v>
@@ -65445,13 +65471,13 @@
         <v>0</v>
       </c>
       <c r="R5" s="195">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S5" s="195">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T5" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U5" s="195">
         <v>6</v>
@@ -65468,25 +65494,25 @@
         <v>2</v>
       </c>
       <c r="O6" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" s="195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="195">
         <v>0</v>
       </c>
       <c r="R6" s="195">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S6" s="195">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" s="195">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U6" s="195">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -65494,7 +65520,7 @@
         <v>5</v>
       </c>
       <c r="M7" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="N7" s="195">
         <v>2</v>
@@ -65512,10 +65538,10 @@
         <v>4</v>
       </c>
       <c r="S7" s="195">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U7" s="195">
         <v>4</v>
@@ -65526,7 +65552,7 @@
         <v>6</v>
       </c>
       <c r="M8" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="N8" s="195">
         <v>2</v>
@@ -65541,10 +65567,10 @@
         <v>0</v>
       </c>
       <c r="R8" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S8" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T8" s="195">
         <v>2</v>
@@ -65558,7 +65584,7 @@
         <v>7</v>
       </c>
       <c r="M9" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="N9" s="195">
         <v>2</v>
@@ -65573,13 +65599,13 @@
         <v>0</v>
       </c>
       <c r="R9" s="195">
+        <v>3</v>
+      </c>
+      <c r="S9" s="195">
+        <v>1</v>
+      </c>
+      <c r="T9" s="195">
         <v>2</v>
-      </c>
-      <c r="S9" s="195">
-        <v>1</v>
-      </c>
-      <c r="T9" s="195">
-        <v>1</v>
       </c>
       <c r="U9" s="195">
         <v>4</v>
@@ -65590,7 +65616,7 @@
         <v>8</v>
       </c>
       <c r="M10" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="N10" s="195">
         <v>2</v>
@@ -65599,22 +65625,22 @@
         <v>1</v>
       </c>
       <c r="P10" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" s="195">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S10" s="195">
+        <v>1</v>
+      </c>
+      <c r="T10" s="195">
+        <v>1</v>
+      </c>
+      <c r="U10" s="195">
         <v>4</v>
-      </c>
-      <c r="T10" s="195">
-        <v>3</v>
-      </c>
-      <c r="U10" s="195">
-        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -65622,10 +65648,10 @@
         <v>9</v>
       </c>
       <c r="M11" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N11" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" s="195">
         <v>1</v>
@@ -65634,13 +65660,13 @@
         <v>0</v>
       </c>
       <c r="Q11" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="195">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S11" s="195">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T11" s="195">
         <v>3</v>
@@ -65654,7 +65680,7 @@
         <v>10</v>
       </c>
       <c r="M12" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="N12" s="195">
         <v>2</v>
@@ -65686,7 +65712,7 @@
         <v>11</v>
       </c>
       <c r="M13" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="N13" s="195">
         <v>2</v>
@@ -65718,7 +65744,7 @@
         <v>12</v>
       </c>
       <c r="M14" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="N14" s="195">
         <v>2</v>
@@ -65739,7 +65765,7 @@
         <v>6</v>
       </c>
       <c r="T14" s="195" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="U14" s="195">
         <v>3</v>
@@ -65750,7 +65776,7 @@
         <v>13</v>
       </c>
       <c r="M15" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="N15" s="195">
         <v>2</v>
@@ -65782,7 +65808,7 @@
         <v>14</v>
       </c>
       <c r="M16" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="N16" s="195">
         <v>2</v>
@@ -65803,7 +65829,7 @@
         <v>3</v>
       </c>
       <c r="T16" s="195" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="U16" s="195">
         <v>1</v>
@@ -65814,7 +65840,7 @@
         <v>15</v>
       </c>
       <c r="M17" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="N17" s="195">
         <v>2</v>
@@ -65835,7 +65861,7 @@
         <v>3</v>
       </c>
       <c r="T17" s="195" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="U17" s="195">
         <v>1</v>
@@ -65846,7 +65872,7 @@
         <v>16</v>
       </c>
       <c r="M18" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="N18" s="195">
         <v>2</v>
@@ -65867,7 +65893,7 @@
         <v>4</v>
       </c>
       <c r="T18" s="195" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="U18" s="195">
         <v>0</v>
@@ -65878,10 +65904,10 @@
         <v>17</v>
       </c>
       <c r="M19" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="N19" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" s="195">
         <v>0</v>
@@ -65890,7 +65916,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19" s="195">
         <v>0</v>
@@ -65899,7 +65925,7 @@
         <v>4</v>
       </c>
       <c r="T19" s="195" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="U19" s="195">
         <v>0</v>
@@ -65910,7 +65936,7 @@
         <v>18</v>
       </c>
       <c r="M20" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="N20" s="195">
         <v>2</v>
@@ -65925,13 +65951,13 @@
         <v>2</v>
       </c>
       <c r="R20" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" s="195">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T20" s="195" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="U20" s="195">
         <v>0</v>
@@ -65942,7 +65968,7 @@
         <v>19</v>
       </c>
       <c r="M21" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="N21" s="195">
         <v>2</v>
@@ -65957,13 +65983,13 @@
         <v>2</v>
       </c>
       <c r="R21" s="195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" s="195">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T21" s="195" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="U21" s="195">
         <v>0</v>
@@ -65974,7 +66000,7 @@
         <v>20</v>
       </c>
       <c r="M22" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="N22" s="195">
         <v>2</v>
@@ -65995,7 +66021,7 @@
         <v>5</v>
       </c>
       <c r="T22" s="195" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="U22" s="195">
         <v>0</v>
@@ -66030,23 +66056,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="218" t="s">
+      <c r="A1" s="196" t="s">
         <v>46</v>
       </c>
       <c r="B1" s="317"/>
       <c r="C1" s="318" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="221"/>
+      <c r="D1" s="199"/>
       <c r="E1" s="319"/>
-      <c r="H1" s="218" t="s">
+      <c r="H1" s="196" t="s">
         <v>47</v>
       </c>
       <c r="I1" s="317"/>
       <c r="J1" s="318" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="221"/>
+      <c r="K1" s="199"/>
       <c r="L1" s="319"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -67023,15 +67049,15 @@
       </c>
       <c r="J30" s="11">
         <f>'Apps &amp; Goals'!U10</f>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K30" s="9">
         <f>'Apps &amp; Goals'!T10</f>
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L30" s="14">
         <f>J30/K30</f>
-        <v>0.26114649681528662</v>
+        <v>0.2634920634920635</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -67135,9 +67161,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="222"/>
-      <c r="G1" s="222"/>
-      <c r="H1" s="222"/>
+      <c r="F1" s="200"/>
+      <c r="G1" s="200"/>
+      <c r="H1" s="200"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -67161,38 +67187,38 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="218" t="s">
+      <c r="E2" s="196" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="219"/>
-      <c r="G2" s="220"/>
-      <c r="H2" s="223" t="s">
+      <c r="F2" s="197"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="201" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="224"/>
-      <c r="J2" s="225"/>
-      <c r="K2" s="218" t="s">
+      <c r="I2" s="202"/>
+      <c r="J2" s="203"/>
+      <c r="K2" s="196" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="219"/>
-      <c r="M2" s="220"/>
-      <c r="N2" s="223" t="s">
+      <c r="L2" s="197"/>
+      <c r="M2" s="198"/>
+      <c r="N2" s="201" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="224"/>
-      <c r="P2" s="225"/>
-      <c r="Q2" s="218" t="s">
+      <c r="O2" s="202"/>
+      <c r="P2" s="203"/>
+      <c r="Q2" s="196" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="219"/>
-      <c r="S2" s="220"/>
-      <c r="T2" s="221" t="s">
+      <c r="R2" s="197"/>
+      <c r="S2" s="198"/>
+      <c r="T2" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="221"/>
-      <c r="V2" s="221"/>
+      <c r="U2" s="199"/>
+      <c r="V2" s="199"/>
       <c r="Z2" s="125">
-        <v>46262</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -67274,7 +67300,7 @@
       </c>
       <c r="E4" s="6">
         <f>'#'!J6</f>
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F4" s="6">
         <f>'#'!K6</f>
@@ -67334,7 +67360,7 @@
       </c>
       <c r="T4" s="2">
         <f t="shared" ref="T4:V4" si="0">SUM(E4,H4,K4,N4,Q4)</f>
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="U4" s="2">
         <f t="shared" ref="U4" si="1">SUM(F4,I4,L4,O4,R4)</f>
@@ -67446,7 +67472,7 @@
       </c>
       <c r="E6" s="6">
         <f>'#'!J8</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" s="6">
         <f>'#'!K8</f>
@@ -67506,7 +67532,7 @@
       </c>
       <c r="T6" s="2">
         <f t="shared" si="2"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="U6" s="2">
         <f t="shared" si="3"/>
@@ -67532,7 +67558,7 @@
       </c>
       <c r="E7" s="6">
         <f>'#'!J9</f>
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F7" s="6">
         <f>'#'!K9</f>
@@ -67592,7 +67618,7 @@
       </c>
       <c r="T7" s="2">
         <f t="shared" si="2"/>
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="U7" s="2">
         <f t="shared" si="3"/>
@@ -67704,7 +67730,7 @@
       </c>
       <c r="E9" s="6">
         <f>'#'!J11</f>
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F9" s="6">
         <f>'#'!K11</f>
@@ -67764,7 +67790,7 @@
       </c>
       <c r="T9" s="2">
         <f t="shared" si="2"/>
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="U9" s="2">
         <f t="shared" si="3"/>
@@ -67790,11 +67816,11 @@
       </c>
       <c r="E10" s="6">
         <f>'#'!J12</f>
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F10" s="6">
         <f>'#'!K12</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G10" s="6">
         <f>'#'!L12</f>
@@ -67850,11 +67876,11 @@
       </c>
       <c r="T10" s="2">
         <f t="shared" si="2"/>
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="U10" s="2">
         <f t="shared" si="3"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V10" s="2">
         <f t="shared" si="4"/>
@@ -67876,7 +67902,7 @@
       </c>
       <c r="E11" s="6">
         <f>'#'!J13</f>
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F11" s="6">
         <f>'#'!K13</f>
@@ -67936,7 +67962,7 @@
       </c>
       <c r="T11" s="2">
         <f t="shared" si="2"/>
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="U11" s="2">
         <f t="shared" si="3"/>
@@ -68474,7 +68500,7 @@
         <v>353</v>
       </c>
       <c r="D18" s="149" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E18" s="6">
         <f>'#'!J20</f>
@@ -68564,7 +68590,7 @@
       </c>
       <c r="E19" s="6">
         <f>'#'!J21</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="6">
         <f>'#'!K21</f>
@@ -68624,7 +68650,7 @@
       </c>
       <c r="T19" s="2">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U19" s="2">
         <f t="shared" si="6"/>
@@ -69080,7 +69106,7 @@
       </c>
       <c r="E25" s="6">
         <f>'#'!J27</f>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F25" s="6">
         <f>'#'!K27</f>
@@ -69140,7 +69166,7 @@
       </c>
       <c r="T25" s="2">
         <f t="shared" si="5"/>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U25" s="2">
         <f t="shared" si="6"/>
@@ -69252,7 +69278,7 @@
       </c>
       <c r="E27" s="6">
         <f>'#'!J29</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F27" s="6">
         <f>'#'!K29</f>
@@ -69260,7 +69286,7 @@
       </c>
       <c r="G27" s="6">
         <f>'#'!L29</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="4">
         <f>'#'!V29</f>
@@ -69312,7 +69338,7 @@
       </c>
       <c r="T27" s="2">
         <f t="shared" si="5"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="U27" s="2">
         <f t="shared" si="6"/>
@@ -69320,7 +69346,7 @@
       </c>
       <c r="V27" s="2">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
@@ -69596,7 +69622,7 @@
       </c>
       <c r="E31" s="6">
         <f>'#'!J33</f>
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F31" s="6">
         <f>'#'!K33</f>
@@ -69656,7 +69682,7 @@
       </c>
       <c r="T31" s="2">
         <f t="shared" si="5"/>
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="U31" s="2">
         <f t="shared" si="6"/>
@@ -69768,7 +69794,7 @@
       </c>
       <c r="E33" s="6">
         <f>'#'!J35</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F33" s="6">
         <f>'#'!K35</f>
@@ -69828,7 +69854,7 @@
       </c>
       <c r="T33" s="2">
         <f t="shared" si="5"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U33" s="2">
         <f t="shared" si="6"/>
@@ -70617,30 +70643,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="216" t="s">
+      <c r="D2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="216"/>
-      <c r="F2" s="217" t="s">
+      <c r="E2" s="206"/>
+      <c r="F2" s="207" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="217"/>
-      <c r="H2" s="216" t="s">
+      <c r="G2" s="207"/>
+      <c r="H2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="216"/>
-      <c r="J2" s="217" t="s">
+      <c r="I2" s="206"/>
+      <c r="J2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="217"/>
-      <c r="L2" s="216" t="s">
+      <c r="K2" s="207"/>
+      <c r="L2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="216"/>
-      <c r="N2" s="221" t="s">
+      <c r="M2" s="206"/>
+      <c r="N2" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="221"/>
+      <c r="O2" s="199"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -72637,30 +72663,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="216" t="s">
+      <c r="D2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="216"/>
-      <c r="F2" s="217" t="s">
+      <c r="E2" s="206"/>
+      <c r="F2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="217"/>
-      <c r="H2" s="216" t="s">
+      <c r="G2" s="207"/>
+      <c r="H2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="216"/>
-      <c r="J2" s="217" t="s">
+      <c r="I2" s="206"/>
+      <c r="J2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="217"/>
-      <c r="L2" s="216" t="s">
+      <c r="K2" s="207"/>
+      <c r="L2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="216"/>
-      <c r="N2" s="221" t="s">
+      <c r="M2" s="206"/>
+      <c r="N2" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="221"/>
+      <c r="O2" s="199"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -74594,30 +74620,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="216" t="s">
+      <c r="D2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="216"/>
-      <c r="F2" s="217" t="s">
+      <c r="E2" s="206"/>
+      <c r="F2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="217"/>
-      <c r="H2" s="216" t="s">
+      <c r="G2" s="207"/>
+      <c r="H2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="216"/>
-      <c r="J2" s="217" t="s">
+      <c r="I2" s="206"/>
+      <c r="J2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="217"/>
-      <c r="L2" s="216" t="s">
+      <c r="K2" s="207"/>
+      <c r="L2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="216"/>
-      <c r="N2" s="221" t="s">
+      <c r="M2" s="206"/>
+      <c r="N2" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="221"/>
+      <c r="O2" s="199"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -76642,30 +76668,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="216" t="s">
+      <c r="D2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="216"/>
-      <c r="F2" s="217" t="s">
+      <c r="E2" s="206"/>
+      <c r="F2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="217"/>
-      <c r="H2" s="216" t="s">
+      <c r="G2" s="207"/>
+      <c r="H2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="216"/>
-      <c r="J2" s="217" t="s">
+      <c r="I2" s="206"/>
+      <c r="J2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="217"/>
-      <c r="L2" s="216" t="s">
+      <c r="K2" s="207"/>
+      <c r="L2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="216"/>
-      <c r="N2" s="221" t="s">
+      <c r="M2" s="206"/>
+      <c r="N2" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="221"/>
+      <c r="O2" s="199"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -78350,30 +78376,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="216" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="216"/>
-      <c r="E2" s="217" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="217"/>
-      <c r="G2" s="216" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="216"/>
-      <c r="I2" s="217" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="217"/>
-      <c r="K2" s="216" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="216"/>
-      <c r="M2" s="221" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="221"/>
+      <c r="N2" s="199"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -80135,30 +80161,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="216" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="216"/>
-      <c r="E2" s="217" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="217"/>
-      <c r="G2" s="216" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="216"/>
-      <c r="I2" s="217" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="217"/>
-      <c r="K2" s="216" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="216"/>
-      <c r="M2" s="221" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="221"/>
+      <c r="N2" s="199"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7849" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{506C9596-0567-4D53-A0C2-9B74059E740B}"/>
+  <xr:revisionPtr revIDLastSave="7854" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE5F58DB-97E3-4469-BCD4-4E004C1E7000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="19" state="hidden" r:id="rId1"/>
@@ -2890,12 +2890,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2903,6 +2897,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2915,6 +2912,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4484,7 +4484,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -4499,7 +4499,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>3</c:v>
@@ -4514,7 +4514,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
@@ -4532,10 +4532,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="25">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>3</c:v>
@@ -6306,7 +6306,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EF694E91-53AF-4BE8-BC2C-7C4893FAEB76}" type="CELLRANGE">
+                    <a:fld id="{33DB2B39-95E5-4254-982A-F94D98921EDF}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6340,7 +6340,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{ED20685B-570B-42BF-9419-4BA737269059}" type="CELLRANGE">
+                    <a:fld id="{B4D194D7-01A5-43F7-80E7-6B101AE006A6}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6374,7 +6374,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1697190C-FEB6-4D72-ABAB-4F14423722A8}" type="CELLRANGE">
+                    <a:fld id="{09CFAE66-297C-4C7A-B574-393E02F2833C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6408,7 +6408,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EA6FB649-2277-4059-A081-B161DC0FE6B7}" type="CELLRANGE">
+                    <a:fld id="{AC312615-4662-4433-99B9-B76C106ECCFB}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6442,7 +6442,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B30A99D4-84EA-4A6A-BA27-EF39ECB6ED16}" type="CELLRANGE">
+                    <a:fld id="{6416F75A-3FFB-43F3-B2EE-87C228C496CF}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6476,7 +6476,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{98C86552-FF2B-4D8A-8B61-578E84526CD4}" type="CELLRANGE">
+                    <a:fld id="{1F424515-B2AC-44A7-9B08-C3C76B6FC3FB}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6510,7 +6510,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{84D1840B-74E6-414D-ABF5-8CB3E1968122}" type="CELLRANGE">
+                    <a:fld id="{8F017D85-ADE8-40B5-959D-122044263FAE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6544,7 +6544,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B28BA611-D3F5-4D85-98AE-21D015434994}" type="CELLRANGE">
+                    <a:fld id="{7837E9CB-9F91-4B48-A0AC-4BF908B06DA5}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6578,7 +6578,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{65A3FD7D-3C13-4246-8584-C9FBDB95D524}" type="CELLRANGE">
+                    <a:fld id="{362AE55E-0218-4504-A276-090D9882CE1C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6612,7 +6612,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A250ABEE-621B-40F5-AC38-3264A8308B8D}" type="CELLRANGE">
+                    <a:fld id="{35712E5C-687C-4B0B-938C-02AAB78753CE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6646,7 +6646,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D911C9FA-CACA-42D8-86FB-4CF33B41F1C9}" type="CELLRANGE">
+                    <a:fld id="{062B2913-4CA8-458D-A092-A7976164EEAD}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6680,7 +6680,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{446CEE18-311D-4220-8C81-BAFCE761BF51}" type="CELLRANGE">
+                    <a:fld id="{9B40638E-9AF7-410D-AF4A-E8F6B85B7A07}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6729,7 +6729,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{4E69E635-9EB5-4C96-8122-FBD29122FB01}" type="CELLRANGE">
+                    <a:fld id="{B1E2B05A-F828-426F-94E1-FF3059B6BE2C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6788,7 +6788,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7D72F8FC-09DD-49FE-A4D0-EC46FEBDD7B8}" type="CELLRANGE">
+                    <a:fld id="{C88E669F-22F9-4A4C-8EFA-7F1971294821}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6822,7 +6822,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2A3919B7-6439-4876-986D-2BC1DEF0CA49}" type="CELLRANGE">
+                    <a:fld id="{9C022F40-DD1C-4BCD-BEBA-025E926F8E86}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6856,7 +6856,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0C607145-ABE3-47B7-A4A0-1A2F5444619D}" type="CELLRANGE">
+                    <a:fld id="{E24260A6-B61F-4F73-825D-117A57037889}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6890,7 +6890,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{45D4EABF-E6A0-44A4-A8BA-75CEB63E06B2}" type="CELLRANGE">
+                    <a:fld id="{7477D038-1376-4A06-8B0A-457712AA9509}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6924,7 +6924,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EE5C6A9B-DAEB-4188-B523-4C1850DEF1F0}" type="CELLRANGE">
+                    <a:fld id="{6C11D983-42B6-45EA-BB82-2B699B9B189C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6958,7 +6958,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5D3C753C-82B4-4889-8ABB-B8AFE8A5AF53}" type="CELLRANGE">
+                    <a:fld id="{5EC24C28-810A-4C40-A673-FCFFD058FD6E}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6992,7 +6992,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CF20D458-E1A8-41A7-B3BA-785ED035D6BF}" type="CELLRANGE">
+                    <a:fld id="{AF14F077-C77A-4F8E-8645-6A4562B95E2E}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7026,7 +7026,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0A76C135-2420-4B13-8564-070D19D08D8B}" type="CELLRANGE">
+                    <a:fld id="{3A32D54F-3BDC-4618-91B7-DFAB5B6B07BC}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7222,7 +7222,7 @@
                   <c:v>123</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>54</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>278</c:v>
@@ -7237,7 +7237,7 @@
                   <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>3</c:v>
@@ -7252,7 +7252,7 @@
                   <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>79</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>90</c:v>
@@ -14222,30 +14222,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="206" t="s">
+      <c r="C1" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="206"/>
-      <c r="E1" s="207" t="s">
+      <c r="D1" s="205"/>
+      <c r="E1" s="206" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="207"/>
-      <c r="G1" s="206" t="s">
+      <c r="F1" s="206"/>
+      <c r="G1" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="206"/>
-      <c r="I1" s="207" t="s">
+      <c r="H1" s="205"/>
+      <c r="I1" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="207"/>
-      <c r="K1" s="206" t="s">
+      <c r="J1" s="206"/>
+      <c r="K1" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="206"/>
-      <c r="M1" s="204" t="s">
+      <c r="L1" s="205"/>
+      <c r="M1" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="205"/>
+      <c r="N1" s="204"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15952,30 +15952,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="205"/>
+      <c r="E2" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="199" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="199"/>
+      <c r="N2" s="202"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17779,30 +17779,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="205"/>
+      <c r="E2" s="206" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="199" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="199"/>
+      <c r="N2" s="202"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19469,30 +19469,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="205"/>
+      <c r="E2" s="206" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="199" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="199"/>
+      <c r="N2" s="202"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21295,30 +21295,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="205"/>
+      <c r="E2" s="206" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="199" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="199"/>
+      <c r="N2" s="202"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23172,31 +23172,31 @@
       </c>
       <c r="D2" s="197"/>
       <c r="E2" s="198"/>
-      <c r="F2" s="201" t="s">
+      <c r="F2" s="199" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="202"/>
-      <c r="H2" s="203"/>
+      <c r="G2" s="200"/>
+      <c r="H2" s="201"/>
       <c r="I2" s="196" t="s">
         <v>108</v>
       </c>
       <c r="J2" s="197"/>
       <c r="K2" s="198"/>
-      <c r="L2" s="201" t="s">
+      <c r="L2" s="199" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="202"/>
-      <c r="N2" s="203"/>
+      <c r="M2" s="200"/>
+      <c r="N2" s="201"/>
       <c r="O2" s="196" t="s">
         <v>39</v>
       </c>
       <c r="P2" s="197"/>
       <c r="Q2" s="198"/>
-      <c r="R2" s="199" t="s">
+      <c r="R2" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="199"/>
-      <c r="T2" s="199"/>
+      <c r="S2" s="202"/>
+      <c r="T2" s="202"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23997,7 +23997,7 @@
       </c>
       <c r="C13" s="6">
         <f>'Premier League'!C13</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="6">
         <f>'Premier League'!D13</f>
@@ -24057,7 +24057,7 @@
       </c>
       <c r="R13" s="2">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S13" s="2">
         <f t="shared" si="2"/>
@@ -24402,7 +24402,7 @@
       </c>
       <c r="C18" s="6">
         <f>'Premier League'!C18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="6">
         <f>'Premier League'!D18</f>
@@ -24462,7 +24462,7 @@
       </c>
       <c r="R18" s="2">
         <f t="shared" ref="R18:R41" si="4">SUM(C18,F18,I18,L18,O18)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="2">
         <f t="shared" ref="S18:S41" si="5">SUM(D18,G18,J18,M18,P18)</f>
@@ -24805,7 +24805,7 @@
       </c>
       <c r="C23" s="6">
         <f>'Premier League'!C23</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="6">
         <f>'Premier League'!D23</f>
@@ -24865,7 +24865,7 @@
       </c>
       <c r="R23" s="2">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S23" s="2">
         <f t="shared" si="5"/>
@@ -25290,7 +25290,7 @@
       </c>
       <c r="C29" s="6">
         <f>'Premier League'!C29</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" s="6">
         <f>'Premier League'!D29</f>
@@ -25350,7 +25350,7 @@
       </c>
       <c r="R29" s="2">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S29" s="2">
         <f t="shared" si="5"/>
@@ -25371,7 +25371,7 @@
       </c>
       <c r="C30" s="6">
         <f>'Premier League'!C30</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" s="6">
         <f>'Premier League'!D30</f>
@@ -25431,7 +25431,7 @@
       </c>
       <c r="R30" s="2">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S30" s="2">
         <f t="shared" si="5"/>
@@ -26384,31 +26384,31 @@
       </c>
       <c r="F1" s="197"/>
       <c r="G1" s="198"/>
-      <c r="H1" s="201" t="s">
+      <c r="H1" s="199" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="202"/>
-      <c r="J1" s="203"/>
+      <c r="I1" s="200"/>
+      <c r="J1" s="201"/>
       <c r="K1" s="196" t="s">
         <v>108</v>
       </c>
       <c r="L1" s="197"/>
       <c r="M1" s="198"/>
-      <c r="N1" s="201" t="s">
+      <c r="N1" s="199" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="202"/>
-      <c r="P1" s="203"/>
+      <c r="O1" s="200"/>
+      <c r="P1" s="201"/>
       <c r="Q1" s="196" t="s">
         <v>39</v>
       </c>
       <c r="R1" s="197"/>
       <c r="S1" s="198"/>
-      <c r="T1" s="199" t="s">
+      <c r="T1" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="199"/>
-      <c r="V1" s="199"/>
+      <c r="U1" s="202"/>
+      <c r="V1" s="202"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -39802,7 +39802,7 @@
       </c>
       <c r="C13" s="58">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="58">
         <f t="shared" si="2"/>
@@ -39817,7 +39817,9 @@
       </c>
       <c r="G13" s="36"/>
       <c r="H13" s="53"/>
-      <c r="I13" s="52"/>
+      <c r="I13" s="52">
+        <v>1</v>
+      </c>
       <c r="J13" s="36"/>
       <c r="K13" s="53"/>
       <c r="L13" s="52"/>
@@ -40474,7 +40476,7 @@
       </c>
       <c r="C18" s="58">
         <f t="shared" ref="C18:C41" si="4">SUM(F18,I18,L18,O18,R18,U18,X18,AA18,AD18,AG18,AJ18,AM18,AP18,AS18,AV18,AY18,BB18,BE18,BH18,BK18,BN18,BQ18,BT18,BW18,BZ18,CC18,CF18,CI18,CL18,CO18,CR18,CU18,CX18,DA18,DD18,DG18,DJ18,DM18)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="58">
         <f t="shared" ref="D18:D41" si="5">SUM(G18,J18,M18,P18,S18,V18,Y18,AB18,AE18,AH18,AK18,AN18,AQ18,AT18,AW18,AZ18,BC18,BF18,BI18,BL18,BO18,BR18,BU18,BX18,CA18,CD18,CG18,CJ18,CM18,CP18,CS18,CV18,CY18,DB18,DE18,DH18,DK18,DN18)</f>
@@ -40487,7 +40489,9 @@
       <c r="F18" s="52"/>
       <c r="G18" s="36"/>
       <c r="H18" s="53"/>
-      <c r="I18" s="52"/>
+      <c r="I18" s="52">
+        <v>1</v>
+      </c>
       <c r="J18" s="36"/>
       <c r="K18" s="53"/>
       <c r="L18" s="52"/>
@@ -41150,7 +41154,7 @@
       </c>
       <c r="C23" s="58">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="58">
         <f t="shared" si="5"/>
@@ -41165,7 +41169,9 @@
       </c>
       <c r="G23" s="36"/>
       <c r="H23" s="53"/>
-      <c r="I23" s="52"/>
+      <c r="I23" s="52">
+        <v>1</v>
+      </c>
       <c r="J23" s="36"/>
       <c r="K23" s="53"/>
       <c r="L23" s="52"/>
@@ -41970,7 +41976,7 @@
       </c>
       <c r="C29" s="58">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" s="58">
         <f t="shared" si="5"/>
@@ -41985,7 +41991,9 @@
       </c>
       <c r="G29" s="36"/>
       <c r="H29" s="53"/>
-      <c r="I29" s="52"/>
+      <c r="I29" s="52">
+        <v>1</v>
+      </c>
       <c r="J29" s="36"/>
       <c r="K29" s="53"/>
       <c r="L29" s="52"/>
@@ -42106,7 +42114,7 @@
       </c>
       <c r="C30" s="58">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" s="58">
         <f t="shared" si="5"/>
@@ -42119,7 +42127,9 @@
       <c r="F30" s="52"/>
       <c r="G30" s="36"/>
       <c r="H30" s="53"/>
-      <c r="I30" s="52"/>
+      <c r="I30" s="52">
+        <v>1</v>
+      </c>
       <c r="J30" s="36"/>
       <c r="K30" s="53"/>
       <c r="L30" s="52"/>
@@ -43733,7 +43743,7 @@
       </c>
       <c r="I42" s="73">
         <f t="shared" ref="I42:BT42" si="8">SUM(I4:I41)</f>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J42" s="73">
         <f t="shared" si="8"/>
@@ -50880,7 +50890,7 @@
       <c r="F15" s="25"/>
       <c r="G15" s="21">
         <f>'Apps &amp; Goals 26-27'!C13</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="21">
         <f>'Apps &amp; Goals 26-27'!D13</f>
@@ -50892,7 +50902,7 @@
       </c>
       <c r="J15" s="25">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K15" s="25">
         <f t="shared" si="1"/>
@@ -51830,7 +51840,7 @@
       <c r="F20" s="25"/>
       <c r="G20" s="21">
         <f>'Apps &amp; Goals 26-27'!C18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="21">
         <f>'Apps &amp; Goals 26-27'!D18</f>
@@ -51842,7 +51852,7 @@
       </c>
       <c r="J20" s="25">
         <f t="shared" ref="J20:J43" si="15">G20+C20</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="25">
         <f t="shared" ref="K20:K43" si="16">H20+D20</f>
@@ -52780,7 +52790,7 @@
       <c r="F25" s="25"/>
       <c r="G25" s="21">
         <f>'Apps &amp; Goals 26-27'!C23</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="21">
         <f>'Apps &amp; Goals 26-27'!D23</f>
@@ -52792,7 +52802,7 @@
       </c>
       <c r="J25" s="25">
         <f t="shared" si="15"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K25" s="25">
         <f t="shared" si="16"/>
@@ -53920,7 +53930,7 @@
       <c r="F31" s="25"/>
       <c r="G31" s="21">
         <f>'Apps &amp; Goals 26-27'!C29</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="21">
         <f>'Apps &amp; Goals 26-27'!D29</f>
@@ -53932,7 +53942,7 @@
       </c>
       <c r="J31" s="25">
         <f t="shared" si="15"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K31" s="25">
         <f t="shared" si="16"/>
@@ -54110,7 +54120,7 @@
       <c r="F32" s="25"/>
       <c r="G32" s="21">
         <f>'Apps &amp; Goals 26-27'!C30</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="21">
         <f>'Apps &amp; Goals 26-27'!D30</f>
@@ -54122,7 +54132,7 @@
       </c>
       <c r="J32" s="25">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" s="25">
         <f t="shared" si="16"/>
@@ -66063,7 +66073,7 @@
       <c r="C1" s="318" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="199"/>
+      <c r="D1" s="202"/>
       <c r="E1" s="319"/>
       <c r="H1" s="196" t="s">
         <v>47</v>
@@ -66072,7 +66082,7 @@
       <c r="J1" s="318" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="199"/>
+      <c r="K1" s="202"/>
       <c r="L1" s="319"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -67161,9 +67171,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -67192,31 +67202,31 @@
       </c>
       <c r="F2" s="197"/>
       <c r="G2" s="198"/>
-      <c r="H2" s="201" t="s">
+      <c r="H2" s="199" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="202"/>
-      <c r="J2" s="203"/>
+      <c r="I2" s="200"/>
+      <c r="J2" s="201"/>
       <c r="K2" s="196" t="s">
         <v>108</v>
       </c>
       <c r="L2" s="197"/>
       <c r="M2" s="198"/>
-      <c r="N2" s="201" t="s">
+      <c r="N2" s="199" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="202"/>
-      <c r="P2" s="203"/>
+      <c r="O2" s="200"/>
+      <c r="P2" s="201"/>
       <c r="Q2" s="196" t="s">
         <v>39</v>
       </c>
       <c r="R2" s="197"/>
       <c r="S2" s="198"/>
-      <c r="T2" s="199" t="s">
+      <c r="T2" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="199"/>
-      <c r="V2" s="199"/>
+      <c r="U2" s="202"/>
+      <c r="V2" s="202"/>
       <c r="Z2" s="125">
         <v>46266</v>
       </c>
@@ -68074,7 +68084,7 @@
       </c>
       <c r="E13" s="6">
         <f>'#'!J15</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F13" s="6">
         <f>'#'!K15</f>
@@ -68134,7 +68144,7 @@
       </c>
       <c r="T13" s="2">
         <f t="shared" si="2"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U13" s="2">
         <f t="shared" si="3"/>
@@ -68504,7 +68514,7 @@
       </c>
       <c r="E18" s="6">
         <f>'#'!J20</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="6">
         <f>'#'!K20</f>
@@ -68564,7 +68574,7 @@
       </c>
       <c r="T18" s="2">
         <f t="shared" ref="T18:T41" si="5">SUM(E18,H18,K18,N18,Q18)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" s="2">
         <f t="shared" ref="U18:U41" si="6">SUM(F18,I18,L18,O18,R18)</f>
@@ -68934,7 +68944,7 @@
       </c>
       <c r="E23" s="6">
         <f>'#'!J25</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F23" s="6">
         <f>'#'!K25</f>
@@ -68994,7 +69004,7 @@
       </c>
       <c r="T23" s="2">
         <f t="shared" si="5"/>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U23" s="2">
         <f t="shared" si="6"/>
@@ -69450,7 +69460,7 @@
       </c>
       <c r="E29" s="6">
         <f>'#'!J31</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F29" s="6">
         <f>'#'!K31</f>
@@ -69510,7 +69520,7 @@
       </c>
       <c r="T29" s="2">
         <f t="shared" si="5"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U29" s="2">
         <f t="shared" si="6"/>
@@ -69536,7 +69546,7 @@
       </c>
       <c r="E30" s="6">
         <f>'#'!J32</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="6">
         <f>'#'!K32</f>
@@ -69596,7 +69606,7 @@
       </c>
       <c r="T30" s="2">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U30" s="2">
         <f t="shared" si="6"/>
@@ -70643,30 +70653,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="205"/>
+      <c r="F2" s="206" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="206"/>
+      <c r="H2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="205"/>
+      <c r="J2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="206"/>
+      <c r="L2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="199" t="s">
+      <c r="M2" s="205"/>
+      <c r="N2" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="199"/>
+      <c r="O2" s="202"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -72663,30 +72673,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="205"/>
+      <c r="F2" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="206"/>
+      <c r="H2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="205"/>
+      <c r="J2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="206"/>
+      <c r="L2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="199" t="s">
+      <c r="M2" s="205"/>
+      <c r="N2" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="199"/>
+      <c r="O2" s="202"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -74620,30 +74630,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="205"/>
+      <c r="F2" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="206"/>
+      <c r="H2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="205"/>
+      <c r="J2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="206"/>
+      <c r="L2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="199" t="s">
+      <c r="M2" s="205"/>
+      <c r="N2" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="199"/>
+      <c r="O2" s="202"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -76668,30 +76678,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="205"/>
+      <c r="F2" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="206"/>
+      <c r="H2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="205"/>
+      <c r="J2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="206"/>
+      <c r="L2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="199" t="s">
+      <c r="M2" s="205"/>
+      <c r="N2" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="199"/>
+      <c r="O2" s="202"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -78376,30 +78386,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="205"/>
+      <c r="E2" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="199" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="199"/>
+      <c r="N2" s="202"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -80161,30 +80171,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="205"/>
+      <c r="E2" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="199" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="199"/>
+      <c r="N2" s="202"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8035" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4642E451-54F0-4D68-B36A-6670900384E5}"/>
+  <xr:revisionPtr revIDLastSave="8036" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E33B02CA-D0DD-4BF8-AA58-CB4A87D8514E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2534,7 +2534,7 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="330">
+  <cellXfs count="329">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2915,6 +2915,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2951,6 +2955,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2960,19 +2973,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
@@ -2987,14 +2988,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3032,6 +3027,15 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3039,6 +3043,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3131,34 +3156,70 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3169,6 +3230,33 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3206,39 +3294,6 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3249,62 +3304,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -3315,97 +3314,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Note" xfId="6" builtinId="10"/>
   </cellStyles>
-  <dxfs count="51">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="42">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -6450,7 +6359,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C35DE94C-B304-42A4-A704-4EC1BDFA40FD}" type="CELLRANGE">
+                    <a:fld id="{09CBB045-FAB9-4ED4-9201-C31742855250}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6484,7 +6393,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{69A8DD85-6943-4DBA-A76E-295566E1D15B}" type="CELLRANGE">
+                    <a:fld id="{1EEBC67C-E781-499C-B02E-F00C854A93D1}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6518,7 +6427,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D4BDAA70-40AB-4454-801C-81A6DA8E9A3C}" type="CELLRANGE">
+                    <a:fld id="{27F408B1-F4D2-4958-A1B9-E388A673856B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6552,7 +6461,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CF4570DB-8AF2-43BC-AF7E-1C0FCFBFCB20}" type="CELLRANGE">
+                    <a:fld id="{D33E060B-3EAD-44D6-92B4-552E88412DE9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6586,7 +6495,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0554A3FB-B4BD-4D9E-88E5-E8D3C63BC550}" type="CELLRANGE">
+                    <a:fld id="{626D3461-E7A5-4D8E-903C-3D9FCA2FB2E8}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6620,7 +6529,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{64DDBFC1-F8AA-4CCA-9201-90CEAA235B69}" type="CELLRANGE">
+                    <a:fld id="{5C59FEB0-5F63-4FA9-A7C4-C64361C3A9FC}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6654,7 +6563,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A57E0308-7FAC-4864-8010-171F6B822F23}" type="CELLRANGE">
+                    <a:fld id="{A8738EC7-12A9-472E-AB4B-BAD51DC703AA}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6688,7 +6597,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{320AB0EE-7D7B-4942-8EB6-6D21976ADBDA}" type="CELLRANGE">
+                    <a:fld id="{B11822CB-F914-4483-9382-C2EBDCFD3368}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6722,7 +6631,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{07DBAD1A-0CE3-41D7-B90F-D3A2DD681751}" type="CELLRANGE">
+                    <a:fld id="{B58C4014-595F-43AC-9BDE-74F9F9A52250}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6756,7 +6665,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B67183B2-E90B-4ABC-B7DA-944C49C38122}" type="CELLRANGE">
+                    <a:fld id="{47A960EA-0D3A-4FB9-AECD-5CB06567568E}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6790,7 +6699,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0A84B9B1-3911-41F0-ACB7-ADA47206674E}" type="CELLRANGE">
+                    <a:fld id="{025A7587-7628-4C53-9C2F-475D9FCDB240}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6824,7 +6733,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{343291AE-C626-4AD2-9CC3-5826FDA90E16}" type="CELLRANGE">
+                    <a:fld id="{DADE368F-19D0-46E5-A0E8-1D92BD5B0A2E}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6873,7 +6782,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{334B2C53-681B-4698-B915-4A14BC2C2072}" type="CELLRANGE">
+                    <a:fld id="{245D981B-9422-45D9-AE73-1E4A8C24091F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6932,7 +6841,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8B68BA7C-947E-43CC-87DB-8693C1EB737A}" type="CELLRANGE">
+                    <a:fld id="{8770C142-21C6-44CD-AFFF-453E97631057}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6966,7 +6875,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0F3A3E07-10A3-4F7B-8873-3DF12E3F1964}" type="CELLRANGE">
+                    <a:fld id="{331FE634-7135-4AA2-9535-1912DEE7E5DE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7000,7 +6909,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{505DD4B6-4853-4F7D-A4EF-8B572D91518F}" type="CELLRANGE">
+                    <a:fld id="{408EBD0C-0007-47B3-B2C3-A6A16FA3747A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7034,7 +6943,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A283A7EB-5597-48F6-B031-1534D5DBDB92}" type="CELLRANGE">
+                    <a:fld id="{36F0D138-D4DD-4253-A403-6A896EA433F1}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7068,7 +6977,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{973E5D38-822F-42D7-AC8C-6D6E1B71B198}" type="CELLRANGE">
+                    <a:fld id="{9F5524F3-78D2-4423-BA85-53AAE9A49738}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14219,30 +14128,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="206" t="s">
+      <c r="C1" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="206"/>
-      <c r="E1" s="207" t="s">
+      <c r="D1" s="210"/>
+      <c r="E1" s="211" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="207"/>
-      <c r="G1" s="206" t="s">
+      <c r="F1" s="211"/>
+      <c r="G1" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="206"/>
-      <c r="I1" s="207" t="s">
+      <c r="H1" s="210"/>
+      <c r="I1" s="211" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="207"/>
-      <c r="K1" s="206" t="s">
+      <c r="J1" s="211"/>
+      <c r="K1" s="210" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="206"/>
-      <c r="M1" s="204" t="s">
+      <c r="L1" s="210"/>
+      <c r="M1" s="208" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="205"/>
+      <c r="N1" s="209"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15882,12 +15791,12 @@
     <mergeCell ref="K1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="M3:M38">
-    <cfRule type="cellIs" dxfId="49" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="3" operator="greaterThan">
       <formula>396</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N38">
-    <cfRule type="cellIs" dxfId="48" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="1" operator="greaterThan">
       <formula>92</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15949,30 +15858,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="210"/>
+      <c r="E2" s="211" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="211"/>
+      <c r="G2" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="210"/>
+      <c r="I2" s="211" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="211"/>
+      <c r="K2" s="210" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="199" t="s">
+      <c r="L2" s="210"/>
+      <c r="M2" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="199"/>
+      <c r="N2" s="203"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17734,7 +17643,7 @@
     <mergeCell ref="K2:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="M4:N41">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="greaterThan">
       <formula>396</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17776,30 +17685,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="210"/>
+      <c r="E2" s="211" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="211"/>
+      <c r="G2" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="210"/>
+      <c r="I2" s="211" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="211"/>
+      <c r="K2" s="210" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="199" t="s">
+      <c r="L2" s="210"/>
+      <c r="M2" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="199"/>
+      <c r="N2" s="203"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19424,7 +19333,7 @@
     <mergeCell ref="K2:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="M4:N38">
-    <cfRule type="cellIs" dxfId="36" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="3" operator="greaterThan">
       <formula>396</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19466,30 +19375,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="210"/>
+      <c r="E2" s="211" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="211"/>
+      <c r="G2" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="210"/>
+      <c r="I2" s="211" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="211"/>
+      <c r="K2" s="210" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="199" t="s">
+      <c r="L2" s="210"/>
+      <c r="M2" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="199"/>
+      <c r="N2" s="203"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21250,7 +21159,7 @@
     <mergeCell ref="K2:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="M4:N41">
-    <cfRule type="cellIs" dxfId="35" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="2" operator="greaterThan">
       <formula>396</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21292,30 +21201,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="210"/>
+      <c r="E2" s="211" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="211"/>
+      <c r="G2" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="210"/>
+      <c r="I2" s="211" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="211"/>
+      <c r="K2" s="210" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="199" t="s">
+      <c r="L2" s="210"/>
+      <c r="M2" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="199"/>
+      <c r="N2" s="203"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23116,7 +23025,7 @@
     <mergeCell ref="K2:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="M4:N42">
-    <cfRule type="cellIs" dxfId="34" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="greaterThan">
       <formula>396</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23164,36 +23073,36 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="196" t="s">
+      <c r="C2" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="197"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="201" t="s">
+      <c r="D2" s="201"/>
+      <c r="E2" s="202"/>
+      <c r="F2" s="205" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="202"/>
-      <c r="H2" s="203"/>
-      <c r="I2" s="196" t="s">
+      <c r="G2" s="206"/>
+      <c r="H2" s="207"/>
+      <c r="I2" s="200" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="197"/>
-      <c r="K2" s="198"/>
-      <c r="L2" s="201" t="s">
+      <c r="J2" s="201"/>
+      <c r="K2" s="202"/>
+      <c r="L2" s="205" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="202"/>
-      <c r="N2" s="203"/>
-      <c r="O2" s="196" t="s">
+      <c r="M2" s="206"/>
+      <c r="N2" s="207"/>
+      <c r="O2" s="200" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="197"/>
-      <c r="Q2" s="198"/>
-      <c r="R2" s="199" t="s">
+      <c r="P2" s="201"/>
+      <c r="Q2" s="202"/>
+      <c r="R2" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="199"/>
-      <c r="T2" s="199"/>
+      <c r="S2" s="203"/>
+      <c r="T2" s="203"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -26094,7 +26003,7 @@
     <mergeCell ref="I2:K2"/>
   </mergeCells>
   <conditionalFormatting sqref="R4:T38">
-    <cfRule type="cellIs" dxfId="33" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="greaterThan">
       <formula>396</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26133,36 +26042,36 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="196" t="s">
+      <c r="E1" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="197"/>
-      <c r="G1" s="198"/>
-      <c r="H1" s="201" t="s">
+      <c r="F1" s="201"/>
+      <c r="G1" s="202"/>
+      <c r="H1" s="205" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="202"/>
-      <c r="J1" s="203"/>
-      <c r="K1" s="196" t="s">
+      <c r="I1" s="206"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="200" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="197"/>
-      <c r="M1" s="198"/>
-      <c r="N1" s="201" t="s">
+      <c r="L1" s="201"/>
+      <c r="M1" s="202"/>
+      <c r="N1" s="205" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="202"/>
-      <c r="P1" s="203"/>
-      <c r="Q1" s="196" t="s">
+      <c r="O1" s="206"/>
+      <c r="P1" s="207"/>
+      <c r="Q1" s="200" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="197"/>
-      <c r="S1" s="198"/>
-      <c r="T1" s="199" t="s">
+      <c r="R1" s="201"/>
+      <c r="S1" s="202"/>
+      <c r="T1" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="199"/>
-      <c r="V1" s="199"/>
+      <c r="U1" s="203"/>
+      <c r="V1" s="203"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37621,17 +37530,17 @@
     <mergeCell ref="Q1:S1"/>
   </mergeCells>
   <conditionalFormatting sqref="T3:T20 T22:T326">
-    <cfRule type="cellIs" dxfId="31" priority="82" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="82" operator="greaterThan">
       <formula>396</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3:V20 U22:V22 U24:V326">
-    <cfRule type="cellIs" dxfId="30" priority="80" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="80" operator="greaterThan">
       <formula>92</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W48:X48">
-    <cfRule type="cellIs" dxfId="28" priority="18" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="18" operator="greaterThan">
       <formula>396</formula>
     </cfRule>
   </conditionalFormatting>
@@ -37692,399 +37601,399 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="211">
-        <v>1</v>
-      </c>
-      <c r="G1" s="212"/>
-      <c r="H1" s="213"/>
-      <c r="I1" s="211">
+      <c r="F1" s="212">
+        <v>1</v>
+      </c>
+      <c r="G1" s="213"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="212">
         <v>2</v>
       </c>
-      <c r="J1" s="212"/>
-      <c r="K1" s="213"/>
-      <c r="L1" s="211">
-        <v>3</v>
-      </c>
-      <c r="M1" s="212"/>
-      <c r="N1" s="213"/>
-      <c r="O1" s="211">
+      <c r="J1" s="213"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="212">
+        <v>3</v>
+      </c>
+      <c r="M1" s="213"/>
+      <c r="N1" s="214"/>
+      <c r="O1" s="212">
         <v>4</v>
       </c>
-      <c r="P1" s="212"/>
-      <c r="Q1" s="213"/>
-      <c r="R1" s="211">
+      <c r="P1" s="213"/>
+      <c r="Q1" s="214"/>
+      <c r="R1" s="212">
         <v>5</v>
       </c>
-      <c r="S1" s="212"/>
-      <c r="T1" s="213"/>
-      <c r="U1" s="211">
+      <c r="S1" s="213"/>
+      <c r="T1" s="214"/>
+      <c r="U1" s="212">
         <v>6</v>
       </c>
-      <c r="V1" s="212"/>
-      <c r="W1" s="213"/>
-      <c r="X1" s="211">
+      <c r="V1" s="213"/>
+      <c r="W1" s="214"/>
+      <c r="X1" s="212">
         <v>7</v>
       </c>
-      <c r="Y1" s="212"/>
-      <c r="Z1" s="213"/>
-      <c r="AA1" s="211">
+      <c r="Y1" s="213"/>
+      <c r="Z1" s="214"/>
+      <c r="AA1" s="212">
         <v>8</v>
       </c>
-      <c r="AB1" s="212"/>
-      <c r="AC1" s="213"/>
-      <c r="AD1" s="211">
+      <c r="AB1" s="213"/>
+      <c r="AC1" s="214"/>
+      <c r="AD1" s="212">
         <v>9</v>
       </c>
-      <c r="AE1" s="212"/>
-      <c r="AF1" s="213"/>
-      <c r="AG1" s="211">
+      <c r="AE1" s="213"/>
+      <c r="AF1" s="214"/>
+      <c r="AG1" s="212">
         <v>10</v>
       </c>
-      <c r="AH1" s="212"/>
-      <c r="AI1" s="213"/>
-      <c r="AJ1" s="211">
+      <c r="AH1" s="213"/>
+      <c r="AI1" s="214"/>
+      <c r="AJ1" s="212">
         <v>11</v>
       </c>
-      <c r="AK1" s="212"/>
-      <c r="AL1" s="213"/>
-      <c r="AM1" s="211">
+      <c r="AK1" s="213"/>
+      <c r="AL1" s="214"/>
+      <c r="AM1" s="212">
         <v>12</v>
       </c>
-      <c r="AN1" s="212"/>
-      <c r="AO1" s="213"/>
-      <c r="AP1" s="211">
+      <c r="AN1" s="213"/>
+      <c r="AO1" s="214"/>
+      <c r="AP1" s="212">
         <v>13</v>
       </c>
-      <c r="AQ1" s="212"/>
-      <c r="AR1" s="213"/>
-      <c r="AS1" s="211">
+      <c r="AQ1" s="213"/>
+      <c r="AR1" s="214"/>
+      <c r="AS1" s="212">
         <v>14</v>
       </c>
-      <c r="AT1" s="212"/>
-      <c r="AU1" s="213"/>
-      <c r="AV1" s="211">
+      <c r="AT1" s="213"/>
+      <c r="AU1" s="214"/>
+      <c r="AV1" s="212">
         <v>15</v>
       </c>
-      <c r="AW1" s="212"/>
-      <c r="AX1" s="213"/>
-      <c r="AY1" s="211">
+      <c r="AW1" s="213"/>
+      <c r="AX1" s="214"/>
+      <c r="AY1" s="212">
         <v>16</v>
       </c>
-      <c r="AZ1" s="212"/>
-      <c r="BA1" s="213"/>
-      <c r="BB1" s="211">
+      <c r="AZ1" s="213"/>
+      <c r="BA1" s="214"/>
+      <c r="BB1" s="212">
         <v>17</v>
       </c>
-      <c r="BC1" s="212"/>
-      <c r="BD1" s="213"/>
-      <c r="BE1" s="211">
+      <c r="BC1" s="213"/>
+      <c r="BD1" s="214"/>
+      <c r="BE1" s="212">
         <v>18</v>
       </c>
-      <c r="BF1" s="212"/>
-      <c r="BG1" s="213"/>
-      <c r="BH1" s="211">
+      <c r="BF1" s="213"/>
+      <c r="BG1" s="214"/>
+      <c r="BH1" s="212">
         <v>19</v>
       </c>
-      <c r="BI1" s="212"/>
-      <c r="BJ1" s="213"/>
-      <c r="BK1" s="211">
+      <c r="BI1" s="213"/>
+      <c r="BJ1" s="214"/>
+      <c r="BK1" s="212">
         <v>20</v>
       </c>
-      <c r="BL1" s="212"/>
-      <c r="BM1" s="213"/>
-      <c r="BN1" s="211">
+      <c r="BL1" s="213"/>
+      <c r="BM1" s="214"/>
+      <c r="BN1" s="212">
         <v>21</v>
       </c>
-      <c r="BO1" s="212"/>
-      <c r="BP1" s="213"/>
-      <c r="BQ1" s="211">
+      <c r="BO1" s="213"/>
+      <c r="BP1" s="214"/>
+      <c r="BQ1" s="212">
         <v>22</v>
       </c>
-      <c r="BR1" s="212"/>
-      <c r="BS1" s="213"/>
-      <c r="BT1" s="211">
+      <c r="BR1" s="213"/>
+      <c r="BS1" s="214"/>
+      <c r="BT1" s="212">
         <v>23</v>
       </c>
-      <c r="BU1" s="212"/>
-      <c r="BV1" s="213"/>
-      <c r="BW1" s="211">
+      <c r="BU1" s="213"/>
+      <c r="BV1" s="214"/>
+      <c r="BW1" s="212">
         <v>24</v>
       </c>
-      <c r="BX1" s="212"/>
-      <c r="BY1" s="213"/>
-      <c r="BZ1" s="211">
+      <c r="BX1" s="213"/>
+      <c r="BY1" s="214"/>
+      <c r="BZ1" s="212">
         <v>25</v>
       </c>
-      <c r="CA1" s="212"/>
-      <c r="CB1" s="213"/>
-      <c r="CC1" s="211">
+      <c r="CA1" s="213"/>
+      <c r="CB1" s="214"/>
+      <c r="CC1" s="212">
         <v>26</v>
       </c>
-      <c r="CD1" s="212"/>
-      <c r="CE1" s="213"/>
-      <c r="CF1" s="211">
+      <c r="CD1" s="213"/>
+      <c r="CE1" s="214"/>
+      <c r="CF1" s="212">
         <v>27</v>
       </c>
-      <c r="CG1" s="212"/>
-      <c r="CH1" s="213"/>
-      <c r="CI1" s="211">
+      <c r="CG1" s="213"/>
+      <c r="CH1" s="214"/>
+      <c r="CI1" s="212">
         <v>28</v>
       </c>
-      <c r="CJ1" s="212"/>
-      <c r="CK1" s="213"/>
-      <c r="CL1" s="211">
+      <c r="CJ1" s="213"/>
+      <c r="CK1" s="214"/>
+      <c r="CL1" s="212">
         <v>29</v>
       </c>
-      <c r="CM1" s="212"/>
-      <c r="CN1" s="213"/>
-      <c r="CO1" s="211">
+      <c r="CM1" s="213"/>
+      <c r="CN1" s="214"/>
+      <c r="CO1" s="212">
         <v>30</v>
       </c>
-      <c r="CP1" s="212"/>
-      <c r="CQ1" s="213"/>
-      <c r="CR1" s="211">
+      <c r="CP1" s="213"/>
+      <c r="CQ1" s="214"/>
+      <c r="CR1" s="212">
         <v>31</v>
       </c>
-      <c r="CS1" s="212"/>
-      <c r="CT1" s="213"/>
-      <c r="CU1" s="211">
+      <c r="CS1" s="213"/>
+      <c r="CT1" s="214"/>
+      <c r="CU1" s="212">
         <v>32</v>
       </c>
-      <c r="CV1" s="212"/>
-      <c r="CW1" s="213"/>
-      <c r="CX1" s="211">
+      <c r="CV1" s="213"/>
+      <c r="CW1" s="214"/>
+      <c r="CX1" s="212">
         <v>33</v>
       </c>
-      <c r="CY1" s="212"/>
-      <c r="CZ1" s="213"/>
-      <c r="DA1" s="211">
+      <c r="CY1" s="213"/>
+      <c r="CZ1" s="214"/>
+      <c r="DA1" s="212">
         <v>34</v>
       </c>
-      <c r="DB1" s="212"/>
-      <c r="DC1" s="213"/>
-      <c r="DD1" s="211">
+      <c r="DB1" s="213"/>
+      <c r="DC1" s="214"/>
+      <c r="DD1" s="212">
         <v>35</v>
       </c>
-      <c r="DE1" s="212"/>
-      <c r="DF1" s="213"/>
-      <c r="DG1" s="211">
+      <c r="DE1" s="213"/>
+      <c r="DF1" s="214"/>
+      <c r="DG1" s="212">
         <v>36</v>
       </c>
-      <c r="DH1" s="212"/>
-      <c r="DI1" s="213"/>
-      <c r="DJ1" s="211">
+      <c r="DH1" s="213"/>
+      <c r="DI1" s="214"/>
+      <c r="DJ1" s="212">
         <v>37</v>
       </c>
-      <c r="DK1" s="212"/>
-      <c r="DL1" s="213"/>
-      <c r="DM1" s="211">
+      <c r="DK1" s="213"/>
+      <c r="DL1" s="214"/>
+      <c r="DM1" s="212">
         <v>38</v>
       </c>
-      <c r="DN1" s="212"/>
-      <c r="DO1" s="213"/>
+      <c r="DN1" s="213"/>
+      <c r="DO1" s="214"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="214" t="s">
+      <c r="C2" s="218" t="s">
         <v>396</v>
       </c>
-      <c r="D2" s="214" t="s">
+      <c r="D2" s="218" t="s">
         <v>397</v>
       </c>
-      <c r="E2" s="214" t="s">
+      <c r="E2" s="218" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="208" t="s">
+      <c r="F2" s="215" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="209"/>
-      <c r="H2" s="210"/>
-      <c r="I2" s="217" t="s">
+      <c r="G2" s="216"/>
+      <c r="H2" s="217"/>
+      <c r="I2" s="220" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="218"/>
-      <c r="K2" s="219"/>
-      <c r="L2" s="208" t="s">
+      <c r="J2" s="221"/>
+      <c r="K2" s="222"/>
+      <c r="L2" s="215" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="209"/>
-      <c r="N2" s="210"/>
-      <c r="O2" s="208" t="s">
+      <c r="M2" s="216"/>
+      <c r="N2" s="217"/>
+      <c r="O2" s="215" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="209"/>
-      <c r="Q2" s="210"/>
-      <c r="R2" s="208" t="s">
+      <c r="P2" s="216"/>
+      <c r="Q2" s="217"/>
+      <c r="R2" s="215" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="209"/>
-      <c r="T2" s="210"/>
-      <c r="U2" s="208" t="s">
+      <c r="S2" s="216"/>
+      <c r="T2" s="217"/>
+      <c r="U2" s="215" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="209"/>
-      <c r="W2" s="210"/>
-      <c r="X2" s="208" t="s">
+      <c r="V2" s="216"/>
+      <c r="W2" s="217"/>
+      <c r="X2" s="215" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="209"/>
-      <c r="Z2" s="210"/>
-      <c r="AA2" s="208" t="s">
+      <c r="Y2" s="216"/>
+      <c r="Z2" s="217"/>
+      <c r="AA2" s="215" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="209"/>
-      <c r="AC2" s="210"/>
-      <c r="AD2" s="208" t="s">
+      <c r="AB2" s="216"/>
+      <c r="AC2" s="217"/>
+      <c r="AD2" s="215" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="209"/>
-      <c r="AF2" s="210"/>
-      <c r="AG2" s="208" t="s">
+      <c r="AE2" s="216"/>
+      <c r="AF2" s="217"/>
+      <c r="AG2" s="215" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="209"/>
-      <c r="AI2" s="210"/>
-      <c r="AJ2" s="208" t="s">
+      <c r="AH2" s="216"/>
+      <c r="AI2" s="217"/>
+      <c r="AJ2" s="215" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="209"/>
-      <c r="AL2" s="210"/>
-      <c r="AM2" s="208" t="s">
+      <c r="AK2" s="216"/>
+      <c r="AL2" s="217"/>
+      <c r="AM2" s="215" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="209"/>
-      <c r="AO2" s="210"/>
-      <c r="AP2" s="208" t="s">
+      <c r="AN2" s="216"/>
+      <c r="AO2" s="217"/>
+      <c r="AP2" s="215" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="209"/>
-      <c r="AR2" s="210"/>
-      <c r="AS2" s="208" t="s">
+      <c r="AQ2" s="216"/>
+      <c r="AR2" s="217"/>
+      <c r="AS2" s="215" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="209"/>
-      <c r="AU2" s="210"/>
-      <c r="AV2" s="208" t="s">
+      <c r="AT2" s="216"/>
+      <c r="AU2" s="217"/>
+      <c r="AV2" s="215" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="209"/>
-      <c r="AX2" s="210"/>
-      <c r="AY2" s="208" t="s">
+      <c r="AW2" s="216"/>
+      <c r="AX2" s="217"/>
+      <c r="AY2" s="215" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="209"/>
-      <c r="BA2" s="210"/>
-      <c r="BB2" s="208" t="s">
+      <c r="AZ2" s="216"/>
+      <c r="BA2" s="217"/>
+      <c r="BB2" s="215" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="209"/>
-      <c r="BD2" s="210"/>
-      <c r="BE2" s="208" t="s">
+      <c r="BC2" s="216"/>
+      <c r="BD2" s="217"/>
+      <c r="BE2" s="215" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="209"/>
-      <c r="BG2" s="210"/>
-      <c r="BH2" s="208" t="s">
+      <c r="BF2" s="216"/>
+      <c r="BG2" s="217"/>
+      <c r="BH2" s="215" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="209"/>
-      <c r="BJ2" s="210"/>
-      <c r="BK2" s="208" t="s">
+      <c r="BI2" s="216"/>
+      <c r="BJ2" s="217"/>
+      <c r="BK2" s="215" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="209"/>
-      <c r="BM2" s="210"/>
-      <c r="BN2" s="208" t="s">
+      <c r="BL2" s="216"/>
+      <c r="BM2" s="217"/>
+      <c r="BN2" s="215" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="209"/>
-      <c r="BP2" s="210"/>
-      <c r="BQ2" s="208" t="s">
+      <c r="BO2" s="216"/>
+      <c r="BP2" s="217"/>
+      <c r="BQ2" s="215" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="209"/>
-      <c r="BS2" s="210"/>
-      <c r="BT2" s="208" t="s">
+      <c r="BR2" s="216"/>
+      <c r="BS2" s="217"/>
+      <c r="BT2" s="215" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="209"/>
-      <c r="BV2" s="210"/>
-      <c r="BW2" s="208" t="s">
+      <c r="BU2" s="216"/>
+      <c r="BV2" s="217"/>
+      <c r="BW2" s="215" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="209"/>
-      <c r="BY2" s="210"/>
-      <c r="BZ2" s="208" t="s">
+      <c r="BX2" s="216"/>
+      <c r="BY2" s="217"/>
+      <c r="BZ2" s="215" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="209"/>
-      <c r="CB2" s="210"/>
-      <c r="CC2" s="208" t="s">
+      <c r="CA2" s="216"/>
+      <c r="CB2" s="217"/>
+      <c r="CC2" s="215" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="209"/>
-      <c r="CE2" s="210"/>
-      <c r="CF2" s="208" t="s">
+      <c r="CD2" s="216"/>
+      <c r="CE2" s="217"/>
+      <c r="CF2" s="215" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="209"/>
-      <c r="CH2" s="210"/>
-      <c r="CI2" s="208" t="s">
+      <c r="CG2" s="216"/>
+      <c r="CH2" s="217"/>
+      <c r="CI2" s="215" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="209"/>
-      <c r="CK2" s="210"/>
-      <c r="CL2" s="208" t="s">
+      <c r="CJ2" s="216"/>
+      <c r="CK2" s="217"/>
+      <c r="CL2" s="215" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="209"/>
-      <c r="CN2" s="210"/>
-      <c r="CO2" s="208" t="s">
+      <c r="CM2" s="216"/>
+      <c r="CN2" s="217"/>
+      <c r="CO2" s="215" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="209"/>
-      <c r="CQ2" s="210"/>
-      <c r="CR2" s="208" t="s">
+      <c r="CP2" s="216"/>
+      <c r="CQ2" s="217"/>
+      <c r="CR2" s="215" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="209"/>
-      <c r="CT2" s="210"/>
-      <c r="CU2" s="208" t="s">
+      <c r="CS2" s="216"/>
+      <c r="CT2" s="217"/>
+      <c r="CU2" s="215" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="209"/>
-      <c r="CW2" s="210"/>
-      <c r="CX2" s="208" t="s">
+      <c r="CV2" s="216"/>
+      <c r="CW2" s="217"/>
+      <c r="CX2" s="215" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="209"/>
-      <c r="CZ2" s="210"/>
-      <c r="DA2" s="208" t="s">
+      <c r="CY2" s="216"/>
+      <c r="CZ2" s="217"/>
+      <c r="DA2" s="215" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="209"/>
-      <c r="DC2" s="210"/>
-      <c r="DD2" s="208" t="s">
+      <c r="DB2" s="216"/>
+      <c r="DC2" s="217"/>
+      <c r="DD2" s="215" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="209"/>
-      <c r="DF2" s="210"/>
-      <c r="DG2" s="208" t="s">
+      <c r="DE2" s="216"/>
+      <c r="DF2" s="217"/>
+      <c r="DG2" s="215" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="209"/>
-      <c r="DI2" s="210"/>
-      <c r="DJ2" s="208" t="s">
+      <c r="DH2" s="216"/>
+      <c r="DI2" s="217"/>
+      <c r="DJ2" s="215" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="209"/>
-      <c r="DL2" s="210"/>
-      <c r="DM2" s="208" t="s">
+      <c r="DK2" s="216"/>
+      <c r="DL2" s="217"/>
+      <c r="DM2" s="215" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="209"/>
-      <c r="DO2" s="210"/>
+      <c r="DN2" s="216"/>
+      <c r="DO2" s="217"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38093,9 +38002,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="215"/>
-      <c r="D3" s="215"/>
-      <c r="E3" s="216"/>
+      <c r="C3" s="223"/>
+      <c r="D3" s="223"/>
+      <c r="E3" s="219"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
       </c>
@@ -43342,399 +43251,336 @@
         <v>0</v>
       </c>
       <c r="AL39" s="73">
-        <f>SUM(AL4:AL38)</f>
+        <f t="shared" ref="AL39:BQ39" si="9">SUM(AL4:AL38)</f>
         <v>0</v>
       </c>
       <c r="AM39" s="73">
-        <f>SUM(AM4:AM38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AN39" s="73">
-        <f>SUM(AN4:AN38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AO39" s="73">
-        <f>SUM(AO4:AO38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AP39" s="73">
-        <f>SUM(AP4:AP38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AQ39" s="73">
-        <f>SUM(AQ4:AQ38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AR39" s="73">
-        <f>SUM(AR4:AR38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AS39" s="73">
-        <f>SUM(AS4:AS38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AT39" s="73">
-        <f>SUM(AT4:AT38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AU39" s="73">
-        <f>SUM(AU4:AU38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AV39" s="73">
-        <f>SUM(AV4:AV38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AW39" s="73">
-        <f>SUM(AW4:AW38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AX39" s="73">
-        <f>SUM(AX4:AX38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AY39" s="73">
-        <f>SUM(AY4:AY38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AZ39" s="73">
-        <f>SUM(AZ4:AZ38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BA39" s="73">
-        <f>SUM(BA4:BA38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BB39" s="73">
-        <f>SUM(BB4:BB38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BC39" s="73">
-        <f>SUM(BC4:BC38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BD39" s="73">
-        <f>SUM(BD4:BD38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BE39" s="73">
-        <f>SUM(BE4:BE38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BF39" s="73">
-        <f>SUM(BF4:BF38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BG39" s="73">
-        <f>SUM(BG4:BG38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BH39" s="73">
-        <f>SUM(BH4:BH38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI39" s="73">
-        <f>SUM(BI4:BI38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BJ39" s="73">
-        <f>SUM(BJ4:BJ38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BK39" s="73">
-        <f>SUM(BK4:BK38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BL39" s="73">
-        <f>SUM(BL4:BL38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BM39" s="73">
-        <f>SUM(BM4:BM38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BN39" s="73">
-        <f>SUM(BN4:BN38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BO39" s="73">
-        <f>SUM(BO4:BO38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BP39" s="73">
-        <f>SUM(BP4:BP38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BQ39" s="73">
-        <f>SUM(BQ4:BQ38)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BR39" s="73">
-        <f>SUM(BR4:BR38)</f>
+        <f t="shared" ref="BR39:CW39" si="10">SUM(BR4:BR38)</f>
         <v>0</v>
       </c>
       <c r="BS39" s="73">
-        <f>SUM(BS4:BS38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BT39" s="73">
-        <f>SUM(BT4:BT38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BU39" s="73">
-        <f>SUM(BU4:BU38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BV39" s="73">
-        <f>SUM(BV4:BV38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BW39" s="73">
-        <f>SUM(BW4:BW38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BX39" s="73">
-        <f>SUM(BX4:BX38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BY39" s="73">
-        <f>SUM(BY4:BY38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BZ39" s="73">
-        <f>SUM(BZ4:BZ38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CA39" s="73">
-        <f>SUM(CA4:CA38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CB39" s="73">
-        <f>SUM(CB4:CB38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CC39" s="73">
-        <f>SUM(CC4:CC38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CD39" s="73">
-        <f>SUM(CD4:CD38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CE39" s="73">
-        <f>SUM(CE4:CE38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CF39" s="73">
-        <f>SUM(CF4:CF38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CG39" s="73">
-        <f>SUM(CG4:CG38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CH39" s="73">
-        <f>SUM(CH4:CH38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CI39" s="73">
-        <f>SUM(CI4:CI38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CJ39" s="73">
-        <f>SUM(CJ4:CJ38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CK39" s="73">
-        <f>SUM(CK4:CK38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CL39" s="73">
-        <f>SUM(CL4:CL38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CM39" s="73">
-        <f>SUM(CM4:CM38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CN39" s="73">
-        <f>SUM(CN4:CN38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CO39" s="73">
-        <f>SUM(CO4:CO38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CP39" s="73">
-        <f>SUM(CP4:CP38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CQ39" s="73">
-        <f>SUM(CQ4:CQ38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CR39" s="73">
-        <f>SUM(CR4:CR38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CS39" s="73">
-        <f>SUM(CS4:CS38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CT39" s="73">
-        <f>SUM(CT4:CT38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CU39" s="73">
-        <f>SUM(CU4:CU38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CV39" s="73">
-        <f>SUM(CV4:CV38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CW39" s="73">
-        <f>SUM(CW4:CW38)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CX39" s="73">
-        <f>SUM(CX4:CX38)</f>
+        <f t="shared" ref="CX39:EC39" si="11">SUM(CX4:CX38)</f>
         <v>0</v>
       </c>
       <c r="CY39" s="73">
-        <f>SUM(CY4:CY38)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="CZ39" s="73">
-        <f>SUM(CZ4:CZ38)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DA39" s="73">
-        <f>SUM(DA4:DA38)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DB39" s="73">
-        <f>SUM(DB4:DB38)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DC39" s="73">
-        <f>SUM(DC4:DC38)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DD39" s="73">
-        <f>SUM(DD4:DD38)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DE39" s="73">
-        <f>SUM(DE4:DE38)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DF39" s="73">
-        <f>SUM(DF4:DF38)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DG39" s="73">
-        <f>SUM(DG4:DG38)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DH39" s="73">
-        <f>SUM(DH4:DH38)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DI39" s="73">
-        <f>SUM(DI4:DI38)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DJ39" s="73">
-        <f>SUM(DJ4:DJ38)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DK39" s="73">
-        <f>SUM(DK4:DK38)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DL39" s="73">
-        <f>SUM(DL4:DL38)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DM39" s="73">
-        <f>SUM(DM4:DM38)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DN39" s="73">
-        <f>SUM(DN4:DN38)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DO39" s="73">
-        <f>SUM(DO4:DO38)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43751,18 +43597,81 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO38">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
       <formula>1</formula>
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DP4:XFD39">
-    <cfRule type="cellIs" dxfId="25" priority="77" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="77" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43786,122 +43695,122 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="232" t="s">
+      <c r="C1" s="233" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="232" t="s">
+      <c r="D1" s="233" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="232" t="s">
+      <c r="E1" s="233" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="223" t="s">
+      <c r="F1" s="224" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="224"/>
-      <c r="H1" s="224"/>
-      <c r="I1" s="224"/>
-      <c r="J1" s="224"/>
-      <c r="K1" s="224"/>
-      <c r="L1" s="224"/>
-      <c r="M1" s="224"/>
-      <c r="N1" s="224"/>
-      <c r="O1" s="224"/>
-      <c r="P1" s="224"/>
-      <c r="Q1" s="224"/>
-      <c r="R1" s="224"/>
-      <c r="S1" s="224"/>
-      <c r="T1" s="224"/>
-      <c r="U1" s="224"/>
-      <c r="V1" s="224"/>
-      <c r="W1" s="224"/>
-      <c r="X1" s="224"/>
-      <c r="Y1" s="224"/>
-      <c r="Z1" s="224"/>
-      <c r="AA1" s="224"/>
-      <c r="AB1" s="224"/>
-      <c r="AC1" s="225"/>
-      <c r="AD1" s="235" t="s">
+      <c r="G1" s="225"/>
+      <c r="H1" s="225"/>
+      <c r="I1" s="225"/>
+      <c r="J1" s="225"/>
+      <c r="K1" s="225"/>
+      <c r="L1" s="225"/>
+      <c r="M1" s="225"/>
+      <c r="N1" s="225"/>
+      <c r="O1" s="225"/>
+      <c r="P1" s="225"/>
+      <c r="Q1" s="225"/>
+      <c r="R1" s="225"/>
+      <c r="S1" s="225"/>
+      <c r="T1" s="225"/>
+      <c r="U1" s="225"/>
+      <c r="V1" s="225"/>
+      <c r="W1" s="225"/>
+      <c r="X1" s="225"/>
+      <c r="Y1" s="225"/>
+      <c r="Z1" s="225"/>
+      <c r="AA1" s="225"/>
+      <c r="AB1" s="225"/>
+      <c r="AC1" s="226"/>
+      <c r="AD1" s="239" t="s">
         <v>281</v>
       </c>
-      <c r="AE1" s="236"/>
-      <c r="AF1" s="236"/>
-      <c r="AG1" s="236"/>
-      <c r="AH1" s="236"/>
-      <c r="AI1" s="237"/>
-      <c r="AJ1" s="223" t="s">
+      <c r="AE1" s="240"/>
+      <c r="AF1" s="240"/>
+      <c r="AG1" s="240"/>
+      <c r="AH1" s="240"/>
+      <c r="AI1" s="241"/>
+      <c r="AJ1" s="224" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="224"/>
-      <c r="AL1" s="224"/>
-      <c r="AM1" s="224"/>
-      <c r="AN1" s="224"/>
-      <c r="AO1" s="225"/>
-      <c r="AP1" s="226" t="s">
+      <c r="AK1" s="225"/>
+      <c r="AL1" s="225"/>
+      <c r="AM1" s="225"/>
+      <c r="AN1" s="225"/>
+      <c r="AO1" s="226"/>
+      <c r="AP1" s="227" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="227"/>
-      <c r="AR1" s="227"/>
-      <c r="AS1" s="227"/>
-      <c r="AT1" s="227"/>
-      <c r="AU1" s="228"/>
-      <c r="AV1" s="229" t="s">
+      <c r="AQ1" s="228"/>
+      <c r="AR1" s="228"/>
+      <c r="AS1" s="228"/>
+      <c r="AT1" s="228"/>
+      <c r="AU1" s="229"/>
+      <c r="AV1" s="230" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="230"/>
-      <c r="AX1" s="231"/>
+      <c r="AW1" s="231"/>
+      <c r="AX1" s="232"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="220"/>
-      <c r="G2" s="221"/>
-      <c r="H2" s="222"/>
-      <c r="I2" s="220"/>
-      <c r="J2" s="221"/>
-      <c r="K2" s="222"/>
-      <c r="L2" s="220"/>
-      <c r="M2" s="221"/>
-      <c r="N2" s="222"/>
-      <c r="O2" s="220"/>
-      <c r="P2" s="221"/>
-      <c r="Q2" s="222"/>
-      <c r="R2" s="220"/>
-      <c r="S2" s="221"/>
-      <c r="T2" s="222"/>
-      <c r="U2" s="220"/>
-      <c r="V2" s="221"/>
-      <c r="W2" s="222"/>
-      <c r="X2" s="220"/>
-      <c r="Y2" s="221"/>
-      <c r="Z2" s="222"/>
-      <c r="AA2" s="220"/>
-      <c r="AB2" s="221"/>
-      <c r="AC2" s="221"/>
-      <c r="AD2" s="220"/>
-      <c r="AE2" s="221"/>
-      <c r="AF2" s="222"/>
-      <c r="AG2" s="220"/>
-      <c r="AH2" s="221"/>
-      <c r="AI2" s="222"/>
-      <c r="AJ2" s="220"/>
-      <c r="AK2" s="221"/>
-      <c r="AL2" s="222"/>
-      <c r="AM2" s="220"/>
-      <c r="AN2" s="221"/>
-      <c r="AO2" s="222"/>
-      <c r="AP2" s="220"/>
-      <c r="AQ2" s="221"/>
-      <c r="AR2" s="222"/>
-      <c r="AS2" s="220"/>
-      <c r="AT2" s="221"/>
-      <c r="AU2" s="222"/>
-      <c r="AV2" s="220"/>
-      <c r="AW2" s="221"/>
-      <c r="AX2" s="222"/>
+      <c r="C2" s="234"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="237"/>
+      <c r="H2" s="238"/>
+      <c r="I2" s="236"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="236"/>
+      <c r="M2" s="237"/>
+      <c r="N2" s="238"/>
+      <c r="O2" s="236"/>
+      <c r="P2" s="237"/>
+      <c r="Q2" s="238"/>
+      <c r="R2" s="236"/>
+      <c r="S2" s="237"/>
+      <c r="T2" s="238"/>
+      <c r="U2" s="236"/>
+      <c r="V2" s="237"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="236"/>
+      <c r="Y2" s="237"/>
+      <c r="Z2" s="238"/>
+      <c r="AA2" s="236"/>
+      <c r="AB2" s="237"/>
+      <c r="AC2" s="237"/>
+      <c r="AD2" s="236"/>
+      <c r="AE2" s="237"/>
+      <c r="AF2" s="238"/>
+      <c r="AG2" s="236"/>
+      <c r="AH2" s="237"/>
+      <c r="AI2" s="238"/>
+      <c r="AJ2" s="236"/>
+      <c r="AK2" s="237"/>
+      <c r="AL2" s="238"/>
+      <c r="AM2" s="236"/>
+      <c r="AN2" s="237"/>
+      <c r="AO2" s="238"/>
+      <c r="AP2" s="236"/>
+      <c r="AQ2" s="237"/>
+      <c r="AR2" s="238"/>
+      <c r="AS2" s="236"/>
+      <c r="AT2" s="237"/>
+      <c r="AU2" s="238"/>
+      <c r="AV2" s="236"/>
+      <c r="AW2" s="237"/>
+      <c r="AX2" s="238"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -43910,9 +43819,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="234"/>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
+      <c r="C3" s="235"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
       <c r="F3" s="170" t="s">
         <v>393</v>
       </c>
@@ -46508,6 +46417,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46524,21 +46440,14 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW32">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:AW38">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="between">
       <formula>1</formula>
       <formula>5</formula>
     </cfRule>
@@ -46565,70 +46474,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="232" t="s">
+      <c r="C1" s="233" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="232" t="s">
+      <c r="D1" s="233" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="232" t="s">
+      <c r="E1" s="233" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="262" t="s">
+      <c r="F1" s="273" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="263"/>
-      <c r="H1" s="264"/>
-      <c r="I1" s="265" t="s">
+      <c r="G1" s="274"/>
+      <c r="H1" s="275"/>
+      <c r="I1" s="276" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="266"/>
-      <c r="K1" s="267"/>
-      <c r="L1" s="269" t="s">
+      <c r="J1" s="277"/>
+      <c r="K1" s="278"/>
+      <c r="L1" s="243" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="270"/>
-      <c r="N1" s="271"/>
-      <c r="O1" s="272" t="s">
+      <c r="M1" s="244"/>
+      <c r="N1" s="245"/>
+      <c r="O1" s="246" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="273"/>
-      <c r="Q1" s="274"/>
-      <c r="R1" s="238" t="s">
+      <c r="P1" s="247"/>
+      <c r="Q1" s="248"/>
+      <c r="R1" s="249" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="239"/>
-      <c r="T1" s="240"/>
-      <c r="U1" s="241" t="s">
+      <c r="S1" s="250"/>
+      <c r="T1" s="251"/>
+      <c r="U1" s="252" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="242"/>
-      <c r="W1" s="243"/>
+      <c r="V1" s="253"/>
+      <c r="W1" s="254"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="244"/>
-      <c r="G2" s="245"/>
-      <c r="H2" s="246"/>
-      <c r="I2" s="259"/>
-      <c r="J2" s="260"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="256"/>
-      <c r="M2" s="257"/>
-      <c r="N2" s="258"/>
-      <c r="O2" s="253"/>
-      <c r="P2" s="254"/>
-      <c r="Q2" s="255"/>
-      <c r="R2" s="250"/>
-      <c r="S2" s="251"/>
-      <c r="T2" s="252"/>
-      <c r="U2" s="247"/>
-      <c r="V2" s="248"/>
-      <c r="W2" s="249"/>
+      <c r="C2" s="234"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="255"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="257"/>
+      <c r="I2" s="270"/>
+      <c r="J2" s="271"/>
+      <c r="K2" s="272"/>
+      <c r="L2" s="267"/>
+      <c r="M2" s="268"/>
+      <c r="N2" s="269"/>
+      <c r="O2" s="264"/>
+      <c r="P2" s="265"/>
+      <c r="Q2" s="266"/>
+      <c r="R2" s="261"/>
+      <c r="S2" s="262"/>
+      <c r="T2" s="263"/>
+      <c r="U2" s="258"/>
+      <c r="V2" s="259"/>
+      <c r="W2" s="260"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46637,9 +46546,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="268"/>
-      <c r="D3" s="268"/>
-      <c r="E3" s="268"/>
+      <c r="C3" s="242"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -48101,11 +48010,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -48116,14 +48020,19 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:W38">
-    <cfRule type="cellIs" dxfId="21" priority="4" operator="between">
+    <cfRule type="cellIs" dxfId="12" priority="4" operator="between">
       <formula>1</formula>
       <formula>5</formula>
     </cfRule>
@@ -55122,72 +55031,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="232" t="s">
+      <c r="C1" s="233" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="232" t="s">
+      <c r="D1" s="233" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="232" t="s">
+      <c r="E1" s="233" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="262" t="s">
+      <c r="F1" s="273" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="263"/>
-      <c r="H1" s="264"/>
-      <c r="I1" s="265" t="s">
+      <c r="G1" s="274"/>
+      <c r="H1" s="275"/>
+      <c r="I1" s="276" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="266"/>
-      <c r="K1" s="267"/>
-      <c r="L1" s="269" t="s">
+      <c r="J1" s="277"/>
+      <c r="K1" s="278"/>
+      <c r="L1" s="243" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="270"/>
-      <c r="N1" s="271"/>
-      <c r="O1" s="272" t="s">
+      <c r="M1" s="244"/>
+      <c r="N1" s="245"/>
+      <c r="O1" s="246" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="273"/>
-      <c r="Q1" s="274"/>
-      <c r="R1" s="238" t="s">
+      <c r="P1" s="247"/>
+      <c r="Q1" s="248"/>
+      <c r="R1" s="249" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="239"/>
-      <c r="T1" s="240"/>
-      <c r="U1" s="241" t="s">
+      <c r="S1" s="250"/>
+      <c r="T1" s="251"/>
+      <c r="U1" s="252" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="242"/>
-      <c r="W1" s="243"/>
+      <c r="V1" s="253"/>
+      <c r="W1" s="254"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="244" t="s">
+      <c r="C2" s="234"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="255" t="s">
         <v>438</v>
       </c>
-      <c r="G2" s="245"/>
-      <c r="H2" s="246"/>
-      <c r="I2" s="259"/>
-      <c r="J2" s="260"/>
-      <c r="K2" s="261"/>
-      <c r="L2" s="256"/>
-      <c r="M2" s="257"/>
-      <c r="N2" s="258"/>
-      <c r="O2" s="253"/>
-      <c r="P2" s="254"/>
-      <c r="Q2" s="255"/>
-      <c r="R2" s="250"/>
-      <c r="S2" s="251"/>
-      <c r="T2" s="252"/>
-      <c r="U2" s="247"/>
-      <c r="V2" s="248"/>
-      <c r="W2" s="249"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="257"/>
+      <c r="I2" s="270"/>
+      <c r="J2" s="271"/>
+      <c r="K2" s="272"/>
+      <c r="L2" s="267"/>
+      <c r="M2" s="268"/>
+      <c r="N2" s="269"/>
+      <c r="O2" s="264"/>
+      <c r="P2" s="265"/>
+      <c r="Q2" s="266"/>
+      <c r="R2" s="261"/>
+      <c r="S2" s="262"/>
+      <c r="T2" s="263"/>
+      <c r="U2" s="258"/>
+      <c r="V2" s="259"/>
+      <c r="W2" s="260"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -55196,9 +55105,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="268"/>
-      <c r="D3" s="268"/>
-      <c r="E3" s="268"/>
+      <c r="C3" s="242"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -56660,6 +56569,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -56670,19 +56584,14 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:W38">
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="between">
       <formula>1</formula>
       <formula>5</formula>
     </cfRule>
@@ -56702,11 +56611,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C1" s="275" t="s">
+      <c r="C1" s="279" t="s">
         <v>340</v>
       </c>
-      <c r="D1" s="276"/>
-      <c r="E1" s="276"/>
+      <c r="D1" s="280"/>
+      <c r="E1" s="280"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -57159,7 +57068,7 @@
     <mergeCell ref="C1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="C3:E37">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="between">
       <formula>1</formula>
       <formula>5</formula>
     </cfRule>
@@ -57181,51 +57090,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="278" t="s">
+      <c r="C1" s="301" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="279"/>
-      <c r="E1" s="279"/>
-      <c r="F1" s="279"/>
-      <c r="G1" s="279"/>
-      <c r="H1" s="279"/>
-      <c r="I1" s="280"/>
+      <c r="D1" s="302"/>
+      <c r="E1" s="302"/>
+      <c r="F1" s="302"/>
+      <c r="G1" s="302"/>
+      <c r="H1" s="302"/>
+      <c r="I1" s="303"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="299" t="s">
+      <c r="L1" s="281" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="302"/>
-      <c r="N1" s="302"/>
-      <c r="O1" s="302"/>
-      <c r="P1" s="302"/>
-      <c r="Q1" s="302"/>
-      <c r="R1" s="302"/>
-      <c r="S1" s="302"/>
-      <c r="T1" s="302"/>
-      <c r="U1" s="302"/>
-      <c r="V1" s="302"/>
-      <c r="W1" s="302"/>
-      <c r="X1" s="302"/>
-      <c r="Y1" s="302"/>
-      <c r="Z1" s="302"/>
-      <c r="AA1" s="302"/>
-      <c r="AB1" s="302"/>
-      <c r="AC1" s="302"/>
-      <c r="AD1" s="302"/>
-      <c r="AE1" s="302"/>
-      <c r="AF1" s="302"/>
-      <c r="AG1" s="303"/>
-      <c r="AH1" s="299" t="s">
+      <c r="M1" s="286"/>
+      <c r="N1" s="286"/>
+      <c r="O1" s="286"/>
+      <c r="P1" s="286"/>
+      <c r="Q1" s="286"/>
+      <c r="R1" s="286"/>
+      <c r="S1" s="286"/>
+      <c r="T1" s="286"/>
+      <c r="U1" s="286"/>
+      <c r="V1" s="286"/>
+      <c r="W1" s="286"/>
+      <c r="X1" s="286"/>
+      <c r="Y1" s="286"/>
+      <c r="Z1" s="286"/>
+      <c r="AA1" s="286"/>
+      <c r="AB1" s="286"/>
+      <c r="AC1" s="286"/>
+      <c r="AD1" s="286"/>
+      <c r="AE1" s="286"/>
+      <c r="AF1" s="286"/>
+      <c r="AG1" s="287"/>
+      <c r="AH1" s="281" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="300"/>
-      <c r="AJ1" s="300"/>
-      <c r="AK1" s="301"/>
+      <c r="AI1" s="282"/>
+      <c r="AJ1" s="282"/>
+      <c r="AK1" s="283"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -62425,15 +62334,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="293" t="s">
+      <c r="K80" s="288" t="s">
         <v>442</v>
       </c>
-      <c r="L80" s="294"/>
-      <c r="M80" s="295"/>
+      <c r="L80" s="289"/>
+      <c r="M80" s="290"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="277"/>
-      <c r="X80" s="277"/>
+      <c r="W80" s="284"/>
+      <c r="X80" s="284"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -62483,15 +62392,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="296"/>
-      <c r="L81" s="297"/>
-      <c r="M81" s="298"/>
+      <c r="K81" s="291"/>
+      <c r="L81" s="292"/>
+      <c r="M81" s="293"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="277" t="s">
+      <c r="W81" s="284" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="277"/>
+      <c r="X81" s="284"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62547,17 +62456,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="308" t="s">
+      <c r="K82" s="294" t="s">
         <v>443</v>
       </c>
-      <c r="L82" s="309"/>
-      <c r="M82" s="310"/>
+      <c r="L82" s="295"/>
+      <c r="M82" s="296"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="277" t="s">
+      <c r="W82" s="284" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="277"/>
+      <c r="X82" s="284"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62613,36 +62522,35 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="320" t="s">
+      <c r="K83" s="297" t="s">
         <v>444</v>
       </c>
-      <c r="L83" s="321"/>
-      <c r="M83" s="322"/>
+      <c r="L83" s="298"/>
+      <c r="M83" s="299"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="323" t="s">
+      <c r="W83" s="285" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="323"/>
-      <c r="Y83" s="324">
+      <c r="X83" s="285"/>
+      <c r="Y83" s="196">
         <v>220</v>
       </c>
-      <c r="Z83" s="324">
+      <c r="Z83" s="196">
         <v>60</v>
       </c>
       <c r="AA83" s="70">
         <v>75</v>
       </c>
-      <c r="AB83" s="327"/>
       <c r="AC83" s="109">
         <f>Y83/SUM($Y$83:$AA$83)</f>
         <v>0.61971830985915488</v>
       </c>
-      <c r="AD83" s="325">
+      <c r="AD83" s="197">
         <f t="shared" ref="AD83:AE83" si="5">Z83/SUM($Y$83:$AA$83)</f>
         <v>0.16901408450704225</v>
       </c>
-      <c r="AE83" s="325">
+      <c r="AE83" s="197">
         <f t="shared" si="5"/>
         <v>0.21126760563380281</v>
       </c>
@@ -62677,22 +62585,21 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="284" t="s">
+      <c r="K84" s="316" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="285"/>
-      <c r="M84" s="286"/>
+      <c r="L84" s="317"/>
+      <c r="M84" s="318"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="328"/>
-      <c r="X84" s="328"/>
-      <c r="Y84" s="326"/>
-      <c r="Z84" s="326"/>
-      <c r="AA84" s="326"/>
-      <c r="AB84" s="327"/>
-      <c r="AC84" s="329"/>
-      <c r="AD84" s="329"/>
-      <c r="AE84" s="329"/>
+      <c r="W84" s="300"/>
+      <c r="X84" s="300"/>
+      <c r="Y84" s="198"/>
+      <c r="Z84" s="198"/>
+      <c r="AA84" s="198"/>
+      <c r="AC84" s="199"/>
+      <c r="AD84" s="199"/>
+      <c r="AE84" s="199"/>
     </row>
     <row r="85" spans="1:31" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="90" t="s">
@@ -62724,9 +62631,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="287"/>
-      <c r="L85" s="288"/>
-      <c r="M85" s="289"/>
+      <c r="K85" s="319"/>
+      <c r="L85" s="320"/>
+      <c r="M85" s="321"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -62760,9 +62667,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="287"/>
-      <c r="L86" s="288"/>
-      <c r="M86" s="289"/>
+      <c r="K86" s="319"/>
+      <c r="L86" s="320"/>
+      <c r="M86" s="321"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -62796,9 +62703,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="287"/>
-      <c r="L87" s="288"/>
-      <c r="M87" s="289"/>
+      <c r="K87" s="319"/>
+      <c r="L87" s="320"/>
+      <c r="M87" s="321"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -62832,9 +62739,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="287"/>
-      <c r="L88" s="288"/>
-      <c r="M88" s="289"/>
+      <c r="K88" s="319"/>
+      <c r="L88" s="320"/>
+      <c r="M88" s="321"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -62868,9 +62775,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="287"/>
-      <c r="L89" s="288"/>
-      <c r="M89" s="289"/>
+      <c r="K89" s="319"/>
+      <c r="L89" s="320"/>
+      <c r="M89" s="321"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -62904,9 +62811,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="287"/>
-      <c r="L90" s="288"/>
-      <c r="M90" s="289"/>
+      <c r="K90" s="319"/>
+      <c r="L90" s="320"/>
+      <c r="M90" s="321"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -62940,9 +62847,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="287"/>
-      <c r="L91" s="288"/>
-      <c r="M91" s="289"/>
+      <c r="K91" s="319"/>
+      <c r="L91" s="320"/>
+      <c r="M91" s="321"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -62976,9 +62883,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="287"/>
-      <c r="L92" s="288"/>
-      <c r="M92" s="289"/>
+      <c r="K92" s="319"/>
+      <c r="L92" s="320"/>
+      <c r="M92" s="321"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -63012,9 +62919,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="287"/>
-      <c r="L93" s="288"/>
-      <c r="M93" s="289"/>
+      <c r="K93" s="319"/>
+      <c r="L93" s="320"/>
+      <c r="M93" s="321"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -63048,9 +62955,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="287"/>
-      <c r="L94" s="288"/>
-      <c r="M94" s="289"/>
+      <c r="K94" s="319"/>
+      <c r="L94" s="320"/>
+      <c r="M94" s="321"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -63084,9 +62991,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="287"/>
-      <c r="L95" s="288"/>
-      <c r="M95" s="289"/>
+      <c r="K95" s="319"/>
+      <c r="L95" s="320"/>
+      <c r="M95" s="321"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -63120,9 +63027,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="287"/>
-      <c r="L96" s="288"/>
-      <c r="M96" s="289"/>
+      <c r="K96" s="319"/>
+      <c r="L96" s="320"/>
+      <c r="M96" s="321"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -63156,9 +63063,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="287"/>
-      <c r="L97" s="288"/>
-      <c r="M97" s="289"/>
+      <c r="K97" s="319"/>
+      <c r="L97" s="320"/>
+      <c r="M97" s="321"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -63192,9 +63099,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="287"/>
-      <c r="L98" s="288"/>
-      <c r="M98" s="289"/>
+      <c r="K98" s="319"/>
+      <c r="L98" s="320"/>
+      <c r="M98" s="321"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -63228,9 +63135,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="287"/>
-      <c r="L99" s="288"/>
-      <c r="M99" s="289"/>
+      <c r="K99" s="319"/>
+      <c r="L99" s="320"/>
+      <c r="M99" s="321"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -63264,9 +63171,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="287"/>
-      <c r="L100" s="288"/>
-      <c r="M100" s="289"/>
+      <c r="K100" s="319"/>
+      <c r="L100" s="320"/>
+      <c r="M100" s="321"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -63300,9 +63207,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="287"/>
-      <c r="L101" s="288"/>
-      <c r="M101" s="289"/>
+      <c r="K101" s="319"/>
+      <c r="L101" s="320"/>
+      <c r="M101" s="321"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -63336,9 +63243,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="287"/>
-      <c r="L102" s="288"/>
-      <c r="M102" s="289"/>
+      <c r="K102" s="319"/>
+      <c r="L102" s="320"/>
+      <c r="M102" s="321"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -63372,9 +63279,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="287"/>
-      <c r="L103" s="288"/>
-      <c r="M103" s="289"/>
+      <c r="K103" s="319"/>
+      <c r="L103" s="320"/>
+      <c r="M103" s="321"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -63408,9 +63315,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="287"/>
-      <c r="L104" s="288"/>
-      <c r="M104" s="289"/>
+      <c r="K104" s="319"/>
+      <c r="L104" s="320"/>
+      <c r="M104" s="321"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -63444,9 +63351,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="290"/>
-      <c r="L105" s="291"/>
-      <c r="M105" s="292"/>
+      <c r="K105" s="322"/>
+      <c r="L105" s="323"/>
+      <c r="M105" s="324"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -63480,11 +63387,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="281" t="s">
+      <c r="K106" s="313" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="282"/>
-      <c r="M106" s="283"/>
+      <c r="L106" s="314"/>
+      <c r="M106" s="315"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63518,11 +63425,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="281" t="s">
+      <c r="K107" s="313" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="282"/>
-      <c r="M107" s="283"/>
+      <c r="L107" s="314"/>
+      <c r="M107" s="315"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63556,11 +63463,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="311" t="s">
+      <c r="K108" s="304" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="312"/>
-      <c r="M108" s="313"/>
+      <c r="L108" s="305"/>
+      <c r="M108" s="306"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63594,9 +63501,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="314"/>
-      <c r="L109" s="315"/>
-      <c r="M109" s="316"/>
+      <c r="K109" s="307"/>
+      <c r="L109" s="308"/>
+      <c r="M109" s="309"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -63630,9 +63537,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="314"/>
-      <c r="L110" s="315"/>
-      <c r="M110" s="316"/>
+      <c r="K110" s="307"/>
+      <c r="L110" s="308"/>
+      <c r="M110" s="309"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -63666,9 +63573,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="314"/>
-      <c r="L111" s="315"/>
-      <c r="M111" s="316"/>
+      <c r="K111" s="307"/>
+      <c r="L111" s="308"/>
+      <c r="M111" s="309"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -63706,9 +63613,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="314"/>
-      <c r="L112" s="315"/>
-      <c r="M112" s="316"/>
+      <c r="K112" s="307"/>
+      <c r="L112" s="308"/>
+      <c r="M112" s="309"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="156" t="s">
@@ -63744,9 +63651,9 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="317"/>
-      <c r="L113" s="318"/>
-      <c r="M113" s="319"/>
+      <c r="K113" s="310"/>
+      <c r="L113" s="311"/>
+      <c r="M113" s="312"/>
     </row>
     <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="93" t="s">
@@ -63786,6 +63693,12 @@
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
+    <mergeCell ref="W84:X84"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K108:M113"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
     <mergeCell ref="W81:X81"/>
@@ -63795,14 +63708,18 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
-    <mergeCell ref="W84:X84"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K108:M113"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
+  <conditionalFormatting sqref="A3:A40">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A3:A44">
     <cfRule type="colorScale" priority="8">
       <colorScale>
@@ -63814,46 +63731,36 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:AK44">
-    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3:K45">
-    <cfRule type="cellIs" dxfId="14" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="42" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="43" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="44" operator="equal">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L46:M46 U46">
-    <cfRule type="cellIs" dxfId="11" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="57" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="58" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="59" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="59" operator="equal">
       <formula>3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3:A40">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -63885,32 +63792,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="304" t="s">
+      <c r="A1" s="325" t="s">
         <v>406</v>
       </c>
-      <c r="B1" s="304"/>
-      <c r="C1" s="304"/>
-      <c r="D1" s="304"/>
-      <c r="E1" s="304"/>
-      <c r="F1" s="304" t="s">
+      <c r="B1" s="325"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325" t="s">
         <v>407</v>
       </c>
-      <c r="G1" s="304"/>
-      <c r="H1" s="304"/>
-      <c r="I1" s="304"/>
-      <c r="J1" s="304"/>
+      <c r="G1" s="325"/>
+      <c r="H1" s="325"/>
+      <c r="I1" s="325"/>
+      <c r="J1" s="325"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="304"/>
-      <c r="B2" s="304"/>
-      <c r="C2" s="304"/>
-      <c r="D2" s="304"/>
-      <c r="E2" s="304"/>
-      <c r="F2" s="304"/>
-      <c r="G2" s="304"/>
-      <c r="H2" s="304"/>
-      <c r="I2" s="304"/>
-      <c r="J2" s="304"/>
+      <c r="A2" s="325"/>
+      <c r="B2" s="325"/>
+      <c r="C2" s="325"/>
+      <c r="D2" s="325"/>
+      <c r="E2" s="325"/>
+      <c r="F2" s="325"/>
+      <c r="G2" s="325"/>
+      <c r="H2" s="325"/>
+      <c r="I2" s="325"/>
+      <c r="J2" s="325"/>
       <c r="L2" t="s">
         <v>410</v>
       </c>
@@ -64671,24 +64578,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="196" t="s">
+      <c r="A1" s="200" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="305"/>
-      <c r="C1" s="306" t="s">
+      <c r="B1" s="326"/>
+      <c r="C1" s="327" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="199"/>
-      <c r="E1" s="307"/>
-      <c r="H1" s="196" t="s">
+      <c r="D1" s="203"/>
+      <c r="E1" s="328"/>
+      <c r="H1" s="200" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="305"/>
-      <c r="J1" s="306" t="s">
+      <c r="I1" s="326"/>
+      <c r="J1" s="327" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="199"/>
-      <c r="L1" s="307"/>
+      <c r="K1" s="203"/>
+      <c r="L1" s="328"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -65776,9 +65683,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -65802,36 +65709,36 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="196" t="s">
+      <c r="E2" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="197"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="201" t="s">
+      <c r="F2" s="201"/>
+      <c r="G2" s="202"/>
+      <c r="H2" s="205" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="202"/>
-      <c r="J2" s="203"/>
-      <c r="K2" s="196" t="s">
+      <c r="I2" s="206"/>
+      <c r="J2" s="207"/>
+      <c r="K2" s="200" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="197"/>
-      <c r="M2" s="198"/>
-      <c r="N2" s="201" t="s">
+      <c r="L2" s="201"/>
+      <c r="M2" s="202"/>
+      <c r="N2" s="205" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="202"/>
-      <c r="P2" s="203"/>
-      <c r="Q2" s="196" t="s">
+      <c r="O2" s="206"/>
+      <c r="P2" s="207"/>
+      <c r="Q2" s="200" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="197"/>
-      <c r="S2" s="198"/>
-      <c r="T2" s="199" t="s">
+      <c r="R2" s="201"/>
+      <c r="S2" s="202"/>
+      <c r="T2" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="199"/>
-      <c r="V2" s="199"/>
+      <c r="U2" s="203"/>
+      <c r="V2" s="203"/>
       <c r="Z2" s="125">
         <v>46266</v>
       </c>
@@ -67286,7 +67193,7 @@
       <c r="C20" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="D20" s="40" t="s">
+      <c r="D20" s="23" t="s">
         <v>263</v>
       </c>
       <c r="E20" s="6">
@@ -68318,7 +68225,7 @@
       <c r="C32" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="D32" s="34" t="s">
+      <c r="D32" s="57" t="s">
         <v>298</v>
       </c>
       <c r="E32" s="6">
@@ -68927,12 +68834,12 @@
     <mergeCell ref="N2:P2"/>
   </mergeCells>
   <conditionalFormatting sqref="T4:T38 V4:V38">
-    <cfRule type="cellIs" dxfId="46" priority="20" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="37" priority="20" operator="greaterThan">
       <formula>396</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U4:U38">
-    <cfRule type="cellIs" dxfId="45" priority="15" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="15" operator="greaterThan">
       <formula>92</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69000,30 +68907,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="210"/>
+      <c r="F2" s="211" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="211"/>
+      <c r="H2" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="210"/>
+      <c r="J2" s="211" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="211"/>
+      <c r="L2" s="210" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="199" t="s">
+      <c r="M2" s="210"/>
+      <c r="N2" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="199"/>
+      <c r="O2" s="203"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -70971,12 +70878,12 @@
     <mergeCell ref="L2:M2"/>
   </mergeCells>
   <conditionalFormatting sqref="N4:N43">
-    <cfRule type="cellIs" dxfId="44" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="greaterThan">
       <formula>396</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4:O43">
-    <cfRule type="cellIs" dxfId="43" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="greaterThan">
       <formula>92</formula>
     </cfRule>
   </conditionalFormatting>
@@ -71020,30 +70927,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="210"/>
+      <c r="F2" s="211" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="211"/>
+      <c r="H2" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="210"/>
+      <c r="J2" s="211" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="211"/>
+      <c r="L2" s="210" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="199" t="s">
+      <c r="M2" s="210"/>
+      <c r="N2" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="199"/>
+      <c r="O2" s="203"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -72932,7 +72839,7 @@
     <mergeCell ref="L2:M2"/>
   </mergeCells>
   <conditionalFormatting sqref="N4:O41">
-    <cfRule type="cellIs" dxfId="42" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="4" operator="greaterThan">
       <formula>396</formula>
     </cfRule>
   </conditionalFormatting>
@@ -72977,30 +72884,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="210"/>
+      <c r="F2" s="211" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="211"/>
+      <c r="H2" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="210"/>
+      <c r="J2" s="211" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="211"/>
+      <c r="L2" s="210" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="199" t="s">
+      <c r="M2" s="210"/>
+      <c r="N2" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="199"/>
+      <c r="O2" s="203"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -74980,7 +74887,7 @@
     <mergeCell ref="L2:M2"/>
   </mergeCells>
   <conditionalFormatting sqref="N4:O43">
-    <cfRule type="cellIs" dxfId="41" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="32" priority="5" operator="greaterThan">
       <formula>396</formula>
     </cfRule>
   </conditionalFormatting>
@@ -75025,30 +74932,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="210"/>
+      <c r="F2" s="211" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="211"/>
+      <c r="H2" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="210"/>
+      <c r="J2" s="211" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="211"/>
+      <c r="L2" s="210" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="199" t="s">
+      <c r="M2" s="210"/>
+      <c r="N2" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="199"/>
+      <c r="O2" s="203"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -76691,7 +76598,7 @@
     <mergeCell ref="L2:M2"/>
   </mergeCells>
   <conditionalFormatting sqref="N4:O36">
-    <cfRule type="cellIs" dxfId="40" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="3" operator="greaterThan">
       <formula>396</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76733,30 +76640,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="210"/>
+      <c r="E2" s="211" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="211"/>
+      <c r="G2" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="210"/>
+      <c r="I2" s="211" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="211"/>
+      <c r="K2" s="210" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="199" t="s">
+      <c r="L2" s="210"/>
+      <c r="M2" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="199"/>
+      <c r="N2" s="203"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -78476,7 +78383,7 @@
     <mergeCell ref="K2:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="M4:N40">
-    <cfRule type="cellIs" dxfId="39" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="greaterThan">
       <formula>396</formula>
     </cfRule>
   </conditionalFormatting>
@@ -78518,30 +78425,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="210"/>
+      <c r="E2" s="211" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="211"/>
+      <c r="G2" s="210" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="210"/>
+      <c r="I2" s="211" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="211"/>
+      <c r="K2" s="210" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="199" t="s">
+      <c r="L2" s="210"/>
+      <c r="M2" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="199"/>
+      <c r="N2" s="203"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -80081,7 +79988,7 @@
     <mergeCell ref="K2:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="M4:N36">
-    <cfRule type="cellIs" dxfId="38" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="greaterThan">
       <formula>396</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8036" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E33B02CA-D0DD-4BF8-AA58-CB4A87D8514E}"/>
+  <xr:revisionPtr revIDLastSave="8046" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{960EF123-6F14-49C1-99E0-87E6DA88490C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2212" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2215" uniqueCount="448">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -1418,6 +1418,12 @@
   <si>
     <t>2026/2027</t>
   </si>
+  <si>
+    <t>Loan</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
 </sst>
 </file>
 
@@ -1714,7 +1720,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="63">
+  <borders count="64">
     <border>
       <left/>
       <right/>
@@ -2524,6 +2530,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2534,7 +2551,7 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="329">
+  <cellXfs count="330">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2955,6 +2972,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2964,16 +2990,10 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
@@ -2988,8 +3008,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3027,15 +3053,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3043,27 +3060,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3156,67 +3152,31 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3294,6 +3254,63 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3304,6 +3321,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -6359,7 +6379,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{09CBB045-FAB9-4ED4-9201-C31742855250}" type="CELLRANGE">
+                    <a:fld id="{0E95CEF5-4DFF-4531-B9FA-5BF1F4D0A289}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6393,7 +6413,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1EEBC67C-E781-499C-B02E-F00C854A93D1}" type="CELLRANGE">
+                    <a:fld id="{FFE71023-5A6A-462F-B2C5-299D5C2A611B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6427,7 +6447,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{27F408B1-F4D2-4958-A1B9-E388A673856B}" type="CELLRANGE">
+                    <a:fld id="{3E800CC7-2B1B-4AD5-A286-B7B3FB6F1B8B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6461,7 +6481,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D33E060B-3EAD-44D6-92B4-552E88412DE9}" type="CELLRANGE">
+                    <a:fld id="{6E9CC1B3-134A-4A3E-80A0-41ED461374DF}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6495,7 +6515,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{626D3461-E7A5-4D8E-903C-3D9FCA2FB2E8}" type="CELLRANGE">
+                    <a:fld id="{E250E64D-61FD-4BD9-A1D8-6F7E17452066}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6529,7 +6549,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5C59FEB0-5F63-4FA9-A7C4-C64361C3A9FC}" type="CELLRANGE">
+                    <a:fld id="{24BA7CA3-2D8F-4B81-8450-9EB351773315}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6563,7 +6583,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A8738EC7-12A9-472E-AB4B-BAD51DC703AA}" type="CELLRANGE">
+                    <a:fld id="{BD60DB80-C7F6-40E7-9AC8-EEB785EEAE51}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6597,7 +6617,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B11822CB-F914-4483-9382-C2EBDCFD3368}" type="CELLRANGE">
+                    <a:fld id="{6ED6A944-90CF-40F4-BF6F-D19BE1B1D046}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6631,7 +6651,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B58C4014-595F-43AC-9BDE-74F9F9A52250}" type="CELLRANGE">
+                    <a:fld id="{85660B1E-F961-4DC7-9E74-900588624100}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6665,7 +6685,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{47A960EA-0D3A-4FB9-AECD-5CB06567568E}" type="CELLRANGE">
+                    <a:fld id="{AE933609-8BB6-411D-80D5-B075312E0B65}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6699,7 +6719,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{025A7587-7628-4C53-9C2F-475D9FCDB240}" type="CELLRANGE">
+                    <a:fld id="{D8C51D39-1E7A-4BF2-9945-FA97A82530C4}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6733,7 +6753,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DADE368F-19D0-46E5-A0E8-1D92BD5B0A2E}" type="CELLRANGE">
+                    <a:fld id="{C7B15057-2DAD-4445-BA2E-CC653EB56EEB}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6782,7 +6802,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{245D981B-9422-45D9-AE73-1E4A8C24091F}" type="CELLRANGE">
+                    <a:fld id="{D4F95C7B-DFFB-4292-8B9B-BD0418395BFF}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6841,7 +6861,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8770C142-21C6-44CD-AFFF-453E97631057}" type="CELLRANGE">
+                    <a:fld id="{7E184E06-D9F4-4FEB-9C72-4F1756B5B22A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6875,7 +6895,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{331FE634-7135-4AA2-9535-1912DEE7E5DE}" type="CELLRANGE">
+                    <a:fld id="{8F215157-10C5-499D-BB8E-65613A1DF761}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6909,7 +6929,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{408EBD0C-0007-47B3-B2C3-A6A16FA3747A}" type="CELLRANGE">
+                    <a:fld id="{94290222-0D1F-4E70-AF99-9DBC6A59407B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6943,7 +6963,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{36F0D138-D4DD-4253-A403-6A896EA433F1}" type="CELLRANGE">
+                    <a:fld id="{EC7DFA01-2001-4821-B728-8A5E87584B17}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6977,7 +6997,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9F5524F3-78D2-4423-BA85-53AAE9A49738}" type="CELLRANGE">
+                    <a:fld id="{827262D4-A65C-430C-92C8-C26552E0C43B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -37601,196 +37621,196 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="212">
-        <v>1</v>
-      </c>
-      <c r="G1" s="213"/>
-      <c r="H1" s="214"/>
-      <c r="I1" s="212">
+      <c r="F1" s="215">
+        <v>1</v>
+      </c>
+      <c r="G1" s="216"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="215">
         <v>2</v>
       </c>
-      <c r="J1" s="213"/>
-      <c r="K1" s="214"/>
-      <c r="L1" s="212">
-        <v>3</v>
-      </c>
-      <c r="M1" s="213"/>
-      <c r="N1" s="214"/>
-      <c r="O1" s="212">
+      <c r="J1" s="216"/>
+      <c r="K1" s="217"/>
+      <c r="L1" s="215">
+        <v>3</v>
+      </c>
+      <c r="M1" s="216"/>
+      <c r="N1" s="217"/>
+      <c r="O1" s="215">
         <v>4</v>
       </c>
-      <c r="P1" s="213"/>
-      <c r="Q1" s="214"/>
-      <c r="R1" s="212">
+      <c r="P1" s="216"/>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="215">
         <v>5</v>
       </c>
-      <c r="S1" s="213"/>
-      <c r="T1" s="214"/>
-      <c r="U1" s="212">
+      <c r="S1" s="216"/>
+      <c r="T1" s="217"/>
+      <c r="U1" s="215">
         <v>6</v>
       </c>
-      <c r="V1" s="213"/>
-      <c r="W1" s="214"/>
-      <c r="X1" s="212">
+      <c r="V1" s="216"/>
+      <c r="W1" s="217"/>
+      <c r="X1" s="215">
         <v>7</v>
       </c>
-      <c r="Y1" s="213"/>
-      <c r="Z1" s="214"/>
-      <c r="AA1" s="212">
+      <c r="Y1" s="216"/>
+      <c r="Z1" s="217"/>
+      <c r="AA1" s="215">
         <v>8</v>
       </c>
-      <c r="AB1" s="213"/>
-      <c r="AC1" s="214"/>
-      <c r="AD1" s="212">
+      <c r="AB1" s="216"/>
+      <c r="AC1" s="217"/>
+      <c r="AD1" s="215">
         <v>9</v>
       </c>
-      <c r="AE1" s="213"/>
-      <c r="AF1" s="214"/>
-      <c r="AG1" s="212">
+      <c r="AE1" s="216"/>
+      <c r="AF1" s="217"/>
+      <c r="AG1" s="215">
         <v>10</v>
       </c>
-      <c r="AH1" s="213"/>
-      <c r="AI1" s="214"/>
-      <c r="AJ1" s="212">
+      <c r="AH1" s="216"/>
+      <c r="AI1" s="217"/>
+      <c r="AJ1" s="215">
         <v>11</v>
       </c>
-      <c r="AK1" s="213"/>
-      <c r="AL1" s="214"/>
-      <c r="AM1" s="212">
+      <c r="AK1" s="216"/>
+      <c r="AL1" s="217"/>
+      <c r="AM1" s="215">
         <v>12</v>
       </c>
-      <c r="AN1" s="213"/>
-      <c r="AO1" s="214"/>
-      <c r="AP1" s="212">
+      <c r="AN1" s="216"/>
+      <c r="AO1" s="217"/>
+      <c r="AP1" s="215">
         <v>13</v>
       </c>
-      <c r="AQ1" s="213"/>
-      <c r="AR1" s="214"/>
-      <c r="AS1" s="212">
+      <c r="AQ1" s="216"/>
+      <c r="AR1" s="217"/>
+      <c r="AS1" s="215">
         <v>14</v>
       </c>
-      <c r="AT1" s="213"/>
-      <c r="AU1" s="214"/>
-      <c r="AV1" s="212">
+      <c r="AT1" s="216"/>
+      <c r="AU1" s="217"/>
+      <c r="AV1" s="215">
         <v>15</v>
       </c>
-      <c r="AW1" s="213"/>
-      <c r="AX1" s="214"/>
-      <c r="AY1" s="212">
+      <c r="AW1" s="216"/>
+      <c r="AX1" s="217"/>
+      <c r="AY1" s="215">
         <v>16</v>
       </c>
-      <c r="AZ1" s="213"/>
-      <c r="BA1" s="214"/>
-      <c r="BB1" s="212">
+      <c r="AZ1" s="216"/>
+      <c r="BA1" s="217"/>
+      <c r="BB1" s="215">
         <v>17</v>
       </c>
-      <c r="BC1" s="213"/>
-      <c r="BD1" s="214"/>
-      <c r="BE1" s="212">
+      <c r="BC1" s="216"/>
+      <c r="BD1" s="217"/>
+      <c r="BE1" s="215">
         <v>18</v>
       </c>
-      <c r="BF1" s="213"/>
-      <c r="BG1" s="214"/>
-      <c r="BH1" s="212">
+      <c r="BF1" s="216"/>
+      <c r="BG1" s="217"/>
+      <c r="BH1" s="215">
         <v>19</v>
       </c>
-      <c r="BI1" s="213"/>
-      <c r="BJ1" s="214"/>
-      <c r="BK1" s="212">
+      <c r="BI1" s="216"/>
+      <c r="BJ1" s="217"/>
+      <c r="BK1" s="215">
         <v>20</v>
       </c>
-      <c r="BL1" s="213"/>
-      <c r="BM1" s="214"/>
-      <c r="BN1" s="212">
+      <c r="BL1" s="216"/>
+      <c r="BM1" s="217"/>
+      <c r="BN1" s="215">
         <v>21</v>
       </c>
-      <c r="BO1" s="213"/>
-      <c r="BP1" s="214"/>
-      <c r="BQ1" s="212">
+      <c r="BO1" s="216"/>
+      <c r="BP1" s="217"/>
+      <c r="BQ1" s="215">
         <v>22</v>
       </c>
-      <c r="BR1" s="213"/>
-      <c r="BS1" s="214"/>
-      <c r="BT1" s="212">
+      <c r="BR1" s="216"/>
+      <c r="BS1" s="217"/>
+      <c r="BT1" s="215">
         <v>23</v>
       </c>
-      <c r="BU1" s="213"/>
-      <c r="BV1" s="214"/>
-      <c r="BW1" s="212">
+      <c r="BU1" s="216"/>
+      <c r="BV1" s="217"/>
+      <c r="BW1" s="215">
         <v>24</v>
       </c>
-      <c r="BX1" s="213"/>
-      <c r="BY1" s="214"/>
-      <c r="BZ1" s="212">
+      <c r="BX1" s="216"/>
+      <c r="BY1" s="217"/>
+      <c r="BZ1" s="215">
         <v>25</v>
       </c>
-      <c r="CA1" s="213"/>
-      <c r="CB1" s="214"/>
-      <c r="CC1" s="212">
+      <c r="CA1" s="216"/>
+      <c r="CB1" s="217"/>
+      <c r="CC1" s="215">
         <v>26</v>
       </c>
-      <c r="CD1" s="213"/>
-      <c r="CE1" s="214"/>
-      <c r="CF1" s="212">
+      <c r="CD1" s="216"/>
+      <c r="CE1" s="217"/>
+      <c r="CF1" s="215">
         <v>27</v>
       </c>
-      <c r="CG1" s="213"/>
-      <c r="CH1" s="214"/>
-      <c r="CI1" s="212">
+      <c r="CG1" s="216"/>
+      <c r="CH1" s="217"/>
+      <c r="CI1" s="215">
         <v>28</v>
       </c>
-      <c r="CJ1" s="213"/>
-      <c r="CK1" s="214"/>
-      <c r="CL1" s="212">
+      <c r="CJ1" s="216"/>
+      <c r="CK1" s="217"/>
+      <c r="CL1" s="215">
         <v>29</v>
       </c>
-      <c r="CM1" s="213"/>
-      <c r="CN1" s="214"/>
-      <c r="CO1" s="212">
+      <c r="CM1" s="216"/>
+      <c r="CN1" s="217"/>
+      <c r="CO1" s="215">
         <v>30</v>
       </c>
-      <c r="CP1" s="213"/>
-      <c r="CQ1" s="214"/>
-      <c r="CR1" s="212">
+      <c r="CP1" s="216"/>
+      <c r="CQ1" s="217"/>
+      <c r="CR1" s="215">
         <v>31</v>
       </c>
-      <c r="CS1" s="213"/>
-      <c r="CT1" s="214"/>
-      <c r="CU1" s="212">
+      <c r="CS1" s="216"/>
+      <c r="CT1" s="217"/>
+      <c r="CU1" s="215">
         <v>32</v>
       </c>
-      <c r="CV1" s="213"/>
-      <c r="CW1" s="214"/>
-      <c r="CX1" s="212">
+      <c r="CV1" s="216"/>
+      <c r="CW1" s="217"/>
+      <c r="CX1" s="215">
         <v>33</v>
       </c>
-      <c r="CY1" s="213"/>
-      <c r="CZ1" s="214"/>
-      <c r="DA1" s="212">
+      <c r="CY1" s="216"/>
+      <c r="CZ1" s="217"/>
+      <c r="DA1" s="215">
         <v>34</v>
       </c>
-      <c r="DB1" s="213"/>
-      <c r="DC1" s="214"/>
-      <c r="DD1" s="212">
+      <c r="DB1" s="216"/>
+      <c r="DC1" s="217"/>
+      <c r="DD1" s="215">
         <v>35</v>
       </c>
-      <c r="DE1" s="213"/>
-      <c r="DF1" s="214"/>
-      <c r="DG1" s="212">
+      <c r="DE1" s="216"/>
+      <c r="DF1" s="217"/>
+      <c r="DG1" s="215">
         <v>36</v>
       </c>
-      <c r="DH1" s="213"/>
-      <c r="DI1" s="214"/>
-      <c r="DJ1" s="212">
+      <c r="DH1" s="216"/>
+      <c r="DI1" s="217"/>
+      <c r="DJ1" s="215">
         <v>37</v>
       </c>
-      <c r="DK1" s="213"/>
-      <c r="DL1" s="214"/>
-      <c r="DM1" s="212">
+      <c r="DK1" s="216"/>
+      <c r="DL1" s="217"/>
+      <c r="DM1" s="215">
         <v>38</v>
       </c>
-      <c r="DN1" s="213"/>
-      <c r="DO1" s="214"/>
+      <c r="DN1" s="216"/>
+      <c r="DO1" s="217"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -37804,196 +37824,196 @@
       <c r="E2" s="218" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="215" t="s">
+      <c r="F2" s="212" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="216"/>
-      <c r="H2" s="217"/>
-      <c r="I2" s="220" t="s">
+      <c r="G2" s="213"/>
+      <c r="H2" s="214"/>
+      <c r="I2" s="221" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="221"/>
-      <c r="K2" s="222"/>
-      <c r="L2" s="215" t="s">
+      <c r="J2" s="222"/>
+      <c r="K2" s="223"/>
+      <c r="L2" s="212" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="216"/>
-      <c r="N2" s="217"/>
-      <c r="O2" s="215" t="s">
+      <c r="M2" s="213"/>
+      <c r="N2" s="214"/>
+      <c r="O2" s="212" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="216"/>
-      <c r="Q2" s="217"/>
-      <c r="R2" s="215" t="s">
+      <c r="P2" s="213"/>
+      <c r="Q2" s="214"/>
+      <c r="R2" s="212" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="216"/>
-      <c r="T2" s="217"/>
-      <c r="U2" s="215" t="s">
+      <c r="S2" s="213"/>
+      <c r="T2" s="214"/>
+      <c r="U2" s="212" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="216"/>
-      <c r="W2" s="217"/>
-      <c r="X2" s="215" t="s">
+      <c r="V2" s="213"/>
+      <c r="W2" s="214"/>
+      <c r="X2" s="212" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="216"/>
-      <c r="Z2" s="217"/>
-      <c r="AA2" s="215" t="s">
+      <c r="Y2" s="213"/>
+      <c r="Z2" s="214"/>
+      <c r="AA2" s="212" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="216"/>
-      <c r="AC2" s="217"/>
-      <c r="AD2" s="215" t="s">
+      <c r="AB2" s="213"/>
+      <c r="AC2" s="214"/>
+      <c r="AD2" s="212" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="216"/>
-      <c r="AF2" s="217"/>
-      <c r="AG2" s="215" t="s">
+      <c r="AE2" s="213"/>
+      <c r="AF2" s="214"/>
+      <c r="AG2" s="212" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="216"/>
-      <c r="AI2" s="217"/>
-      <c r="AJ2" s="215" t="s">
+      <c r="AH2" s="213"/>
+      <c r="AI2" s="214"/>
+      <c r="AJ2" s="212" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="216"/>
-      <c r="AL2" s="217"/>
-      <c r="AM2" s="215" t="s">
+      <c r="AK2" s="213"/>
+      <c r="AL2" s="214"/>
+      <c r="AM2" s="212" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="216"/>
-      <c r="AO2" s="217"/>
-      <c r="AP2" s="215" t="s">
+      <c r="AN2" s="213"/>
+      <c r="AO2" s="214"/>
+      <c r="AP2" s="212" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="216"/>
-      <c r="AR2" s="217"/>
-      <c r="AS2" s="215" t="s">
+      <c r="AQ2" s="213"/>
+      <c r="AR2" s="214"/>
+      <c r="AS2" s="212" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="216"/>
-      <c r="AU2" s="217"/>
-      <c r="AV2" s="215" t="s">
+      <c r="AT2" s="213"/>
+      <c r="AU2" s="214"/>
+      <c r="AV2" s="212" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="216"/>
-      <c r="AX2" s="217"/>
-      <c r="AY2" s="215" t="s">
+      <c r="AW2" s="213"/>
+      <c r="AX2" s="214"/>
+      <c r="AY2" s="212" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="216"/>
-      <c r="BA2" s="217"/>
-      <c r="BB2" s="215" t="s">
+      <c r="AZ2" s="213"/>
+      <c r="BA2" s="214"/>
+      <c r="BB2" s="212" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="216"/>
-      <c r="BD2" s="217"/>
-      <c r="BE2" s="215" t="s">
+      <c r="BC2" s="213"/>
+      <c r="BD2" s="214"/>
+      <c r="BE2" s="212" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="216"/>
-      <c r="BG2" s="217"/>
-      <c r="BH2" s="215" t="s">
+      <c r="BF2" s="213"/>
+      <c r="BG2" s="214"/>
+      <c r="BH2" s="212" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="216"/>
-      <c r="BJ2" s="217"/>
-      <c r="BK2" s="215" t="s">
+      <c r="BI2" s="213"/>
+      <c r="BJ2" s="214"/>
+      <c r="BK2" s="212" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="216"/>
-      <c r="BM2" s="217"/>
-      <c r="BN2" s="215" t="s">
+      <c r="BL2" s="213"/>
+      <c r="BM2" s="214"/>
+      <c r="BN2" s="212" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="216"/>
-      <c r="BP2" s="217"/>
-      <c r="BQ2" s="215" t="s">
+      <c r="BO2" s="213"/>
+      <c r="BP2" s="214"/>
+      <c r="BQ2" s="212" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="216"/>
-      <c r="BS2" s="217"/>
-      <c r="BT2" s="215" t="s">
+      <c r="BR2" s="213"/>
+      <c r="BS2" s="214"/>
+      <c r="BT2" s="212" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="216"/>
-      <c r="BV2" s="217"/>
-      <c r="BW2" s="215" t="s">
+      <c r="BU2" s="213"/>
+      <c r="BV2" s="214"/>
+      <c r="BW2" s="212" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="216"/>
-      <c r="BY2" s="217"/>
-      <c r="BZ2" s="215" t="s">
+      <c r="BX2" s="213"/>
+      <c r="BY2" s="214"/>
+      <c r="BZ2" s="212" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="216"/>
-      <c r="CB2" s="217"/>
-      <c r="CC2" s="215" t="s">
+      <c r="CA2" s="213"/>
+      <c r="CB2" s="214"/>
+      <c r="CC2" s="212" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="216"/>
-      <c r="CE2" s="217"/>
-      <c r="CF2" s="215" t="s">
+      <c r="CD2" s="213"/>
+      <c r="CE2" s="214"/>
+      <c r="CF2" s="212" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="216"/>
-      <c r="CH2" s="217"/>
-      <c r="CI2" s="215" t="s">
+      <c r="CG2" s="213"/>
+      <c r="CH2" s="214"/>
+      <c r="CI2" s="212" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="216"/>
-      <c r="CK2" s="217"/>
-      <c r="CL2" s="215" t="s">
+      <c r="CJ2" s="213"/>
+      <c r="CK2" s="214"/>
+      <c r="CL2" s="212" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="216"/>
-      <c r="CN2" s="217"/>
-      <c r="CO2" s="215" t="s">
+      <c r="CM2" s="213"/>
+      <c r="CN2" s="214"/>
+      <c r="CO2" s="212" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="216"/>
-      <c r="CQ2" s="217"/>
-      <c r="CR2" s="215" t="s">
+      <c r="CP2" s="213"/>
+      <c r="CQ2" s="214"/>
+      <c r="CR2" s="212" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="216"/>
-      <c r="CT2" s="217"/>
-      <c r="CU2" s="215" t="s">
+      <c r="CS2" s="213"/>
+      <c r="CT2" s="214"/>
+      <c r="CU2" s="212" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="216"/>
-      <c r="CW2" s="217"/>
-      <c r="CX2" s="215" t="s">
+      <c r="CV2" s="213"/>
+      <c r="CW2" s="214"/>
+      <c r="CX2" s="212" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="216"/>
-      <c r="CZ2" s="217"/>
-      <c r="DA2" s="215" t="s">
+      <c r="CY2" s="213"/>
+      <c r="CZ2" s="214"/>
+      <c r="DA2" s="212" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="216"/>
-      <c r="DC2" s="217"/>
-      <c r="DD2" s="215" t="s">
+      <c r="DB2" s="213"/>
+      <c r="DC2" s="214"/>
+      <c r="DD2" s="212" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="216"/>
-      <c r="DF2" s="217"/>
-      <c r="DG2" s="215" t="s">
+      <c r="DE2" s="213"/>
+      <c r="DF2" s="214"/>
+      <c r="DG2" s="212" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="216"/>
-      <c r="DI2" s="217"/>
-      <c r="DJ2" s="215" t="s">
+      <c r="DH2" s="213"/>
+      <c r="DI2" s="214"/>
+      <c r="DJ2" s="212" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="216"/>
-      <c r="DL2" s="217"/>
-      <c r="DM2" s="215" t="s">
+      <c r="DK2" s="213"/>
+      <c r="DL2" s="214"/>
+      <c r="DM2" s="212" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="216"/>
-      <c r="DO2" s="217"/>
+      <c r="DN2" s="213"/>
+      <c r="DO2" s="214"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38002,9 +38022,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="223"/>
-      <c r="D3" s="223"/>
-      <c r="E3" s="219"/>
+      <c r="C3" s="219"/>
+      <c r="D3" s="219"/>
+      <c r="E3" s="220"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
       </c>
@@ -43507,7 +43527,7 @@
         <v>0</v>
       </c>
       <c r="CX39" s="73">
-        <f t="shared" ref="CX39:EC39" si="11">SUM(CX4:CX38)</f>
+        <f t="shared" ref="CX39:DO39" si="11">SUM(CX4:CX38)</f>
         <v>0</v>
       </c>
       <c r="CY39" s="73">
@@ -43581,6 +43601,69 @@
     </row>
   </sheetData>
   <mergeCells count="79">
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43597,69 +43680,6 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO38">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -43695,41 +43715,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="233" t="s">
+      <c r="C1" s="236" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="233" t="s">
+      <c r="D1" s="236" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="233" t="s">
+      <c r="E1" s="236" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="224" t="s">
+      <c r="F1" s="227" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="225"/>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
-      <c r="J1" s="225"/>
-      <c r="K1" s="225"/>
-      <c r="L1" s="225"/>
-      <c r="M1" s="225"/>
-      <c r="N1" s="225"/>
-      <c r="O1" s="225"/>
-      <c r="P1" s="225"/>
-      <c r="Q1" s="225"/>
-      <c r="R1" s="225"/>
-      <c r="S1" s="225"/>
-      <c r="T1" s="225"/>
-      <c r="U1" s="225"/>
-      <c r="V1" s="225"/>
-      <c r="W1" s="225"/>
-      <c r="X1" s="225"/>
-      <c r="Y1" s="225"/>
-      <c r="Z1" s="225"/>
-      <c r="AA1" s="225"/>
-      <c r="AB1" s="225"/>
-      <c r="AC1" s="226"/>
+      <c r="G1" s="228"/>
+      <c r="H1" s="228"/>
+      <c r="I1" s="228"/>
+      <c r="J1" s="228"/>
+      <c r="K1" s="228"/>
+      <c r="L1" s="228"/>
+      <c r="M1" s="228"/>
+      <c r="N1" s="228"/>
+      <c r="O1" s="228"/>
+      <c r="P1" s="228"/>
+      <c r="Q1" s="228"/>
+      <c r="R1" s="228"/>
+      <c r="S1" s="228"/>
+      <c r="T1" s="228"/>
+      <c r="U1" s="228"/>
+      <c r="V1" s="228"/>
+      <c r="W1" s="228"/>
+      <c r="X1" s="228"/>
+      <c r="Y1" s="228"/>
+      <c r="Z1" s="228"/>
+      <c r="AA1" s="228"/>
+      <c r="AB1" s="228"/>
+      <c r="AC1" s="229"/>
       <c r="AD1" s="239" t="s">
         <v>281</v>
       </c>
@@ -43738,79 +43758,79 @@
       <c r="AG1" s="240"/>
       <c r="AH1" s="240"/>
       <c r="AI1" s="241"/>
-      <c r="AJ1" s="224" t="s">
+      <c r="AJ1" s="227" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="225"/>
-      <c r="AL1" s="225"/>
-      <c r="AM1" s="225"/>
-      <c r="AN1" s="225"/>
-      <c r="AO1" s="226"/>
-      <c r="AP1" s="227" t="s">
+      <c r="AK1" s="228"/>
+      <c r="AL1" s="228"/>
+      <c r="AM1" s="228"/>
+      <c r="AN1" s="228"/>
+      <c r="AO1" s="229"/>
+      <c r="AP1" s="230" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="228"/>
-      <c r="AR1" s="228"/>
-      <c r="AS1" s="228"/>
-      <c r="AT1" s="228"/>
-      <c r="AU1" s="229"/>
-      <c r="AV1" s="230" t="s">
+      <c r="AQ1" s="231"/>
+      <c r="AR1" s="231"/>
+      <c r="AS1" s="231"/>
+      <c r="AT1" s="231"/>
+      <c r="AU1" s="232"/>
+      <c r="AV1" s="233" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="231"/>
-      <c r="AX1" s="232"/>
+      <c r="AW1" s="234"/>
+      <c r="AX1" s="235"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="234"/>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="237"/>
-      <c r="H2" s="238"/>
-      <c r="I2" s="236"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="236"/>
-      <c r="M2" s="237"/>
-      <c r="N2" s="238"/>
-      <c r="O2" s="236"/>
-      <c r="P2" s="237"/>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="236"/>
-      <c r="S2" s="237"/>
-      <c r="T2" s="238"/>
-      <c r="U2" s="236"/>
-      <c r="V2" s="237"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="236"/>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="238"/>
-      <c r="AA2" s="236"/>
-      <c r="AB2" s="237"/>
-      <c r="AC2" s="237"/>
-      <c r="AD2" s="236"/>
-      <c r="AE2" s="237"/>
-      <c r="AF2" s="238"/>
-      <c r="AG2" s="236"/>
-      <c r="AH2" s="237"/>
-      <c r="AI2" s="238"/>
-      <c r="AJ2" s="236"/>
-      <c r="AK2" s="237"/>
-      <c r="AL2" s="238"/>
-      <c r="AM2" s="236"/>
-      <c r="AN2" s="237"/>
-      <c r="AO2" s="238"/>
-      <c r="AP2" s="236"/>
-      <c r="AQ2" s="237"/>
-      <c r="AR2" s="238"/>
-      <c r="AS2" s="236"/>
-      <c r="AT2" s="237"/>
-      <c r="AU2" s="238"/>
-      <c r="AV2" s="236"/>
-      <c r="AW2" s="237"/>
-      <c r="AX2" s="238"/>
+      <c r="C2" s="237"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="224"/>
+      <c r="G2" s="225"/>
+      <c r="H2" s="226"/>
+      <c r="I2" s="224"/>
+      <c r="J2" s="225"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="224"/>
+      <c r="M2" s="225"/>
+      <c r="N2" s="226"/>
+      <c r="O2" s="224"/>
+      <c r="P2" s="225"/>
+      <c r="Q2" s="226"/>
+      <c r="R2" s="224"/>
+      <c r="S2" s="225"/>
+      <c r="T2" s="226"/>
+      <c r="U2" s="224"/>
+      <c r="V2" s="225"/>
+      <c r="W2" s="226"/>
+      <c r="X2" s="224"/>
+      <c r="Y2" s="225"/>
+      <c r="Z2" s="226"/>
+      <c r="AA2" s="224"/>
+      <c r="AB2" s="225"/>
+      <c r="AC2" s="225"/>
+      <c r="AD2" s="224"/>
+      <c r="AE2" s="225"/>
+      <c r="AF2" s="226"/>
+      <c r="AG2" s="224"/>
+      <c r="AH2" s="225"/>
+      <c r="AI2" s="226"/>
+      <c r="AJ2" s="224"/>
+      <c r="AK2" s="225"/>
+      <c r="AL2" s="226"/>
+      <c r="AM2" s="224"/>
+      <c r="AN2" s="225"/>
+      <c r="AO2" s="226"/>
+      <c r="AP2" s="224"/>
+      <c r="AQ2" s="225"/>
+      <c r="AR2" s="226"/>
+      <c r="AS2" s="224"/>
+      <c r="AT2" s="225"/>
+      <c r="AU2" s="226"/>
+      <c r="AV2" s="224"/>
+      <c r="AW2" s="225"/>
+      <c r="AX2" s="226"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -43819,9 +43839,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="235"/>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
+      <c r="C3" s="238"/>
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
       <c r="F3" s="170" t="s">
         <v>393</v>
       </c>
@@ -46417,13 +46437,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46440,6 +46453,13 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW32">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46474,70 +46494,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="233" t="s">
+      <c r="C1" s="236" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="233" t="s">
+      <c r="D1" s="236" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="233" t="s">
+      <c r="E1" s="236" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="273" t="s">
+      <c r="F1" s="266" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="274"/>
-      <c r="H1" s="275"/>
-      <c r="I1" s="276" t="s">
+      <c r="G1" s="267"/>
+      <c r="H1" s="268"/>
+      <c r="I1" s="269" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="277"/>
-      <c r="K1" s="278"/>
-      <c r="L1" s="243" t="s">
+      <c r="J1" s="270"/>
+      <c r="K1" s="271"/>
+      <c r="L1" s="273" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="244"/>
-      <c r="N1" s="245"/>
-      <c r="O1" s="246" t="s">
+      <c r="M1" s="274"/>
+      <c r="N1" s="275"/>
+      <c r="O1" s="276" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="247"/>
-      <c r="Q1" s="248"/>
-      <c r="R1" s="249" t="s">
+      <c r="P1" s="277"/>
+      <c r="Q1" s="278"/>
+      <c r="R1" s="242" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="250"/>
-      <c r="T1" s="251"/>
-      <c r="U1" s="252" t="s">
+      <c r="S1" s="243"/>
+      <c r="T1" s="244"/>
+      <c r="U1" s="245" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="253"/>
-      <c r="W1" s="254"/>
+      <c r="V1" s="246"/>
+      <c r="W1" s="247"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="234"/>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="255"/>
-      <c r="G2" s="256"/>
-      <c r="H2" s="257"/>
-      <c r="I2" s="270"/>
-      <c r="J2" s="271"/>
-      <c r="K2" s="272"/>
-      <c r="L2" s="267"/>
-      <c r="M2" s="268"/>
-      <c r="N2" s="269"/>
-      <c r="O2" s="264"/>
-      <c r="P2" s="265"/>
-      <c r="Q2" s="266"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="262"/>
-      <c r="T2" s="263"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="259"/>
-      <c r="W2" s="260"/>
+      <c r="C2" s="237"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="264"/>
+      <c r="K2" s="265"/>
+      <c r="L2" s="260"/>
+      <c r="M2" s="261"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="257"/>
+      <c r="P2" s="258"/>
+      <c r="Q2" s="259"/>
+      <c r="R2" s="254"/>
+      <c r="S2" s="255"/>
+      <c r="T2" s="256"/>
+      <c r="U2" s="251"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="253"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46546,9 +46566,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="242"/>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
+      <c r="C3" s="272"/>
+      <c r="D3" s="272"/>
+      <c r="E3" s="272"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -48010,6 +48030,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -48020,11 +48045,6 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -55031,72 +55051,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="233" t="s">
+      <c r="C1" s="236" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="233" t="s">
+      <c r="D1" s="236" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="233" t="s">
+      <c r="E1" s="236" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="273" t="s">
+      <c r="F1" s="266" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="274"/>
-      <c r="H1" s="275"/>
-      <c r="I1" s="276" t="s">
+      <c r="G1" s="267"/>
+      <c r="H1" s="268"/>
+      <c r="I1" s="269" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="277"/>
-      <c r="K1" s="278"/>
-      <c r="L1" s="243" t="s">
+      <c r="J1" s="270"/>
+      <c r="K1" s="271"/>
+      <c r="L1" s="273" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="244"/>
-      <c r="N1" s="245"/>
-      <c r="O1" s="246" t="s">
+      <c r="M1" s="274"/>
+      <c r="N1" s="275"/>
+      <c r="O1" s="276" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="247"/>
-      <c r="Q1" s="248"/>
-      <c r="R1" s="249" t="s">
+      <c r="P1" s="277"/>
+      <c r="Q1" s="278"/>
+      <c r="R1" s="242" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="250"/>
-      <c r="T1" s="251"/>
-      <c r="U1" s="252" t="s">
+      <c r="S1" s="243"/>
+      <c r="T1" s="244"/>
+      <c r="U1" s="245" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="253"/>
-      <c r="W1" s="254"/>
+      <c r="V1" s="246"/>
+      <c r="W1" s="247"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="234"/>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="255" t="s">
+      <c r="C2" s="237"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="248" t="s">
         <v>438</v>
       </c>
-      <c r="G2" s="256"/>
-      <c r="H2" s="257"/>
-      <c r="I2" s="270"/>
-      <c r="J2" s="271"/>
-      <c r="K2" s="272"/>
-      <c r="L2" s="267"/>
-      <c r="M2" s="268"/>
-      <c r="N2" s="269"/>
-      <c r="O2" s="264"/>
-      <c r="P2" s="265"/>
-      <c r="Q2" s="266"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="262"/>
-      <c r="T2" s="263"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="259"/>
-      <c r="W2" s="260"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="264"/>
+      <c r="K2" s="265"/>
+      <c r="L2" s="260"/>
+      <c r="M2" s="261"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="257"/>
+      <c r="P2" s="258"/>
+      <c r="Q2" s="259"/>
+      <c r="R2" s="254"/>
+      <c r="S2" s="255"/>
+      <c r="T2" s="256"/>
+      <c r="U2" s="251"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="253"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -55105,9 +55125,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="242"/>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
+      <c r="C3" s="272"/>
+      <c r="D3" s="272"/>
+      <c r="E3" s="272"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -56569,11 +56589,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -56584,6 +56599,11 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -57090,51 +57110,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="301" t="s">
+      <c r="C1" s="282" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="302"/>
-      <c r="E1" s="302"/>
-      <c r="F1" s="302"/>
-      <c r="G1" s="302"/>
-      <c r="H1" s="302"/>
-      <c r="I1" s="303"/>
+      <c r="D1" s="283"/>
+      <c r="E1" s="283"/>
+      <c r="F1" s="283"/>
+      <c r="G1" s="283"/>
+      <c r="H1" s="283"/>
+      <c r="I1" s="284"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="281" t="s">
+      <c r="L1" s="306" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="286"/>
-      <c r="N1" s="286"/>
-      <c r="O1" s="286"/>
-      <c r="P1" s="286"/>
-      <c r="Q1" s="286"/>
-      <c r="R1" s="286"/>
-      <c r="S1" s="286"/>
-      <c r="T1" s="286"/>
-      <c r="U1" s="286"/>
-      <c r="V1" s="286"/>
-      <c r="W1" s="286"/>
-      <c r="X1" s="286"/>
-      <c r="Y1" s="286"/>
-      <c r="Z1" s="286"/>
-      <c r="AA1" s="286"/>
-      <c r="AB1" s="286"/>
-      <c r="AC1" s="286"/>
-      <c r="AD1" s="286"/>
-      <c r="AE1" s="286"/>
-      <c r="AF1" s="286"/>
-      <c r="AG1" s="287"/>
-      <c r="AH1" s="281" t="s">
+      <c r="M1" s="311"/>
+      <c r="N1" s="311"/>
+      <c r="O1" s="311"/>
+      <c r="P1" s="311"/>
+      <c r="Q1" s="311"/>
+      <c r="R1" s="311"/>
+      <c r="S1" s="311"/>
+      <c r="T1" s="311"/>
+      <c r="U1" s="311"/>
+      <c r="V1" s="311"/>
+      <c r="W1" s="311"/>
+      <c r="X1" s="311"/>
+      <c r="Y1" s="311"/>
+      <c r="Z1" s="311"/>
+      <c r="AA1" s="311"/>
+      <c r="AB1" s="311"/>
+      <c r="AC1" s="311"/>
+      <c r="AD1" s="311"/>
+      <c r="AE1" s="311"/>
+      <c r="AF1" s="311"/>
+      <c r="AG1" s="312"/>
+      <c r="AH1" s="306" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="282"/>
-      <c r="AJ1" s="282"/>
-      <c r="AK1" s="283"/>
+      <c r="AI1" s="307"/>
+      <c r="AJ1" s="307"/>
+      <c r="AK1" s="308"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -62334,15 +62354,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="288" t="s">
+      <c r="K80" s="313" t="s">
         <v>442</v>
       </c>
-      <c r="L80" s="289"/>
-      <c r="M80" s="290"/>
+      <c r="L80" s="314"/>
+      <c r="M80" s="315"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="284"/>
-      <c r="X80" s="284"/>
+      <c r="W80" s="309"/>
+      <c r="X80" s="309"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -62392,15 +62412,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="291"/>
-      <c r="L81" s="292"/>
-      <c r="M81" s="293"/>
+      <c r="K81" s="316"/>
+      <c r="L81" s="317"/>
+      <c r="M81" s="318"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="284" t="s">
+      <c r="W81" s="309" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="284"/>
+      <c r="X81" s="309"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62456,17 +62476,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="294" t="s">
+      <c r="K82" s="319" t="s">
         <v>443</v>
       </c>
-      <c r="L82" s="295"/>
-      <c r="M82" s="296"/>
+      <c r="L82" s="320"/>
+      <c r="M82" s="321"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="284" t="s">
+      <c r="W82" s="309" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="284"/>
+      <c r="X82" s="309"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62522,17 +62542,17 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="297" t="s">
+      <c r="K83" s="322" t="s">
         <v>444</v>
       </c>
-      <c r="L83" s="298"/>
-      <c r="M83" s="299"/>
+      <c r="L83" s="323"/>
+      <c r="M83" s="324"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="285" t="s">
+      <c r="W83" s="310" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="285"/>
+      <c r="X83" s="310"/>
       <c r="Y83" s="196">
         <v>220</v>
       </c>
@@ -62585,15 +62605,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="316" t="s">
+      <c r="K84" s="297" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="317"/>
-      <c r="M84" s="318"/>
+      <c r="L84" s="298"/>
+      <c r="M84" s="299"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="300"/>
-      <c r="X84" s="300"/>
+      <c r="W84" s="281"/>
+      <c r="X84" s="281"/>
       <c r="Y84" s="198"/>
       <c r="Z84" s="198"/>
       <c r="AA84" s="198"/>
@@ -62631,9 +62651,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="319"/>
-      <c r="L85" s="320"/>
-      <c r="M85" s="321"/>
+      <c r="K85" s="300"/>
+      <c r="L85" s="301"/>
+      <c r="M85" s="302"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -62667,9 +62687,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="319"/>
-      <c r="L86" s="320"/>
-      <c r="M86" s="321"/>
+      <c r="K86" s="300"/>
+      <c r="L86" s="301"/>
+      <c r="M86" s="302"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -62703,9 +62723,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="319"/>
-      <c r="L87" s="320"/>
-      <c r="M87" s="321"/>
+      <c r="K87" s="300"/>
+      <c r="L87" s="301"/>
+      <c r="M87" s="302"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -62739,9 +62759,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="319"/>
-      <c r="L88" s="320"/>
-      <c r="M88" s="321"/>
+      <c r="K88" s="300"/>
+      <c r="L88" s="301"/>
+      <c r="M88" s="302"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -62775,9 +62795,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="319"/>
-      <c r="L89" s="320"/>
-      <c r="M89" s="321"/>
+      <c r="K89" s="300"/>
+      <c r="L89" s="301"/>
+      <c r="M89" s="302"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -62811,9 +62831,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="319"/>
-      <c r="L90" s="320"/>
-      <c r="M90" s="321"/>
+      <c r="K90" s="300"/>
+      <c r="L90" s="301"/>
+      <c r="M90" s="302"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -62847,9 +62867,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="319"/>
-      <c r="L91" s="320"/>
-      <c r="M91" s="321"/>
+      <c r="K91" s="300"/>
+      <c r="L91" s="301"/>
+      <c r="M91" s="302"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -62883,9 +62903,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="319"/>
-      <c r="L92" s="320"/>
-      <c r="M92" s="321"/>
+      <c r="K92" s="300"/>
+      <c r="L92" s="301"/>
+      <c r="M92" s="302"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -62919,9 +62939,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="319"/>
-      <c r="L93" s="320"/>
-      <c r="M93" s="321"/>
+      <c r="K93" s="300"/>
+      <c r="L93" s="301"/>
+      <c r="M93" s="302"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -62955,9 +62975,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="319"/>
-      <c r="L94" s="320"/>
-      <c r="M94" s="321"/>
+      <c r="K94" s="300"/>
+      <c r="L94" s="301"/>
+      <c r="M94" s="302"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -62991,9 +63011,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="319"/>
-      <c r="L95" s="320"/>
-      <c r="M95" s="321"/>
+      <c r="K95" s="300"/>
+      <c r="L95" s="301"/>
+      <c r="M95" s="302"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -63027,9 +63047,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="319"/>
-      <c r="L96" s="320"/>
-      <c r="M96" s="321"/>
+      <c r="K96" s="300"/>
+      <c r="L96" s="301"/>
+      <c r="M96" s="302"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -63063,9 +63083,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="319"/>
-      <c r="L97" s="320"/>
-      <c r="M97" s="321"/>
+      <c r="K97" s="300"/>
+      <c r="L97" s="301"/>
+      <c r="M97" s="302"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -63099,9 +63119,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="319"/>
-      <c r="L98" s="320"/>
-      <c r="M98" s="321"/>
+      <c r="K98" s="300"/>
+      <c r="L98" s="301"/>
+      <c r="M98" s="302"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -63135,9 +63155,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="319"/>
-      <c r="L99" s="320"/>
-      <c r="M99" s="321"/>
+      <c r="K99" s="300"/>
+      <c r="L99" s="301"/>
+      <c r="M99" s="302"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -63171,9 +63191,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="319"/>
-      <c r="L100" s="320"/>
-      <c r="M100" s="321"/>
+      <c r="K100" s="300"/>
+      <c r="L100" s="301"/>
+      <c r="M100" s="302"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -63207,9 +63227,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="319"/>
-      <c r="L101" s="320"/>
-      <c r="M101" s="321"/>
+      <c r="K101" s="300"/>
+      <c r="L101" s="301"/>
+      <c r="M101" s="302"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -63243,9 +63263,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="319"/>
-      <c r="L102" s="320"/>
-      <c r="M102" s="321"/>
+      <c r="K102" s="300"/>
+      <c r="L102" s="301"/>
+      <c r="M102" s="302"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -63279,9 +63299,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="319"/>
-      <c r="L103" s="320"/>
-      <c r="M103" s="321"/>
+      <c r="K103" s="300"/>
+      <c r="L103" s="301"/>
+      <c r="M103" s="302"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -63315,9 +63335,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="319"/>
-      <c r="L104" s="320"/>
-      <c r="M104" s="321"/>
+      <c r="K104" s="300"/>
+      <c r="L104" s="301"/>
+      <c r="M104" s="302"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -63351,9 +63371,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="322"/>
-      <c r="L105" s="323"/>
-      <c r="M105" s="324"/>
+      <c r="K105" s="303"/>
+      <c r="L105" s="304"/>
+      <c r="M105" s="305"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -63387,11 +63407,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="313" t="s">
+      <c r="K106" s="294" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="314"/>
-      <c r="M106" s="315"/>
+      <c r="L106" s="295"/>
+      <c r="M106" s="296"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63425,11 +63445,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="313" t="s">
+      <c r="K107" s="294" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="314"/>
-      <c r="M107" s="315"/>
+      <c r="L107" s="295"/>
+      <c r="M107" s="296"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63463,11 +63483,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="304" t="s">
+      <c r="K108" s="285" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="305"/>
-      <c r="M108" s="306"/>
+      <c r="L108" s="286"/>
+      <c r="M108" s="287"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63501,9 +63521,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="307"/>
-      <c r="L109" s="308"/>
-      <c r="M109" s="309"/>
+      <c r="K109" s="288"/>
+      <c r="L109" s="289"/>
+      <c r="M109" s="290"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -63537,9 +63557,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="307"/>
-      <c r="L110" s="308"/>
-      <c r="M110" s="309"/>
+      <c r="K110" s="288"/>
+      <c r="L110" s="289"/>
+      <c r="M110" s="290"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -63573,9 +63593,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="307"/>
-      <c r="L111" s="308"/>
-      <c r="M111" s="309"/>
+      <c r="K111" s="288"/>
+      <c r="L111" s="289"/>
+      <c r="M111" s="290"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -63613,9 +63633,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="307"/>
-      <c r="L112" s="308"/>
-      <c r="M112" s="309"/>
+      <c r="K112" s="288"/>
+      <c r="L112" s="289"/>
+      <c r="M112" s="290"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="156" t="s">
@@ -63651,9 +63671,9 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="310"/>
-      <c r="L113" s="311"/>
-      <c r="M113" s="312"/>
+      <c r="K113" s="291"/>
+      <c r="L113" s="292"/>
+      <c r="M113" s="293"/>
     </row>
     <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="93" t="s">
@@ -63693,12 +63713,6 @@
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
-    <mergeCell ref="W84:X84"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K108:M113"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
     <mergeCell ref="W81:X81"/>
@@ -63708,6 +63722,12 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
+    <mergeCell ref="W84:X84"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K108:M113"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -65740,7 +65760,7 @@
       <c r="U2" s="203"/>
       <c r="V2" s="203"/>
       <c r="Z2" s="125">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -65806,6 +65826,9 @@
       <c r="V3" s="8" t="s">
         <v>395</v>
       </c>
+      <c r="W3" s="329" t="s">
+        <v>446</v>
+      </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
@@ -66925,7 +66948,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>15</v>
       </c>
@@ -67011,7 +67034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -67097,7 +67120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>20</v>
       </c>
@@ -67183,7 +67206,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="56">
         <v>22</v>
       </c>
@@ -67193,7 +67216,7 @@
       <c r="C20" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="37" t="s">
         <v>263</v>
       </c>
       <c r="E20" s="6">
@@ -67268,8 +67291,11 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W20" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>23</v>
       </c>
@@ -67355,7 +67381,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>29</v>
       </c>
@@ -67441,7 +67467,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>30</v>
       </c>
@@ -67527,7 +67553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>33</v>
       </c>
@@ -67613,7 +67639,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>35</v>
       </c>
@@ -67699,7 +67725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>36</v>
       </c>
@@ -67785,7 +67811,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>39</v>
       </c>
@@ -67871,7 +67897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="56">
         <v>40</v>
       </c>
@@ -67957,7 +67983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>41</v>
       </c>
@@ -68043,7 +68069,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="56">
         <v>43</v>
       </c>
@@ -68129,7 +68155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="28">
         <v>44</v>
       </c>
@@ -68215,7 +68241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>46</v>
       </c>
@@ -68225,7 +68251,7 @@
       <c r="C32" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="D32" s="57" t="s">
+      <c r="D32" s="34" t="s">
         <v>298</v>
       </c>
       <c r="E32" s="6">
@@ -68299,6 +68325,9 @@
       <c r="V32" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
+      </c>
+      <c r="W32" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8046" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{960EF123-6F14-49C1-99E0-87E6DA88490C}"/>
+  <xr:revisionPtr revIDLastSave="8123" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C897D48-7673-454A-A9DC-12BC6684119A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="19" state="hidden" r:id="rId1"/>
@@ -36,11 +36,12 @@
     <sheet name="Other (CS)" sheetId="11" r:id="rId21"/>
     <sheet name="Season Breakdown" sheetId="21" r:id="rId22"/>
     <sheet name="Match" sheetId="31" r:id="rId23"/>
-    <sheet name="All-time records" sheetId="4" r:id="rId24"/>
+    <sheet name="Ratings" sheetId="32" r:id="rId24"/>
+    <sheet name="All-time records" sheetId="4" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'#'!$A$5:$BG$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'All-time records'!$H$2:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'All-time records'!$H$2:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Apps &amp; Goals'!$A$3:$U$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Apps &amp; Goals 16-17'!$A$3:$O$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Apps &amp; Goals 17-18'!$A$3:$O$38</definedName>
@@ -79,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2215" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2261" uniqueCount="476">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -1424,13 +1425,98 @@
   <si>
     <t>Y</t>
   </si>
+  <si>
+    <t>LB</t>
+  </si>
+  <si>
+    <t>CB</t>
+  </si>
+  <si>
+    <t>RB</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>CM</t>
+  </si>
+  <si>
+    <t>CAM</t>
+  </si>
+  <si>
+    <t>LW</t>
+  </si>
+  <si>
+    <t>RW</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>Raya</t>
+  </si>
+  <si>
+    <t>Calafiori</t>
+  </si>
+  <si>
+    <t>Gabriel</t>
+  </si>
+  <si>
+    <t>Mosquera</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>Lewis-Skelly</t>
+  </si>
+  <si>
+    <t>Rice</t>
+  </si>
+  <si>
+    <t>Odegaard</t>
+  </si>
+  <si>
+    <t>Tzolis</t>
+  </si>
+  <si>
+    <t>Saka</t>
+  </si>
+  <si>
+    <t>Havertz</t>
+  </si>
+  <si>
+    <t>Sub</t>
+  </si>
+  <si>
+    <t>Eze</t>
+  </si>
+  <si>
+    <t>Subbed</t>
+  </si>
+  <si>
+    <t>Merino</t>
+  </si>
+  <si>
+    <t>Guimares</t>
+  </si>
+  <si>
+    <t>Konsa</t>
+  </si>
+  <si>
+    <t>Zubimendi</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="31" x14ac:knownFonts="1">
     <font>
@@ -2551,7 +2637,7 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="330">
+  <cellXfs count="331">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2936,6 +3022,9 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2972,6 +3061,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2981,19 +3079,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
@@ -3008,14 +3094,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3053,6 +3133,15 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3060,6 +3149,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3152,31 +3262,67 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3254,63 +3400,6 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3321,9 +3410,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -6379,7 +6466,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0E95CEF5-4DFF-4531-B9FA-5BF1F4D0A289}" type="CELLRANGE">
+                    <a:fld id="{A8D9D3BA-55AE-4E33-9A27-93FBD8900B25}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6413,7 +6500,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FFE71023-5A6A-462F-B2C5-299D5C2A611B}" type="CELLRANGE">
+                    <a:fld id="{447C6899-1E49-4519-9DEE-898B6FC7AD42}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6447,7 +6534,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3E800CC7-2B1B-4AD5-A286-B7B3FB6F1B8B}" type="CELLRANGE">
+                    <a:fld id="{ECE13C4D-C703-4B20-A493-FD96A62BE61E}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6481,7 +6568,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6E9CC1B3-134A-4A3E-80A0-41ED461374DF}" type="CELLRANGE">
+                    <a:fld id="{EB80AA49-1910-4DD3-A68C-486F41E7E192}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6515,7 +6602,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E250E64D-61FD-4BD9-A1D8-6F7E17452066}" type="CELLRANGE">
+                    <a:fld id="{6ED82E4F-615F-469A-9508-59618FF011F8}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6549,7 +6636,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{24BA7CA3-2D8F-4B81-8450-9EB351773315}" type="CELLRANGE">
+                    <a:fld id="{71019908-35E2-4249-B5A8-3A80F8058B84}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6583,7 +6670,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BD60DB80-C7F6-40E7-9AC8-EEB785EEAE51}" type="CELLRANGE">
+                    <a:fld id="{BEA9914C-33C1-4158-9584-0A264933B1B3}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6617,7 +6704,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6ED6A944-90CF-40F4-BF6F-D19BE1B1D046}" type="CELLRANGE">
+                    <a:fld id="{168F9F10-017C-4B64-9313-5DCD9C998FFD}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6651,7 +6738,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{85660B1E-F961-4DC7-9E74-900588624100}" type="CELLRANGE">
+                    <a:fld id="{8790A575-A1D5-47AB-B9A7-B5FAEC9F5706}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6685,7 +6772,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AE933609-8BB6-411D-80D5-B075312E0B65}" type="CELLRANGE">
+                    <a:fld id="{2BE6183B-6D80-481E-8D98-B8FDB68F7379}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6719,7 +6806,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D8C51D39-1E7A-4BF2-9945-FA97A82530C4}" type="CELLRANGE">
+                    <a:fld id="{6A2C9AF7-A3C0-42DF-96A1-2B283EFE6FB6}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6753,7 +6840,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C7B15057-2DAD-4445-BA2E-CC653EB56EEB}" type="CELLRANGE">
+                    <a:fld id="{0722E446-40EB-4925-B2A7-D19E16AE3963}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6802,7 +6889,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{D4F95C7B-DFFB-4292-8B9B-BD0418395BFF}" type="CELLRANGE">
+                    <a:fld id="{AEFBB2BC-4D06-4DC2-B5EE-90C427AB85EE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6861,7 +6948,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7E184E06-D9F4-4FEB-9C72-4F1756B5B22A}" type="CELLRANGE">
+                    <a:fld id="{CA76E409-3428-48F8-B3D2-A5C11E8512DC}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6895,7 +6982,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8F215157-10C5-499D-BB8E-65613A1DF761}" type="CELLRANGE">
+                    <a:fld id="{C9FB726D-2015-4CFD-8CDE-C583AC6562DF}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6929,7 +7016,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{94290222-0D1F-4E70-AF99-9DBC6A59407B}" type="CELLRANGE">
+                    <a:fld id="{EFA745E7-2BD8-432E-BC17-F42EA6E86FB8}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6963,7 +7050,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EC7DFA01-2001-4821-B728-8A5E87584B17}" type="CELLRANGE">
+                    <a:fld id="{22C6CFC9-B2B2-43CB-A3A7-83B6D0AA7B6A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6997,7 +7084,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{827262D4-A65C-430C-92C8-C26552E0C43B}" type="CELLRANGE">
+                    <a:fld id="{E78E07B5-1218-496D-85AD-A530619752AE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14148,30 +14235,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="210" t="s">
+      <c r="C1" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="210"/>
-      <c r="E1" s="211" t="s">
+      <c r="D1" s="211"/>
+      <c r="E1" s="212" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="211"/>
-      <c r="G1" s="210" t="s">
+      <c r="F1" s="212"/>
+      <c r="G1" s="211" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="210"/>
-      <c r="I1" s="211" t="s">
+      <c r="H1" s="211"/>
+      <c r="I1" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="211"/>
-      <c r="K1" s="210" t="s">
+      <c r="J1" s="212"/>
+      <c r="K1" s="211" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="210"/>
-      <c r="M1" s="208" t="s">
+      <c r="L1" s="211"/>
+      <c r="M1" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="209"/>
+      <c r="N1" s="210"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15878,30 +15965,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="210" t="s">
+      <c r="C2" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="210"/>
-      <c r="E2" s="211" t="s">
+      <c r="D2" s="211"/>
+      <c r="E2" s="212" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="211"/>
-      <c r="G2" s="210" t="s">
+      <c r="F2" s="212"/>
+      <c r="G2" s="211" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="210"/>
-      <c r="I2" s="211" t="s">
+      <c r="H2" s="211"/>
+      <c r="I2" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="211"/>
-      <c r="K2" s="210" t="s">
+      <c r="J2" s="212"/>
+      <c r="K2" s="211" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="210"/>
-      <c r="M2" s="203" t="s">
+      <c r="L2" s="211"/>
+      <c r="M2" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="203"/>
+      <c r="N2" s="204"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17705,30 +17792,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="210" t="s">
+      <c r="C2" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="210"/>
-      <c r="E2" s="211" t="s">
+      <c r="D2" s="211"/>
+      <c r="E2" s="212" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="211"/>
-      <c r="G2" s="210" t="s">
+      <c r="F2" s="212"/>
+      <c r="G2" s="211" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="210"/>
-      <c r="I2" s="211" t="s">
+      <c r="H2" s="211"/>
+      <c r="I2" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="211"/>
-      <c r="K2" s="210" t="s">
+      <c r="J2" s="212"/>
+      <c r="K2" s="211" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="210"/>
-      <c r="M2" s="203" t="s">
+      <c r="L2" s="211"/>
+      <c r="M2" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="203"/>
+      <c r="N2" s="204"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19395,30 +19482,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="210" t="s">
+      <c r="C2" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="210"/>
-      <c r="E2" s="211" t="s">
+      <c r="D2" s="211"/>
+      <c r="E2" s="212" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="211"/>
-      <c r="G2" s="210" t="s">
+      <c r="F2" s="212"/>
+      <c r="G2" s="211" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="210"/>
-      <c r="I2" s="211" t="s">
+      <c r="H2" s="211"/>
+      <c r="I2" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="211"/>
-      <c r="K2" s="210" t="s">
+      <c r="J2" s="212"/>
+      <c r="K2" s="211" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="210"/>
-      <c r="M2" s="203" t="s">
+      <c r="L2" s="211"/>
+      <c r="M2" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="203"/>
+      <c r="N2" s="204"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21221,30 +21308,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="210" t="s">
+      <c r="C2" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="210"/>
-      <c r="E2" s="211" t="s">
+      <c r="D2" s="211"/>
+      <c r="E2" s="212" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="211"/>
-      <c r="G2" s="210" t="s">
+      <c r="F2" s="212"/>
+      <c r="G2" s="211" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="210"/>
-      <c r="I2" s="211" t="s">
+      <c r="H2" s="211"/>
+      <c r="I2" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="211"/>
-      <c r="K2" s="210" t="s">
+      <c r="J2" s="212"/>
+      <c r="K2" s="211" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="210"/>
-      <c r="M2" s="203" t="s">
+      <c r="L2" s="211"/>
+      <c r="M2" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="203"/>
+      <c r="N2" s="204"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23093,36 +23180,36 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="200" t="s">
+      <c r="C2" s="201" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="201"/>
-      <c r="E2" s="202"/>
-      <c r="F2" s="205" t="s">
+      <c r="D2" s="202"/>
+      <c r="E2" s="203"/>
+      <c r="F2" s="206" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="206"/>
-      <c r="H2" s="207"/>
-      <c r="I2" s="200" t="s">
+      <c r="G2" s="207"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="201" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="201"/>
-      <c r="K2" s="202"/>
-      <c r="L2" s="205" t="s">
+      <c r="J2" s="202"/>
+      <c r="K2" s="203"/>
+      <c r="L2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="207"/>
-      <c r="O2" s="200" t="s">
+      <c r="M2" s="207"/>
+      <c r="N2" s="208"/>
+      <c r="O2" s="201" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="201"/>
-      <c r="Q2" s="202"/>
-      <c r="R2" s="203" t="s">
+      <c r="P2" s="202"/>
+      <c r="Q2" s="203"/>
+      <c r="R2" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="203"/>
-      <c r="T2" s="203"/>
+      <c r="S2" s="204"/>
+      <c r="T2" s="204"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -26062,36 +26149,36 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="200" t="s">
+      <c r="E1" s="201" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="201"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="205" t="s">
+      <c r="F1" s="202"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="206" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="206"/>
-      <c r="J1" s="207"/>
-      <c r="K1" s="200" t="s">
+      <c r="I1" s="207"/>
+      <c r="J1" s="208"/>
+      <c r="K1" s="201" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="201"/>
-      <c r="M1" s="202"/>
-      <c r="N1" s="205" t="s">
+      <c r="L1" s="202"/>
+      <c r="M1" s="203"/>
+      <c r="N1" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="206"/>
-      <c r="P1" s="207"/>
-      <c r="Q1" s="200" t="s">
+      <c r="O1" s="207"/>
+      <c r="P1" s="208"/>
+      <c r="Q1" s="201" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="201"/>
-      <c r="S1" s="202"/>
-      <c r="T1" s="203" t="s">
+      <c r="R1" s="202"/>
+      <c r="S1" s="203"/>
+      <c r="T1" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="203"/>
-      <c r="V1" s="203"/>
+      <c r="U1" s="204"/>
+      <c r="V1" s="204"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37621,399 +37708,399 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="215">
-        <v>1</v>
-      </c>
-      <c r="G1" s="216"/>
-      <c r="H1" s="217"/>
-      <c r="I1" s="215">
+      <c r="F1" s="213">
+        <v>1</v>
+      </c>
+      <c r="G1" s="214"/>
+      <c r="H1" s="215"/>
+      <c r="I1" s="213">
         <v>2</v>
       </c>
-      <c r="J1" s="216"/>
-      <c r="K1" s="217"/>
-      <c r="L1" s="215">
-        <v>3</v>
-      </c>
-      <c r="M1" s="216"/>
-      <c r="N1" s="217"/>
-      <c r="O1" s="215">
+      <c r="J1" s="214"/>
+      <c r="K1" s="215"/>
+      <c r="L1" s="213">
+        <v>3</v>
+      </c>
+      <c r="M1" s="214"/>
+      <c r="N1" s="215"/>
+      <c r="O1" s="213">
         <v>4</v>
       </c>
-      <c r="P1" s="216"/>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="215">
+      <c r="P1" s="214"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="213">
         <v>5</v>
       </c>
-      <c r="S1" s="216"/>
-      <c r="T1" s="217"/>
-      <c r="U1" s="215">
+      <c r="S1" s="214"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="213">
         <v>6</v>
       </c>
-      <c r="V1" s="216"/>
-      <c r="W1" s="217"/>
-      <c r="X1" s="215">
+      <c r="V1" s="214"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="213">
         <v>7</v>
       </c>
-      <c r="Y1" s="216"/>
-      <c r="Z1" s="217"/>
-      <c r="AA1" s="215">
+      <c r="Y1" s="214"/>
+      <c r="Z1" s="215"/>
+      <c r="AA1" s="213">
         <v>8</v>
       </c>
-      <c r="AB1" s="216"/>
-      <c r="AC1" s="217"/>
-      <c r="AD1" s="215">
+      <c r="AB1" s="214"/>
+      <c r="AC1" s="215"/>
+      <c r="AD1" s="213">
         <v>9</v>
       </c>
-      <c r="AE1" s="216"/>
-      <c r="AF1" s="217"/>
-      <c r="AG1" s="215">
+      <c r="AE1" s="214"/>
+      <c r="AF1" s="215"/>
+      <c r="AG1" s="213">
         <v>10</v>
       </c>
-      <c r="AH1" s="216"/>
-      <c r="AI1" s="217"/>
-      <c r="AJ1" s="215">
+      <c r="AH1" s="214"/>
+      <c r="AI1" s="215"/>
+      <c r="AJ1" s="213">
         <v>11</v>
       </c>
-      <c r="AK1" s="216"/>
-      <c r="AL1" s="217"/>
-      <c r="AM1" s="215">
+      <c r="AK1" s="214"/>
+      <c r="AL1" s="215"/>
+      <c r="AM1" s="213">
         <v>12</v>
       </c>
-      <c r="AN1" s="216"/>
-      <c r="AO1" s="217"/>
-      <c r="AP1" s="215">
+      <c r="AN1" s="214"/>
+      <c r="AO1" s="215"/>
+      <c r="AP1" s="213">
         <v>13</v>
       </c>
-      <c r="AQ1" s="216"/>
-      <c r="AR1" s="217"/>
-      <c r="AS1" s="215">
+      <c r="AQ1" s="214"/>
+      <c r="AR1" s="215"/>
+      <c r="AS1" s="213">
         <v>14</v>
       </c>
-      <c r="AT1" s="216"/>
-      <c r="AU1" s="217"/>
-      <c r="AV1" s="215">
+      <c r="AT1" s="214"/>
+      <c r="AU1" s="215"/>
+      <c r="AV1" s="213">
         <v>15</v>
       </c>
-      <c r="AW1" s="216"/>
-      <c r="AX1" s="217"/>
-      <c r="AY1" s="215">
+      <c r="AW1" s="214"/>
+      <c r="AX1" s="215"/>
+      <c r="AY1" s="213">
         <v>16</v>
       </c>
-      <c r="AZ1" s="216"/>
-      <c r="BA1" s="217"/>
-      <c r="BB1" s="215">
+      <c r="AZ1" s="214"/>
+      <c r="BA1" s="215"/>
+      <c r="BB1" s="213">
         <v>17</v>
       </c>
-      <c r="BC1" s="216"/>
-      <c r="BD1" s="217"/>
-      <c r="BE1" s="215">
+      <c r="BC1" s="214"/>
+      <c r="BD1" s="215"/>
+      <c r="BE1" s="213">
         <v>18</v>
       </c>
-      <c r="BF1" s="216"/>
-      <c r="BG1" s="217"/>
-      <c r="BH1" s="215">
+      <c r="BF1" s="214"/>
+      <c r="BG1" s="215"/>
+      <c r="BH1" s="213">
         <v>19</v>
       </c>
-      <c r="BI1" s="216"/>
-      <c r="BJ1" s="217"/>
-      <c r="BK1" s="215">
+      <c r="BI1" s="214"/>
+      <c r="BJ1" s="215"/>
+      <c r="BK1" s="213">
         <v>20</v>
       </c>
-      <c r="BL1" s="216"/>
-      <c r="BM1" s="217"/>
-      <c r="BN1" s="215">
+      <c r="BL1" s="214"/>
+      <c r="BM1" s="215"/>
+      <c r="BN1" s="213">
         <v>21</v>
       </c>
-      <c r="BO1" s="216"/>
-      <c r="BP1" s="217"/>
-      <c r="BQ1" s="215">
+      <c r="BO1" s="214"/>
+      <c r="BP1" s="215"/>
+      <c r="BQ1" s="213">
         <v>22</v>
       </c>
-      <c r="BR1" s="216"/>
-      <c r="BS1" s="217"/>
-      <c r="BT1" s="215">
+      <c r="BR1" s="214"/>
+      <c r="BS1" s="215"/>
+      <c r="BT1" s="213">
         <v>23</v>
       </c>
-      <c r="BU1" s="216"/>
-      <c r="BV1" s="217"/>
-      <c r="BW1" s="215">
+      <c r="BU1" s="214"/>
+      <c r="BV1" s="215"/>
+      <c r="BW1" s="213">
         <v>24</v>
       </c>
-      <c r="BX1" s="216"/>
-      <c r="BY1" s="217"/>
-      <c r="BZ1" s="215">
+      <c r="BX1" s="214"/>
+      <c r="BY1" s="215"/>
+      <c r="BZ1" s="213">
         <v>25</v>
       </c>
-      <c r="CA1" s="216"/>
-      <c r="CB1" s="217"/>
-      <c r="CC1" s="215">
+      <c r="CA1" s="214"/>
+      <c r="CB1" s="215"/>
+      <c r="CC1" s="213">
         <v>26</v>
       </c>
-      <c r="CD1" s="216"/>
-      <c r="CE1" s="217"/>
-      <c r="CF1" s="215">
+      <c r="CD1" s="214"/>
+      <c r="CE1" s="215"/>
+      <c r="CF1" s="213">
         <v>27</v>
       </c>
-      <c r="CG1" s="216"/>
-      <c r="CH1" s="217"/>
-      <c r="CI1" s="215">
+      <c r="CG1" s="214"/>
+      <c r="CH1" s="215"/>
+      <c r="CI1" s="213">
         <v>28</v>
       </c>
-      <c r="CJ1" s="216"/>
-      <c r="CK1" s="217"/>
-      <c r="CL1" s="215">
+      <c r="CJ1" s="214"/>
+      <c r="CK1" s="215"/>
+      <c r="CL1" s="213">
         <v>29</v>
       </c>
-      <c r="CM1" s="216"/>
-      <c r="CN1" s="217"/>
-      <c r="CO1" s="215">
+      <c r="CM1" s="214"/>
+      <c r="CN1" s="215"/>
+      <c r="CO1" s="213">
         <v>30</v>
       </c>
-      <c r="CP1" s="216"/>
-      <c r="CQ1" s="217"/>
-      <c r="CR1" s="215">
+      <c r="CP1" s="214"/>
+      <c r="CQ1" s="215"/>
+      <c r="CR1" s="213">
         <v>31</v>
       </c>
-      <c r="CS1" s="216"/>
-      <c r="CT1" s="217"/>
-      <c r="CU1" s="215">
+      <c r="CS1" s="214"/>
+      <c r="CT1" s="215"/>
+      <c r="CU1" s="213">
         <v>32</v>
       </c>
-      <c r="CV1" s="216"/>
-      <c r="CW1" s="217"/>
-      <c r="CX1" s="215">
+      <c r="CV1" s="214"/>
+      <c r="CW1" s="215"/>
+      <c r="CX1" s="213">
         <v>33</v>
       </c>
-      <c r="CY1" s="216"/>
-      <c r="CZ1" s="217"/>
-      <c r="DA1" s="215">
+      <c r="CY1" s="214"/>
+      <c r="CZ1" s="215"/>
+      <c r="DA1" s="213">
         <v>34</v>
       </c>
-      <c r="DB1" s="216"/>
-      <c r="DC1" s="217"/>
-      <c r="DD1" s="215">
+      <c r="DB1" s="214"/>
+      <c r="DC1" s="215"/>
+      <c r="DD1" s="213">
         <v>35</v>
       </c>
-      <c r="DE1" s="216"/>
-      <c r="DF1" s="217"/>
-      <c r="DG1" s="215">
+      <c r="DE1" s="214"/>
+      <c r="DF1" s="215"/>
+      <c r="DG1" s="213">
         <v>36</v>
       </c>
-      <c r="DH1" s="216"/>
-      <c r="DI1" s="217"/>
-      <c r="DJ1" s="215">
+      <c r="DH1" s="214"/>
+      <c r="DI1" s="215"/>
+      <c r="DJ1" s="213">
         <v>37</v>
       </c>
-      <c r="DK1" s="216"/>
-      <c r="DL1" s="217"/>
-      <c r="DM1" s="215">
+      <c r="DK1" s="214"/>
+      <c r="DL1" s="215"/>
+      <c r="DM1" s="213">
         <v>38</v>
       </c>
-      <c r="DN1" s="216"/>
-      <c r="DO1" s="217"/>
+      <c r="DN1" s="214"/>
+      <c r="DO1" s="215"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="218" t="s">
+      <c r="C2" s="219" t="s">
         <v>396</v>
       </c>
-      <c r="D2" s="218" t="s">
+      <c r="D2" s="219" t="s">
         <v>397</v>
       </c>
-      <c r="E2" s="218" t="s">
+      <c r="E2" s="219" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="212" t="s">
+      <c r="F2" s="216" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="213"/>
-      <c r="H2" s="214"/>
+      <c r="G2" s="217"/>
+      <c r="H2" s="218"/>
       <c r="I2" s="221" t="s">
         <v>331</v>
       </c>
       <c r="J2" s="222"/>
       <c r="K2" s="223"/>
-      <c r="L2" s="212" t="s">
+      <c r="L2" s="216" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="213"/>
-      <c r="N2" s="214"/>
-      <c r="O2" s="212" t="s">
+      <c r="M2" s="217"/>
+      <c r="N2" s="218"/>
+      <c r="O2" s="216" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="213"/>
-      <c r="Q2" s="214"/>
-      <c r="R2" s="212" t="s">
+      <c r="P2" s="217"/>
+      <c r="Q2" s="218"/>
+      <c r="R2" s="216" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="213"/>
-      <c r="T2" s="214"/>
-      <c r="U2" s="212" t="s">
+      <c r="S2" s="217"/>
+      <c r="T2" s="218"/>
+      <c r="U2" s="216" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="213"/>
-      <c r="W2" s="214"/>
-      <c r="X2" s="212" t="s">
+      <c r="V2" s="217"/>
+      <c r="W2" s="218"/>
+      <c r="X2" s="216" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="213"/>
-      <c r="Z2" s="214"/>
-      <c r="AA2" s="212" t="s">
+      <c r="Y2" s="217"/>
+      <c r="Z2" s="218"/>
+      <c r="AA2" s="216" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="213"/>
-      <c r="AC2" s="214"/>
-      <c r="AD2" s="212" t="s">
+      <c r="AB2" s="217"/>
+      <c r="AC2" s="218"/>
+      <c r="AD2" s="216" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="213"/>
-      <c r="AF2" s="214"/>
-      <c r="AG2" s="212" t="s">
+      <c r="AE2" s="217"/>
+      <c r="AF2" s="218"/>
+      <c r="AG2" s="216" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="213"/>
-      <c r="AI2" s="214"/>
-      <c r="AJ2" s="212" t="s">
+      <c r="AH2" s="217"/>
+      <c r="AI2" s="218"/>
+      <c r="AJ2" s="216" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="213"/>
-      <c r="AL2" s="214"/>
-      <c r="AM2" s="212" t="s">
+      <c r="AK2" s="217"/>
+      <c r="AL2" s="218"/>
+      <c r="AM2" s="216" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="213"/>
-      <c r="AO2" s="214"/>
-      <c r="AP2" s="212" t="s">
+      <c r="AN2" s="217"/>
+      <c r="AO2" s="218"/>
+      <c r="AP2" s="216" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="213"/>
-      <c r="AR2" s="214"/>
-      <c r="AS2" s="212" t="s">
+      <c r="AQ2" s="217"/>
+      <c r="AR2" s="218"/>
+      <c r="AS2" s="216" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="213"/>
-      <c r="AU2" s="214"/>
-      <c r="AV2" s="212" t="s">
+      <c r="AT2" s="217"/>
+      <c r="AU2" s="218"/>
+      <c r="AV2" s="216" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="213"/>
-      <c r="AX2" s="214"/>
-      <c r="AY2" s="212" t="s">
+      <c r="AW2" s="217"/>
+      <c r="AX2" s="218"/>
+      <c r="AY2" s="216" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="213"/>
-      <c r="BA2" s="214"/>
-      <c r="BB2" s="212" t="s">
+      <c r="AZ2" s="217"/>
+      <c r="BA2" s="218"/>
+      <c r="BB2" s="216" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="213"/>
-      <c r="BD2" s="214"/>
-      <c r="BE2" s="212" t="s">
+      <c r="BC2" s="217"/>
+      <c r="BD2" s="218"/>
+      <c r="BE2" s="216" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="213"/>
-      <c r="BG2" s="214"/>
-      <c r="BH2" s="212" t="s">
+      <c r="BF2" s="217"/>
+      <c r="BG2" s="218"/>
+      <c r="BH2" s="216" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="213"/>
-      <c r="BJ2" s="214"/>
-      <c r="BK2" s="212" t="s">
+      <c r="BI2" s="217"/>
+      <c r="BJ2" s="218"/>
+      <c r="BK2" s="216" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="213"/>
-      <c r="BM2" s="214"/>
-      <c r="BN2" s="212" t="s">
+      <c r="BL2" s="217"/>
+      <c r="BM2" s="218"/>
+      <c r="BN2" s="216" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="213"/>
-      <c r="BP2" s="214"/>
-      <c r="BQ2" s="212" t="s">
+      <c r="BO2" s="217"/>
+      <c r="BP2" s="218"/>
+      <c r="BQ2" s="216" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="213"/>
-      <c r="BS2" s="214"/>
-      <c r="BT2" s="212" t="s">
+      <c r="BR2" s="217"/>
+      <c r="BS2" s="218"/>
+      <c r="BT2" s="216" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="213"/>
-      <c r="BV2" s="214"/>
-      <c r="BW2" s="212" t="s">
+      <c r="BU2" s="217"/>
+      <c r="BV2" s="218"/>
+      <c r="BW2" s="216" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="213"/>
-      <c r="BY2" s="214"/>
-      <c r="BZ2" s="212" t="s">
+      <c r="BX2" s="217"/>
+      <c r="BY2" s="218"/>
+      <c r="BZ2" s="216" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="213"/>
-      <c r="CB2" s="214"/>
-      <c r="CC2" s="212" t="s">
+      <c r="CA2" s="217"/>
+      <c r="CB2" s="218"/>
+      <c r="CC2" s="216" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="213"/>
-      <c r="CE2" s="214"/>
-      <c r="CF2" s="212" t="s">
+      <c r="CD2" s="217"/>
+      <c r="CE2" s="218"/>
+      <c r="CF2" s="216" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="213"/>
-      <c r="CH2" s="214"/>
-      <c r="CI2" s="212" t="s">
+      <c r="CG2" s="217"/>
+      <c r="CH2" s="218"/>
+      <c r="CI2" s="216" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="213"/>
-      <c r="CK2" s="214"/>
-      <c r="CL2" s="212" t="s">
+      <c r="CJ2" s="217"/>
+      <c r="CK2" s="218"/>
+      <c r="CL2" s="216" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="213"/>
-      <c r="CN2" s="214"/>
-      <c r="CO2" s="212" t="s">
+      <c r="CM2" s="217"/>
+      <c r="CN2" s="218"/>
+      <c r="CO2" s="216" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="213"/>
-      <c r="CQ2" s="214"/>
-      <c r="CR2" s="212" t="s">
+      <c r="CP2" s="217"/>
+      <c r="CQ2" s="218"/>
+      <c r="CR2" s="216" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="213"/>
-      <c r="CT2" s="214"/>
-      <c r="CU2" s="212" t="s">
+      <c r="CS2" s="217"/>
+      <c r="CT2" s="218"/>
+      <c r="CU2" s="216" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="213"/>
-      <c r="CW2" s="214"/>
-      <c r="CX2" s="212" t="s">
+      <c r="CV2" s="217"/>
+      <c r="CW2" s="218"/>
+      <c r="CX2" s="216" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="213"/>
-      <c r="CZ2" s="214"/>
-      <c r="DA2" s="212" t="s">
+      <c r="CY2" s="217"/>
+      <c r="CZ2" s="218"/>
+      <c r="DA2" s="216" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="213"/>
-      <c r="DC2" s="214"/>
-      <c r="DD2" s="212" t="s">
+      <c r="DB2" s="217"/>
+      <c r="DC2" s="218"/>
+      <c r="DD2" s="216" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="213"/>
-      <c r="DF2" s="214"/>
-      <c r="DG2" s="212" t="s">
+      <c r="DE2" s="217"/>
+      <c r="DF2" s="218"/>
+      <c r="DG2" s="216" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="213"/>
-      <c r="DI2" s="214"/>
-      <c r="DJ2" s="212" t="s">
+      <c r="DH2" s="217"/>
+      <c r="DI2" s="218"/>
+      <c r="DJ2" s="216" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="213"/>
-      <c r="DL2" s="214"/>
-      <c r="DM2" s="212" t="s">
+      <c r="DK2" s="217"/>
+      <c r="DL2" s="218"/>
+      <c r="DM2" s="216" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="213"/>
-      <c r="DO2" s="214"/>
+      <c r="DN2" s="217"/>
+      <c r="DO2" s="218"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38022,8 +38109,8 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="219"/>
-      <c r="D3" s="219"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="224"/>
       <c r="E3" s="220"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
@@ -43601,69 +43688,6 @@
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43680,6 +43704,69 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO38">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -43715,122 +43802,122 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="236" t="s">
+      <c r="C1" s="234" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="236" t="s">
+      <c r="D1" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="236" t="s">
+      <c r="E1" s="234" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="227" t="s">
+      <c r="F1" s="225" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="228"/>
-      <c r="H1" s="228"/>
-      <c r="I1" s="228"/>
-      <c r="J1" s="228"/>
-      <c r="K1" s="228"/>
-      <c r="L1" s="228"/>
-      <c r="M1" s="228"/>
-      <c r="N1" s="228"/>
-      <c r="O1" s="228"/>
-      <c r="P1" s="228"/>
-      <c r="Q1" s="228"/>
-      <c r="R1" s="228"/>
-      <c r="S1" s="228"/>
-      <c r="T1" s="228"/>
-      <c r="U1" s="228"/>
-      <c r="V1" s="228"/>
-      <c r="W1" s="228"/>
-      <c r="X1" s="228"/>
-      <c r="Y1" s="228"/>
-      <c r="Z1" s="228"/>
-      <c r="AA1" s="228"/>
-      <c r="AB1" s="228"/>
-      <c r="AC1" s="229"/>
-      <c r="AD1" s="239" t="s">
+      <c r="G1" s="226"/>
+      <c r="H1" s="226"/>
+      <c r="I1" s="226"/>
+      <c r="J1" s="226"/>
+      <c r="K1" s="226"/>
+      <c r="L1" s="226"/>
+      <c r="M1" s="226"/>
+      <c r="N1" s="226"/>
+      <c r="O1" s="226"/>
+      <c r="P1" s="226"/>
+      <c r="Q1" s="226"/>
+      <c r="R1" s="226"/>
+      <c r="S1" s="226"/>
+      <c r="T1" s="226"/>
+      <c r="U1" s="226"/>
+      <c r="V1" s="226"/>
+      <c r="W1" s="226"/>
+      <c r="X1" s="226"/>
+      <c r="Y1" s="226"/>
+      <c r="Z1" s="226"/>
+      <c r="AA1" s="226"/>
+      <c r="AB1" s="226"/>
+      <c r="AC1" s="227"/>
+      <c r="AD1" s="240" t="s">
         <v>281</v>
       </c>
-      <c r="AE1" s="240"/>
-      <c r="AF1" s="240"/>
-      <c r="AG1" s="240"/>
-      <c r="AH1" s="240"/>
-      <c r="AI1" s="241"/>
-      <c r="AJ1" s="227" t="s">
+      <c r="AE1" s="241"/>
+      <c r="AF1" s="241"/>
+      <c r="AG1" s="241"/>
+      <c r="AH1" s="241"/>
+      <c r="AI1" s="242"/>
+      <c r="AJ1" s="225" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="228"/>
-      <c r="AL1" s="228"/>
-      <c r="AM1" s="228"/>
-      <c r="AN1" s="228"/>
-      <c r="AO1" s="229"/>
-      <c r="AP1" s="230" t="s">
+      <c r="AK1" s="226"/>
+      <c r="AL1" s="226"/>
+      <c r="AM1" s="226"/>
+      <c r="AN1" s="226"/>
+      <c r="AO1" s="227"/>
+      <c r="AP1" s="228" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="231"/>
-      <c r="AR1" s="231"/>
-      <c r="AS1" s="231"/>
-      <c r="AT1" s="231"/>
-      <c r="AU1" s="232"/>
-      <c r="AV1" s="233" t="s">
+      <c r="AQ1" s="229"/>
+      <c r="AR1" s="229"/>
+      <c r="AS1" s="229"/>
+      <c r="AT1" s="229"/>
+      <c r="AU1" s="230"/>
+      <c r="AV1" s="231" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="234"/>
-      <c r="AX1" s="235"/>
+      <c r="AW1" s="232"/>
+      <c r="AX1" s="233"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="237"/>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="224"/>
-      <c r="G2" s="225"/>
-      <c r="H2" s="226"/>
-      <c r="I2" s="224"/>
-      <c r="J2" s="225"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="224"/>
-      <c r="M2" s="225"/>
-      <c r="N2" s="226"/>
-      <c r="O2" s="224"/>
-      <c r="P2" s="225"/>
-      <c r="Q2" s="226"/>
-      <c r="R2" s="224"/>
-      <c r="S2" s="225"/>
-      <c r="T2" s="226"/>
-      <c r="U2" s="224"/>
-      <c r="V2" s="225"/>
-      <c r="W2" s="226"/>
-      <c r="X2" s="224"/>
-      <c r="Y2" s="225"/>
-      <c r="Z2" s="226"/>
-      <c r="AA2" s="224"/>
-      <c r="AB2" s="225"/>
-      <c r="AC2" s="225"/>
-      <c r="AD2" s="224"/>
-      <c r="AE2" s="225"/>
-      <c r="AF2" s="226"/>
-      <c r="AG2" s="224"/>
-      <c r="AH2" s="225"/>
-      <c r="AI2" s="226"/>
-      <c r="AJ2" s="224"/>
-      <c r="AK2" s="225"/>
-      <c r="AL2" s="226"/>
-      <c r="AM2" s="224"/>
-      <c r="AN2" s="225"/>
-      <c r="AO2" s="226"/>
-      <c r="AP2" s="224"/>
-      <c r="AQ2" s="225"/>
-      <c r="AR2" s="226"/>
-      <c r="AS2" s="224"/>
-      <c r="AT2" s="225"/>
-      <c r="AU2" s="226"/>
-      <c r="AV2" s="224"/>
-      <c r="AW2" s="225"/>
-      <c r="AX2" s="226"/>
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="237"/>
+      <c r="G2" s="238"/>
+      <c r="H2" s="239"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="239"/>
+      <c r="L2" s="237"/>
+      <c r="M2" s="238"/>
+      <c r="N2" s="239"/>
+      <c r="O2" s="237"/>
+      <c r="P2" s="238"/>
+      <c r="Q2" s="239"/>
+      <c r="R2" s="237"/>
+      <c r="S2" s="238"/>
+      <c r="T2" s="239"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="238"/>
+      <c r="W2" s="239"/>
+      <c r="X2" s="237"/>
+      <c r="Y2" s="238"/>
+      <c r="Z2" s="239"/>
+      <c r="AA2" s="237"/>
+      <c r="AB2" s="238"/>
+      <c r="AC2" s="238"/>
+      <c r="AD2" s="237"/>
+      <c r="AE2" s="238"/>
+      <c r="AF2" s="239"/>
+      <c r="AG2" s="237"/>
+      <c r="AH2" s="238"/>
+      <c r="AI2" s="239"/>
+      <c r="AJ2" s="237"/>
+      <c r="AK2" s="238"/>
+      <c r="AL2" s="239"/>
+      <c r="AM2" s="237"/>
+      <c r="AN2" s="238"/>
+      <c r="AO2" s="239"/>
+      <c r="AP2" s="237"/>
+      <c r="AQ2" s="238"/>
+      <c r="AR2" s="239"/>
+      <c r="AS2" s="237"/>
+      <c r="AT2" s="238"/>
+      <c r="AU2" s="239"/>
+      <c r="AV2" s="237"/>
+      <c r="AW2" s="238"/>
+      <c r="AX2" s="239"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -43839,9 +43926,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="238"/>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
+      <c r="C3" s="236"/>
+      <c r="D3" s="236"/>
+      <c r="E3" s="236"/>
       <c r="F3" s="170" t="s">
         <v>393</v>
       </c>
@@ -46437,6 +46524,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46453,13 +46547,6 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW32">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46494,70 +46581,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="236" t="s">
+      <c r="C1" s="234" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="236" t="s">
+      <c r="D1" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="236" t="s">
+      <c r="E1" s="234" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="266" t="s">
+      <c r="F1" s="274" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="267"/>
-      <c r="H1" s="268"/>
-      <c r="I1" s="269" t="s">
+      <c r="G1" s="275"/>
+      <c r="H1" s="276"/>
+      <c r="I1" s="277" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="270"/>
-      <c r="K1" s="271"/>
-      <c r="L1" s="273" t="s">
+      <c r="J1" s="278"/>
+      <c r="K1" s="279"/>
+      <c r="L1" s="244" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="274"/>
-      <c r="N1" s="275"/>
-      <c r="O1" s="276" t="s">
+      <c r="M1" s="245"/>
+      <c r="N1" s="246"/>
+      <c r="O1" s="247" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="277"/>
-      <c r="Q1" s="278"/>
-      <c r="R1" s="242" t="s">
+      <c r="P1" s="248"/>
+      <c r="Q1" s="249"/>
+      <c r="R1" s="250" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="243"/>
-      <c r="T1" s="244"/>
-      <c r="U1" s="245" t="s">
+      <c r="S1" s="251"/>
+      <c r="T1" s="252"/>
+      <c r="U1" s="253" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="246"/>
-      <c r="W1" s="247"/>
+      <c r="V1" s="254"/>
+      <c r="W1" s="255"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="237"/>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="250"/>
-      <c r="I2" s="263"/>
-      <c r="J2" s="264"/>
-      <c r="K2" s="265"/>
-      <c r="L2" s="260"/>
-      <c r="M2" s="261"/>
-      <c r="N2" s="262"/>
-      <c r="O2" s="257"/>
-      <c r="P2" s="258"/>
-      <c r="Q2" s="259"/>
-      <c r="R2" s="254"/>
-      <c r="S2" s="255"/>
-      <c r="T2" s="256"/>
-      <c r="U2" s="251"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="253"/>
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="256"/>
+      <c r="G2" s="257"/>
+      <c r="H2" s="258"/>
+      <c r="I2" s="271"/>
+      <c r="J2" s="272"/>
+      <c r="K2" s="273"/>
+      <c r="L2" s="268"/>
+      <c r="M2" s="269"/>
+      <c r="N2" s="270"/>
+      <c r="O2" s="265"/>
+      <c r="P2" s="266"/>
+      <c r="Q2" s="267"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="264"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="261"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46566,9 +46653,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="272"/>
-      <c r="D3" s="272"/>
-      <c r="E3" s="272"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -48030,11 +48117,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -48045,6 +48127,11 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -55051,72 +55138,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="236" t="s">
+      <c r="C1" s="234" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="236" t="s">
+      <c r="D1" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="236" t="s">
+      <c r="E1" s="234" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="266" t="s">
+      <c r="F1" s="274" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="267"/>
-      <c r="H1" s="268"/>
-      <c r="I1" s="269" t="s">
+      <c r="G1" s="275"/>
+      <c r="H1" s="276"/>
+      <c r="I1" s="277" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="270"/>
-      <c r="K1" s="271"/>
-      <c r="L1" s="273" t="s">
+      <c r="J1" s="278"/>
+      <c r="K1" s="279"/>
+      <c r="L1" s="244" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="274"/>
-      <c r="N1" s="275"/>
-      <c r="O1" s="276" t="s">
+      <c r="M1" s="245"/>
+      <c r="N1" s="246"/>
+      <c r="O1" s="247" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="277"/>
-      <c r="Q1" s="278"/>
-      <c r="R1" s="242" t="s">
+      <c r="P1" s="248"/>
+      <c r="Q1" s="249"/>
+      <c r="R1" s="250" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="243"/>
-      <c r="T1" s="244"/>
-      <c r="U1" s="245" t="s">
+      <c r="S1" s="251"/>
+      <c r="T1" s="252"/>
+      <c r="U1" s="253" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="246"/>
-      <c r="W1" s="247"/>
+      <c r="V1" s="254"/>
+      <c r="W1" s="255"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="237"/>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="248" t="s">
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="256" t="s">
         <v>438</v>
       </c>
-      <c r="G2" s="249"/>
-      <c r="H2" s="250"/>
-      <c r="I2" s="263"/>
-      <c r="J2" s="264"/>
-      <c r="K2" s="265"/>
-      <c r="L2" s="260"/>
-      <c r="M2" s="261"/>
-      <c r="N2" s="262"/>
-      <c r="O2" s="257"/>
-      <c r="P2" s="258"/>
-      <c r="Q2" s="259"/>
-      <c r="R2" s="254"/>
-      <c r="S2" s="255"/>
-      <c r="T2" s="256"/>
-      <c r="U2" s="251"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="253"/>
+      <c r="G2" s="257"/>
+      <c r="H2" s="258"/>
+      <c r="I2" s="271"/>
+      <c r="J2" s="272"/>
+      <c r="K2" s="273"/>
+      <c r="L2" s="268"/>
+      <c r="M2" s="269"/>
+      <c r="N2" s="270"/>
+      <c r="O2" s="265"/>
+      <c r="P2" s="266"/>
+      <c r="Q2" s="267"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="264"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="261"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -55125,9 +55212,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="272"/>
-      <c r="D3" s="272"/>
-      <c r="E3" s="272"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -56589,6 +56676,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -56599,11 +56691,6 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -56631,11 +56718,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C1" s="279" t="s">
+      <c r="C1" s="280" t="s">
         <v>340</v>
       </c>
-      <c r="D1" s="280"/>
-      <c r="E1" s="280"/>
+      <c r="D1" s="281"/>
+      <c r="E1" s="281"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -57110,51 +57197,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="282" t="s">
+      <c r="C1" s="302" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="283"/>
-      <c r="E1" s="283"/>
-      <c r="F1" s="283"/>
-      <c r="G1" s="283"/>
-      <c r="H1" s="283"/>
-      <c r="I1" s="284"/>
+      <c r="D1" s="303"/>
+      <c r="E1" s="303"/>
+      <c r="F1" s="303"/>
+      <c r="G1" s="303"/>
+      <c r="H1" s="303"/>
+      <c r="I1" s="304"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="306" t="s">
+      <c r="L1" s="282" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="311"/>
-      <c r="N1" s="311"/>
-      <c r="O1" s="311"/>
-      <c r="P1" s="311"/>
-      <c r="Q1" s="311"/>
-      <c r="R1" s="311"/>
-      <c r="S1" s="311"/>
-      <c r="T1" s="311"/>
-      <c r="U1" s="311"/>
-      <c r="V1" s="311"/>
-      <c r="W1" s="311"/>
-      <c r="X1" s="311"/>
-      <c r="Y1" s="311"/>
-      <c r="Z1" s="311"/>
-      <c r="AA1" s="311"/>
-      <c r="AB1" s="311"/>
-      <c r="AC1" s="311"/>
-      <c r="AD1" s="311"/>
-      <c r="AE1" s="311"/>
-      <c r="AF1" s="311"/>
-      <c r="AG1" s="312"/>
-      <c r="AH1" s="306" t="s">
+      <c r="M1" s="287"/>
+      <c r="N1" s="287"/>
+      <c r="O1" s="287"/>
+      <c r="P1" s="287"/>
+      <c r="Q1" s="287"/>
+      <c r="R1" s="287"/>
+      <c r="S1" s="287"/>
+      <c r="T1" s="287"/>
+      <c r="U1" s="287"/>
+      <c r="V1" s="287"/>
+      <c r="W1" s="287"/>
+      <c r="X1" s="287"/>
+      <c r="Y1" s="287"/>
+      <c r="Z1" s="287"/>
+      <c r="AA1" s="287"/>
+      <c r="AB1" s="287"/>
+      <c r="AC1" s="287"/>
+      <c r="AD1" s="287"/>
+      <c r="AE1" s="287"/>
+      <c r="AF1" s="287"/>
+      <c r="AG1" s="288"/>
+      <c r="AH1" s="282" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="307"/>
-      <c r="AJ1" s="307"/>
-      <c r="AK1" s="308"/>
+      <c r="AI1" s="283"/>
+      <c r="AJ1" s="283"/>
+      <c r="AK1" s="284"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -62354,15 +62441,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="313" t="s">
+      <c r="K80" s="289" t="s">
         <v>442</v>
       </c>
-      <c r="L80" s="314"/>
-      <c r="M80" s="315"/>
+      <c r="L80" s="290"/>
+      <c r="M80" s="291"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="309"/>
-      <c r="X80" s="309"/>
+      <c r="W80" s="285"/>
+      <c r="X80" s="285"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -62412,15 +62499,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="316"/>
-      <c r="L81" s="317"/>
-      <c r="M81" s="318"/>
+      <c r="K81" s="292"/>
+      <c r="L81" s="293"/>
+      <c r="M81" s="294"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="309" t="s">
+      <c r="W81" s="285" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="309"/>
+      <c r="X81" s="285"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62476,17 +62563,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="319" t="s">
+      <c r="K82" s="295" t="s">
         <v>443</v>
       </c>
-      <c r="L82" s="320"/>
-      <c r="M82" s="321"/>
+      <c r="L82" s="296"/>
+      <c r="M82" s="297"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="309" t="s">
+      <c r="W82" s="285" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="309"/>
+      <c r="X82" s="285"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62542,17 +62629,17 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="322" t="s">
+      <c r="K83" s="298" t="s">
         <v>444</v>
       </c>
-      <c r="L83" s="323"/>
-      <c r="M83" s="324"/>
+      <c r="L83" s="299"/>
+      <c r="M83" s="300"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="310" t="s">
+      <c r="W83" s="286" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="310"/>
+      <c r="X83" s="286"/>
       <c r="Y83" s="196">
         <v>220</v>
       </c>
@@ -62605,15 +62692,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="297" t="s">
+      <c r="K84" s="317" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="298"/>
-      <c r="M84" s="299"/>
+      <c r="L84" s="318"/>
+      <c r="M84" s="319"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="281"/>
-      <c r="X84" s="281"/>
+      <c r="W84" s="301"/>
+      <c r="X84" s="301"/>
       <c r="Y84" s="198"/>
       <c r="Z84" s="198"/>
       <c r="AA84" s="198"/>
@@ -62651,9 +62738,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="300"/>
-      <c r="L85" s="301"/>
-      <c r="M85" s="302"/>
+      <c r="K85" s="320"/>
+      <c r="L85" s="321"/>
+      <c r="M85" s="322"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -62687,9 +62774,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="300"/>
-      <c r="L86" s="301"/>
-      <c r="M86" s="302"/>
+      <c r="K86" s="320"/>
+      <c r="L86" s="321"/>
+      <c r="M86" s="322"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -62723,9 +62810,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="300"/>
-      <c r="L87" s="301"/>
-      <c r="M87" s="302"/>
+      <c r="K87" s="320"/>
+      <c r="L87" s="321"/>
+      <c r="M87" s="322"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -62759,9 +62846,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="300"/>
-      <c r="L88" s="301"/>
-      <c r="M88" s="302"/>
+      <c r="K88" s="320"/>
+      <c r="L88" s="321"/>
+      <c r="M88" s="322"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -62795,9 +62882,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="300"/>
-      <c r="L89" s="301"/>
-      <c r="M89" s="302"/>
+      <c r="K89" s="320"/>
+      <c r="L89" s="321"/>
+      <c r="M89" s="322"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -62831,9 +62918,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="300"/>
-      <c r="L90" s="301"/>
-      <c r="M90" s="302"/>
+      <c r="K90" s="320"/>
+      <c r="L90" s="321"/>
+      <c r="M90" s="322"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -62867,9 +62954,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="300"/>
-      <c r="L91" s="301"/>
-      <c r="M91" s="302"/>
+      <c r="K91" s="320"/>
+      <c r="L91" s="321"/>
+      <c r="M91" s="322"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -62903,9 +62990,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="300"/>
-      <c r="L92" s="301"/>
-      <c r="M92" s="302"/>
+      <c r="K92" s="320"/>
+      <c r="L92" s="321"/>
+      <c r="M92" s="322"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -62939,9 +63026,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="300"/>
-      <c r="L93" s="301"/>
-      <c r="M93" s="302"/>
+      <c r="K93" s="320"/>
+      <c r="L93" s="321"/>
+      <c r="M93" s="322"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -62975,9 +63062,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="300"/>
-      <c r="L94" s="301"/>
-      <c r="M94" s="302"/>
+      <c r="K94" s="320"/>
+      <c r="L94" s="321"/>
+      <c r="M94" s="322"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -63011,9 +63098,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="300"/>
-      <c r="L95" s="301"/>
-      <c r="M95" s="302"/>
+      <c r="K95" s="320"/>
+      <c r="L95" s="321"/>
+      <c r="M95" s="322"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -63047,9 +63134,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="300"/>
-      <c r="L96" s="301"/>
-      <c r="M96" s="302"/>
+      <c r="K96" s="320"/>
+      <c r="L96" s="321"/>
+      <c r="M96" s="322"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -63083,9 +63170,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="300"/>
-      <c r="L97" s="301"/>
-      <c r="M97" s="302"/>
+      <c r="K97" s="320"/>
+      <c r="L97" s="321"/>
+      <c r="M97" s="322"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -63119,9 +63206,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="300"/>
-      <c r="L98" s="301"/>
-      <c r="M98" s="302"/>
+      <c r="K98" s="320"/>
+      <c r="L98" s="321"/>
+      <c r="M98" s="322"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -63155,9 +63242,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="300"/>
-      <c r="L99" s="301"/>
-      <c r="M99" s="302"/>
+      <c r="K99" s="320"/>
+      <c r="L99" s="321"/>
+      <c r="M99" s="322"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -63191,9 +63278,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="300"/>
-      <c r="L100" s="301"/>
-      <c r="M100" s="302"/>
+      <c r="K100" s="320"/>
+      <c r="L100" s="321"/>
+      <c r="M100" s="322"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -63227,9 +63314,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="300"/>
-      <c r="L101" s="301"/>
-      <c r="M101" s="302"/>
+      <c r="K101" s="320"/>
+      <c r="L101" s="321"/>
+      <c r="M101" s="322"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -63263,9 +63350,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="300"/>
-      <c r="L102" s="301"/>
-      <c r="M102" s="302"/>
+      <c r="K102" s="320"/>
+      <c r="L102" s="321"/>
+      <c r="M102" s="322"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -63299,9 +63386,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="300"/>
-      <c r="L103" s="301"/>
-      <c r="M103" s="302"/>
+      <c r="K103" s="320"/>
+      <c r="L103" s="321"/>
+      <c r="M103" s="322"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -63335,9 +63422,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="300"/>
-      <c r="L104" s="301"/>
-      <c r="M104" s="302"/>
+      <c r="K104" s="320"/>
+      <c r="L104" s="321"/>
+      <c r="M104" s="322"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -63371,9 +63458,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="303"/>
-      <c r="L105" s="304"/>
-      <c r="M105" s="305"/>
+      <c r="K105" s="323"/>
+      <c r="L105" s="324"/>
+      <c r="M105" s="325"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -63407,11 +63494,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="294" t="s">
+      <c r="K106" s="314" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="295"/>
-      <c r="M106" s="296"/>
+      <c r="L106" s="315"/>
+      <c r="M106" s="316"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63445,11 +63532,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="294" t="s">
+      <c r="K107" s="314" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="295"/>
-      <c r="M107" s="296"/>
+      <c r="L107" s="315"/>
+      <c r="M107" s="316"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63483,11 +63570,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="285" t="s">
+      <c r="K108" s="305" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="286"/>
-      <c r="M108" s="287"/>
+      <c r="L108" s="306"/>
+      <c r="M108" s="307"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63521,9 +63608,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="288"/>
-      <c r="L109" s="289"/>
-      <c r="M109" s="290"/>
+      <c r="K109" s="308"/>
+      <c r="L109" s="309"/>
+      <c r="M109" s="310"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -63557,9 +63644,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="288"/>
-      <c r="L110" s="289"/>
-      <c r="M110" s="290"/>
+      <c r="K110" s="308"/>
+      <c r="L110" s="309"/>
+      <c r="M110" s="310"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -63593,9 +63680,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="288"/>
-      <c r="L111" s="289"/>
-      <c r="M111" s="290"/>
+      <c r="K111" s="308"/>
+      <c r="L111" s="309"/>
+      <c r="M111" s="310"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -63633,9 +63720,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="288"/>
-      <c r="L112" s="289"/>
-      <c r="M112" s="290"/>
+      <c r="K112" s="308"/>
+      <c r="L112" s="309"/>
+      <c r="M112" s="310"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="156" t="s">
@@ -63671,9 +63758,9 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="291"/>
-      <c r="L113" s="292"/>
-      <c r="M113" s="293"/>
+      <c r="K113" s="311"/>
+      <c r="L113" s="312"/>
+      <c r="M113" s="313"/>
     </row>
     <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="93" t="s">
@@ -63713,6 +63800,12 @@
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
+    <mergeCell ref="W84:X84"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K108:M113"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
     <mergeCell ref="W81:X81"/>
@@ -63722,12 +63815,6 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
-    <mergeCell ref="W84:X84"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K108:M113"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -63812,32 +63899,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="325" t="s">
+      <c r="A1" s="326" t="s">
         <v>406</v>
       </c>
-      <c r="B1" s="325"/>
-      <c r="C1" s="325"/>
-      <c r="D1" s="325"/>
-      <c r="E1" s="325"/>
-      <c r="F1" s="325" t="s">
+      <c r="B1" s="326"/>
+      <c r="C1" s="326"/>
+      <c r="D1" s="326"/>
+      <c r="E1" s="326"/>
+      <c r="F1" s="326" t="s">
         <v>407</v>
       </c>
-      <c r="G1" s="325"/>
-      <c r="H1" s="325"/>
-      <c r="I1" s="325"/>
-      <c r="J1" s="325"/>
+      <c r="G1" s="326"/>
+      <c r="H1" s="326"/>
+      <c r="I1" s="326"/>
+      <c r="J1" s="326"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="325"/>
-      <c r="B2" s="325"/>
-      <c r="C2" s="325"/>
-      <c r="D2" s="325"/>
-      <c r="E2" s="325"/>
-      <c r="F2" s="325"/>
-      <c r="G2" s="325"/>
-      <c r="H2" s="325"/>
-      <c r="I2" s="325"/>
-      <c r="J2" s="325"/>
+      <c r="A2" s="326"/>
+      <c r="B2" s="326"/>
+      <c r="C2" s="326"/>
+      <c r="D2" s="326"/>
+      <c r="E2" s="326"/>
+      <c r="F2" s="326"/>
+      <c r="G2" s="326"/>
+      <c r="H2" s="326"/>
+      <c r="I2" s="326"/>
+      <c r="J2" s="326"/>
       <c r="L2" t="s">
         <v>410</v>
       </c>
@@ -64580,6 +64667,257 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44DFF815-59E5-49DB-A710-CC57B82C1BDD}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C2">
+        <v>6.6</v>
+      </c>
+      <c r="D2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>448</v>
+      </c>
+      <c r="B3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C3">
+        <v>7.4</v>
+      </c>
+      <c r="D3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>449</v>
+      </c>
+      <c r="B4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C4">
+        <v>7.2</v>
+      </c>
+      <c r="D4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>449</v>
+      </c>
+      <c r="B5" t="s">
+        <v>461</v>
+      </c>
+      <c r="C5">
+        <v>6.6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>450</v>
+      </c>
+      <c r="B6" t="s">
+        <v>462</v>
+      </c>
+      <c r="C6">
+        <v>7.2</v>
+      </c>
+      <c r="D6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>453</v>
+      </c>
+      <c r="B7" t="s">
+        <v>463</v>
+      </c>
+      <c r="C7">
+        <v>6.7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B8" t="s">
+        <v>464</v>
+      </c>
+      <c r="C8">
+        <v>7.2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>454</v>
+      </c>
+      <c r="B9" t="s">
+        <v>465</v>
+      </c>
+      <c r="C9">
+        <v>6.6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>455</v>
+      </c>
+      <c r="B10" t="s">
+        <v>466</v>
+      </c>
+      <c r="C10" s="330">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>456</v>
+      </c>
+      <c r="B11" t="s">
+        <v>467</v>
+      </c>
+      <c r="C11">
+        <v>8.1</v>
+      </c>
+      <c r="D11">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>457</v>
+      </c>
+      <c r="B12" t="s">
+        <v>468</v>
+      </c>
+      <c r="C12">
+        <v>6.3</v>
+      </c>
+      <c r="D12">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>455</v>
+      </c>
+      <c r="B13" t="s">
+        <v>470</v>
+      </c>
+      <c r="C13">
+        <v>6.3</v>
+      </c>
+      <c r="D13" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>454</v>
+      </c>
+      <c r="B14" t="s">
+        <v>472</v>
+      </c>
+      <c r="C14">
+        <v>6.7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>453</v>
+      </c>
+      <c r="B15" t="s">
+        <v>473</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>449</v>
+      </c>
+      <c r="B16" t="s">
+        <v>474</v>
+      </c>
+      <c r="C16">
+        <v>6.2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>453</v>
+      </c>
+      <c r="B17" t="s">
+        <v>475</v>
+      </c>
+      <c r="C17">
+        <v>6.3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>469</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Arkusz4"/>
   <dimension ref="A1:L32"/>
@@ -64598,24 +64936,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="200" t="s">
+      <c r="A1" s="201" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="326"/>
-      <c r="C1" s="327" t="s">
+      <c r="B1" s="327"/>
+      <c r="C1" s="328" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="203"/>
-      <c r="E1" s="328"/>
-      <c r="H1" s="200" t="s">
+      <c r="D1" s="204"/>
+      <c r="E1" s="329"/>
+      <c r="H1" s="201" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="326"/>
-      <c r="J1" s="327" t="s">
+      <c r="I1" s="327"/>
+      <c r="J1" s="328" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="203"/>
-      <c r="L1" s="328"/>
+      <c r="K1" s="204"/>
+      <c r="L1" s="329"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -65703,9 +66041,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
+      <c r="F1" s="205"/>
+      <c r="G1" s="205"/>
+      <c r="H1" s="205"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -65729,36 +66067,36 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="200" t="s">
+      <c r="E2" s="201" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="201"/>
-      <c r="G2" s="202"/>
-      <c r="H2" s="205" t="s">
+      <c r="F2" s="202"/>
+      <c r="G2" s="203"/>
+      <c r="H2" s="206" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207"/>
-      <c r="K2" s="200" t="s">
+      <c r="I2" s="207"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="201" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="201"/>
-      <c r="M2" s="202"/>
-      <c r="N2" s="205" t="s">
+      <c r="L2" s="202"/>
+      <c r="M2" s="203"/>
+      <c r="N2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="206"/>
-      <c r="P2" s="207"/>
-      <c r="Q2" s="200" t="s">
+      <c r="O2" s="207"/>
+      <c r="P2" s="208"/>
+      <c r="Q2" s="201" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="201"/>
-      <c r="S2" s="202"/>
-      <c r="T2" s="203" t="s">
+      <c r="R2" s="202"/>
+      <c r="S2" s="203"/>
+      <c r="T2" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="203"/>
-      <c r="V2" s="203"/>
+      <c r="U2" s="204"/>
+      <c r="V2" s="204"/>
       <c r="Z2" s="125">
         <v>46267</v>
       </c>
@@ -65826,7 +66164,7 @@
       <c r="V3" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="W3" s="329" t="s">
+      <c r="W3" s="200" t="s">
         <v>446</v>
       </c>
     </row>
@@ -68936,30 +69274,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="210" t="s">
+      <c r="D2" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="210"/>
-      <c r="F2" s="211" t="s">
+      <c r="E2" s="211"/>
+      <c r="F2" s="212" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="211"/>
-      <c r="H2" s="210" t="s">
+      <c r="G2" s="212"/>
+      <c r="H2" s="211" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="210"/>
-      <c r="J2" s="211" t="s">
+      <c r="I2" s="211"/>
+      <c r="J2" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="211"/>
-      <c r="L2" s="210" t="s">
+      <c r="K2" s="212"/>
+      <c r="L2" s="211" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="210"/>
-      <c r="N2" s="203" t="s">
+      <c r="M2" s="211"/>
+      <c r="N2" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="203"/>
+      <c r="O2" s="204"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -70956,30 +71294,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="210" t="s">
+      <c r="D2" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="210"/>
-      <c r="F2" s="211" t="s">
+      <c r="E2" s="211"/>
+      <c r="F2" s="212" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="211"/>
-      <c r="H2" s="210" t="s">
+      <c r="G2" s="212"/>
+      <c r="H2" s="211" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="210"/>
-      <c r="J2" s="211" t="s">
+      <c r="I2" s="211"/>
+      <c r="J2" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="211"/>
-      <c r="L2" s="210" t="s">
+      <c r="K2" s="212"/>
+      <c r="L2" s="211" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="210"/>
-      <c r="N2" s="203" t="s">
+      <c r="M2" s="211"/>
+      <c r="N2" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="203"/>
+      <c r="O2" s="204"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -72913,30 +73251,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="210" t="s">
+      <c r="D2" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="210"/>
-      <c r="F2" s="211" t="s">
+      <c r="E2" s="211"/>
+      <c r="F2" s="212" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="211"/>
-      <c r="H2" s="210" t="s">
+      <c r="G2" s="212"/>
+      <c r="H2" s="211" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="210"/>
-      <c r="J2" s="211" t="s">
+      <c r="I2" s="211"/>
+      <c r="J2" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="211"/>
-      <c r="L2" s="210" t="s">
+      <c r="K2" s="212"/>
+      <c r="L2" s="211" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="210"/>
-      <c r="N2" s="203" t="s">
+      <c r="M2" s="211"/>
+      <c r="N2" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="203"/>
+      <c r="O2" s="204"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -74961,30 +75299,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="210" t="s">
+      <c r="D2" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="210"/>
-      <c r="F2" s="211" t="s">
+      <c r="E2" s="211"/>
+      <c r="F2" s="212" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="211"/>
-      <c r="H2" s="210" t="s">
+      <c r="G2" s="212"/>
+      <c r="H2" s="211" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="210"/>
-      <c r="J2" s="211" t="s">
+      <c r="I2" s="211"/>
+      <c r="J2" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="211"/>
-      <c r="L2" s="210" t="s">
+      <c r="K2" s="212"/>
+      <c r="L2" s="211" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="210"/>
-      <c r="N2" s="203" t="s">
+      <c r="M2" s="211"/>
+      <c r="N2" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="203"/>
+      <c r="O2" s="204"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -76669,30 +77007,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="210" t="s">
+      <c r="C2" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="210"/>
-      <c r="E2" s="211" t="s">
+      <c r="D2" s="211"/>
+      <c r="E2" s="212" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="211"/>
-      <c r="G2" s="210" t="s">
+      <c r="F2" s="212"/>
+      <c r="G2" s="211" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="210"/>
-      <c r="I2" s="211" t="s">
+      <c r="H2" s="211"/>
+      <c r="I2" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="211"/>
-      <c r="K2" s="210" t="s">
+      <c r="J2" s="212"/>
+      <c r="K2" s="211" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="210"/>
-      <c r="M2" s="203" t="s">
+      <c r="L2" s="211"/>
+      <c r="M2" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="203"/>
+      <c r="N2" s="204"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -78454,30 +78792,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="210" t="s">
+      <c r="C2" s="211" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="210"/>
-      <c r="E2" s="211" t="s">
+      <c r="D2" s="211"/>
+      <c r="E2" s="212" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="211"/>
-      <c r="G2" s="210" t="s">
+      <c r="F2" s="212"/>
+      <c r="G2" s="211" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="210"/>
-      <c r="I2" s="211" t="s">
+      <c r="H2" s="211"/>
+      <c r="I2" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="211"/>
-      <c r="K2" s="210" t="s">
+      <c r="J2" s="212"/>
+      <c r="K2" s="211" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="210"/>
-      <c r="M2" s="203" t="s">
+      <c r="L2" s="211"/>
+      <c r="M2" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="203"/>
+      <c r="N2" s="204"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8123" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C897D48-7673-454A-A9DC-12BC6684119A}"/>
+  <xr:revisionPtr revIDLastSave="8126" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC5B4784-A036-463C-8FE0-E726CB9134FB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2261" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="479">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -1508,6 +1508,15 @@
   </si>
   <si>
     <t>Zubimendi</t>
+  </si>
+  <si>
+    <t>Goal/Assist</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -3025,6 +3034,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3049,17 +3071,14 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3070,16 +3089,10 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
@@ -3094,8 +3107,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3133,15 +3152,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3149,27 +3159,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3262,67 +3251,31 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3400,6 +3353,63 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3410,7 +3420,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -6466,7 +6475,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A8D9D3BA-55AE-4E33-9A27-93FBD8900B25}" type="CELLRANGE">
+                    <a:fld id="{05DFE6B4-0DD6-4000-BB6B-CB06232603D6}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6500,7 +6509,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{447C6899-1E49-4519-9DEE-898B6FC7AD42}" type="CELLRANGE">
+                    <a:fld id="{CDFCC17D-6990-4CAE-BBF4-ED35F7A73DC3}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6534,7 +6543,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{ECE13C4D-C703-4B20-A493-FD96A62BE61E}" type="CELLRANGE">
+                    <a:fld id="{DB1144B3-755C-4973-AE61-D69CDA9DBFB3}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6568,7 +6577,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EB80AA49-1910-4DD3-A68C-486F41E7E192}" type="CELLRANGE">
+                    <a:fld id="{50C36341-8D57-4489-A6F7-98B4D547316A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6602,7 +6611,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6ED82E4F-615F-469A-9508-59618FF011F8}" type="CELLRANGE">
+                    <a:fld id="{107761F8-8E42-447B-BFA8-9B7013BA3CDD}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6636,7 +6645,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{71019908-35E2-4249-B5A8-3A80F8058B84}" type="CELLRANGE">
+                    <a:fld id="{2AA5BC38-49CD-44AE-99D2-0161B8B10356}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6670,7 +6679,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BEA9914C-33C1-4158-9584-0A264933B1B3}" type="CELLRANGE">
+                    <a:fld id="{10933851-C34F-43F6-8CE2-E140C5529DBF}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6704,7 +6713,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{168F9F10-017C-4B64-9313-5DCD9C998FFD}" type="CELLRANGE">
+                    <a:fld id="{0CEDE7EA-4417-43F3-AB62-399A97C36623}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6738,7 +6747,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8790A575-A1D5-47AB-B9A7-B5FAEC9F5706}" type="CELLRANGE">
+                    <a:fld id="{C0047237-4522-4D0D-BC21-77561446F7E0}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6772,7 +6781,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2BE6183B-6D80-481E-8D98-B8FDB68F7379}" type="CELLRANGE">
+                    <a:fld id="{7A047A7D-C4F9-4345-94CD-B88407EDDD8F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6806,7 +6815,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6A2C9AF7-A3C0-42DF-96A1-2B283EFE6FB6}" type="CELLRANGE">
+                    <a:fld id="{DFD5DB4C-9E61-4106-95BA-61ED74C4E264}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6840,7 +6849,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0722E446-40EB-4925-B2A7-D19E16AE3963}" type="CELLRANGE">
+                    <a:fld id="{730BE71E-1276-41B9-917D-558F534210C8}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6889,7 +6898,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{AEFBB2BC-4D06-4DC2-B5EE-90C427AB85EE}" type="CELLRANGE">
+                    <a:fld id="{62ABC2AE-231E-43D2-AF34-1757E66827E7}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6948,7 +6957,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CA76E409-3428-48F8-B3D2-A5C11E8512DC}" type="CELLRANGE">
+                    <a:fld id="{B5C7245B-45FE-4A05-A79D-3CC83593244B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6982,7 +6991,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C9FB726D-2015-4CFD-8CDE-C583AC6562DF}" type="CELLRANGE">
+                    <a:fld id="{A237FCCD-6B39-42CD-B231-8EA70F341F17}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7016,7 +7025,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EFA745E7-2BD8-432E-BC17-F42EA6E86FB8}" type="CELLRANGE">
+                    <a:fld id="{BE4CBA91-015E-4CAE-88BA-9C26A6D74CB4}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7050,7 +7059,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{22C6CFC9-B2B2-43CB-A3A7-83B6D0AA7B6A}" type="CELLRANGE">
+                    <a:fld id="{3D09A289-CB9E-4D33-9612-9334004D7CAF}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7084,7 +7093,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E78E07B5-1218-496D-85AD-A530619752AE}" type="CELLRANGE">
+                    <a:fld id="{C0D751DB-0EE1-426E-A3AF-07693760F4B0}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14235,30 +14244,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="211" t="s">
+      <c r="C1" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="211"/>
-      <c r="E1" s="212" t="s">
+      <c r="D1" s="204"/>
+      <c r="E1" s="205" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="212"/>
-      <c r="G1" s="211" t="s">
+      <c r="F1" s="205"/>
+      <c r="G1" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="211"/>
-      <c r="I1" s="212" t="s">
+      <c r="H1" s="204"/>
+      <c r="I1" s="205" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="212"/>
-      <c r="K1" s="211" t="s">
+      <c r="J1" s="205"/>
+      <c r="K1" s="204" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="211"/>
-      <c r="M1" s="209" t="s">
+      <c r="L1" s="204"/>
+      <c r="M1" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="210"/>
+      <c r="N1" s="203"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15965,30 +15974,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="211" t="s">
+      <c r="C2" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="211"/>
-      <c r="E2" s="212" t="s">
+      <c r="D2" s="204"/>
+      <c r="E2" s="205" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="212"/>
-      <c r="G2" s="211" t="s">
+      <c r="F2" s="205"/>
+      <c r="G2" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="211"/>
-      <c r="I2" s="212" t="s">
+      <c r="H2" s="204"/>
+      <c r="I2" s="205" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="212"/>
-      <c r="K2" s="211" t="s">
+      <c r="J2" s="205"/>
+      <c r="K2" s="204" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="211"/>
-      <c r="M2" s="204" t="s">
+      <c r="L2" s="204"/>
+      <c r="M2" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="204"/>
+      <c r="N2" s="209"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17792,30 +17801,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="211" t="s">
+      <c r="C2" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="211"/>
-      <c r="E2" s="212" t="s">
+      <c r="D2" s="204"/>
+      <c r="E2" s="205" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="212"/>
-      <c r="G2" s="211" t="s">
+      <c r="F2" s="205"/>
+      <c r="G2" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="211"/>
-      <c r="I2" s="212" t="s">
+      <c r="H2" s="204"/>
+      <c r="I2" s="205" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="212"/>
-      <c r="K2" s="211" t="s">
+      <c r="J2" s="205"/>
+      <c r="K2" s="204" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="211"/>
-      <c r="M2" s="204" t="s">
+      <c r="L2" s="204"/>
+      <c r="M2" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="204"/>
+      <c r="N2" s="209"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19482,30 +19491,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="211" t="s">
+      <c r="C2" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="211"/>
-      <c r="E2" s="212" t="s">
+      <c r="D2" s="204"/>
+      <c r="E2" s="205" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="212"/>
-      <c r="G2" s="211" t="s">
+      <c r="F2" s="205"/>
+      <c r="G2" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="211"/>
-      <c r="I2" s="212" t="s">
+      <c r="H2" s="204"/>
+      <c r="I2" s="205" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="212"/>
-      <c r="K2" s="211" t="s">
+      <c r="J2" s="205"/>
+      <c r="K2" s="204" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="211"/>
-      <c r="M2" s="204" t="s">
+      <c r="L2" s="204"/>
+      <c r="M2" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="204"/>
+      <c r="N2" s="209"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21308,30 +21317,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="211" t="s">
+      <c r="C2" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="211"/>
-      <c r="E2" s="212" t="s">
+      <c r="D2" s="204"/>
+      <c r="E2" s="205" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="212"/>
-      <c r="G2" s="211" t="s">
+      <c r="F2" s="205"/>
+      <c r="G2" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="211"/>
-      <c r="I2" s="212" t="s">
+      <c r="H2" s="204"/>
+      <c r="I2" s="205" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="212"/>
-      <c r="K2" s="211" t="s">
+      <c r="J2" s="205"/>
+      <c r="K2" s="204" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="211"/>
-      <c r="M2" s="204" t="s">
+      <c r="L2" s="204"/>
+      <c r="M2" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="204"/>
+      <c r="N2" s="209"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23180,36 +23189,36 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="201" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="202"/>
-      <c r="E2" s="203"/>
-      <c r="F2" s="206" t="s">
+      <c r="D2" s="207"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="211" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="208"/>
-      <c r="I2" s="201" t="s">
+      <c r="G2" s="212"/>
+      <c r="H2" s="213"/>
+      <c r="I2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="202"/>
-      <c r="K2" s="203"/>
-      <c r="L2" s="206" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="211" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="207"/>
-      <c r="N2" s="208"/>
-      <c r="O2" s="201" t="s">
+      <c r="M2" s="212"/>
+      <c r="N2" s="213"/>
+      <c r="O2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="202"/>
-      <c r="Q2" s="203"/>
-      <c r="R2" s="204" t="s">
+      <c r="P2" s="207"/>
+      <c r="Q2" s="208"/>
+      <c r="R2" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="204"/>
-      <c r="T2" s="204"/>
+      <c r="S2" s="209"/>
+      <c r="T2" s="209"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -26149,36 +26158,36 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="201" t="s">
+      <c r="E1" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="202"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="206" t="s">
+      <c r="F1" s="207"/>
+      <c r="G1" s="208"/>
+      <c r="H1" s="211" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="207"/>
-      <c r="J1" s="208"/>
-      <c r="K1" s="201" t="s">
+      <c r="I1" s="212"/>
+      <c r="J1" s="213"/>
+      <c r="K1" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="202"/>
-      <c r="M1" s="203"/>
-      <c r="N1" s="206" t="s">
+      <c r="L1" s="207"/>
+      <c r="M1" s="208"/>
+      <c r="N1" s="211" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="207"/>
-      <c r="P1" s="208"/>
-      <c r="Q1" s="201" t="s">
+      <c r="O1" s="212"/>
+      <c r="P1" s="213"/>
+      <c r="Q1" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="202"/>
-      <c r="S1" s="203"/>
-      <c r="T1" s="204" t="s">
+      <c r="R1" s="207"/>
+      <c r="S1" s="208"/>
+      <c r="T1" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="204"/>
-      <c r="V1" s="204"/>
+      <c r="U1" s="209"/>
+      <c r="V1" s="209"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37708,399 +37717,399 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="213">
-        <v>1</v>
-      </c>
-      <c r="G1" s="214"/>
-      <c r="H1" s="215"/>
-      <c r="I1" s="213">
+      <c r="F1" s="217">
+        <v>1</v>
+      </c>
+      <c r="G1" s="218"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="217">
         <v>2</v>
       </c>
-      <c r="J1" s="214"/>
-      <c r="K1" s="215"/>
-      <c r="L1" s="213">
-        <v>3</v>
-      </c>
-      <c r="M1" s="214"/>
-      <c r="N1" s="215"/>
-      <c r="O1" s="213">
+      <c r="J1" s="218"/>
+      <c r="K1" s="219"/>
+      <c r="L1" s="217">
+        <v>3</v>
+      </c>
+      <c r="M1" s="218"/>
+      <c r="N1" s="219"/>
+      <c r="O1" s="217">
         <v>4</v>
       </c>
-      <c r="P1" s="214"/>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="213">
+      <c r="P1" s="218"/>
+      <c r="Q1" s="219"/>
+      <c r="R1" s="217">
         <v>5</v>
       </c>
-      <c r="S1" s="214"/>
-      <c r="T1" s="215"/>
-      <c r="U1" s="213">
+      <c r="S1" s="218"/>
+      <c r="T1" s="219"/>
+      <c r="U1" s="217">
         <v>6</v>
       </c>
-      <c r="V1" s="214"/>
-      <c r="W1" s="215"/>
-      <c r="X1" s="213">
+      <c r="V1" s="218"/>
+      <c r="W1" s="219"/>
+      <c r="X1" s="217">
         <v>7</v>
       </c>
-      <c r="Y1" s="214"/>
-      <c r="Z1" s="215"/>
-      <c r="AA1" s="213">
+      <c r="Y1" s="218"/>
+      <c r="Z1" s="219"/>
+      <c r="AA1" s="217">
         <v>8</v>
       </c>
-      <c r="AB1" s="214"/>
-      <c r="AC1" s="215"/>
-      <c r="AD1" s="213">
+      <c r="AB1" s="218"/>
+      <c r="AC1" s="219"/>
+      <c r="AD1" s="217">
         <v>9</v>
       </c>
-      <c r="AE1" s="214"/>
-      <c r="AF1" s="215"/>
-      <c r="AG1" s="213">
+      <c r="AE1" s="218"/>
+      <c r="AF1" s="219"/>
+      <c r="AG1" s="217">
         <v>10</v>
       </c>
-      <c r="AH1" s="214"/>
-      <c r="AI1" s="215"/>
-      <c r="AJ1" s="213">
+      <c r="AH1" s="218"/>
+      <c r="AI1" s="219"/>
+      <c r="AJ1" s="217">
         <v>11</v>
       </c>
-      <c r="AK1" s="214"/>
-      <c r="AL1" s="215"/>
-      <c r="AM1" s="213">
+      <c r="AK1" s="218"/>
+      <c r="AL1" s="219"/>
+      <c r="AM1" s="217">
         <v>12</v>
       </c>
-      <c r="AN1" s="214"/>
-      <c r="AO1" s="215"/>
-      <c r="AP1" s="213">
+      <c r="AN1" s="218"/>
+      <c r="AO1" s="219"/>
+      <c r="AP1" s="217">
         <v>13</v>
       </c>
-      <c r="AQ1" s="214"/>
-      <c r="AR1" s="215"/>
-      <c r="AS1" s="213">
+      <c r="AQ1" s="218"/>
+      <c r="AR1" s="219"/>
+      <c r="AS1" s="217">
         <v>14</v>
       </c>
-      <c r="AT1" s="214"/>
-      <c r="AU1" s="215"/>
-      <c r="AV1" s="213">
+      <c r="AT1" s="218"/>
+      <c r="AU1" s="219"/>
+      <c r="AV1" s="217">
         <v>15</v>
       </c>
-      <c r="AW1" s="214"/>
-      <c r="AX1" s="215"/>
-      <c r="AY1" s="213">
+      <c r="AW1" s="218"/>
+      <c r="AX1" s="219"/>
+      <c r="AY1" s="217">
         <v>16</v>
       </c>
-      <c r="AZ1" s="214"/>
-      <c r="BA1" s="215"/>
-      <c r="BB1" s="213">
+      <c r="AZ1" s="218"/>
+      <c r="BA1" s="219"/>
+      <c r="BB1" s="217">
         <v>17</v>
       </c>
-      <c r="BC1" s="214"/>
-      <c r="BD1" s="215"/>
-      <c r="BE1" s="213">
+      <c r="BC1" s="218"/>
+      <c r="BD1" s="219"/>
+      <c r="BE1" s="217">
         <v>18</v>
       </c>
-      <c r="BF1" s="214"/>
-      <c r="BG1" s="215"/>
-      <c r="BH1" s="213">
+      <c r="BF1" s="218"/>
+      <c r="BG1" s="219"/>
+      <c r="BH1" s="217">
         <v>19</v>
       </c>
-      <c r="BI1" s="214"/>
-      <c r="BJ1" s="215"/>
-      <c r="BK1" s="213">
+      <c r="BI1" s="218"/>
+      <c r="BJ1" s="219"/>
+      <c r="BK1" s="217">
         <v>20</v>
       </c>
-      <c r="BL1" s="214"/>
-      <c r="BM1" s="215"/>
-      <c r="BN1" s="213">
+      <c r="BL1" s="218"/>
+      <c r="BM1" s="219"/>
+      <c r="BN1" s="217">
         <v>21</v>
       </c>
-      <c r="BO1" s="214"/>
-      <c r="BP1" s="215"/>
-      <c r="BQ1" s="213">
+      <c r="BO1" s="218"/>
+      <c r="BP1" s="219"/>
+      <c r="BQ1" s="217">
         <v>22</v>
       </c>
-      <c r="BR1" s="214"/>
-      <c r="BS1" s="215"/>
-      <c r="BT1" s="213">
+      <c r="BR1" s="218"/>
+      <c r="BS1" s="219"/>
+      <c r="BT1" s="217">
         <v>23</v>
       </c>
-      <c r="BU1" s="214"/>
-      <c r="BV1" s="215"/>
-      <c r="BW1" s="213">
+      <c r="BU1" s="218"/>
+      <c r="BV1" s="219"/>
+      <c r="BW1" s="217">
         <v>24</v>
       </c>
-      <c r="BX1" s="214"/>
-      <c r="BY1" s="215"/>
-      <c r="BZ1" s="213">
+      <c r="BX1" s="218"/>
+      <c r="BY1" s="219"/>
+      <c r="BZ1" s="217">
         <v>25</v>
       </c>
-      <c r="CA1" s="214"/>
-      <c r="CB1" s="215"/>
-      <c r="CC1" s="213">
+      <c r="CA1" s="218"/>
+      <c r="CB1" s="219"/>
+      <c r="CC1" s="217">
         <v>26</v>
       </c>
-      <c r="CD1" s="214"/>
-      <c r="CE1" s="215"/>
-      <c r="CF1" s="213">
+      <c r="CD1" s="218"/>
+      <c r="CE1" s="219"/>
+      <c r="CF1" s="217">
         <v>27</v>
       </c>
-      <c r="CG1" s="214"/>
-      <c r="CH1" s="215"/>
-      <c r="CI1" s="213">
+      <c r="CG1" s="218"/>
+      <c r="CH1" s="219"/>
+      <c r="CI1" s="217">
         <v>28</v>
       </c>
-      <c r="CJ1" s="214"/>
-      <c r="CK1" s="215"/>
-      <c r="CL1" s="213">
+      <c r="CJ1" s="218"/>
+      <c r="CK1" s="219"/>
+      <c r="CL1" s="217">
         <v>29</v>
       </c>
-      <c r="CM1" s="214"/>
-      <c r="CN1" s="215"/>
-      <c r="CO1" s="213">
+      <c r="CM1" s="218"/>
+      <c r="CN1" s="219"/>
+      <c r="CO1" s="217">
         <v>30</v>
       </c>
-      <c r="CP1" s="214"/>
-      <c r="CQ1" s="215"/>
-      <c r="CR1" s="213">
+      <c r="CP1" s="218"/>
+      <c r="CQ1" s="219"/>
+      <c r="CR1" s="217">
         <v>31</v>
       </c>
-      <c r="CS1" s="214"/>
-      <c r="CT1" s="215"/>
-      <c r="CU1" s="213">
+      <c r="CS1" s="218"/>
+      <c r="CT1" s="219"/>
+      <c r="CU1" s="217">
         <v>32</v>
       </c>
-      <c r="CV1" s="214"/>
-      <c r="CW1" s="215"/>
-      <c r="CX1" s="213">
+      <c r="CV1" s="218"/>
+      <c r="CW1" s="219"/>
+      <c r="CX1" s="217">
         <v>33</v>
       </c>
-      <c r="CY1" s="214"/>
-      <c r="CZ1" s="215"/>
-      <c r="DA1" s="213">
+      <c r="CY1" s="218"/>
+      <c r="CZ1" s="219"/>
+      <c r="DA1" s="217">
         <v>34</v>
       </c>
-      <c r="DB1" s="214"/>
-      <c r="DC1" s="215"/>
-      <c r="DD1" s="213">
+      <c r="DB1" s="218"/>
+      <c r="DC1" s="219"/>
+      <c r="DD1" s="217">
         <v>35</v>
       </c>
-      <c r="DE1" s="214"/>
-      <c r="DF1" s="215"/>
-      <c r="DG1" s="213">
+      <c r="DE1" s="218"/>
+      <c r="DF1" s="219"/>
+      <c r="DG1" s="217">
         <v>36</v>
       </c>
-      <c r="DH1" s="214"/>
-      <c r="DI1" s="215"/>
-      <c r="DJ1" s="213">
+      <c r="DH1" s="218"/>
+      <c r="DI1" s="219"/>
+      <c r="DJ1" s="217">
         <v>37</v>
       </c>
-      <c r="DK1" s="214"/>
-      <c r="DL1" s="215"/>
-      <c r="DM1" s="213">
+      <c r="DK1" s="218"/>
+      <c r="DL1" s="219"/>
+      <c r="DM1" s="217">
         <v>38</v>
       </c>
-      <c r="DN1" s="214"/>
-      <c r="DO1" s="215"/>
+      <c r="DN1" s="218"/>
+      <c r="DO1" s="219"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="219" t="s">
+      <c r="C2" s="220" t="s">
         <v>396</v>
       </c>
-      <c r="D2" s="219" t="s">
+      <c r="D2" s="220" t="s">
         <v>397</v>
       </c>
-      <c r="E2" s="219" t="s">
+      <c r="E2" s="220" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="216" t="s">
+      <c r="F2" s="214" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="217"/>
-      <c r="H2" s="218"/>
-      <c r="I2" s="221" t="s">
+      <c r="G2" s="215"/>
+      <c r="H2" s="216"/>
+      <c r="I2" s="223" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="222"/>
-      <c r="K2" s="223"/>
-      <c r="L2" s="216" t="s">
+      <c r="J2" s="224"/>
+      <c r="K2" s="225"/>
+      <c r="L2" s="214" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="217"/>
-      <c r="N2" s="218"/>
-      <c r="O2" s="216" t="s">
+      <c r="M2" s="215"/>
+      <c r="N2" s="216"/>
+      <c r="O2" s="214" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="217"/>
-      <c r="Q2" s="218"/>
-      <c r="R2" s="216" t="s">
+      <c r="P2" s="215"/>
+      <c r="Q2" s="216"/>
+      <c r="R2" s="214" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="217"/>
-      <c r="T2" s="218"/>
-      <c r="U2" s="216" t="s">
+      <c r="S2" s="215"/>
+      <c r="T2" s="216"/>
+      <c r="U2" s="214" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="217"/>
-      <c r="W2" s="218"/>
-      <c r="X2" s="216" t="s">
+      <c r="V2" s="215"/>
+      <c r="W2" s="216"/>
+      <c r="X2" s="214" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="217"/>
-      <c r="Z2" s="218"/>
-      <c r="AA2" s="216" t="s">
+      <c r="Y2" s="215"/>
+      <c r="Z2" s="216"/>
+      <c r="AA2" s="214" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="217"/>
-      <c r="AC2" s="218"/>
-      <c r="AD2" s="216" t="s">
+      <c r="AB2" s="215"/>
+      <c r="AC2" s="216"/>
+      <c r="AD2" s="214" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="217"/>
-      <c r="AF2" s="218"/>
-      <c r="AG2" s="216" t="s">
+      <c r="AE2" s="215"/>
+      <c r="AF2" s="216"/>
+      <c r="AG2" s="214" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="217"/>
-      <c r="AI2" s="218"/>
-      <c r="AJ2" s="216" t="s">
+      <c r="AH2" s="215"/>
+      <c r="AI2" s="216"/>
+      <c r="AJ2" s="214" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="217"/>
-      <c r="AL2" s="218"/>
-      <c r="AM2" s="216" t="s">
+      <c r="AK2" s="215"/>
+      <c r="AL2" s="216"/>
+      <c r="AM2" s="214" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="217"/>
-      <c r="AO2" s="218"/>
-      <c r="AP2" s="216" t="s">
+      <c r="AN2" s="215"/>
+      <c r="AO2" s="216"/>
+      <c r="AP2" s="214" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="217"/>
-      <c r="AR2" s="218"/>
-      <c r="AS2" s="216" t="s">
+      <c r="AQ2" s="215"/>
+      <c r="AR2" s="216"/>
+      <c r="AS2" s="214" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="217"/>
-      <c r="AU2" s="218"/>
-      <c r="AV2" s="216" t="s">
+      <c r="AT2" s="215"/>
+      <c r="AU2" s="216"/>
+      <c r="AV2" s="214" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="217"/>
-      <c r="AX2" s="218"/>
-      <c r="AY2" s="216" t="s">
+      <c r="AW2" s="215"/>
+      <c r="AX2" s="216"/>
+      <c r="AY2" s="214" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="217"/>
-      <c r="BA2" s="218"/>
-      <c r="BB2" s="216" t="s">
+      <c r="AZ2" s="215"/>
+      <c r="BA2" s="216"/>
+      <c r="BB2" s="214" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="217"/>
-      <c r="BD2" s="218"/>
-      <c r="BE2" s="216" t="s">
+      <c r="BC2" s="215"/>
+      <c r="BD2" s="216"/>
+      <c r="BE2" s="214" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="217"/>
-      <c r="BG2" s="218"/>
-      <c r="BH2" s="216" t="s">
+      <c r="BF2" s="215"/>
+      <c r="BG2" s="216"/>
+      <c r="BH2" s="214" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="217"/>
-      <c r="BJ2" s="218"/>
-      <c r="BK2" s="216" t="s">
+      <c r="BI2" s="215"/>
+      <c r="BJ2" s="216"/>
+      <c r="BK2" s="214" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="217"/>
-      <c r="BM2" s="218"/>
-      <c r="BN2" s="216" t="s">
+      <c r="BL2" s="215"/>
+      <c r="BM2" s="216"/>
+      <c r="BN2" s="214" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="217"/>
-      <c r="BP2" s="218"/>
-      <c r="BQ2" s="216" t="s">
+      <c r="BO2" s="215"/>
+      <c r="BP2" s="216"/>
+      <c r="BQ2" s="214" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="217"/>
-      <c r="BS2" s="218"/>
-      <c r="BT2" s="216" t="s">
+      <c r="BR2" s="215"/>
+      <c r="BS2" s="216"/>
+      <c r="BT2" s="214" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="217"/>
-      <c r="BV2" s="218"/>
-      <c r="BW2" s="216" t="s">
+      <c r="BU2" s="215"/>
+      <c r="BV2" s="216"/>
+      <c r="BW2" s="214" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="217"/>
-      <c r="BY2" s="218"/>
-      <c r="BZ2" s="216" t="s">
+      <c r="BX2" s="215"/>
+      <c r="BY2" s="216"/>
+      <c r="BZ2" s="214" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="217"/>
-      <c r="CB2" s="218"/>
-      <c r="CC2" s="216" t="s">
+      <c r="CA2" s="215"/>
+      <c r="CB2" s="216"/>
+      <c r="CC2" s="214" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="217"/>
-      <c r="CE2" s="218"/>
-      <c r="CF2" s="216" t="s">
+      <c r="CD2" s="215"/>
+      <c r="CE2" s="216"/>
+      <c r="CF2" s="214" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="217"/>
-      <c r="CH2" s="218"/>
-      <c r="CI2" s="216" t="s">
+      <c r="CG2" s="215"/>
+      <c r="CH2" s="216"/>
+      <c r="CI2" s="214" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="217"/>
-      <c r="CK2" s="218"/>
-      <c r="CL2" s="216" t="s">
+      <c r="CJ2" s="215"/>
+      <c r="CK2" s="216"/>
+      <c r="CL2" s="214" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="217"/>
-      <c r="CN2" s="218"/>
-      <c r="CO2" s="216" t="s">
+      <c r="CM2" s="215"/>
+      <c r="CN2" s="216"/>
+      <c r="CO2" s="214" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="217"/>
-      <c r="CQ2" s="218"/>
-      <c r="CR2" s="216" t="s">
+      <c r="CP2" s="215"/>
+      <c r="CQ2" s="216"/>
+      <c r="CR2" s="214" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="217"/>
-      <c r="CT2" s="218"/>
-      <c r="CU2" s="216" t="s">
+      <c r="CS2" s="215"/>
+      <c r="CT2" s="216"/>
+      <c r="CU2" s="214" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="217"/>
-      <c r="CW2" s="218"/>
-      <c r="CX2" s="216" t="s">
+      <c r="CV2" s="215"/>
+      <c r="CW2" s="216"/>
+      <c r="CX2" s="214" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="217"/>
-      <c r="CZ2" s="218"/>
-      <c r="DA2" s="216" t="s">
+      <c r="CY2" s="215"/>
+      <c r="CZ2" s="216"/>
+      <c r="DA2" s="214" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="217"/>
-      <c r="DC2" s="218"/>
-      <c r="DD2" s="216" t="s">
+      <c r="DB2" s="215"/>
+      <c r="DC2" s="216"/>
+      <c r="DD2" s="214" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="217"/>
-      <c r="DF2" s="218"/>
-      <c r="DG2" s="216" t="s">
+      <c r="DE2" s="215"/>
+      <c r="DF2" s="216"/>
+      <c r="DG2" s="214" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="217"/>
-      <c r="DI2" s="218"/>
-      <c r="DJ2" s="216" t="s">
+      <c r="DH2" s="215"/>
+      <c r="DI2" s="216"/>
+      <c r="DJ2" s="214" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="217"/>
-      <c r="DL2" s="218"/>
-      <c r="DM2" s="216" t="s">
+      <c r="DK2" s="215"/>
+      <c r="DL2" s="216"/>
+      <c r="DM2" s="214" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="217"/>
-      <c r="DO2" s="218"/>
+      <c r="DN2" s="215"/>
+      <c r="DO2" s="216"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38109,9 +38118,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="224"/>
-      <c r="D3" s="224"/>
-      <c r="E3" s="220"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="221"/>
+      <c r="E3" s="222"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
       </c>
@@ -43688,6 +43697,69 @@
     </row>
   </sheetData>
   <mergeCells count="79">
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43704,69 +43776,6 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO38">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -43802,122 +43811,122 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="234" t="s">
+      <c r="C1" s="238" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="234" t="s">
+      <c r="D1" s="238" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="234" t="s">
+      <c r="E1" s="238" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="225" t="s">
+      <c r="F1" s="229" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="226"/>
-      <c r="H1" s="226"/>
-      <c r="I1" s="226"/>
-      <c r="J1" s="226"/>
-      <c r="K1" s="226"/>
-      <c r="L1" s="226"/>
-      <c r="M1" s="226"/>
-      <c r="N1" s="226"/>
-      <c r="O1" s="226"/>
-      <c r="P1" s="226"/>
-      <c r="Q1" s="226"/>
-      <c r="R1" s="226"/>
-      <c r="S1" s="226"/>
-      <c r="T1" s="226"/>
-      <c r="U1" s="226"/>
-      <c r="V1" s="226"/>
-      <c r="W1" s="226"/>
-      <c r="X1" s="226"/>
-      <c r="Y1" s="226"/>
-      <c r="Z1" s="226"/>
-      <c r="AA1" s="226"/>
-      <c r="AB1" s="226"/>
-      <c r="AC1" s="227"/>
-      <c r="AD1" s="240" t="s">
+      <c r="G1" s="230"/>
+      <c r="H1" s="230"/>
+      <c r="I1" s="230"/>
+      <c r="J1" s="230"/>
+      <c r="K1" s="230"/>
+      <c r="L1" s="230"/>
+      <c r="M1" s="230"/>
+      <c r="N1" s="230"/>
+      <c r="O1" s="230"/>
+      <c r="P1" s="230"/>
+      <c r="Q1" s="230"/>
+      <c r="R1" s="230"/>
+      <c r="S1" s="230"/>
+      <c r="T1" s="230"/>
+      <c r="U1" s="230"/>
+      <c r="V1" s="230"/>
+      <c r="W1" s="230"/>
+      <c r="X1" s="230"/>
+      <c r="Y1" s="230"/>
+      <c r="Z1" s="230"/>
+      <c r="AA1" s="230"/>
+      <c r="AB1" s="230"/>
+      <c r="AC1" s="231"/>
+      <c r="AD1" s="241" t="s">
         <v>281</v>
       </c>
-      <c r="AE1" s="241"/>
-      <c r="AF1" s="241"/>
-      <c r="AG1" s="241"/>
-      <c r="AH1" s="241"/>
-      <c r="AI1" s="242"/>
-      <c r="AJ1" s="225" t="s">
+      <c r="AE1" s="242"/>
+      <c r="AF1" s="242"/>
+      <c r="AG1" s="242"/>
+      <c r="AH1" s="242"/>
+      <c r="AI1" s="243"/>
+      <c r="AJ1" s="229" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="226"/>
-      <c r="AL1" s="226"/>
-      <c r="AM1" s="226"/>
-      <c r="AN1" s="226"/>
-      <c r="AO1" s="227"/>
-      <c r="AP1" s="228" t="s">
+      <c r="AK1" s="230"/>
+      <c r="AL1" s="230"/>
+      <c r="AM1" s="230"/>
+      <c r="AN1" s="230"/>
+      <c r="AO1" s="231"/>
+      <c r="AP1" s="232" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="229"/>
-      <c r="AR1" s="229"/>
-      <c r="AS1" s="229"/>
-      <c r="AT1" s="229"/>
-      <c r="AU1" s="230"/>
-      <c r="AV1" s="231" t="s">
+      <c r="AQ1" s="233"/>
+      <c r="AR1" s="233"/>
+      <c r="AS1" s="233"/>
+      <c r="AT1" s="233"/>
+      <c r="AU1" s="234"/>
+      <c r="AV1" s="235" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="232"/>
-      <c r="AX1" s="233"/>
+      <c r="AW1" s="236"/>
+      <c r="AX1" s="237"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="237"/>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239"/>
-      <c r="I2" s="237"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="239"/>
-      <c r="L2" s="237"/>
-      <c r="M2" s="238"/>
-      <c r="N2" s="239"/>
-      <c r="O2" s="237"/>
-      <c r="P2" s="238"/>
-      <c r="Q2" s="239"/>
-      <c r="R2" s="237"/>
-      <c r="S2" s="238"/>
-      <c r="T2" s="239"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="239"/>
-      <c r="X2" s="237"/>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="239"/>
-      <c r="AA2" s="237"/>
-      <c r="AB2" s="238"/>
-      <c r="AC2" s="238"/>
-      <c r="AD2" s="237"/>
-      <c r="AE2" s="238"/>
-      <c r="AF2" s="239"/>
-      <c r="AG2" s="237"/>
-      <c r="AH2" s="238"/>
-      <c r="AI2" s="239"/>
-      <c r="AJ2" s="237"/>
-      <c r="AK2" s="238"/>
-      <c r="AL2" s="239"/>
-      <c r="AM2" s="237"/>
-      <c r="AN2" s="238"/>
-      <c r="AO2" s="239"/>
-      <c r="AP2" s="237"/>
-      <c r="AQ2" s="238"/>
-      <c r="AR2" s="239"/>
-      <c r="AS2" s="237"/>
-      <c r="AT2" s="238"/>
-      <c r="AU2" s="239"/>
-      <c r="AV2" s="237"/>
-      <c r="AW2" s="238"/>
-      <c r="AX2" s="239"/>
+      <c r="C2" s="239"/>
+      <c r="D2" s="239"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="227"/>
+      <c r="H2" s="228"/>
+      <c r="I2" s="226"/>
+      <c r="J2" s="227"/>
+      <c r="K2" s="228"/>
+      <c r="L2" s="226"/>
+      <c r="M2" s="227"/>
+      <c r="N2" s="228"/>
+      <c r="O2" s="226"/>
+      <c r="P2" s="227"/>
+      <c r="Q2" s="228"/>
+      <c r="R2" s="226"/>
+      <c r="S2" s="227"/>
+      <c r="T2" s="228"/>
+      <c r="U2" s="226"/>
+      <c r="V2" s="227"/>
+      <c r="W2" s="228"/>
+      <c r="X2" s="226"/>
+      <c r="Y2" s="227"/>
+      <c r="Z2" s="228"/>
+      <c r="AA2" s="226"/>
+      <c r="AB2" s="227"/>
+      <c r="AC2" s="227"/>
+      <c r="AD2" s="226"/>
+      <c r="AE2" s="227"/>
+      <c r="AF2" s="228"/>
+      <c r="AG2" s="226"/>
+      <c r="AH2" s="227"/>
+      <c r="AI2" s="228"/>
+      <c r="AJ2" s="226"/>
+      <c r="AK2" s="227"/>
+      <c r="AL2" s="228"/>
+      <c r="AM2" s="226"/>
+      <c r="AN2" s="227"/>
+      <c r="AO2" s="228"/>
+      <c r="AP2" s="226"/>
+      <c r="AQ2" s="227"/>
+      <c r="AR2" s="228"/>
+      <c r="AS2" s="226"/>
+      <c r="AT2" s="227"/>
+      <c r="AU2" s="228"/>
+      <c r="AV2" s="226"/>
+      <c r="AW2" s="227"/>
+      <c r="AX2" s="228"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -43926,9 +43935,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="236"/>
-      <c r="D3" s="236"/>
-      <c r="E3" s="236"/>
+      <c r="C3" s="240"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
       <c r="F3" s="170" t="s">
         <v>393</v>
       </c>
@@ -46524,13 +46533,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46547,6 +46549,13 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW32">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46581,70 +46590,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="234" t="s">
+      <c r="C1" s="238" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="234" t="s">
+      <c r="D1" s="238" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="234" t="s">
+      <c r="E1" s="238" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="274" t="s">
+      <c r="F1" s="268" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="275"/>
-      <c r="H1" s="276"/>
-      <c r="I1" s="277" t="s">
+      <c r="G1" s="269"/>
+      <c r="H1" s="270"/>
+      <c r="I1" s="271" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="278"/>
-      <c r="K1" s="279"/>
-      <c r="L1" s="244" t="s">
+      <c r="J1" s="272"/>
+      <c r="K1" s="273"/>
+      <c r="L1" s="275" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="245"/>
-      <c r="N1" s="246"/>
-      <c r="O1" s="247" t="s">
+      <c r="M1" s="276"/>
+      <c r="N1" s="277"/>
+      <c r="O1" s="278" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="248"/>
-      <c r="Q1" s="249"/>
-      <c r="R1" s="250" t="s">
+      <c r="P1" s="279"/>
+      <c r="Q1" s="280"/>
+      <c r="R1" s="244" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="251"/>
-      <c r="T1" s="252"/>
-      <c r="U1" s="253" t="s">
+      <c r="S1" s="245"/>
+      <c r="T1" s="246"/>
+      <c r="U1" s="247" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="254"/>
-      <c r="W1" s="255"/>
+      <c r="V1" s="248"/>
+      <c r="W1" s="249"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="257"/>
-      <c r="H2" s="258"/>
-      <c r="I2" s="271"/>
-      <c r="J2" s="272"/>
-      <c r="K2" s="273"/>
-      <c r="L2" s="268"/>
-      <c r="M2" s="269"/>
-      <c r="N2" s="270"/>
-      <c r="O2" s="265"/>
-      <c r="P2" s="266"/>
-      <c r="Q2" s="267"/>
-      <c r="R2" s="262"/>
-      <c r="S2" s="263"/>
-      <c r="T2" s="264"/>
-      <c r="U2" s="259"/>
-      <c r="V2" s="260"/>
-      <c r="W2" s="261"/>
+      <c r="C2" s="239"/>
+      <c r="D2" s="239"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="250"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252"/>
+      <c r="I2" s="265"/>
+      <c r="J2" s="266"/>
+      <c r="K2" s="267"/>
+      <c r="L2" s="262"/>
+      <c r="M2" s="263"/>
+      <c r="N2" s="264"/>
+      <c r="O2" s="259"/>
+      <c r="P2" s="260"/>
+      <c r="Q2" s="261"/>
+      <c r="R2" s="256"/>
+      <c r="S2" s="257"/>
+      <c r="T2" s="258"/>
+      <c r="U2" s="253"/>
+      <c r="V2" s="254"/>
+      <c r="W2" s="255"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46653,9 +46662,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="243"/>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
+      <c r="C3" s="274"/>
+      <c r="D3" s="274"/>
+      <c r="E3" s="274"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -48117,6 +48126,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -48127,11 +48141,6 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -55138,72 +55147,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="234" t="s">
+      <c r="C1" s="238" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="234" t="s">
+      <c r="D1" s="238" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="234" t="s">
+      <c r="E1" s="238" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="274" t="s">
+      <c r="F1" s="268" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="275"/>
-      <c r="H1" s="276"/>
-      <c r="I1" s="277" t="s">
+      <c r="G1" s="269"/>
+      <c r="H1" s="270"/>
+      <c r="I1" s="271" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="278"/>
-      <c r="K1" s="279"/>
-      <c r="L1" s="244" t="s">
+      <c r="J1" s="272"/>
+      <c r="K1" s="273"/>
+      <c r="L1" s="275" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="245"/>
-      <c r="N1" s="246"/>
-      <c r="O1" s="247" t="s">
+      <c r="M1" s="276"/>
+      <c r="N1" s="277"/>
+      <c r="O1" s="278" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="248"/>
-      <c r="Q1" s="249"/>
-      <c r="R1" s="250" t="s">
+      <c r="P1" s="279"/>
+      <c r="Q1" s="280"/>
+      <c r="R1" s="244" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="251"/>
-      <c r="T1" s="252"/>
-      <c r="U1" s="253" t="s">
+      <c r="S1" s="245"/>
+      <c r="T1" s="246"/>
+      <c r="U1" s="247" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="254"/>
-      <c r="W1" s="255"/>
+      <c r="V1" s="248"/>
+      <c r="W1" s="249"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="256" t="s">
+      <c r="C2" s="239"/>
+      <c r="D2" s="239"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="250" t="s">
         <v>438</v>
       </c>
-      <c r="G2" s="257"/>
-      <c r="H2" s="258"/>
-      <c r="I2" s="271"/>
-      <c r="J2" s="272"/>
-      <c r="K2" s="273"/>
-      <c r="L2" s="268"/>
-      <c r="M2" s="269"/>
-      <c r="N2" s="270"/>
-      <c r="O2" s="265"/>
-      <c r="P2" s="266"/>
-      <c r="Q2" s="267"/>
-      <c r="R2" s="262"/>
-      <c r="S2" s="263"/>
-      <c r="T2" s="264"/>
-      <c r="U2" s="259"/>
-      <c r="V2" s="260"/>
-      <c r="W2" s="261"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252"/>
+      <c r="I2" s="265"/>
+      <c r="J2" s="266"/>
+      <c r="K2" s="267"/>
+      <c r="L2" s="262"/>
+      <c r="M2" s="263"/>
+      <c r="N2" s="264"/>
+      <c r="O2" s="259"/>
+      <c r="P2" s="260"/>
+      <c r="Q2" s="261"/>
+      <c r="R2" s="256"/>
+      <c r="S2" s="257"/>
+      <c r="T2" s="258"/>
+      <c r="U2" s="253"/>
+      <c r="V2" s="254"/>
+      <c r="W2" s="255"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -55212,9 +55221,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="243"/>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
+      <c r="C3" s="274"/>
+      <c r="D3" s="274"/>
+      <c r="E3" s="274"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -56676,11 +56685,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -56691,6 +56695,11 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -56718,11 +56727,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C1" s="280" t="s">
+      <c r="C1" s="281" t="s">
         <v>340</v>
       </c>
-      <c r="D1" s="281"/>
-      <c r="E1" s="281"/>
+      <c r="D1" s="282"/>
+      <c r="E1" s="282"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -57197,51 +57206,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="302" t="s">
+      <c r="C1" s="284" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="303"/>
-      <c r="E1" s="303"/>
-      <c r="F1" s="303"/>
-      <c r="G1" s="303"/>
-      <c r="H1" s="303"/>
-      <c r="I1" s="304"/>
+      <c r="D1" s="285"/>
+      <c r="E1" s="285"/>
+      <c r="F1" s="285"/>
+      <c r="G1" s="285"/>
+      <c r="H1" s="285"/>
+      <c r="I1" s="286"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="282" t="s">
+      <c r="L1" s="308" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="287"/>
-      <c r="N1" s="287"/>
-      <c r="O1" s="287"/>
-      <c r="P1" s="287"/>
-      <c r="Q1" s="287"/>
-      <c r="R1" s="287"/>
-      <c r="S1" s="287"/>
-      <c r="T1" s="287"/>
-      <c r="U1" s="287"/>
-      <c r="V1" s="287"/>
-      <c r="W1" s="287"/>
-      <c r="X1" s="287"/>
-      <c r="Y1" s="287"/>
-      <c r="Z1" s="287"/>
-      <c r="AA1" s="287"/>
-      <c r="AB1" s="287"/>
-      <c r="AC1" s="287"/>
-      <c r="AD1" s="287"/>
-      <c r="AE1" s="287"/>
-      <c r="AF1" s="287"/>
-      <c r="AG1" s="288"/>
-      <c r="AH1" s="282" t="s">
+      <c r="M1" s="313"/>
+      <c r="N1" s="313"/>
+      <c r="O1" s="313"/>
+      <c r="P1" s="313"/>
+      <c r="Q1" s="313"/>
+      <c r="R1" s="313"/>
+      <c r="S1" s="313"/>
+      <c r="T1" s="313"/>
+      <c r="U1" s="313"/>
+      <c r="V1" s="313"/>
+      <c r="W1" s="313"/>
+      <c r="X1" s="313"/>
+      <c r="Y1" s="313"/>
+      <c r="Z1" s="313"/>
+      <c r="AA1" s="313"/>
+      <c r="AB1" s="313"/>
+      <c r="AC1" s="313"/>
+      <c r="AD1" s="313"/>
+      <c r="AE1" s="313"/>
+      <c r="AF1" s="313"/>
+      <c r="AG1" s="314"/>
+      <c r="AH1" s="308" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="283"/>
-      <c r="AJ1" s="283"/>
-      <c r="AK1" s="284"/>
+      <c r="AI1" s="309"/>
+      <c r="AJ1" s="309"/>
+      <c r="AK1" s="310"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -62441,15 +62450,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="289" t="s">
+      <c r="K80" s="315" t="s">
         <v>442</v>
       </c>
-      <c r="L80" s="290"/>
-      <c r="M80" s="291"/>
+      <c r="L80" s="316"/>
+      <c r="M80" s="317"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="285"/>
-      <c r="X80" s="285"/>
+      <c r="W80" s="311"/>
+      <c r="X80" s="311"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -62499,15 +62508,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="292"/>
-      <c r="L81" s="293"/>
-      <c r="M81" s="294"/>
+      <c r="K81" s="318"/>
+      <c r="L81" s="319"/>
+      <c r="M81" s="320"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="285" t="s">
+      <c r="W81" s="311" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="285"/>
+      <c r="X81" s="311"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62563,17 +62572,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="295" t="s">
+      <c r="K82" s="321" t="s">
         <v>443</v>
       </c>
-      <c r="L82" s="296"/>
-      <c r="M82" s="297"/>
+      <c r="L82" s="322"/>
+      <c r="M82" s="323"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="285" t="s">
+      <c r="W82" s="311" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="285"/>
+      <c r="X82" s="311"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62629,17 +62638,17 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="298" t="s">
+      <c r="K83" s="324" t="s">
         <v>444</v>
       </c>
-      <c r="L83" s="299"/>
-      <c r="M83" s="300"/>
+      <c r="L83" s="325"/>
+      <c r="M83" s="326"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="286" t="s">
+      <c r="W83" s="312" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="286"/>
+      <c r="X83" s="312"/>
       <c r="Y83" s="196">
         <v>220</v>
       </c>
@@ -62692,15 +62701,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="317" t="s">
+      <c r="K84" s="299" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="318"/>
-      <c r="M84" s="319"/>
+      <c r="L84" s="300"/>
+      <c r="M84" s="301"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="301"/>
-      <c r="X84" s="301"/>
+      <c r="W84" s="283"/>
+      <c r="X84" s="283"/>
       <c r="Y84" s="198"/>
       <c r="Z84" s="198"/>
       <c r="AA84" s="198"/>
@@ -62738,9 +62747,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="320"/>
-      <c r="L85" s="321"/>
-      <c r="M85" s="322"/>
+      <c r="K85" s="302"/>
+      <c r="L85" s="303"/>
+      <c r="M85" s="304"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -62774,9 +62783,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="320"/>
-      <c r="L86" s="321"/>
-      <c r="M86" s="322"/>
+      <c r="K86" s="302"/>
+      <c r="L86" s="303"/>
+      <c r="M86" s="304"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -62810,9 +62819,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="320"/>
-      <c r="L87" s="321"/>
-      <c r="M87" s="322"/>
+      <c r="K87" s="302"/>
+      <c r="L87" s="303"/>
+      <c r="M87" s="304"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -62846,9 +62855,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="320"/>
-      <c r="L88" s="321"/>
-      <c r="M88" s="322"/>
+      <c r="K88" s="302"/>
+      <c r="L88" s="303"/>
+      <c r="M88" s="304"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -62882,9 +62891,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="320"/>
-      <c r="L89" s="321"/>
-      <c r="M89" s="322"/>
+      <c r="K89" s="302"/>
+      <c r="L89" s="303"/>
+      <c r="M89" s="304"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -62918,9 +62927,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="320"/>
-      <c r="L90" s="321"/>
-      <c r="M90" s="322"/>
+      <c r="K90" s="302"/>
+      <c r="L90" s="303"/>
+      <c r="M90" s="304"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -62954,9 +62963,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="320"/>
-      <c r="L91" s="321"/>
-      <c r="M91" s="322"/>
+      <c r="K91" s="302"/>
+      <c r="L91" s="303"/>
+      <c r="M91" s="304"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -62990,9 +62999,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="320"/>
-      <c r="L92" s="321"/>
-      <c r="M92" s="322"/>
+      <c r="K92" s="302"/>
+      <c r="L92" s="303"/>
+      <c r="M92" s="304"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -63026,9 +63035,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="320"/>
-      <c r="L93" s="321"/>
-      <c r="M93" s="322"/>
+      <c r="K93" s="302"/>
+      <c r="L93" s="303"/>
+      <c r="M93" s="304"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -63062,9 +63071,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="320"/>
-      <c r="L94" s="321"/>
-      <c r="M94" s="322"/>
+      <c r="K94" s="302"/>
+      <c r="L94" s="303"/>
+      <c r="M94" s="304"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -63098,9 +63107,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="320"/>
-      <c r="L95" s="321"/>
-      <c r="M95" s="322"/>
+      <c r="K95" s="302"/>
+      <c r="L95" s="303"/>
+      <c r="M95" s="304"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -63134,9 +63143,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="320"/>
-      <c r="L96" s="321"/>
-      <c r="M96" s="322"/>
+      <c r="K96" s="302"/>
+      <c r="L96" s="303"/>
+      <c r="M96" s="304"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -63170,9 +63179,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="320"/>
-      <c r="L97" s="321"/>
-      <c r="M97" s="322"/>
+      <c r="K97" s="302"/>
+      <c r="L97" s="303"/>
+      <c r="M97" s="304"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -63206,9 +63215,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="320"/>
-      <c r="L98" s="321"/>
-      <c r="M98" s="322"/>
+      <c r="K98" s="302"/>
+      <c r="L98" s="303"/>
+      <c r="M98" s="304"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -63242,9 +63251,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="320"/>
-      <c r="L99" s="321"/>
-      <c r="M99" s="322"/>
+      <c r="K99" s="302"/>
+      <c r="L99" s="303"/>
+      <c r="M99" s="304"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -63278,9 +63287,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="320"/>
-      <c r="L100" s="321"/>
-      <c r="M100" s="322"/>
+      <c r="K100" s="302"/>
+      <c r="L100" s="303"/>
+      <c r="M100" s="304"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -63314,9 +63323,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="320"/>
-      <c r="L101" s="321"/>
-      <c r="M101" s="322"/>
+      <c r="K101" s="302"/>
+      <c r="L101" s="303"/>
+      <c r="M101" s="304"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -63350,9 +63359,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="320"/>
-      <c r="L102" s="321"/>
-      <c r="M102" s="322"/>
+      <c r="K102" s="302"/>
+      <c r="L102" s="303"/>
+      <c r="M102" s="304"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -63386,9 +63395,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="320"/>
-      <c r="L103" s="321"/>
-      <c r="M103" s="322"/>
+      <c r="K103" s="302"/>
+      <c r="L103" s="303"/>
+      <c r="M103" s="304"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -63422,9 +63431,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="320"/>
-      <c r="L104" s="321"/>
-      <c r="M104" s="322"/>
+      <c r="K104" s="302"/>
+      <c r="L104" s="303"/>
+      <c r="M104" s="304"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -63458,9 +63467,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="323"/>
-      <c r="L105" s="324"/>
-      <c r="M105" s="325"/>
+      <c r="K105" s="305"/>
+      <c r="L105" s="306"/>
+      <c r="M105" s="307"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -63494,11 +63503,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="314" t="s">
+      <c r="K106" s="296" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="315"/>
-      <c r="M106" s="316"/>
+      <c r="L106" s="297"/>
+      <c r="M106" s="298"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63532,11 +63541,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="314" t="s">
+      <c r="K107" s="296" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="315"/>
-      <c r="M107" s="316"/>
+      <c r="L107" s="297"/>
+      <c r="M107" s="298"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63570,11 +63579,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="305" t="s">
+      <c r="K108" s="287" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="306"/>
-      <c r="M108" s="307"/>
+      <c r="L108" s="288"/>
+      <c r="M108" s="289"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63608,9 +63617,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="308"/>
-      <c r="L109" s="309"/>
-      <c r="M109" s="310"/>
+      <c r="K109" s="290"/>
+      <c r="L109" s="291"/>
+      <c r="M109" s="292"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -63644,9 +63653,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="308"/>
-      <c r="L110" s="309"/>
-      <c r="M110" s="310"/>
+      <c r="K110" s="290"/>
+      <c r="L110" s="291"/>
+      <c r="M110" s="292"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -63680,9 +63689,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="308"/>
-      <c r="L111" s="309"/>
-      <c r="M111" s="310"/>
+      <c r="K111" s="290"/>
+      <c r="L111" s="291"/>
+      <c r="M111" s="292"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -63720,9 +63729,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="308"/>
-      <c r="L112" s="309"/>
-      <c r="M112" s="310"/>
+      <c r="K112" s="290"/>
+      <c r="L112" s="291"/>
+      <c r="M112" s="292"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="156" t="s">
@@ -63758,9 +63767,9 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="311"/>
-      <c r="L113" s="312"/>
-      <c r="M113" s="313"/>
+      <c r="K113" s="293"/>
+      <c r="L113" s="294"/>
+      <c r="M113" s="295"/>
     </row>
     <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="93" t="s">
@@ -63800,12 +63809,6 @@
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
-    <mergeCell ref="W84:X84"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K108:M113"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
     <mergeCell ref="W81:X81"/>
@@ -63815,6 +63818,12 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
+    <mergeCell ref="W84:X84"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K108:M113"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -63899,32 +63908,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="326" t="s">
+      <c r="A1" s="327" t="s">
         <v>406</v>
       </c>
-      <c r="B1" s="326"/>
-      <c r="C1" s="326"/>
-      <c r="D1" s="326"/>
-      <c r="E1" s="326"/>
-      <c r="F1" s="326" t="s">
+      <c r="B1" s="327"/>
+      <c r="C1" s="327"/>
+      <c r="D1" s="327"/>
+      <c r="E1" s="327"/>
+      <c r="F1" s="327" t="s">
         <v>407</v>
       </c>
-      <c r="G1" s="326"/>
-      <c r="H1" s="326"/>
-      <c r="I1" s="326"/>
-      <c r="J1" s="326"/>
+      <c r="G1" s="327"/>
+      <c r="H1" s="327"/>
+      <c r="I1" s="327"/>
+      <c r="J1" s="327"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="326"/>
-      <c r="B2" s="326"/>
-      <c r="C2" s="326"/>
-      <c r="D2" s="326"/>
-      <c r="E2" s="326"/>
-      <c r="F2" s="326"/>
-      <c r="G2" s="326"/>
-      <c r="H2" s="326"/>
-      <c r="I2" s="326"/>
-      <c r="J2" s="326"/>
+      <c r="A2" s="327"/>
+      <c r="B2" s="327"/>
+      <c r="C2" s="327"/>
+      <c r="D2" s="327"/>
+      <c r="E2" s="327"/>
+      <c r="F2" s="327"/>
+      <c r="G2" s="327"/>
+      <c r="H2" s="327"/>
+      <c r="I2" s="327"/>
+      <c r="J2" s="327"/>
       <c r="L2" t="s">
         <v>410</v>
       </c>
@@ -64668,13 +64677,13 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44DFF815-59E5-49DB-A710-CC57B82C1BDD}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>410</v>
       </c>
@@ -64687,8 +64696,11 @@
       <c r="D1" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>350</v>
       </c>
@@ -64702,7 +64714,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>448</v>
       </c>
@@ -64715,8 +64727,11 @@
       <c r="D3">
         <v>90</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>449</v>
       </c>
@@ -64730,7 +64745,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>449</v>
       </c>
@@ -64744,7 +64759,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>450</v>
       </c>
@@ -64758,7 +64773,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>453</v>
       </c>
@@ -64772,7 +64787,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>453</v>
       </c>
@@ -64786,7 +64801,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>454</v>
       </c>
@@ -64800,21 +64815,21 @@
         <v>471</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>455</v>
       </c>
       <c r="B10" t="s">
         <v>466</v>
       </c>
-      <c r="C10" s="330">
+      <c r="C10" s="201">
         <v>6</v>
       </c>
       <c r="D10" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>456</v>
       </c>
@@ -64827,8 +64842,11 @@
       <c r="D11">
         <v>90</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>457</v>
       </c>
@@ -64842,7 +64860,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>455</v>
       </c>
@@ -64856,7 +64874,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>454</v>
       </c>
@@ -64870,7 +64888,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>453</v>
       </c>
@@ -64884,7 +64902,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>449</v>
       </c>
@@ -64936,24 +64954,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="201" t="s">
+      <c r="A1" s="206" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="327"/>
-      <c r="C1" s="328" t="s">
+      <c r="B1" s="328"/>
+      <c r="C1" s="329" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="204"/>
-      <c r="E1" s="329"/>
-      <c r="H1" s="201" t="s">
+      <c r="D1" s="209"/>
+      <c r="E1" s="330"/>
+      <c r="H1" s="206" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="327"/>
-      <c r="J1" s="328" t="s">
+      <c r="I1" s="328"/>
+      <c r="J1" s="329" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="204"/>
-      <c r="L1" s="329"/>
+      <c r="K1" s="209"/>
+      <c r="L1" s="330"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -66041,9 +66059,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="205"/>
-      <c r="G1" s="205"/>
-      <c r="H1" s="205"/>
+      <c r="F1" s="210"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -66067,36 +66085,36 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="201" t="s">
+      <c r="E2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="202"/>
-      <c r="G2" s="203"/>
-      <c r="H2" s="206" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="208"/>
+      <c r="H2" s="211" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="207"/>
-      <c r="J2" s="208"/>
-      <c r="K2" s="201" t="s">
+      <c r="I2" s="212"/>
+      <c r="J2" s="213"/>
+      <c r="K2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="202"/>
-      <c r="M2" s="203"/>
-      <c r="N2" s="206" t="s">
+      <c r="L2" s="207"/>
+      <c r="M2" s="208"/>
+      <c r="N2" s="211" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="207"/>
-      <c r="P2" s="208"/>
-      <c r="Q2" s="201" t="s">
+      <c r="O2" s="212"/>
+      <c r="P2" s="213"/>
+      <c r="Q2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="202"/>
-      <c r="S2" s="203"/>
-      <c r="T2" s="204" t="s">
+      <c r="R2" s="207"/>
+      <c r="S2" s="208"/>
+      <c r="T2" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="204"/>
-      <c r="V2" s="204"/>
+      <c r="U2" s="209"/>
+      <c r="V2" s="209"/>
       <c r="Z2" s="125">
         <v>46267</v>
       </c>
@@ -69274,30 +69292,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="211" t="s">
+      <c r="D2" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="211"/>
-      <c r="F2" s="212" t="s">
+      <c r="E2" s="204"/>
+      <c r="F2" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="212"/>
-      <c r="H2" s="211" t="s">
+      <c r="G2" s="205"/>
+      <c r="H2" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="211"/>
-      <c r="J2" s="212" t="s">
+      <c r="I2" s="204"/>
+      <c r="J2" s="205" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="212"/>
-      <c r="L2" s="211" t="s">
+      <c r="K2" s="205"/>
+      <c r="L2" s="204" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="211"/>
-      <c r="N2" s="204" t="s">
+      <c r="M2" s="204"/>
+      <c r="N2" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="204"/>
+      <c r="O2" s="209"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -71294,30 +71312,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="211" t="s">
+      <c r="D2" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="211"/>
-      <c r="F2" s="212" t="s">
+      <c r="E2" s="204"/>
+      <c r="F2" s="205" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="212"/>
-      <c r="H2" s="211" t="s">
+      <c r="G2" s="205"/>
+      <c r="H2" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="211"/>
-      <c r="J2" s="212" t="s">
+      <c r="I2" s="204"/>
+      <c r="J2" s="205" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="212"/>
-      <c r="L2" s="211" t="s">
+      <c r="K2" s="205"/>
+      <c r="L2" s="204" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="211"/>
-      <c r="N2" s="204" t="s">
+      <c r="M2" s="204"/>
+      <c r="N2" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="204"/>
+      <c r="O2" s="209"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -73251,30 +73269,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="211" t="s">
+      <c r="D2" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="211"/>
-      <c r="F2" s="212" t="s">
+      <c r="E2" s="204"/>
+      <c r="F2" s="205" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="212"/>
-      <c r="H2" s="211" t="s">
+      <c r="G2" s="205"/>
+      <c r="H2" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="211"/>
-      <c r="J2" s="212" t="s">
+      <c r="I2" s="204"/>
+      <c r="J2" s="205" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="212"/>
-      <c r="L2" s="211" t="s">
+      <c r="K2" s="205"/>
+      <c r="L2" s="204" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="211"/>
-      <c r="N2" s="204" t="s">
+      <c r="M2" s="204"/>
+      <c r="N2" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="204"/>
+      <c r="O2" s="209"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -75299,30 +75317,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="211" t="s">
+      <c r="D2" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="211"/>
-      <c r="F2" s="212" t="s">
+      <c r="E2" s="204"/>
+      <c r="F2" s="205" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="212"/>
-      <c r="H2" s="211" t="s">
+      <c r="G2" s="205"/>
+      <c r="H2" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="211"/>
-      <c r="J2" s="212" t="s">
+      <c r="I2" s="204"/>
+      <c r="J2" s="205" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="212"/>
-      <c r="L2" s="211" t="s">
+      <c r="K2" s="205"/>
+      <c r="L2" s="204" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="211"/>
-      <c r="N2" s="204" t="s">
+      <c r="M2" s="204"/>
+      <c r="N2" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="204"/>
+      <c r="O2" s="209"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -77007,30 +77025,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="211" t="s">
+      <c r="C2" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="211"/>
-      <c r="E2" s="212" t="s">
+      <c r="D2" s="204"/>
+      <c r="E2" s="205" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="212"/>
-      <c r="G2" s="211" t="s">
+      <c r="F2" s="205"/>
+      <c r="G2" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="211"/>
-      <c r="I2" s="212" t="s">
+      <c r="H2" s="204"/>
+      <c r="I2" s="205" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="212"/>
-      <c r="K2" s="211" t="s">
+      <c r="J2" s="205"/>
+      <c r="K2" s="204" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="211"/>
-      <c r="M2" s="204" t="s">
+      <c r="L2" s="204"/>
+      <c r="M2" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="204"/>
+      <c r="N2" s="209"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -78792,30 +78810,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="211" t="s">
+      <c r="C2" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="211"/>
-      <c r="E2" s="212" t="s">
+      <c r="D2" s="204"/>
+      <c r="E2" s="205" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="212"/>
-      <c r="G2" s="211" t="s">
+      <c r="F2" s="205"/>
+      <c r="G2" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="211"/>
-      <c r="I2" s="212" t="s">
+      <c r="H2" s="204"/>
+      <c r="I2" s="205" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="212"/>
-      <c r="K2" s="211" t="s">
+      <c r="J2" s="205"/>
+      <c r="K2" s="204" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="211"/>
-      <c r="M2" s="204" t="s">
+      <c r="L2" s="204"/>
+      <c r="M2" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="204"/>
+      <c r="N2" s="209"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
